--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -821,14 +821,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1299"/>
+  <dimension ref="A1:U1330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -20603,7 +20603,9 @@
       <c r="C1290" s="6">
         <v>2</v>
       </c>
-      <c r="D1290" s="2"/>
+      <c r="D1290" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1291" spans="1:7">
       <c r="A1291" s="7">
@@ -20615,7 +20617,9 @@
       <c r="C1291" s="6">
         <v>2</v>
       </c>
-      <c r="D1291" s="2"/>
+      <c r="D1291" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1292" spans="1:7">
       <c r="A1292" s="7">
@@ -20627,7 +20631,9 @@
       <c r="C1292" s="6">
         <v>5</v>
       </c>
-      <c r="D1292" s="2"/>
+      <c r="D1292" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1293" spans="1:7">
       <c r="A1293" s="7">
@@ -20639,7 +20645,9 @@
       <c r="C1293" s="6">
         <v>5</v>
       </c>
-      <c r="D1293" s="2"/>
+      <c r="D1293" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1294" spans="1:7">
       <c r="A1294" s="7">
@@ -20651,7 +20659,9 @@
       <c r="C1294" s="6">
         <v>3</v>
       </c>
-      <c r="D1294" s="2"/>
+      <c r="D1294" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1295" spans="1:7">
       <c r="A1295" s="7">
@@ -20663,7 +20673,9 @@
       <c r="C1295" s="6">
         <v>3</v>
       </c>
-      <c r="D1295" s="2"/>
+      <c r="D1295" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1296" spans="1:7">
       <c r="A1296" s="7">
@@ -20675,9 +20687,11 @@
       <c r="C1296" s="6">
         <v>2</v>
       </c>
-      <c r="D1296" s="2"/>
-    </row>
-    <row r="1297" spans="1:4">
+      <c r="D1296" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:7">
       <c r="A1297" s="7">
         <v>46077</v>
       </c>
@@ -20687,31 +20701,483 @@
       <c r="C1297" s="6">
         <v>2</v>
       </c>
-      <c r="D1297" s="2"/>
-    </row>
-    <row r="1298" spans="1:4">
+      <c r="D1297" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:7">
       <c r="A1298" s="7">
         <v>46077</v>
       </c>
-      <c r="B1298" s="2" t="s">
+      <c r="B1298" s="70" t="s">
         <v>23</v>
       </c>
       <c r="C1298" s="6">
         <v>5</v>
       </c>
-      <c r="D1298" s="2"/>
-    </row>
-    <row r="1299" spans="1:4">
+      <c r="D1298" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:7">
       <c r="A1299" s="7">
         <v>46077</v>
       </c>
-      <c r="B1299" s="2" t="s">
+      <c r="B1299" s="70" t="s">
         <v>21</v>
       </c>
       <c r="C1299" s="2">
         <v>5</v>
       </c>
-      <c r="D1299" s="2"/>
+      <c r="D1299" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:7">
+      <c r="A1300" s="7">
+        <v>46077</v>
+      </c>
+      <c r="B1300" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1300" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1300" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:7">
+      <c r="A1301" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1301" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1301" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1301" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1301" s="1"/>
+      <c r="G1301" s="22"/>
+    </row>
+    <row r="1302" spans="1:7">
+      <c r="A1302" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1302" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1302" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1302" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1302" s="1"/>
+      <c r="G1302" s="22"/>
+    </row>
+    <row r="1303" spans="1:7">
+      <c r="A1303" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1303" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1303" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1303" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1303" s="1"/>
+      <c r="G1303" s="22"/>
+    </row>
+    <row r="1304" spans="1:7">
+      <c r="A1304" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1304" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1304" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1304" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1304" s="1"/>
+      <c r="G1304" s="22"/>
+    </row>
+    <row r="1305" spans="1:7">
+      <c r="A1305" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1305" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1305" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1305" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1305" s="1"/>
+      <c r="G1305" s="22"/>
+    </row>
+    <row r="1306" spans="1:7">
+      <c r="A1306" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1306" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1306" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1306" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1306" s="1"/>
+      <c r="G1306" s="22"/>
+    </row>
+    <row r="1307" spans="1:7">
+      <c r="A1307" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1307" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1307" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1307" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1307" s="1"/>
+      <c r="G1307" s="22"/>
+    </row>
+    <row r="1308" spans="1:7">
+      <c r="A1308" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1308" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1308" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1308" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1308" s="1"/>
+      <c r="G1308" s="22"/>
+    </row>
+    <row r="1309" spans="1:7">
+      <c r="A1309" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1309" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1309" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1309" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:7">
+      <c r="A1310" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1310" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1310" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1310" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:7">
+      <c r="A1311" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1311" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1311" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1311" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:7">
+      <c r="A1312" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B1312" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1312" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1312" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:7">
+      <c r="A1313" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1313" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1313" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1313" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:7">
+      <c r="A1314" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1314" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1314" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1314" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:7">
+      <c r="A1315" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1315" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1315" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1315" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:7">
+      <c r="A1316" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1316" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1316" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1316" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1316" s="1"/>
+      <c r="G1316" s="22"/>
+    </row>
+    <row r="1317" spans="1:7">
+      <c r="A1317" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1317" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1317" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1317" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1317" s="1"/>
+      <c r="G1317" s="22"/>
+    </row>
+    <row r="1318" spans="1:7">
+      <c r="A1318" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1318" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1318" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1318" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1318" s="1"/>
+      <c r="G1318" s="22"/>
+    </row>
+    <row r="1319" spans="1:7">
+      <c r="A1319" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1319" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1319" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1319" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1319" s="1"/>
+      <c r="G1319" s="22"/>
+    </row>
+    <row r="1320" spans="1:7">
+      <c r="A1320" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B1320" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1320" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1320" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1320" s="1"/>
+      <c r="G1320" s="22"/>
+    </row>
+    <row r="1321" spans="1:7">
+      <c r="A1321" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1321" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1321" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1321" s="2"/>
+      <c r="F1321" s="1"/>
+      <c r="G1321" s="22"/>
+    </row>
+    <row r="1322" spans="1:7">
+      <c r="A1322" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1322" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1322" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1322" s="2"/>
+      <c r="F1322" s="1"/>
+      <c r="G1322" s="22"/>
+    </row>
+    <row r="1323" spans="1:7">
+      <c r="A1323" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1323" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1323" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1323" s="2"/>
+      <c r="F1323" s="1"/>
+      <c r="G1323" s="22"/>
+    </row>
+    <row r="1324" spans="1:7">
+      <c r="A1324" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1324" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1324" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1324" s="2"/>
+    </row>
+    <row r="1325" spans="1:7">
+      <c r="A1325" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1325" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1325" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1325" s="2"/>
+    </row>
+    <row r="1326" spans="1:7">
+      <c r="A1326" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1326" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1326" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1326" s="2"/>
+    </row>
+    <row r="1327" spans="1:7">
+      <c r="A1327" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1327" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1327" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1327" s="2"/>
+    </row>
+    <row r="1328" spans="1:7">
+      <c r="A1328" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1328" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1328" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1328" s="2"/>
+    </row>
+    <row r="1329" spans="1:4">
+      <c r="A1329" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1329" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1329" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1329" s="2"/>
+    </row>
+    <row r="1330" spans="1:4">
+      <c r="A1330" s="7">
+        <v>46080</v>
+      </c>
+      <c r="B1330" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1330" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1330" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1330"/>
+  <dimension ref="A1:U1357"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -21063,7 +21063,9 @@
       <c r="C1321" s="6">
         <v>3</v>
       </c>
-      <c r="D1321" s="2"/>
+      <c r="D1321" s="2">
+        <v>0</v>
+      </c>
       <c r="F1321" s="1"/>
       <c r="G1321" s="22"/>
     </row>
@@ -21077,7 +21079,9 @@
       <c r="C1322" s="6">
         <v>3</v>
       </c>
-      <c r="D1322" s="2"/>
+      <c r="D1322" s="2">
+        <v>0</v>
+      </c>
       <c r="F1322" s="1"/>
       <c r="G1322" s="22"/>
     </row>
@@ -21091,7 +21095,9 @@
       <c r="C1323" s="6">
         <v>9</v>
       </c>
-      <c r="D1323" s="2"/>
+      <c r="D1323" s="2">
+        <v>0</v>
+      </c>
       <c r="F1323" s="1"/>
       <c r="G1323" s="22"/>
     </row>
@@ -21105,7 +21111,9 @@
       <c r="C1324" s="6">
         <v>9</v>
       </c>
-      <c r="D1324" s="2"/>
+      <c r="D1324" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1325" spans="1:7">
       <c r="A1325" s="7">
@@ -21117,7 +21125,9 @@
       <c r="C1325" s="6">
         <v>5</v>
       </c>
-      <c r="D1325" s="2"/>
+      <c r="D1325" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1326" spans="1:7">
       <c r="A1326" s="7">
@@ -21129,7 +21139,9 @@
       <c r="C1326" s="6">
         <v>5</v>
       </c>
-      <c r="D1326" s="2"/>
+      <c r="D1326" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1327" spans="1:7">
       <c r="A1327" s="7">
@@ -21141,7 +21153,9 @@
       <c r="C1327" s="6">
         <v>5</v>
       </c>
-      <c r="D1327" s="2"/>
+      <c r="D1327" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1328" spans="1:7">
       <c r="A1328" s="7">
@@ -21153,9 +21167,11 @@
       <c r="C1328" s="6">
         <v>5</v>
       </c>
-      <c r="D1328" s="2"/>
-    </row>
-    <row r="1329" spans="1:4">
+      <c r="D1328" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:8">
       <c r="A1329" s="7">
         <v>46080</v>
       </c>
@@ -21165,9 +21181,11 @@
       <c r="C1329" s="6">
         <v>7</v>
       </c>
-      <c r="D1329" s="2"/>
-    </row>
-    <row r="1330" spans="1:4">
+      <c r="D1329" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:8">
       <c r="A1330" s="7">
         <v>46080</v>
       </c>
@@ -21177,7 +21195,403 @@
       <c r="C1330" s="6">
         <v>7</v>
       </c>
-      <c r="D1330" s="2"/>
+      <c r="D1330" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:8">
+      <c r="A1331" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1331" s="6">
+        <v>10</v>
+      </c>
+      <c r="D1331" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1331" s="1"/>
+      <c r="H1331" s="22"/>
+    </row>
+    <row r="1332" spans="1:8">
+      <c r="A1332" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B1332" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1332" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1332" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1332" s="1"/>
+      <c r="H1332" s="22"/>
+    </row>
+    <row r="1333" spans="1:8">
+      <c r="A1333" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B1333" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1333" s="6">
+        <v>13</v>
+      </c>
+      <c r="D1333" s="2">
+        <v>14</v>
+      </c>
+      <c r="G1333" s="1"/>
+      <c r="H1333" s="22"/>
+    </row>
+    <row r="1334" spans="1:8">
+      <c r="A1334" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B1334" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1334" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1334" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1334" s="1"/>
+      <c r="H1334" s="22"/>
+    </row>
+    <row r="1335" spans="1:8">
+      <c r="A1335" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B1335" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1335" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1335" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1335" s="1"/>
+      <c r="H1335" s="22"/>
+    </row>
+    <row r="1336" spans="1:8">
+      <c r="A1336" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1336" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1336" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1336" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:8">
+      <c r="A1337" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1337" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1337" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1337" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1337" s="1"/>
+      <c r="G1337" s="22"/>
+    </row>
+    <row r="1338" spans="1:8">
+      <c r="A1338" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1338" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1338" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1338" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1338" s="1"/>
+      <c r="G1338" s="22"/>
+    </row>
+    <row r="1339" spans="1:8">
+      <c r="A1339" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1339" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1339" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1339" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1339" s="1"/>
+      <c r="G1339" s="22"/>
+    </row>
+    <row r="1340" spans="1:8">
+      <c r="A1340" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1340" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1340" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1340" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1340" s="1"/>
+      <c r="G1340" s="22"/>
+    </row>
+    <row r="1341" spans="1:8">
+      <c r="A1341" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1341" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1341" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1341" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1341" s="1"/>
+      <c r="G1341" s="22"/>
+    </row>
+    <row r="1342" spans="1:8">
+      <c r="A1342" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1342" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1342" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1342" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1342" s="1"/>
+      <c r="G1342" s="22"/>
+    </row>
+    <row r="1343" spans="1:8">
+      <c r="A1343" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1343" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1343" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1343" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1343" s="1"/>
+      <c r="G1343" s="22"/>
+    </row>
+    <row r="1344" spans="1:8">
+      <c r="A1344" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1344" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1344" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1344" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1344" s="1"/>
+      <c r="G1344" s="22"/>
+    </row>
+    <row r="1345" spans="1:7">
+      <c r="A1345" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1345" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1345" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1345" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1345" s="1"/>
+      <c r="G1345" s="22"/>
+    </row>
+    <row r="1346" spans="1:7">
+      <c r="A1346" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1346" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1346" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1346" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1346" s="1"/>
+      <c r="G1346" s="22"/>
+    </row>
+    <row r="1347" spans="1:7">
+      <c r="A1347" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1347" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1347" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1347" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1347" s="1"/>
+      <c r="G1347" s="22"/>
+    </row>
+    <row r="1348" spans="1:7">
+      <c r="A1348" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1348" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1348" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1348" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:7">
+      <c r="A1349" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B1349" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1349" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1349" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:7">
+      <c r="A1350" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1350" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1350" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1350" s="2"/>
+    </row>
+    <row r="1351" spans="1:7">
+      <c r="A1351" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1351" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1351" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1351" s="2"/>
+    </row>
+    <row r="1352" spans="1:7">
+      <c r="A1352" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1352" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1352" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1352" s="2"/>
+    </row>
+    <row r="1353" spans="1:7">
+      <c r="A1353" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1353" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1353" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1353" s="2"/>
+    </row>
+    <row r="1354" spans="1:7">
+      <c r="A1354" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1354" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1354" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1354" s="2"/>
+    </row>
+    <row r="1355" spans="1:7">
+      <c r="A1355" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1355" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1355" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1355" s="2"/>
+    </row>
+    <row r="1356" spans="1:7">
+      <c r="A1356" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1356" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1356" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1356" s="2"/>
+    </row>
+    <row r="1357" spans="1:7">
+      <c r="A1357" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1357" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1357" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1357" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>CATANIA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>TT iniziali</t>
   </si>
 </sst>
 </file>
@@ -295,7 +298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -364,23 +367,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -525,7 +517,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -845,8 +836,8 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74">
-        <v>3</v>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>14</v>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -92,7 +92,7 @@
     <t>CATANIA GIUSEPPE</t>
   </si>
   <si>
-    <t>TT iniziali</t>
+    <t>Giacenza iniziale</t>
   </si>
 </sst>
 </file>
@@ -817,7 +817,7 @@
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="9" width="29.42578125" customWidth="1"/>
@@ -829,7 +829,7 @@
     <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="30">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -812,15 +812,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1357"/>
+  <dimension ref="A1:U1374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="9" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -829,7 +829,7 @@
     <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -21492,97 +21492,305 @@
       <c r="A1350" s="7">
         <v>46084</v>
       </c>
-      <c r="B1350" s="70" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1350" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1350" s="2"/>
+      <c r="B1350" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1350" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1350" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1351" spans="1:7">
       <c r="A1351" s="7">
         <v>46084</v>
       </c>
-      <c r="B1351" s="70" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1351" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1351" s="2"/>
+      <c r="B1351" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1351" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1351" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1352" spans="1:7">
       <c r="A1352" s="7">
         <v>46084</v>
       </c>
-      <c r="B1352" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1352" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1352" s="2"/>
+      <c r="B1352" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1352" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1352" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1353" spans="1:7">
       <c r="A1353" s="7">
         <v>46084</v>
       </c>
-      <c r="B1353" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1353" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1353" s="2"/>
+      <c r="B1353" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1353" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1353" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1354" spans="1:7">
       <c r="A1354" s="7">
         <v>46084</v>
       </c>
-      <c r="B1354" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1354" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1354" s="2"/>
+      <c r="B1354" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1354" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1354" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1355" spans="1:7">
       <c r="A1355" s="7">
         <v>46084</v>
       </c>
-      <c r="B1355" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1355" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1355" s="2"/>
+      <c r="B1355" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1355" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1355" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1356" spans="1:7">
       <c r="A1356" s="7">
         <v>46084</v>
       </c>
-      <c r="B1356" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1356" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1356" s="2"/>
+      <c r="B1356" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1356" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1356" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1357" spans="1:7">
       <c r="A1357" s="7">
         <v>46084</v>
       </c>
-      <c r="B1357" s="64" t="s">
+      <c r="B1357" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1357" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1357" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:7">
+      <c r="A1358" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1358" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1358" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1358" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1358" s="1"/>
+      <c r="G1358" s="22"/>
+    </row>
+    <row r="1359" spans="1:7">
+      <c r="A1359" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1359" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1359" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1359" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1359" s="1"/>
+      <c r="G1359" s="22"/>
+    </row>
+    <row r="1360" spans="1:7">
+      <c r="A1360" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1360" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1360" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1360" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1360" s="1"/>
+      <c r="G1360" s="22"/>
+    </row>
+    <row r="1361" spans="1:8">
+      <c r="A1361" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1361" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1361" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1361" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1361" s="1"/>
+      <c r="G1361" s="22"/>
+    </row>
+    <row r="1362" spans="1:8">
+      <c r="A1362" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1362" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1362" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1362" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1362" s="1"/>
+      <c r="G1362" s="22"/>
+    </row>
+    <row r="1363" spans="1:8">
+      <c r="A1363" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1363" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1363" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1363" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1363" s="1"/>
+      <c r="G1363" s="22"/>
+    </row>
+    <row r="1364" spans="1:8">
+      <c r="A1364" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B1364" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="C1357" s="2">
-        <v>1</v>
-      </c>
-      <c r="D1357" s="2"/>
+      <c r="C1364" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1364" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1364" s="1"/>
+      <c r="G1364" s="22"/>
+    </row>
+    <row r="1365" spans="1:8">
+      <c r="A1365" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1365" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1365" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1365" s="2"/>
+      <c r="F1365" s="1"/>
+    </row>
+    <row r="1366" spans="1:8">
+      <c r="A1366" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1366" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1366" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1366" s="2"/>
+      <c r="F1366" s="1"/>
+      <c r="G1366" s="1"/>
+      <c r="H1366" s="22"/>
+    </row>
+    <row r="1367" spans="1:8">
+      <c r="A1367" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1367" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1367" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1367" s="2"/>
+      <c r="G1367" s="1"/>
+      <c r="H1367" s="22"/>
+    </row>
+    <row r="1368" spans="1:8">
+      <c r="A1368" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1368" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1368" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1368" s="2"/>
+      <c r="G1368" s="1"/>
+      <c r="H1368" s="22"/>
+    </row>
+    <row r="1369" spans="1:8">
+      <c r="G1369" s="1"/>
+      <c r="H1369" s="22"/>
+    </row>
+    <row r="1370" spans="1:8">
+      <c r="G1370" s="1"/>
+      <c r="H1370" s="22"/>
+    </row>
+    <row r="1371" spans="1:8">
+      <c r="G1371" s="1"/>
+      <c r="H1371" s="22"/>
+    </row>
+    <row r="1372" spans="1:8">
+      <c r="G1372" s="1"/>
+      <c r="H1372" s="22"/>
+    </row>
+    <row r="1373" spans="1:8">
+      <c r="G1373" s="1"/>
+      <c r="H1373" s="22"/>
+    </row>
+    <row r="1374" spans="1:8">
+      <c r="G1374" s="1"/>
+      <c r="H1374" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -812,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1374"/>
+  <dimension ref="A1:U1379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -21722,7 +21722,9 @@
       <c r="C1365" s="6">
         <v>1</v>
       </c>
-      <c r="D1365" s="2"/>
+      <c r="D1365" s="2">
+        <v>4</v>
+      </c>
       <c r="F1365" s="1"/>
     </row>
     <row r="1366" spans="1:8">
@@ -21735,7 +21737,9 @@
       <c r="C1366" s="6">
         <v>7</v>
       </c>
-      <c r="D1366" s="2"/>
+      <c r="D1366" s="2">
+        <v>5</v>
+      </c>
       <c r="F1366" s="1"/>
       <c r="G1366" s="1"/>
       <c r="H1366" s="22"/>
@@ -21750,7 +21754,9 @@
       <c r="C1367" s="6">
         <v>2</v>
       </c>
-      <c r="D1367" s="2"/>
+      <c r="D1367" s="2">
+        <v>0</v>
+      </c>
       <c r="G1367" s="1"/>
       <c r="H1367" s="22"/>
     </row>
@@ -21764,33 +21770,163 @@
       <c r="C1368" s="6">
         <v>2</v>
       </c>
-      <c r="D1368" s="2"/>
+      <c r="D1368" s="2">
+        <v>0</v>
+      </c>
       <c r="G1368" s="1"/>
       <c r="H1368" s="22"/>
     </row>
     <row r="1369" spans="1:8">
+      <c r="A1369" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1369" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1369" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1369" s="2">
+        <v>1</v>
+      </c>
       <c r="G1369" s="1"/>
       <c r="H1369" s="22"/>
     </row>
     <row r="1370" spans="1:8">
+      <c r="A1370" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1370" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1370" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1370" s="2">
+        <v>1</v>
+      </c>
       <c r="G1370" s="1"/>
       <c r="H1370" s="22"/>
     </row>
     <row r="1371" spans="1:8">
+      <c r="A1371" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1371" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1371" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1371" s="2">
+        <v>2</v>
+      </c>
       <c r="G1371" s="1"/>
       <c r="H1371" s="22"/>
     </row>
     <row r="1372" spans="1:8">
+      <c r="A1372" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1372" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1372" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1372" s="2">
+        <v>2</v>
+      </c>
       <c r="G1372" s="1"/>
       <c r="H1372" s="22"/>
     </row>
     <row r="1373" spans="1:8">
-      <c r="G1373" s="1"/>
-      <c r="H1373" s="22"/>
+      <c r="A1373" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1373" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1373" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1373" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1374" spans="1:8">
-      <c r="G1374" s="1"/>
-      <c r="H1374" s="22"/>
+      <c r="A1374" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B1374" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1374" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1374" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:8">
+      <c r="A1375" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1375" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1375" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1375" s="2"/>
+    </row>
+    <row r="1376" spans="1:8">
+      <c r="A1376" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1376" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1376" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1376" s="2"/>
+    </row>
+    <row r="1377" spans="1:4">
+      <c r="A1377" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1377" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1377" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1377" s="2"/>
+    </row>
+    <row r="1378" spans="1:4">
+      <c r="A1378" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1378" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1378" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1378" s="2"/>
+    </row>
+    <row r="1379" spans="1:4">
+      <c r="A1379" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1379" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1379" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1379" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -812,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1379"/>
+  <dimension ref="A1:U1380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -21872,7 +21872,7 @@
       <c r="A1375" s="7">
         <v>46086</v>
       </c>
-      <c r="B1375" s="2" t="s">
+      <c r="B1375" s="47" t="s">
         <v>2</v>
       </c>
       <c r="C1375" s="6">
@@ -21884,12 +21884,10 @@
       <c r="A1376" s="7">
         <v>46086</v>
       </c>
-      <c r="B1376" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1376" s="6">
-        <v>3</v>
-      </c>
+      <c r="B1376" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1376" s="6"/>
       <c r="D1376" s="2"/>
     </row>
     <row r="1377" spans="1:4">
@@ -21897,9 +21895,9 @@
         <v>46086</v>
       </c>
       <c r="B1377" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1377" s="2">
+        <v>6</v>
+      </c>
+      <c r="C1377" s="6">
         <v>3</v>
       </c>
       <c r="D1377" s="2"/>
@@ -21908,11 +21906,11 @@
       <c r="A1378" s="7">
         <v>46086</v>
       </c>
-      <c r="B1378" s="57" t="s">
-        <v>23</v>
+      <c r="B1378" s="56" t="s">
+        <v>10</v>
       </c>
       <c r="C1378" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1378" s="2"/>
     </row>
@@ -21921,12 +21919,24 @@
         <v>46086</v>
       </c>
       <c r="B1379" s="57" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C1379" s="2">
         <v>5</v>
       </c>
       <c r="D1379" s="2"/>
+    </row>
+    <row r="1380" spans="1:4">
+      <c r="A1380" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1380" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1380" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1380" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -812,14 +812,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1380"/>
+  <dimension ref="A1:U1389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
     <col min="8" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -21878,7 +21879,9 @@
       <c r="C1375" s="6">
         <v>4</v>
       </c>
-      <c r="D1375" s="2"/>
+      <c r="D1375" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1376" spans="1:8">
       <c r="A1376" s="7">
@@ -21887,10 +21890,16 @@
       <c r="B1376" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C1376" s="6"/>
-      <c r="D1376" s="2"/>
-    </row>
-    <row r="1377" spans="1:4">
+      <c r="C1376" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1376" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1376" s="1"/>
+      <c r="H1376" s="22"/>
+    </row>
+    <row r="1377" spans="1:8">
       <c r="A1377" s="7">
         <v>46086</v>
       </c>
@@ -21900,9 +21909,13 @@
       <c r="C1377" s="6">
         <v>3</v>
       </c>
-      <c r="D1377" s="2"/>
-    </row>
-    <row r="1378" spans="1:4">
+      <c r="D1377" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1377" s="1"/>
+      <c r="H1377" s="22"/>
+    </row>
+    <row r="1378" spans="1:8">
       <c r="A1378" s="7">
         <v>46086</v>
       </c>
@@ -21912,9 +21925,13 @@
       <c r="C1378" s="2">
         <v>3</v>
       </c>
-      <c r="D1378" s="2"/>
-    </row>
-    <row r="1379" spans="1:4">
+      <c r="D1378" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1378" s="1"/>
+      <c r="H1378" s="22"/>
+    </row>
+    <row r="1379" spans="1:8">
       <c r="A1379" s="7">
         <v>46086</v>
       </c>
@@ -21924,9 +21941,13 @@
       <c r="C1379" s="2">
         <v>5</v>
       </c>
-      <c r="D1379" s="2"/>
-    </row>
-    <row r="1380" spans="1:4">
+      <c r="D1379" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1379" s="1"/>
+      <c r="H1379" s="22"/>
+    </row>
+    <row r="1380" spans="1:8">
       <c r="A1380" s="7">
         <v>46086</v>
       </c>
@@ -21936,7 +21957,125 @@
       <c r="C1380" s="2">
         <v>5</v>
       </c>
-      <c r="D1380" s="2"/>
+      <c r="D1380" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1380" s="1"/>
+      <c r="H1380" s="22"/>
+    </row>
+    <row r="1381" spans="1:8">
+      <c r="A1381" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1381" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1381" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1381" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1381" s="1"/>
+      <c r="H1381" s="22"/>
+    </row>
+    <row r="1382" spans="1:8">
+      <c r="A1382" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B1382" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1382" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1382" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:8">
+      <c r="A1383" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1383" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1383" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1383" s="2"/>
+    </row>
+    <row r="1384" spans="1:8">
+      <c r="A1384" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1384" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1384" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1384" s="2"/>
+    </row>
+    <row r="1385" spans="1:8">
+      <c r="A1385" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1385" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1385" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1385" s="2"/>
+    </row>
+    <row r="1386" spans="1:8">
+      <c r="A1386" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1386" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1386" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1386" s="2"/>
+    </row>
+    <row r="1387" spans="1:8">
+      <c r="A1387" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1387" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1387" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1387" s="2"/>
+    </row>
+    <row r="1388" spans="1:8">
+      <c r="A1388" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1388" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1388" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1388" s="2"/>
+    </row>
+    <row r="1389" spans="1:8">
+      <c r="A1389" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B1389" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1389" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1389" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Giacenza iniziale</t>
+  </si>
+  <si>
+    <t>CANNARELLA ENZO</t>
   </si>
 </sst>
 </file>
@@ -812,16 +815,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1389"/>
+  <dimension ref="A1:U1402"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="9" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -22003,7 +22005,9 @@
       <c r="C1383" s="6">
         <v>2</v>
       </c>
-      <c r="D1383" s="2"/>
+      <c r="D1383" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1384" spans="1:8">
       <c r="A1384" s="7">
@@ -22015,7 +22019,11 @@
       <c r="C1384" s="6">
         <v>2</v>
       </c>
-      <c r="D1384" s="2"/>
+      <c r="D1384" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1384" s="1"/>
+      <c r="G1384" s="22"/>
     </row>
     <row r="1385" spans="1:8">
       <c r="A1385" s="7">
@@ -22027,7 +22035,11 @@
       <c r="C1385" s="6">
         <v>1</v>
       </c>
-      <c r="D1385" s="2"/>
+      <c r="D1385" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1385" s="1"/>
+      <c r="G1385" s="22"/>
     </row>
     <row r="1386" spans="1:8">
       <c r="A1386" s="7">
@@ -22039,7 +22051,11 @@
       <c r="C1386" s="2">
         <v>1</v>
       </c>
-      <c r="D1386" s="2"/>
+      <c r="D1386" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1386" s="1"/>
+      <c r="G1386" s="22"/>
     </row>
     <row r="1387" spans="1:8">
       <c r="A1387" s="7">
@@ -22051,7 +22067,11 @@
       <c r="C1387" s="2">
         <v>2</v>
       </c>
-      <c r="D1387" s="2"/>
+      <c r="D1387" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1387" s="1"/>
+      <c r="G1387" s="22"/>
     </row>
     <row r="1388" spans="1:8">
       <c r="A1388" s="7">
@@ -22063,7 +22083,11 @@
       <c r="C1388" s="2">
         <v>2</v>
       </c>
-      <c r="D1388" s="2"/>
+      <c r="D1388" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1388" s="1"/>
+      <c r="G1388" s="22"/>
     </row>
     <row r="1389" spans="1:8">
       <c r="A1389" s="7">
@@ -22075,7 +22099,189 @@
       <c r="C1389" s="2">
         <v>7</v>
       </c>
-      <c r="D1389" s="2"/>
+      <c r="D1389" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1389" s="1"/>
+      <c r="G1389" s="22"/>
+    </row>
+    <row r="1390" spans="1:8">
+      <c r="A1390" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B1390" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1390" s="6">
+        <v>10</v>
+      </c>
+      <c r="D1390" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:8">
+      <c r="A1391" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B1391" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1391" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1391" s="6">
+        <v>6</v>
+      </c>
+      <c r="F1391" s="1"/>
+      <c r="G1391" s="22"/>
+    </row>
+    <row r="1392" spans="1:8">
+      <c r="A1392" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B1392" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1392" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1392" s="6">
+        <v>6</v>
+      </c>
+      <c r="F1392" s="1"/>
+      <c r="G1392" s="22"/>
+    </row>
+    <row r="1393" spans="1:7">
+      <c r="A1393" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B1393" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1393" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1393" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1393" s="1"/>
+      <c r="G1393" s="22"/>
+    </row>
+    <row r="1394" spans="1:7">
+      <c r="A1394" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B1394" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1394" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1394" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1394" s="1"/>
+      <c r="G1394" s="22"/>
+    </row>
+    <row r="1395" spans="1:7">
+      <c r="A1395" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1395" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1395" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1395" s="2"/>
+      <c r="F1395" s="1"/>
+      <c r="G1395" s="22"/>
+    </row>
+    <row r="1396" spans="1:7">
+      <c r="A1396" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1396" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1396" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1396" s="2"/>
+      <c r="F1396" s="1"/>
+      <c r="G1396" s="22"/>
+    </row>
+    <row r="1397" spans="1:7">
+      <c r="A1397" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1397" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1397" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1397" s="2"/>
+    </row>
+    <row r="1398" spans="1:7">
+      <c r="A1398" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1398" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1398" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1398" s="2"/>
+    </row>
+    <row r="1399" spans="1:7">
+      <c r="A1399" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1399" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1399" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1399" s="2"/>
+    </row>
+    <row r="1400" spans="1:7">
+      <c r="A1400" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1400" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1400" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1400" s="2"/>
+    </row>
+    <row r="1401" spans="1:7">
+      <c r="A1401" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1401" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1401" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1401" s="2"/>
+    </row>
+    <row r="1402" spans="1:7">
+      <c r="A1402" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1402" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1402" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1402" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -815,14 +815,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1402"/>
+  <dimension ref="A1:U1409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -22193,9 +22193,9 @@
       <c r="C1395" s="6">
         <v>2</v>
       </c>
-      <c r="D1395" s="2"/>
-      <c r="F1395" s="1"/>
-      <c r="G1395" s="22"/>
+      <c r="D1395" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="1396" spans="1:7">
       <c r="A1396" s="7">
@@ -22207,7 +22207,9 @@
       <c r="C1396" s="6">
         <v>2</v>
       </c>
-      <c r="D1396" s="2"/>
+      <c r="D1396" s="2">
+        <v>5</v>
+      </c>
       <c r="F1396" s="1"/>
       <c r="G1396" s="22"/>
     </row>
@@ -22221,7 +22223,11 @@
       <c r="C1397" s="6">
         <v>1</v>
       </c>
-      <c r="D1397" s="2"/>
+      <c r="D1397" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1397" s="1"/>
+      <c r="G1397" s="22"/>
     </row>
     <row r="1398" spans="1:7">
       <c r="A1398" s="7">
@@ -22233,7 +22239,11 @@
       <c r="C1398" s="6">
         <v>1</v>
       </c>
-      <c r="D1398" s="2"/>
+      <c r="D1398" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1398" s="1"/>
+      <c r="G1398" s="22"/>
     </row>
     <row r="1399" spans="1:7">
       <c r="A1399" s="7">
@@ -22245,7 +22255,11 @@
       <c r="C1399" s="6">
         <v>1</v>
       </c>
-      <c r="D1399" s="2"/>
+      <c r="D1399" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1399" s="1"/>
+      <c r="G1399" s="22"/>
     </row>
     <row r="1400" spans="1:7">
       <c r="A1400" s="7">
@@ -22257,7 +22271,11 @@
       <c r="C1400" s="6">
         <v>1</v>
       </c>
-      <c r="D1400" s="2"/>
+      <c r="D1400" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1400" s="1"/>
+      <c r="G1400" s="22"/>
     </row>
     <row r="1401" spans="1:7">
       <c r="A1401" s="7">
@@ -22269,7 +22287,11 @@
       <c r="C1401" s="6">
         <v>3</v>
       </c>
-      <c r="D1401" s="2"/>
+      <c r="D1401" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1401" s="1"/>
+      <c r="G1401" s="22"/>
     </row>
     <row r="1402" spans="1:7">
       <c r="A1402" s="7">
@@ -22281,7 +22303,97 @@
       <c r="C1402" s="6">
         <v>3</v>
       </c>
-      <c r="D1402" s="2"/>
+      <c r="D1402" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1402" s="1"/>
+      <c r="G1402" s="22"/>
+    </row>
+    <row r="1403" spans="1:7">
+      <c r="A1403" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B1403" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1403" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1403" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:7">
+      <c r="A1404" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1404" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1404" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1404" s="2"/>
+    </row>
+    <row r="1405" spans="1:7">
+      <c r="A1405" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1405" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1405" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1405" s="2"/>
+    </row>
+    <row r="1406" spans="1:7">
+      <c r="A1406" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1406" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1406" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1406" s="2"/>
+    </row>
+    <row r="1407" spans="1:7">
+      <c r="A1407" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1407" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1407" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1407" s="2"/>
+    </row>
+    <row r="1408" spans="1:7">
+      <c r="A1408" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1408" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1408" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1408" s="2"/>
+    </row>
+    <row r="1409" spans="1:4">
+      <c r="A1409" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1409" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1409" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1409" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -815,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1409"/>
+  <dimension ref="A1:U1419"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22333,7 +22333,9 @@
       <c r="C1404" s="6">
         <v>3</v>
       </c>
-      <c r="D1404" s="2"/>
+      <c r="D1404" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1405" spans="1:7">
       <c r="A1405" s="7">
@@ -22345,7 +22347,9 @@
       <c r="C1405" s="6">
         <v>3</v>
       </c>
-      <c r="D1405" s="2"/>
+      <c r="D1405" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1406" spans="1:7">
       <c r="A1406" s="7">
@@ -22357,7 +22361,9 @@
       <c r="C1406" s="6">
         <v>4</v>
       </c>
-      <c r="D1406" s="2"/>
+      <c r="D1406" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1407" spans="1:7">
       <c r="A1407" s="7">
@@ -22369,7 +22375,9 @@
       <c r="C1407" s="2">
         <v>4</v>
       </c>
-      <c r="D1407" s="2"/>
+      <c r="D1407" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1408" spans="1:7">
       <c r="A1408" s="7">
@@ -22381,7 +22389,9 @@
       <c r="C1408" s="2">
         <v>1</v>
       </c>
-      <c r="D1408" s="2"/>
+      <c r="D1408" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1409" spans="1:4">
       <c r="A1409" s="7">
@@ -22393,7 +22403,133 @@
       <c r="C1409" s="2">
         <v>1</v>
       </c>
-      <c r="D1409" s="2"/>
+      <c r="D1409" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4">
+      <c r="A1410" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1410" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1410" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1410" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4">
+      <c r="A1411" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B1411" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1411" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1411" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4">
+      <c r="A1412" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1412" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1412" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1412" s="2"/>
+    </row>
+    <row r="1413" spans="1:4">
+      <c r="A1413" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1413" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1413" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1413" s="2"/>
+    </row>
+    <row r="1414" spans="1:4">
+      <c r="A1414" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1414" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1414" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1414" s="2"/>
+    </row>
+    <row r="1415" spans="1:4">
+      <c r="A1415" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1415" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1415" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1415" s="2"/>
+    </row>
+    <row r="1416" spans="1:4">
+      <c r="A1416" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1416" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1416" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1416" s="2"/>
+    </row>
+    <row r="1417" spans="1:4">
+      <c r="A1417" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1417" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1417" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1417" s="2"/>
+    </row>
+    <row r="1418" spans="1:4">
+      <c r="A1418" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1418" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1418" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1418" s="2"/>
+    </row>
+    <row r="1419" spans="1:4">
+      <c r="A1419" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1419" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1419" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1419" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -815,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1419"/>
+  <dimension ref="A1:U1438"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22393,7 +22393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1409" spans="1:4">
+    <row r="1409" spans="1:7">
       <c r="A1409" s="7">
         <v>46091</v>
       </c>
@@ -22407,7 +22407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1410" spans="1:4">
+    <row r="1410" spans="1:7">
       <c r="A1410" s="7">
         <v>46091</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1411" spans="1:4">
+    <row r="1411" spans="1:7">
       <c r="A1411" s="7">
         <v>46091</v>
       </c>
@@ -22435,7 +22435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1412" spans="1:4">
+    <row r="1412" spans="1:7">
       <c r="A1412" s="7">
         <v>46092</v>
       </c>
@@ -22445,9 +22445,11 @@
       <c r="C1412" s="6">
         <v>5</v>
       </c>
-      <c r="D1412" s="2"/>
-    </row>
-    <row r="1413" spans="1:4">
+      <c r="D1412" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:7">
       <c r="A1413" s="7">
         <v>46092</v>
       </c>
@@ -22457,9 +22459,13 @@
       <c r="C1413" s="6">
         <v>5</v>
       </c>
-      <c r="D1413" s="2"/>
-    </row>
-    <row r="1414" spans="1:4">
+      <c r="D1413" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1413" s="1"/>
+      <c r="G1413" s="22"/>
+    </row>
+    <row r="1414" spans="1:7">
       <c r="A1414" s="7">
         <v>46092</v>
       </c>
@@ -22469,9 +22475,13 @@
       <c r="C1414" s="6">
         <v>6</v>
       </c>
-      <c r="D1414" s="2"/>
-    </row>
-    <row r="1415" spans="1:4">
+      <c r="D1414" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1414" s="1"/>
+      <c r="G1414" s="22"/>
+    </row>
+    <row r="1415" spans="1:7">
       <c r="A1415" s="7">
         <v>46092</v>
       </c>
@@ -22481,9 +22491,13 @@
       <c r="C1415" s="6">
         <v>6</v>
       </c>
-      <c r="D1415" s="2"/>
-    </row>
-    <row r="1416" spans="1:4">
+      <c r="D1415" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1415" s="1"/>
+      <c r="G1415" s="22"/>
+    </row>
+    <row r="1416" spans="1:7">
       <c r="A1416" s="7">
         <v>46092</v>
       </c>
@@ -22493,9 +22507,13 @@
       <c r="C1416" s="6">
         <v>1</v>
       </c>
-      <c r="D1416" s="2"/>
-    </row>
-    <row r="1417" spans="1:4">
+      <c r="D1416" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1416" s="1"/>
+      <c r="G1416" s="22"/>
+    </row>
+    <row r="1417" spans="1:7">
       <c r="A1417" s="7">
         <v>46092</v>
       </c>
@@ -22505,9 +22523,13 @@
       <c r="C1417" s="6">
         <v>1</v>
       </c>
-      <c r="D1417" s="2"/>
-    </row>
-    <row r="1418" spans="1:4">
+      <c r="D1417" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1417" s="1"/>
+      <c r="G1417" s="22"/>
+    </row>
+    <row r="1418" spans="1:7">
       <c r="A1418" s="7">
         <v>46092</v>
       </c>
@@ -22517,9 +22539,13 @@
       <c r="C1418" s="6">
         <v>3</v>
       </c>
-      <c r="D1418" s="2"/>
-    </row>
-    <row r="1419" spans="1:4">
+      <c r="D1418" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1418" s="1"/>
+      <c r="G1418" s="22"/>
+    </row>
+    <row r="1419" spans="1:7">
       <c r="A1419" s="7">
         <v>46092</v>
       </c>
@@ -22529,7 +22555,285 @@
       <c r="C1419" s="6">
         <v>3</v>
       </c>
-      <c r="D1419" s="2"/>
+      <c r="D1419" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:7">
+      <c r="A1420" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1420" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1420" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1420" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:7">
+      <c r="A1421" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B1421" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1421" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1421" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:7">
+      <c r="A1422" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1422" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1422" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1422" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:7">
+      <c r="A1423" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1423" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1423" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1423" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1423" s="1"/>
+      <c r="G1423" s="22"/>
+    </row>
+    <row r="1424" spans="1:7">
+      <c r="A1424" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1424" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1424" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1424" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1424" s="1"/>
+      <c r="G1424" s="22"/>
+    </row>
+    <row r="1425" spans="1:7">
+      <c r="A1425" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1425" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1425" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1425" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1425" s="1"/>
+      <c r="G1425" s="22"/>
+    </row>
+    <row r="1426" spans="1:7">
+      <c r="A1426" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1426" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1426" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1426" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1426" s="1"/>
+      <c r="G1426" s="22"/>
+    </row>
+    <row r="1427" spans="1:7">
+      <c r="A1427" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1427" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1427" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1427" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1427" s="1"/>
+      <c r="G1427" s="22"/>
+    </row>
+    <row r="1428" spans="1:7">
+      <c r="A1428" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1428" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1428" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1428" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1428" s="1"/>
+      <c r="G1428" s="22"/>
+    </row>
+    <row r="1429" spans="1:7">
+      <c r="A1429" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1429" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1429" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1429" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1429" s="1"/>
+      <c r="G1429" s="22"/>
+    </row>
+    <row r="1430" spans="1:7">
+      <c r="A1430" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1430" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1430" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1430" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1430" s="1"/>
+      <c r="G1430" s="22"/>
+    </row>
+    <row r="1431" spans="1:7">
+      <c r="A1431" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B1431" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1431" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1431" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1431" s="1"/>
+      <c r="G1431" s="22"/>
+    </row>
+    <row r="1432" spans="1:7">
+      <c r="A1432" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1432" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1432" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1432" s="2"/>
+      <c r="F1432" s="1"/>
+      <c r="G1432" s="22"/>
+    </row>
+    <row r="1433" spans="1:7">
+      <c r="A1433" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1433" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1433" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1433" s="2"/>
+      <c r="F1433" s="1"/>
+      <c r="G1433" s="22"/>
+    </row>
+    <row r="1434" spans="1:7">
+      <c r="A1434" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1434" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1434" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1434" s="2"/>
+      <c r="F1434" s="1"/>
+      <c r="G1434" s="22"/>
+    </row>
+    <row r="1435" spans="1:7">
+      <c r="A1435" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1435" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1435" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1435" s="2"/>
+    </row>
+    <row r="1436" spans="1:7">
+      <c r="A1436" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1436" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1436" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1436" s="2"/>
+    </row>
+    <row r="1437" spans="1:7">
+      <c r="A1437" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1437" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1437" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1437" s="2"/>
+    </row>
+    <row r="1438" spans="1:7">
+      <c r="A1438" s="7">
+        <v>44998</v>
+      </c>
+      <c r="B1438" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1438" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1438" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>CANNARELLA ENZO</t>
+  </si>
+  <si>
+    <t>DI BARTOLOMEO DANIELE</t>
+  </si>
+  <si>
+    <t>TRECCARICHI GIOVANNI</t>
   </si>
 </sst>
 </file>
@@ -815,14 +821,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1438"/>
+  <dimension ref="A1:U1453"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -22747,7 +22753,7 @@
     </row>
     <row r="1432" spans="1:7">
       <c r="A1432" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1432" s="30" t="s">
         <v>17</v>
@@ -22755,13 +22761,13 @@
       <c r="C1432" s="6">
         <v>6</v>
       </c>
-      <c r="D1432" s="2"/>
-      <c r="F1432" s="1"/>
-      <c r="G1432" s="22"/>
+      <c r="D1432" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1433" spans="1:7">
       <c r="A1433" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1433" s="30" t="s">
         <v>7</v>
@@ -22769,13 +22775,15 @@
       <c r="C1433" s="6">
         <v>6</v>
       </c>
-      <c r="D1433" s="2"/>
+      <c r="D1433" s="2">
+        <v>2</v>
+      </c>
       <c r="F1433" s="1"/>
       <c r="G1433" s="22"/>
     </row>
     <row r="1434" spans="1:7">
       <c r="A1434" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1434" s="14" t="s">
         <v>6</v>
@@ -22783,13 +22791,15 @@
       <c r="C1434" s="6">
         <v>2</v>
       </c>
-      <c r="D1434" s="2"/>
+      <c r="D1434" s="2">
+        <v>0</v>
+      </c>
       <c r="F1434" s="1"/>
       <c r="G1434" s="22"/>
     </row>
     <row r="1435" spans="1:7">
       <c r="A1435" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1435" s="14" t="s">
         <v>10</v>
@@ -22797,11 +22807,15 @@
       <c r="C1435" s="6">
         <v>2</v>
       </c>
-      <c r="D1435" s="2"/>
+      <c r="D1435" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1435" s="1"/>
+      <c r="G1435" s="22"/>
     </row>
     <row r="1436" spans="1:7">
       <c r="A1436" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1436" s="2" t="s">
         <v>23</v>
@@ -22809,11 +22823,15 @@
       <c r="C1436" s="6">
         <v>2</v>
       </c>
-      <c r="D1436" s="2"/>
+      <c r="D1436" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1436" s="1"/>
+      <c r="G1436" s="22"/>
     </row>
     <row r="1437" spans="1:7">
       <c r="A1437" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1437" s="59" t="s">
         <v>5</v>
@@ -22821,11 +22839,15 @@
       <c r="C1437" s="6">
         <v>2</v>
       </c>
-      <c r="D1437" s="2"/>
+      <c r="D1437" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1437" s="1"/>
+      <c r="G1437" s="22"/>
     </row>
     <row r="1438" spans="1:7">
       <c r="A1438" s="7">
-        <v>44998</v>
+        <v>46094</v>
       </c>
       <c r="B1438" s="59" t="s">
         <v>25</v>
@@ -22833,7 +22855,211 @@
       <c r="C1438" s="6">
         <v>2</v>
       </c>
-      <c r="D1438" s="2"/>
+      <c r="D1438" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:7">
+      <c r="A1439" s="7">
+        <v>46094</v>
+      </c>
+      <c r="B1439" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1439" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1439" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:7">
+      <c r="A1440" s="7">
+        <v>46094</v>
+      </c>
+      <c r="B1440" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1440" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1440" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:7">
+      <c r="A1441" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B1441" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1441" s="6">
+        <v>11</v>
+      </c>
+      <c r="D1441" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:7">
+      <c r="A1442" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B1442" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1442" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1442" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1442" s="1"/>
+      <c r="G1442" s="22"/>
+    </row>
+    <row r="1443" spans="1:7">
+      <c r="A1443" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B1443" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1443" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1443" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1443" s="1"/>
+      <c r="G1443" s="22"/>
+    </row>
+    <row r="1444" spans="1:7">
+      <c r="A1444" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B1444" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1444" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1444" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1444" s="1"/>
+      <c r="G1444" s="22"/>
+    </row>
+    <row r="1445" spans="1:7">
+      <c r="A1445" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1445" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1445" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1445" s="2"/>
+      <c r="F1445" s="1"/>
+      <c r="G1445" s="22"/>
+    </row>
+    <row r="1446" spans="1:7">
+      <c r="A1446" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1446" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1446" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1446" s="2"/>
+      <c r="F1446" s="1"/>
+      <c r="G1446" s="22"/>
+    </row>
+    <row r="1447" spans="1:7">
+      <c r="A1447" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1447" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1447" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1447" s="2"/>
+    </row>
+    <row r="1448" spans="1:7">
+      <c r="A1448" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1448" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1448" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1448" s="2"/>
+    </row>
+    <row r="1449" spans="1:7">
+      <c r="A1449" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1449" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1449" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1449" s="2"/>
+    </row>
+    <row r="1450" spans="1:7">
+      <c r="A1450" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1450" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1450" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1450" s="2"/>
+    </row>
+    <row r="1451" spans="1:7">
+      <c r="A1451" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1451" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1451" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1451" s="2"/>
+    </row>
+    <row r="1452" spans="1:7">
+      <c r="A1452" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1452" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1452" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1452" s="2"/>
+    </row>
+    <row r="1453" spans="1:7">
+      <c r="A1453" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1453" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1453" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1453" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,14 +821,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1453"/>
+  <dimension ref="A1:U1460"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -22959,7 +22959,9 @@
       <c r="C1445" s="6">
         <v>2</v>
       </c>
-      <c r="D1445" s="2"/>
+      <c r="D1445" s="2">
+        <v>0</v>
+      </c>
       <c r="F1445" s="1"/>
       <c r="G1445" s="22"/>
     </row>
@@ -22973,9 +22975,9 @@
       <c r="C1446" s="6">
         <v>2</v>
       </c>
-      <c r="D1446" s="2"/>
-      <c r="F1446" s="1"/>
-      <c r="G1446" s="22"/>
+      <c r="D1446" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1447" spans="1:7">
       <c r="A1447" s="7">
@@ -22987,7 +22989,11 @@
       <c r="C1447" s="6">
         <v>1</v>
       </c>
-      <c r="D1447" s="2"/>
+      <c r="D1447" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1447" s="1"/>
+      <c r="G1447" s="22"/>
     </row>
     <row r="1448" spans="1:7">
       <c r="A1448" s="7">
@@ -22999,7 +23005,11 @@
       <c r="C1448" s="6">
         <v>1</v>
       </c>
-      <c r="D1448" s="2"/>
+      <c r="D1448" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1448" s="1"/>
+      <c r="G1448" s="22"/>
     </row>
     <row r="1449" spans="1:7">
       <c r="A1449" s="7">
@@ -23011,7 +23021,11 @@
       <c r="C1449" s="6">
         <v>6</v>
       </c>
-      <c r="D1449" s="2"/>
+      <c r="D1449" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1449" s="1"/>
+      <c r="G1449" s="22"/>
     </row>
     <row r="1450" spans="1:7">
       <c r="A1450" s="7">
@@ -23023,7 +23037,11 @@
       <c r="C1450" s="6">
         <v>3</v>
       </c>
-      <c r="D1450" s="2"/>
+      <c r="D1450" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1450" s="1"/>
+      <c r="G1450" s="22"/>
     </row>
     <row r="1451" spans="1:7">
       <c r="A1451" s="7">
@@ -23035,7 +23053,11 @@
       <c r="C1451" s="6">
         <v>3</v>
       </c>
-      <c r="D1451" s="2"/>
+      <c r="D1451" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1451" s="1"/>
+      <c r="G1451" s="22"/>
     </row>
     <row r="1452" spans="1:7">
       <c r="A1452" s="7">
@@ -23047,7 +23069,11 @@
       <c r="C1452" s="6">
         <v>3</v>
       </c>
-      <c r="D1452" s="2"/>
+      <c r="D1452" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1452" s="1"/>
+      <c r="G1452" s="22"/>
     </row>
     <row r="1453" spans="1:7">
       <c r="A1453" s="7">
@@ -23059,7 +23085,103 @@
       <c r="C1453" s="6">
         <v>3</v>
       </c>
-      <c r="D1453" s="2"/>
+      <c r="D1453" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1453" s="1"/>
+      <c r="G1453" s="22"/>
+    </row>
+    <row r="1454" spans="1:7">
+      <c r="A1454" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1454" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1454" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1454" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1454" s="1"/>
+      <c r="G1454" s="22"/>
+    </row>
+    <row r="1455" spans="1:7">
+      <c r="A1455" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B1455" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1455" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1455" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1455" s="1"/>
+      <c r="G1455" s="22"/>
+    </row>
+    <row r="1456" spans="1:7">
+      <c r="A1456" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B1456" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1456" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1456" s="2"/>
+    </row>
+    <row r="1457" spans="1:4">
+      <c r="A1457" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B1457" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1457" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1457" s="2"/>
+    </row>
+    <row r="1458" spans="1:4">
+      <c r="A1458" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B1458" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1458" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1458" s="2"/>
+    </row>
+    <row r="1459" spans="1:4">
+      <c r="A1459" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B1459" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1459" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1459" s="2"/>
+    </row>
+    <row r="1460" spans="1:4">
+      <c r="A1460" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B1460" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1460" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1460" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1460"/>
+  <dimension ref="A1:U1470"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23133,9 +23133,11 @@
       <c r="C1456" s="6">
         <v>8</v>
       </c>
-      <c r="D1456" s="2"/>
-    </row>
-    <row r="1457" spans="1:4">
+      <c r="D1456" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:7">
       <c r="A1457" s="7">
         <v>46098</v>
       </c>
@@ -23145,9 +23147,13 @@
       <c r="C1457" s="6">
         <v>5</v>
       </c>
-      <c r="D1457" s="2"/>
-    </row>
-    <row r="1458" spans="1:4">
+      <c r="D1457" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1457" s="1"/>
+      <c r="G1457" s="22"/>
+    </row>
+    <row r="1458" spans="1:7">
       <c r="A1458" s="7">
         <v>46098</v>
       </c>
@@ -23157,9 +23163,13 @@
       <c r="C1458" s="6">
         <v>5</v>
       </c>
-      <c r="D1458" s="2"/>
-    </row>
-    <row r="1459" spans="1:4">
+      <c r="D1458" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1458" s="1"/>
+      <c r="G1458" s="22"/>
+    </row>
+    <row r="1459" spans="1:7">
       <c r="A1459" s="7">
         <v>46098</v>
       </c>
@@ -23169,9 +23179,13 @@
       <c r="C1459" s="6">
         <v>4</v>
       </c>
-      <c r="D1459" s="2"/>
-    </row>
-    <row r="1460" spans="1:4">
+      <c r="D1459" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1459" s="1"/>
+      <c r="G1459" s="22"/>
+    </row>
+    <row r="1460" spans="1:7">
       <c r="A1460" s="7">
         <v>46098</v>
       </c>
@@ -23181,7 +23195,133 @@
       <c r="C1460" s="6">
         <v>4</v>
       </c>
-      <c r="D1460" s="2"/>
+      <c r="D1460" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1460" s="1"/>
+      <c r="G1460" s="22"/>
+    </row>
+    <row r="1461" spans="1:7">
+      <c r="A1461" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1461" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1461" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1461" s="2"/>
+      <c r="F1461" s="1"/>
+      <c r="G1461" s="22"/>
+    </row>
+    <row r="1462" spans="1:7">
+      <c r="A1462" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1462" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1462" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1462" s="2"/>
+    </row>
+    <row r="1463" spans="1:7">
+      <c r="A1463" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1463" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1463" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1463" s="2"/>
+    </row>
+    <row r="1464" spans="1:7">
+      <c r="A1464" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1464" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1464" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1464" s="2"/>
+    </row>
+    <row r="1465" spans="1:7">
+      <c r="A1465" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1465" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1465" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1465" s="2"/>
+    </row>
+    <row r="1466" spans="1:7">
+      <c r="A1466" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1466" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1466" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1466" s="2"/>
+    </row>
+    <row r="1467" spans="1:7">
+      <c r="A1467" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1467" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1467" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1467" s="2"/>
+    </row>
+    <row r="1468" spans="1:7">
+      <c r="A1468" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1468" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1468" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1468" s="2"/>
+    </row>
+    <row r="1469" spans="1:7">
+      <c r="A1469" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1469" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1469" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1469" s="2"/>
+    </row>
+    <row r="1470" spans="1:7">
+      <c r="A1470" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1470" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1470" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1470" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1470"/>
+  <dimension ref="A1:U1478"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23211,9 +23211,9 @@
       <c r="C1461" s="6">
         <v>3</v>
       </c>
-      <c r="D1461" s="2"/>
-      <c r="F1461" s="1"/>
-      <c r="G1461" s="22"/>
+      <c r="D1461" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1462" spans="1:7">
       <c r="A1462" s="7">
@@ -23225,7 +23225,11 @@
       <c r="C1462" s="6">
         <v>3</v>
       </c>
-      <c r="D1462" s="2"/>
+      <c r="D1462" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1462" s="1"/>
+      <c r="G1462" s="22"/>
     </row>
     <row r="1463" spans="1:7">
       <c r="A1463" s="7">
@@ -23237,7 +23241,11 @@
       <c r="C1463" s="6">
         <v>2</v>
       </c>
-      <c r="D1463" s="2"/>
+      <c r="D1463" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1463" s="1"/>
+      <c r="G1463" s="22"/>
     </row>
     <row r="1464" spans="1:7">
       <c r="A1464" s="7">
@@ -23249,7 +23257,11 @@
       <c r="C1464" s="6">
         <v>2</v>
       </c>
-      <c r="D1464" s="2"/>
+      <c r="D1464" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1464" s="1"/>
+      <c r="G1464" s="22"/>
     </row>
     <row r="1465" spans="1:7">
       <c r="A1465" s="7">
@@ -23261,7 +23273,11 @@
       <c r="C1465" s="6">
         <v>2</v>
       </c>
-      <c r="D1465" s="2"/>
+      <c r="D1465" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1465" s="1"/>
+      <c r="G1465" s="22"/>
     </row>
     <row r="1466" spans="1:7">
       <c r="A1466" s="7">
@@ -23273,7 +23289,11 @@
       <c r="C1466" s="6">
         <v>4</v>
       </c>
-      <c r="D1466" s="2"/>
+      <c r="D1466" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1466" s="1"/>
+      <c r="G1466" s="22"/>
     </row>
     <row r="1467" spans="1:7">
       <c r="A1467" s="7">
@@ -23285,7 +23305,11 @@
       <c r="C1467" s="6">
         <v>4</v>
       </c>
-      <c r="D1467" s="2"/>
+      <c r="D1467" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1467" s="1"/>
+      <c r="G1467" s="22"/>
     </row>
     <row r="1468" spans="1:7">
       <c r="A1468" s="7">
@@ -23297,7 +23321,11 @@
       <c r="C1468" s="6">
         <v>4</v>
       </c>
-      <c r="D1468" s="2"/>
+      <c r="D1468" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1468" s="1"/>
+      <c r="G1468" s="22"/>
     </row>
     <row r="1469" spans="1:7">
       <c r="A1469" s="7">
@@ -23309,7 +23337,11 @@
       <c r="C1469" s="6">
         <v>2</v>
       </c>
-      <c r="D1469" s="2"/>
+      <c r="D1469" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1469" s="1"/>
+      <c r="G1469" s="22"/>
     </row>
     <row r="1470" spans="1:7">
       <c r="A1470" s="7">
@@ -23321,7 +23353,109 @@
       <c r="C1470" s="6">
         <v>2</v>
       </c>
-      <c r="D1470" s="2"/>
+      <c r="D1470" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:7">
+      <c r="A1471" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1471" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1471" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1471" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:7">
+      <c r="A1472" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B1472" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1472" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1472" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4">
+      <c r="A1473" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1473" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1473" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1473" s="2"/>
+    </row>
+    <row r="1474" spans="1:4">
+      <c r="A1474" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1474" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1474" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1474" s="2"/>
+    </row>
+    <row r="1475" spans="1:4">
+      <c r="A1475" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1475" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1475" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1475" s="2"/>
+    </row>
+    <row r="1476" spans="1:4">
+      <c r="A1476" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1476" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1476" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1476" s="2"/>
+    </row>
+    <row r="1477" spans="1:4">
+      <c r="A1477" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1477" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1477" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1477" s="2"/>
+    </row>
+    <row r="1478" spans="1:4">
+      <c r="A1478" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B1478" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1478" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1478" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1478"/>
+  <dimension ref="A1:U1501"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23385,7 +23385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1473" spans="1:4">
+    <row r="1473" spans="1:7">
       <c r="A1473" s="7">
         <v>46100</v>
       </c>
@@ -23395,9 +23395,11 @@
       <c r="C1473" s="6">
         <v>3</v>
       </c>
-      <c r="D1473" s="2"/>
-    </row>
-    <row r="1474" spans="1:4">
+      <c r="D1473" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:7">
       <c r="A1474" s="7">
         <v>46100</v>
       </c>
@@ -23407,9 +23409,13 @@
       <c r="C1474" s="6">
         <v>3</v>
       </c>
-      <c r="D1474" s="2"/>
-    </row>
-    <row r="1475" spans="1:4">
+      <c r="D1474" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1474" s="1"/>
+      <c r="G1474" s="22"/>
+    </row>
+    <row r="1475" spans="1:7">
       <c r="A1475" s="7">
         <v>46100</v>
       </c>
@@ -23419,9 +23425,13 @@
       <c r="C1475" s="6">
         <v>3</v>
       </c>
-      <c r="D1475" s="2"/>
-    </row>
-    <row r="1476" spans="1:4">
+      <c r="D1475" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1475" s="1"/>
+      <c r="G1475" s="22"/>
+    </row>
+    <row r="1476" spans="1:7">
       <c r="A1476" s="7">
         <v>46100</v>
       </c>
@@ -23431,9 +23441,13 @@
       <c r="C1476" s="6">
         <v>5</v>
       </c>
-      <c r="D1476" s="2"/>
-    </row>
-    <row r="1477" spans="1:4">
+      <c r="D1476" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1476" s="1"/>
+      <c r="G1476" s="22"/>
+    </row>
+    <row r="1477" spans="1:7">
       <c r="A1477" s="7">
         <v>46100</v>
       </c>
@@ -23443,9 +23457,13 @@
       <c r="C1477" s="6">
         <v>5</v>
       </c>
-      <c r="D1477" s="2"/>
-    </row>
-    <row r="1478" spans="1:4">
+      <c r="D1477" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1477" s="1"/>
+      <c r="G1477" s="22"/>
+    </row>
+    <row r="1478" spans="1:7">
       <c r="A1478" s="7">
         <v>46100</v>
       </c>
@@ -23455,7 +23473,341 @@
       <c r="C1478" s="6">
         <v>5</v>
       </c>
-      <c r="D1478" s="2"/>
+      <c r="D1478" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1478" s="1"/>
+      <c r="G1478" s="22"/>
+    </row>
+    <row r="1479" spans="1:7">
+      <c r="A1479" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1479" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1479" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1479" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:7">
+      <c r="A1480" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1480" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1480" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1480" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1480" s="1"/>
+      <c r="G1480" s="22"/>
+    </row>
+    <row r="1481" spans="1:7">
+      <c r="A1481" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1481" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1481" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1481" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1481" s="1"/>
+      <c r="G1481" s="22"/>
+    </row>
+    <row r="1482" spans="1:7">
+      <c r="A1482" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1482" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1482" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1482" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1482" s="1"/>
+      <c r="G1482" s="22"/>
+    </row>
+    <row r="1483" spans="1:7">
+      <c r="A1483" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1483" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1483" s="6">
+        <v>10</v>
+      </c>
+      <c r="D1483" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1483" s="1"/>
+      <c r="G1483" s="22"/>
+    </row>
+    <row r="1484" spans="1:7">
+      <c r="A1484" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1484" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1484" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1484" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1484" s="1"/>
+      <c r="G1484" s="22"/>
+    </row>
+    <row r="1485" spans="1:7">
+      <c r="A1485" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1485" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1485" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1485" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:7">
+      <c r="A1486" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1486" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1486" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1486" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:7">
+      <c r="A1487" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1487" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1487" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1487" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:7">
+      <c r="A1488" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B1488" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1488" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1488" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:7">
+      <c r="A1489" s="7">
+        <v>46102</v>
+      </c>
+      <c r="B1489" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1489" s="6">
+        <v>10</v>
+      </c>
+      <c r="D1489" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:7">
+      <c r="A1490" s="7">
+        <v>46102</v>
+      </c>
+      <c r="B1490" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1490" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1490" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1490" s="1"/>
+      <c r="G1490" s="22"/>
+    </row>
+    <row r="1491" spans="1:7">
+      <c r="A1491" s="7">
+        <v>46102</v>
+      </c>
+      <c r="B1491" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1491" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1491" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1491" s="1"/>
+      <c r="G1491" s="22"/>
+    </row>
+    <row r="1492" spans="1:7">
+      <c r="A1492" s="7">
+        <v>46102</v>
+      </c>
+      <c r="B1492" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1492" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1492" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1492" s="1"/>
+      <c r="G1492" s="22"/>
+    </row>
+    <row r="1493" spans="1:7">
+      <c r="A1493" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1493" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1493" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1493" s="2"/>
+      <c r="F1493" s="1"/>
+      <c r="G1493" s="22"/>
+    </row>
+    <row r="1494" spans="1:7">
+      <c r="A1494" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1494" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1494" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1494" s="2"/>
+      <c r="F1494" s="1"/>
+      <c r="G1494" s="22"/>
+    </row>
+    <row r="1495" spans="1:7">
+      <c r="A1495" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1495" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1495" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1495" s="2"/>
+      <c r="F1495" s="1"/>
+      <c r="G1495" s="22"/>
+    </row>
+    <row r="1496" spans="1:7">
+      <c r="A1496" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1496" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1496" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1496" s="2"/>
+      <c r="F1496" s="1"/>
+      <c r="G1496" s="22"/>
+    </row>
+    <row r="1497" spans="1:7">
+      <c r="A1497" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1497" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1497" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1497" s="2"/>
+      <c r="F1497" s="1"/>
+      <c r="G1497" s="22"/>
+    </row>
+    <row r="1498" spans="1:7">
+      <c r="A1498" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1498" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1498" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1498" s="2"/>
+    </row>
+    <row r="1499" spans="1:7">
+      <c r="A1499" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1499" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1499" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1499" s="2"/>
+    </row>
+    <row r="1500" spans="1:7">
+      <c r="A1500" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1500" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1500" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1500" s="2"/>
+    </row>
+    <row r="1501" spans="1:7">
+      <c r="A1501" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B1501" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1501" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1501" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1501"/>
+  <dimension ref="A1:U1513"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23688,8 +23688,6 @@
       <c r="D1492" s="2">
         <v>1</v>
       </c>
-      <c r="F1492" s="1"/>
-      <c r="G1492" s="22"/>
     </row>
     <row r="1493" spans="1:7">
       <c r="A1493" s="7">
@@ -23701,7 +23699,9 @@
       <c r="C1493" s="6">
         <v>8</v>
       </c>
-      <c r="D1493" s="2"/>
+      <c r="D1493" s="2">
+        <v>2</v>
+      </c>
       <c r="F1493" s="1"/>
       <c r="G1493" s="22"/>
     </row>
@@ -23715,7 +23715,9 @@
       <c r="C1494" s="6">
         <v>8</v>
       </c>
-      <c r="D1494" s="2"/>
+      <c r="D1494" s="2">
+        <v>2</v>
+      </c>
       <c r="F1494" s="1"/>
       <c r="G1494" s="22"/>
     </row>
@@ -23729,7 +23731,9 @@
       <c r="C1495" s="6">
         <v>4</v>
       </c>
-      <c r="D1495" s="2"/>
+      <c r="D1495" s="2">
+        <v>3</v>
+      </c>
       <c r="F1495" s="1"/>
       <c r="G1495" s="22"/>
     </row>
@@ -23743,7 +23747,9 @@
       <c r="C1496" s="6">
         <v>2</v>
       </c>
-      <c r="D1496" s="2"/>
+      <c r="D1496" s="2">
+        <v>3</v>
+      </c>
       <c r="F1496" s="1"/>
       <c r="G1496" s="22"/>
     </row>
@@ -23757,7 +23763,9 @@
       <c r="C1497" s="6">
         <v>2</v>
       </c>
-      <c r="D1497" s="2"/>
+      <c r="D1497" s="2">
+        <v>3</v>
+      </c>
       <c r="F1497" s="1"/>
       <c r="G1497" s="22"/>
     </row>
@@ -23771,7 +23779,11 @@
       <c r="C1498" s="6">
         <v>3</v>
       </c>
-      <c r="D1498" s="2"/>
+      <c r="D1498" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1498" s="1"/>
+      <c r="G1498" s="22"/>
     </row>
     <row r="1499" spans="1:7">
       <c r="A1499" s="7">
@@ -23783,7 +23795,11 @@
       <c r="C1499" s="6">
         <v>3</v>
       </c>
-      <c r="D1499" s="2"/>
+      <c r="D1499" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1499" s="1"/>
+      <c r="G1499" s="22"/>
     </row>
     <row r="1500" spans="1:7">
       <c r="A1500" s="7">
@@ -23795,7 +23811,9 @@
       <c r="C1500" s="6">
         <v>1</v>
       </c>
-      <c r="D1500" s="2"/>
+      <c r="D1500" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1501" spans="1:7">
       <c r="A1501" s="7">
@@ -23807,7 +23825,153 @@
       <c r="C1501" s="6">
         <v>1</v>
       </c>
-      <c r="D1501" s="2"/>
+      <c r="D1501" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:7">
+      <c r="A1502" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1502" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1502" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1502" s="2"/>
+    </row>
+    <row r="1503" spans="1:7">
+      <c r="A1503" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1503" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1503" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1503" s="2"/>
+    </row>
+    <row r="1504" spans="1:7">
+      <c r="A1504" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1504" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1504" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1504" s="2"/>
+    </row>
+    <row r="1505" spans="1:4">
+      <c r="A1505" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1505" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1505" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1505" s="2"/>
+    </row>
+    <row r="1506" spans="1:4">
+      <c r="A1506" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1506" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1506" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1506" s="2"/>
+    </row>
+    <row r="1507" spans="1:4">
+      <c r="A1507" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1507" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1507" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1507" s="2"/>
+    </row>
+    <row r="1508" spans="1:4">
+      <c r="A1508" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1508" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1508" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1508" s="2"/>
+    </row>
+    <row r="1509" spans="1:4">
+      <c r="A1509" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1509" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1509" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1509" s="2"/>
+    </row>
+    <row r="1510" spans="1:4">
+      <c r="A1510" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1510" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1510" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1510" s="2"/>
+    </row>
+    <row r="1511" spans="1:4">
+      <c r="A1511" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1511" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1511" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1511" s="2"/>
+    </row>
+    <row r="1512" spans="1:4">
+      <c r="A1512" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1512" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1512" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1512" s="2"/>
+    </row>
+    <row r="1513" spans="1:4">
+      <c r="A1513" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B1513" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1513" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1513" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1513"/>
+  <dimension ref="A1:U1522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23839,7 +23839,9 @@
       <c r="C1502" s="6">
         <v>3</v>
       </c>
-      <c r="D1502" s="2"/>
+      <c r="D1502" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1503" spans="1:7">
       <c r="A1503" s="7">
@@ -23851,7 +23853,11 @@
       <c r="C1503" s="6">
         <v>3</v>
       </c>
-      <c r="D1503" s="2"/>
+      <c r="D1503" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1503" s="1"/>
+      <c r="G1503" s="22"/>
     </row>
     <row r="1504" spans="1:7">
       <c r="A1504" s="7">
@@ -23863,9 +23869,13 @@
       <c r="C1504" s="6">
         <v>4</v>
       </c>
-      <c r="D1504" s="2"/>
-    </row>
-    <row r="1505" spans="1:4">
+      <c r="D1504" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1504" s="1"/>
+      <c r="G1504" s="22"/>
+    </row>
+    <row r="1505" spans="1:7">
       <c r="A1505" s="7">
         <v>46105</v>
       </c>
@@ -23875,9 +23885,13 @@
       <c r="C1505" s="6">
         <v>4</v>
       </c>
-      <c r="D1505" s="2"/>
-    </row>
-    <row r="1506" spans="1:4">
+      <c r="D1505" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1505" s="1"/>
+      <c r="G1505" s="22"/>
+    </row>
+    <row r="1506" spans="1:7">
       <c r="A1506" s="7">
         <v>46105</v>
       </c>
@@ -23887,9 +23901,13 @@
       <c r="C1506" s="6">
         <v>4</v>
       </c>
-      <c r="D1506" s="2"/>
-    </row>
-    <row r="1507" spans="1:4">
+      <c r="D1506" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1506" s="1"/>
+      <c r="G1506" s="22"/>
+    </row>
+    <row r="1507" spans="1:7">
       <c r="A1507" s="7">
         <v>46105</v>
       </c>
@@ -23899,9 +23917,13 @@
       <c r="C1507" s="6">
         <v>4</v>
       </c>
-      <c r="D1507" s="2"/>
-    </row>
-    <row r="1508" spans="1:4">
+      <c r="D1507" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1507" s="1"/>
+      <c r="G1507" s="22"/>
+    </row>
+    <row r="1508" spans="1:7">
       <c r="A1508" s="7">
         <v>46105</v>
       </c>
@@ -23911,9 +23933,13 @@
       <c r="C1508" s="6">
         <v>5</v>
       </c>
-      <c r="D1508" s="2"/>
-    </row>
-    <row r="1509" spans="1:4">
+      <c r="D1508" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1508" s="1"/>
+      <c r="G1508" s="22"/>
+    </row>
+    <row r="1509" spans="1:7">
       <c r="A1509" s="7">
         <v>46105</v>
       </c>
@@ -23923,9 +23949,13 @@
       <c r="C1509" s="6">
         <v>5</v>
       </c>
-      <c r="D1509" s="2"/>
-    </row>
-    <row r="1510" spans="1:4">
+      <c r="D1509" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1509" s="1"/>
+      <c r="G1509" s="22"/>
+    </row>
+    <row r="1510" spans="1:7">
       <c r="A1510" s="7">
         <v>46105</v>
       </c>
@@ -23935,9 +23965,13 @@
       <c r="C1510" s="6">
         <v>1</v>
       </c>
-      <c r="D1510" s="2"/>
-    </row>
-    <row r="1511" spans="1:4">
+      <c r="D1510" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1510" s="1"/>
+      <c r="G1510" s="22"/>
+    </row>
+    <row r="1511" spans="1:7">
       <c r="A1511" s="7">
         <v>46105</v>
       </c>
@@ -23947,9 +23981,11 @@
       <c r="C1511" s="6">
         <v>1</v>
       </c>
-      <c r="D1511" s="2"/>
-    </row>
-    <row r="1512" spans="1:4">
+      <c r="D1511" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:7">
       <c r="A1512" s="7">
         <v>46105</v>
       </c>
@@ -23959,9 +23995,11 @@
       <c r="C1512" s="6">
         <v>7</v>
       </c>
-      <c r="D1512" s="2"/>
-    </row>
-    <row r="1513" spans="1:4">
+      <c r="D1512" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:7">
       <c r="A1513" s="7">
         <v>46105</v>
       </c>
@@ -23971,7 +24009,117 @@
       <c r="C1513" s="2">
         <v>7</v>
       </c>
-      <c r="D1513" s="2"/>
+      <c r="D1513" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:7">
+      <c r="A1514" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1514" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1514" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1514" s="2"/>
+    </row>
+    <row r="1515" spans="1:7">
+      <c r="A1515" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1515" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1515" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1515" s="2"/>
+    </row>
+    <row r="1516" spans="1:7">
+      <c r="A1516" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1516" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1516" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1516" s="2"/>
+    </row>
+    <row r="1517" spans="1:7">
+      <c r="A1517" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1517" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1517" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1517" s="2"/>
+    </row>
+    <row r="1518" spans="1:7">
+      <c r="A1518" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1518" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1518" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1518" s="2"/>
+    </row>
+    <row r="1519" spans="1:7">
+      <c r="A1519" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1519" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1519" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1519" s="2"/>
+    </row>
+    <row r="1520" spans="1:7">
+      <c r="A1520" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1520" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1520" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1520" s="2"/>
+    </row>
+    <row r="1521" spans="1:4">
+      <c r="A1521" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1521" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1521" s="6">
+        <v>11</v>
+      </c>
+      <c r="D1521" s="2"/>
+    </row>
+    <row r="1522" spans="1:4">
+      <c r="A1522" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1522" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1522" s="6">
+        <v>11</v>
+      </c>
+      <c r="D1522" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1522"/>
+  <dimension ref="A1:U1529"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -24023,7 +24023,9 @@
       <c r="C1514" s="6">
         <v>2</v>
       </c>
-      <c r="D1514" s="2"/>
+      <c r="D1514" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="1515" spans="1:7">
       <c r="A1515" s="7">
@@ -24035,7 +24037,11 @@
       <c r="C1515" s="6">
         <v>2</v>
       </c>
-      <c r="D1515" s="2"/>
+      <c r="D1515" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1515" s="1"/>
+      <c r="G1515" s="22"/>
     </row>
     <row r="1516" spans="1:7">
       <c r="A1516" s="7">
@@ -24047,7 +24053,11 @@
       <c r="C1516" s="6">
         <v>1</v>
       </c>
-      <c r="D1516" s="2"/>
+      <c r="D1516" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1516" s="1"/>
+      <c r="G1516" s="22"/>
     </row>
     <row r="1517" spans="1:7">
       <c r="A1517" s="7">
@@ -24059,7 +24069,11 @@
       <c r="C1517" s="6">
         <v>1</v>
       </c>
-      <c r="D1517" s="2"/>
+      <c r="D1517" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1517" s="1"/>
+      <c r="G1517" s="22"/>
     </row>
     <row r="1518" spans="1:7">
       <c r="A1518" s="7">
@@ -24071,7 +24085,11 @@
       <c r="C1518" s="6">
         <v>6</v>
       </c>
-      <c r="D1518" s="2"/>
+      <c r="D1518" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1518" s="1"/>
+      <c r="G1518" s="22"/>
     </row>
     <row r="1519" spans="1:7">
       <c r="A1519" s="7">
@@ -24083,7 +24101,11 @@
       <c r="C1519" s="6">
         <v>5</v>
       </c>
-      <c r="D1519" s="2"/>
+      <c r="D1519" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1519" s="1"/>
+      <c r="G1519" s="22"/>
     </row>
     <row r="1520" spans="1:7">
       <c r="A1520" s="7">
@@ -24095,7 +24117,11 @@
       <c r="C1520" s="6">
         <v>5</v>
       </c>
-      <c r="D1520" s="2"/>
+      <c r="D1520" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1520" s="1"/>
+      <c r="G1520" s="22"/>
     </row>
     <row r="1521" spans="1:4">
       <c r="A1521" s="7">
@@ -24107,7 +24133,9 @@
       <c r="C1521" s="6">
         <v>11</v>
       </c>
-      <c r="D1521" s="2"/>
+      <c r="D1521" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1522" spans="1:4">
       <c r="A1522" s="7">
@@ -24119,7 +24147,97 @@
       <c r="C1522" s="6">
         <v>11</v>
       </c>
-      <c r="D1522" s="2"/>
+      <c r="D1522" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4">
+      <c r="A1523" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1523" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1523" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1523" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4">
+      <c r="A1524" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B1524" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1524" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1524" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4">
+      <c r="A1525" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B1525" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1525" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1525" s="2"/>
+    </row>
+    <row r="1526" spans="1:4">
+      <c r="A1526" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B1526" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1526" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1526" s="2"/>
+    </row>
+    <row r="1527" spans="1:4">
+      <c r="A1527" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B1527" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1527" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1527" s="2"/>
+    </row>
+    <row r="1528" spans="1:4">
+      <c r="A1528" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B1528" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1528" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1528" s="2"/>
+    </row>
+    <row r="1529" spans="1:4">
+      <c r="A1529" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B1529" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1529" s="6">
+        <v>12</v>
+      </c>
+      <c r="D1529" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1529"/>
+  <dimension ref="A1:U1556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -829,7 +829,8 @@
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="9" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="8" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -24123,7 +24124,7 @@
       <c r="F1520" s="1"/>
       <c r="G1520" s="22"/>
     </row>
-    <row r="1521" spans="1:4">
+    <row r="1521" spans="1:7">
       <c r="A1521" s="7">
         <v>46106</v>
       </c>
@@ -24137,7 +24138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1522" spans="1:4">
+    <row r="1522" spans="1:7">
       <c r="A1522" s="7">
         <v>46106</v>
       </c>
@@ -24151,7 +24152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1523" spans="1:4">
+    <row r="1523" spans="1:7">
       <c r="A1523" s="7">
         <v>46106</v>
       </c>
@@ -24165,7 +24166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1524" spans="1:4">
+    <row r="1524" spans="1:7">
       <c r="A1524" s="7">
         <v>46106</v>
       </c>
@@ -24179,7 +24180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1525" spans="1:4">
+    <row r="1525" spans="1:7">
       <c r="A1525" s="7">
         <v>46107</v>
       </c>
@@ -24189,9 +24190,11 @@
       <c r="C1525" s="6">
         <v>7</v>
       </c>
-      <c r="D1525" s="2"/>
-    </row>
-    <row r="1526" spans="1:4">
+      <c r="D1525" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:7">
       <c r="A1526" s="7">
         <v>46107</v>
       </c>
@@ -24201,9 +24204,13 @@
       <c r="C1526" s="6">
         <v>6</v>
       </c>
-      <c r="D1526" s="2"/>
-    </row>
-    <row r="1527" spans="1:4">
+      <c r="D1526" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1526" s="1"/>
+      <c r="G1526" s="22"/>
+    </row>
+    <row r="1527" spans="1:7">
       <c r="A1527" s="7">
         <v>46107</v>
       </c>
@@ -24213,9 +24220,13 @@
       <c r="C1527" s="6">
         <v>4</v>
       </c>
-      <c r="D1527" s="2"/>
-    </row>
-    <row r="1528" spans="1:4">
+      <c r="D1527" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1527" s="1"/>
+      <c r="G1527" s="22"/>
+    </row>
+    <row r="1528" spans="1:7">
       <c r="A1528" s="7">
         <v>46107</v>
       </c>
@@ -24225,9 +24236,13 @@
       <c r="C1528" s="6">
         <v>4</v>
       </c>
-      <c r="D1528" s="2"/>
-    </row>
-    <row r="1529" spans="1:4">
+      <c r="D1528" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1528" s="1"/>
+      <c r="G1528" s="22"/>
+    </row>
+    <row r="1529" spans="1:7">
       <c r="A1529" s="7">
         <v>46107</v>
       </c>
@@ -24237,7 +24252,397 @@
       <c r="C1529" s="6">
         <v>12</v>
       </c>
-      <c r="D1529" s="2"/>
+      <c r="D1529" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1529" s="1"/>
+      <c r="G1529" s="22"/>
+    </row>
+    <row r="1530" spans="1:7">
+      <c r="A1530" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1530" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1530" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1530" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:7">
+      <c r="A1531" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1531" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1531" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1531" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1531" s="1"/>
+      <c r="G1531" s="22"/>
+    </row>
+    <row r="1532" spans="1:7">
+      <c r="A1532" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1532" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1532" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1532" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1532" s="1"/>
+      <c r="G1532" s="22"/>
+    </row>
+    <row r="1533" spans="1:7">
+      <c r="A1533" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1533" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1533" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1533" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1533" s="1"/>
+      <c r="G1533" s="22"/>
+    </row>
+    <row r="1534" spans="1:7">
+      <c r="A1534" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1534" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1534" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1534" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1534" s="1"/>
+      <c r="G1534" s="22"/>
+    </row>
+    <row r="1535" spans="1:7">
+      <c r="A1535" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1535" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1535" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1535" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1535" s="1"/>
+      <c r="G1535" s="22"/>
+    </row>
+    <row r="1536" spans="1:7">
+      <c r="A1536" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1536" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1536" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1536" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1536" s="1"/>
+      <c r="G1536" s="22"/>
+    </row>
+    <row r="1537" spans="1:8">
+      <c r="A1537" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1537" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1537" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1537" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1537" s="1"/>
+      <c r="G1537" s="22"/>
+    </row>
+    <row r="1538" spans="1:8">
+      <c r="A1538" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1538" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1538" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1538" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1538" s="1"/>
+      <c r="G1538" s="22"/>
+    </row>
+    <row r="1539" spans="1:8">
+      <c r="A1539" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B1539" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1539" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1539" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:8">
+      <c r="A1540" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1540" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1540" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1540" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:8">
+      <c r="A1541" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1541" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1541" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1541" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1541" s="1"/>
+      <c r="H1541" s="22"/>
+    </row>
+    <row r="1542" spans="1:8">
+      <c r="A1542" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1542" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1542" s="6">
+        <v>9</v>
+      </c>
+      <c r="D1542" s="2">
+        <v>8</v>
+      </c>
+      <c r="G1542" s="1"/>
+      <c r="H1542" s="22"/>
+    </row>
+    <row r="1543" spans="1:8">
+      <c r="A1543" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1543" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1543" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1543" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1543" s="1"/>
+      <c r="H1543" s="22"/>
+    </row>
+    <row r="1544" spans="1:8">
+      <c r="A1544" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1544" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1544" s="6">
+        <v>12</v>
+      </c>
+      <c r="D1544" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1544" s="1"/>
+      <c r="H1544" s="22"/>
+    </row>
+    <row r="1545" spans="1:8">
+      <c r="A1545" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1545" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1545" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1545" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1545" s="1"/>
+      <c r="H1545" s="22"/>
+    </row>
+    <row r="1546" spans="1:8">
+      <c r="A1546" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B1546" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1546" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1546" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1546" s="1"/>
+      <c r="H1546" s="22"/>
+    </row>
+    <row r="1547" spans="1:8">
+      <c r="A1547" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1547" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1547" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1547" s="2"/>
+    </row>
+    <row r="1548" spans="1:8">
+      <c r="A1548" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1548" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1548" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1548" s="2"/>
+    </row>
+    <row r="1549" spans="1:8">
+      <c r="A1549" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1549" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1549" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1549" s="2"/>
+    </row>
+    <row r="1550" spans="1:8">
+      <c r="A1550" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1550" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1550" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1550" s="2"/>
+    </row>
+    <row r="1551" spans="1:8">
+      <c r="A1551" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1551" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1551" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1551" s="2"/>
+    </row>
+    <row r="1552" spans="1:8">
+      <c r="A1552" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1552" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1552" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1552" s="2"/>
+    </row>
+    <row r="1553" spans="1:4">
+      <c r="A1553" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1553" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1553" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1553" s="2"/>
+    </row>
+    <row r="1554" spans="1:4">
+      <c r="A1554" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1554" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1554" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1554" s="2"/>
+    </row>
+    <row r="1555" spans="1:4">
+      <c r="A1555" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1555" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1555" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1555" s="2"/>
+    </row>
+    <row r="1556" spans="1:4">
+      <c r="A1556" s="7">
+        <v>46110</v>
+      </c>
+      <c r="B1556" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1556" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1556" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1556"/>
+  <dimension ref="A1:U1568"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -24526,7 +24526,7 @@
     </row>
     <row r="1547" spans="1:8">
       <c r="A1547" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1547" s="14" t="s">
         <v>3</v>
@@ -24534,11 +24534,13 @@
       <c r="C1547" s="6">
         <v>6</v>
       </c>
-      <c r="D1547" s="2"/>
+      <c r="D1547" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1548" spans="1:8">
       <c r="A1548" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1548" s="14" t="s">
         <v>8</v>
@@ -24546,11 +24548,13 @@
       <c r="C1548" s="6">
         <v>6</v>
       </c>
-      <c r="D1548" s="2"/>
+      <c r="D1548" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1549" spans="1:8">
       <c r="A1549" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1549" s="57" t="s">
         <v>11</v>
@@ -24558,11 +24562,13 @@
       <c r="C1549" s="6">
         <v>4</v>
       </c>
-      <c r="D1549" s="2"/>
+      <c r="D1549" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1550" spans="1:8">
       <c r="A1550" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1550" s="57" t="s">
         <v>7</v>
@@ -24570,11 +24576,13 @@
       <c r="C1550" s="2">
         <v>4</v>
       </c>
-      <c r="D1550" s="2"/>
+      <c r="D1550" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1551" spans="1:8">
       <c r="A1551" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1551" s="56" t="s">
         <v>6</v>
@@ -24582,11 +24590,13 @@
       <c r="C1551" s="2">
         <v>3</v>
       </c>
-      <c r="D1551" s="2"/>
+      <c r="D1551" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1552" spans="1:8">
       <c r="A1552" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1552" s="56" t="s">
         <v>10</v>
@@ -24594,11 +24604,13 @@
       <c r="C1552" s="2">
         <v>3</v>
       </c>
-      <c r="D1552" s="2"/>
+      <c r="D1552" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1553" spans="1:4">
       <c r="A1553" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1553" s="16" t="s">
         <v>15</v>
@@ -24606,11 +24618,13 @@
       <c r="C1553" s="2">
         <v>5</v>
       </c>
-      <c r="D1553" s="2"/>
+      <c r="D1553" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1554" spans="1:4">
       <c r="A1554" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1554" s="16" t="s">
         <v>9</v>
@@ -24618,11 +24632,13 @@
       <c r="C1554" s="2">
         <v>5</v>
       </c>
-      <c r="D1554" s="2"/>
+      <c r="D1554" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1555" spans="1:4">
       <c r="A1555" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1555" s="66" t="s">
         <v>5</v>
@@ -24630,11 +24646,13 @@
       <c r="C1555" s="2">
         <v>3</v>
       </c>
-      <c r="D1555" s="2"/>
+      <c r="D1555" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1556" spans="1:4">
       <c r="A1556" s="7">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B1556" s="66" t="s">
         <v>25</v>
@@ -24642,7 +24660,153 @@
       <c r="C1556" s="2">
         <v>2</v>
       </c>
-      <c r="D1556" s="2"/>
+      <c r="D1556" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4">
+      <c r="A1557" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1557" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1557" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1557" s="2"/>
+    </row>
+    <row r="1558" spans="1:4">
+      <c r="A1558" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1558" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1558" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1558" s="2"/>
+    </row>
+    <row r="1559" spans="1:4">
+      <c r="A1559" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1559" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1559" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1559" s="2"/>
+    </row>
+    <row r="1560" spans="1:4">
+      <c r="A1560" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1560" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1560" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1560" s="2"/>
+    </row>
+    <row r="1561" spans="1:4">
+      <c r="A1561" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1561" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1561" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1561" s="2"/>
+    </row>
+    <row r="1562" spans="1:4">
+      <c r="A1562" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1562" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1562" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1562" s="2"/>
+    </row>
+    <row r="1563" spans="1:4">
+      <c r="A1563" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1563" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1563" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1563" s="2"/>
+    </row>
+    <row r="1564" spans="1:4">
+      <c r="A1564" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1564" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1564" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1564" s="2"/>
+    </row>
+    <row r="1565" spans="1:4">
+      <c r="A1565" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1565" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1565" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1565" s="2"/>
+    </row>
+    <row r="1566" spans="1:4">
+      <c r="A1566" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1566" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1566" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1566" s="2"/>
+    </row>
+    <row r="1567" spans="1:4">
+      <c r="A1567" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1567" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1567" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1567" s="2"/>
+    </row>
+    <row r="1568" spans="1:4">
+      <c r="A1568" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B1568" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1568" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1568" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1568"/>
+  <dimension ref="A1:U1579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -829,8 +829,7 @@
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="9" width="29.42578125" customWidth="1"/>
+    <col min="7" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="11" width="22.7109375" customWidth="1"/>
     <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -24608,7 +24607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1553" spans="1:4">
+    <row r="1553" spans="1:7">
       <c r="A1553" s="7">
         <v>46111</v>
       </c>
@@ -24622,7 +24621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1554" spans="1:4">
+    <row r="1554" spans="1:7">
       <c r="A1554" s="7">
         <v>46111</v>
       </c>
@@ -24636,7 +24635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1555" spans="1:4">
+    <row r="1555" spans="1:7">
       <c r="A1555" s="7">
         <v>46111</v>
       </c>
@@ -24650,7 +24649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1556" spans="1:4">
+    <row r="1556" spans="1:7">
       <c r="A1556" s="7">
         <v>46111</v>
       </c>
@@ -24664,7 +24663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1557" spans="1:4">
+    <row r="1557" spans="1:7">
       <c r="A1557" s="7">
         <v>46112</v>
       </c>
@@ -24674,9 +24673,11 @@
       <c r="C1557" s="6">
         <v>5</v>
       </c>
-      <c r="D1557" s="2"/>
-    </row>
-    <row r="1558" spans="1:4">
+      <c r="D1557" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:7">
       <c r="A1558" s="7">
         <v>46112</v>
       </c>
@@ -24686,9 +24687,11 @@
       <c r="C1558" s="6">
         <v>5</v>
       </c>
-      <c r="D1558" s="2"/>
-    </row>
-    <row r="1559" spans="1:4">
+      <c r="D1558" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:7">
       <c r="A1559" s="7">
         <v>46112</v>
       </c>
@@ -24698,9 +24701,13 @@
       <c r="C1559" s="6">
         <v>2</v>
       </c>
-      <c r="D1559" s="2"/>
-    </row>
-    <row r="1560" spans="1:4">
+      <c r="D1559" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1559" s="1"/>
+      <c r="G1559" s="22"/>
+    </row>
+    <row r="1560" spans="1:7">
       <c r="A1560" s="7">
         <v>46112</v>
       </c>
@@ -24710,9 +24717,13 @@
       <c r="C1560" s="6">
         <v>2</v>
       </c>
-      <c r="D1560" s="2"/>
-    </row>
-    <row r="1561" spans="1:4">
+      <c r="D1560" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1560" s="1"/>
+      <c r="G1560" s="22"/>
+    </row>
+    <row r="1561" spans="1:7">
       <c r="A1561" s="7">
         <v>46112</v>
       </c>
@@ -24722,9 +24733,13 @@
       <c r="C1561" s="6">
         <v>6</v>
       </c>
-      <c r="D1561" s="2"/>
-    </row>
-    <row r="1562" spans="1:4">
+      <c r="D1561" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1561" s="1"/>
+      <c r="G1561" s="22"/>
+    </row>
+    <row r="1562" spans="1:7">
       <c r="A1562" s="7">
         <v>46112</v>
       </c>
@@ -24734,9 +24749,13 @@
       <c r="C1562" s="6">
         <v>6</v>
       </c>
-      <c r="D1562" s="2"/>
-    </row>
-    <row r="1563" spans="1:4">
+      <c r="D1562" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1562" s="1"/>
+      <c r="G1562" s="22"/>
+    </row>
+    <row r="1563" spans="1:7">
       <c r="A1563" s="7">
         <v>46112</v>
       </c>
@@ -24746,9 +24765,13 @@
       <c r="C1563" s="6">
         <v>5</v>
       </c>
-      <c r="D1563" s="2"/>
-    </row>
-    <row r="1564" spans="1:4">
+      <c r="D1563" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1563" s="1"/>
+      <c r="G1563" s="22"/>
+    </row>
+    <row r="1564" spans="1:7">
       <c r="A1564" s="7">
         <v>46112</v>
       </c>
@@ -24758,9 +24781,13 @@
       <c r="C1564" s="6">
         <v>5</v>
       </c>
-      <c r="D1564" s="2"/>
-    </row>
-    <row r="1565" spans="1:4">
+      <c r="D1564" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1564" s="1"/>
+      <c r="G1564" s="22"/>
+    </row>
+    <row r="1565" spans="1:7">
       <c r="A1565" s="7">
         <v>46112</v>
       </c>
@@ -24770,9 +24797,13 @@
       <c r="C1565" s="6">
         <v>4</v>
       </c>
-      <c r="D1565" s="2"/>
-    </row>
-    <row r="1566" spans="1:4">
+      <c r="D1565" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1565" s="1"/>
+      <c r="G1565" s="22"/>
+    </row>
+    <row r="1566" spans="1:7">
       <c r="A1566" s="7">
         <v>46112</v>
       </c>
@@ -24782,9 +24813,13 @@
       <c r="C1566" s="6">
         <v>4</v>
       </c>
-      <c r="D1566" s="2"/>
-    </row>
-    <row r="1567" spans="1:4">
+      <c r="D1566" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1566" s="1"/>
+      <c r="G1566" s="22"/>
+    </row>
+    <row r="1567" spans="1:7">
       <c r="A1567" s="7">
         <v>46112</v>
       </c>
@@ -24794,9 +24829,13 @@
       <c r="C1567" s="6">
         <v>3</v>
       </c>
-      <c r="D1567" s="2"/>
-    </row>
-    <row r="1568" spans="1:4">
+      <c r="D1567" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1567" s="1"/>
+      <c r="G1567" s="22"/>
+    </row>
+    <row r="1568" spans="1:7">
       <c r="A1568" s="7">
         <v>46112</v>
       </c>
@@ -24806,7 +24845,141 @@
       <c r="C1568" s="6">
         <v>3</v>
       </c>
-      <c r="D1568" s="2"/>
+      <c r="D1568" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4">
+      <c r="A1569" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1569" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1569" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1569" s="2"/>
+    </row>
+    <row r="1570" spans="1:4">
+      <c r="A1570" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1570" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1570" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1570" s="2"/>
+    </row>
+    <row r="1571" spans="1:4">
+      <c r="A1571" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1571" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1571" s="6">
+        <v>5</v>
+      </c>
+      <c r="D1571" s="2"/>
+    </row>
+    <row r="1572" spans="1:4">
+      <c r="A1572" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1572" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1572" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1572" s="2"/>
+    </row>
+    <row r="1573" spans="1:4">
+      <c r="A1573" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1573" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1573" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1573" s="2"/>
+    </row>
+    <row r="1574" spans="1:4">
+      <c r="A1574" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1574" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1574" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1574" s="2"/>
+    </row>
+    <row r="1575" spans="1:4">
+      <c r="A1575" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1575" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1575" s="6">
+        <v>7</v>
+      </c>
+      <c r="D1575" s="2"/>
+    </row>
+    <row r="1576" spans="1:4">
+      <c r="A1576" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1576" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1576" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1576" s="2"/>
+    </row>
+    <row r="1577" spans="1:4">
+      <c r="A1577" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1577" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1577" s="6">
+        <v>4</v>
+      </c>
+      <c r="D1577" s="2"/>
+    </row>
+    <row r="1578" spans="1:4">
+      <c r="A1578" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1578" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1578" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1578" s="2"/>
+    </row>
+    <row r="1579" spans="1:4">
+      <c r="A1579" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B1579" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1579" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1579" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1579"/>
+  <dimension ref="A1:U1587"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -24849,7 +24849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1569" spans="1:4">
+    <row r="1569" spans="1:7">
       <c r="A1569" s="7">
         <v>46113</v>
       </c>
@@ -24859,9 +24859,11 @@
       <c r="C1569" s="6">
         <v>1</v>
       </c>
-      <c r="D1569" s="2"/>
-    </row>
-    <row r="1570" spans="1:4">
+      <c r="D1569" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:7">
       <c r="A1570" s="7">
         <v>46113</v>
       </c>
@@ -24871,9 +24873,13 @@
       <c r="C1570" s="6">
         <v>1</v>
       </c>
-      <c r="D1570" s="2"/>
-    </row>
-    <row r="1571" spans="1:4">
+      <c r="D1570" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1570" s="1"/>
+      <c r="G1570" s="22"/>
+    </row>
+    <row r="1571" spans="1:7">
       <c r="A1571" s="7">
         <v>46113</v>
       </c>
@@ -24883,9 +24889,13 @@
       <c r="C1571" s="6">
         <v>5</v>
       </c>
-      <c r="D1571" s="2"/>
-    </row>
-    <row r="1572" spans="1:4">
+      <c r="D1571" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1571" s="1"/>
+      <c r="G1571" s="22"/>
+    </row>
+    <row r="1572" spans="1:7">
       <c r="A1572" s="7">
         <v>46113</v>
       </c>
@@ -24895,9 +24905,13 @@
       <c r="C1572" s="6">
         <v>6</v>
       </c>
-      <c r="D1572" s="2"/>
-    </row>
-    <row r="1573" spans="1:4">
+      <c r="D1572" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1572" s="1"/>
+      <c r="G1572" s="22"/>
+    </row>
+    <row r="1573" spans="1:7">
       <c r="A1573" s="7">
         <v>46113</v>
       </c>
@@ -24907,9 +24921,13 @@
       <c r="C1573" s="6">
         <v>3</v>
       </c>
-      <c r="D1573" s="2"/>
-    </row>
-    <row r="1574" spans="1:4">
+      <c r="D1573" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1573" s="1"/>
+      <c r="G1573" s="22"/>
+    </row>
+    <row r="1574" spans="1:7">
       <c r="A1574" s="7">
         <v>46113</v>
       </c>
@@ -24919,9 +24937,13 @@
       <c r="C1574" s="6">
         <v>3</v>
       </c>
-      <c r="D1574" s="2"/>
-    </row>
-    <row r="1575" spans="1:4">
+      <c r="D1574" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1574" s="1"/>
+      <c r="G1574" s="22"/>
+    </row>
+    <row r="1575" spans="1:7">
       <c r="A1575" s="7">
         <v>46113</v>
       </c>
@@ -24931,9 +24953,13 @@
       <c r="C1575" s="6">
         <v>7</v>
       </c>
-      <c r="D1575" s="2"/>
-    </row>
-    <row r="1576" spans="1:4">
+      <c r="D1575" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1575" s="1"/>
+      <c r="G1575" s="22"/>
+    </row>
+    <row r="1576" spans="1:7">
       <c r="A1576" s="7">
         <v>46113</v>
       </c>
@@ -24943,9 +24969,13 @@
       <c r="C1576" s="6">
         <v>4</v>
       </c>
-      <c r="D1576" s="2"/>
-    </row>
-    <row r="1577" spans="1:4">
+      <c r="D1576" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1576" s="1"/>
+      <c r="G1576" s="22"/>
+    </row>
+    <row r="1577" spans="1:7">
       <c r="A1577" s="7">
         <v>46113</v>
       </c>
@@ -24955,9 +24985,11 @@
       <c r="C1577" s="6">
         <v>4</v>
       </c>
-      <c r="D1577" s="2"/>
-    </row>
-    <row r="1578" spans="1:4">
+      <c r="D1577" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:7">
       <c r="A1578" s="7">
         <v>46113</v>
       </c>
@@ -24967,9 +24999,11 @@
       <c r="C1578" s="6">
         <v>6</v>
       </c>
-      <c r="D1578" s="2"/>
-    </row>
-    <row r="1579" spans="1:4">
+      <c r="D1578" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:7">
       <c r="A1579" s="7">
         <v>46113</v>
       </c>
@@ -24979,7 +25013,105 @@
       <c r="C1579" s="6">
         <v>6</v>
       </c>
-      <c r="D1579" s="2"/>
+      <c r="D1579" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:7">
+      <c r="A1580" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1580" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1580" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1580" s="2"/>
+    </row>
+    <row r="1581" spans="1:7">
+      <c r="A1581" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1581" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1581" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1581" s="2"/>
+    </row>
+    <row r="1582" spans="1:7">
+      <c r="A1582" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1582" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1582" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1582" s="2"/>
+    </row>
+    <row r="1583" spans="1:7">
+      <c r="A1583" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1583" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1583" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1583" s="2"/>
+    </row>
+    <row r="1584" spans="1:7">
+      <c r="A1584" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1584" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1584" s="6">
+        <v>8</v>
+      </c>
+      <c r="D1584" s="2"/>
+    </row>
+    <row r="1585" spans="1:4">
+      <c r="A1585" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1585" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1585" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1585" s="2"/>
+    </row>
+    <row r="1586" spans="1:4">
+      <c r="A1586" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1586" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1586" s="6">
+        <v>6</v>
+      </c>
+      <c r="D1586" s="2"/>
+    </row>
+    <row r="1587" spans="1:4">
+      <c r="A1587" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B1587" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1587" s="6">
+        <v>12</v>
+      </c>
+      <c r="D1587" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D106"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -100,6 +100,9 @@
   <si>
     <t>D'ANDREA MARCO</t>
   </si>
+  <si>
+    <t>LITTERI DANIELE</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,6 +239,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -265,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -301,6 +310,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -596,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F738"/>
+  <dimension ref="A1:G769"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -11233,73 +11244,539 @@
       <c r="A733" s="6">
         <v>46121</v>
       </c>
-      <c r="B733" s="2" t="s">
-        <v>3</v>
+      <c r="B733" s="18" t="s">
+        <v>2</v>
       </c>
       <c r="C733" s="5">
-        <v>5</v>
-      </c>
-      <c r="D733" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D733" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="734" spans="1:4">
       <c r="A734" s="6">
         <v>46121</v>
       </c>
       <c r="B734" s="18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C734" s="5">
-        <v>2</v>
-      </c>
-      <c r="D734" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D734" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="735" spans="1:4">
       <c r="A735" s="6">
         <v>46121</v>
       </c>
-      <c r="B735" s="18" t="s">
-        <v>6</v>
+      <c r="B735" s="28" t="s">
+        <v>13</v>
       </c>
       <c r="C735" s="5">
-        <v>2</v>
-      </c>
-      <c r="D735" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D735" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="736" spans="1:4">
       <c r="A736" s="6">
         <v>46121</v>
       </c>
-      <c r="B736" s="13" t="s">
-        <v>5</v>
+      <c r="B736" s="28" t="s">
+        <v>8</v>
       </c>
       <c r="C736" s="5">
-        <v>1</v>
-      </c>
-      <c r="D736" s="2"/>
-    </row>
-    <row r="737" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D736" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7">
       <c r="A737" s="6">
         <v>46121</v>
       </c>
-      <c r="B737" s="13" t="s">
-        <v>9</v>
+      <c r="B737" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C737" s="5">
-        <v>1</v>
-      </c>
-      <c r="D737" s="2"/>
-    </row>
-    <row r="738" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D737" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7">
       <c r="A738" s="6">
         <v>46121</v>
       </c>
-      <c r="B738" s="2" t="s">
+      <c r="B738" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C738" s="5">
+        <v>2</v>
+      </c>
+      <c r="D738" s="2">
+        <v>1</v>
+      </c>
+      <c r="F738" s="1"/>
+      <c r="G738" s="27"/>
+    </row>
+    <row r="739" spans="1:7">
+      <c r="A739" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B739" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C739" s="5">
+        <v>2</v>
+      </c>
+      <c r="D739" s="2">
+        <v>1</v>
+      </c>
+      <c r="F739" s="1"/>
+      <c r="G739" s="27"/>
+    </row>
+    <row r="740" spans="1:7">
+      <c r="A740" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B740" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C740" s="5">
+        <v>1</v>
+      </c>
+      <c r="D740" s="2">
+        <v>0</v>
+      </c>
+      <c r="F740" s="1"/>
+      <c r="G740" s="27"/>
+    </row>
+    <row r="741" spans="1:7">
+      <c r="A741" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B741" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C741" s="5">
+        <v>1</v>
+      </c>
+      <c r="D741" s="2">
+        <v>0</v>
+      </c>
+      <c r="F741" s="1"/>
+      <c r="G741" s="27"/>
+    </row>
+    <row r="742" spans="1:7">
+      <c r="A742" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B742" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C738" s="5">
-        <v>3</v>
-      </c>
-      <c r="D738" s="2"/>
+      <c r="C742" s="5">
+        <v>3</v>
+      </c>
+      <c r="D742" s="2">
+        <v>2</v>
+      </c>
+      <c r="F742" s="1"/>
+      <c r="G742" s="27"/>
+    </row>
+    <row r="743" spans="1:7">
+      <c r="A743" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C743" s="5">
+        <v>0</v>
+      </c>
+      <c r="D743" s="2">
+        <v>1</v>
+      </c>
+      <c r="F743" s="1"/>
+      <c r="G743" s="27"/>
+    </row>
+    <row r="744" spans="1:7">
+      <c r="A744" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C744" s="5">
+        <v>0</v>
+      </c>
+      <c r="D744" s="2">
+        <v>1</v>
+      </c>
+      <c r="F744" s="1"/>
+      <c r="G744" s="27"/>
+    </row>
+    <row r="745" spans="1:7">
+      <c r="A745" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C745" s="5">
+        <v>0</v>
+      </c>
+      <c r="D745" s="2">
+        <v>1</v>
+      </c>
+      <c r="F745" s="1"/>
+      <c r="G745" s="27"/>
+    </row>
+    <row r="746" spans="1:7">
+      <c r="A746" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C746" s="5">
+        <v>0</v>
+      </c>
+      <c r="D746" s="2">
+        <v>1</v>
+      </c>
+      <c r="F746" s="1"/>
+      <c r="G746" s="27"/>
+    </row>
+    <row r="747" spans="1:7">
+      <c r="A747" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B747" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C747" s="5">
+        <v>0</v>
+      </c>
+      <c r="D747" s="2">
+        <v>2</v>
+      </c>
+      <c r="F747" s="1"/>
+      <c r="G747" s="27"/>
+    </row>
+    <row r="748" spans="1:7">
+      <c r="A748" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B748" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C748" s="5">
+        <v>0</v>
+      </c>
+      <c r="D748" s="2">
+        <v>2</v>
+      </c>
+      <c r="F748" s="1"/>
+      <c r="G748" s="27"/>
+    </row>
+    <row r="749" spans="1:7">
+      <c r="A749" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B749" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C749" s="5">
+        <v>6</v>
+      </c>
+      <c r="D749" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7">
+      <c r="A750" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B750" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C750" s="5">
+        <v>6</v>
+      </c>
+      <c r="D750" s="2">
+        <v>3</v>
+      </c>
+      <c r="F750" s="1"/>
+      <c r="G750" s="27"/>
+    </row>
+    <row r="751" spans="1:7">
+      <c r="A751" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B751" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C751" s="5">
+        <v>5</v>
+      </c>
+      <c r="D751" s="2">
+        <v>2</v>
+      </c>
+      <c r="F751" s="1"/>
+      <c r="G751" s="27"/>
+    </row>
+    <row r="752" spans="1:7">
+      <c r="A752" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B752" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C752" s="5">
+        <v>5</v>
+      </c>
+      <c r="D752" s="2">
+        <v>2</v>
+      </c>
+      <c r="F752" s="1"/>
+      <c r="G752" s="27"/>
+    </row>
+    <row r="753" spans="1:7">
+      <c r="A753" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B753" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C753" s="5">
+        <v>6</v>
+      </c>
+      <c r="D753" s="2">
+        <v>0</v>
+      </c>
+      <c r="F753" s="1"/>
+      <c r="G753" s="27"/>
+    </row>
+    <row r="754" spans="1:7">
+      <c r="A754" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B754" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C754" s="5">
+        <v>6</v>
+      </c>
+      <c r="D754" s="2">
+        <v>0</v>
+      </c>
+      <c r="F754" s="1"/>
+      <c r="G754" s="27"/>
+    </row>
+    <row r="755" spans="1:7">
+      <c r="A755" s="6">
+        <v>46123</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C755" s="5">
+        <v>8</v>
+      </c>
+      <c r="D755" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="756" spans="1:7">
+      <c r="A756" s="6">
+        <v>46123</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C756" s="5">
+        <v>9</v>
+      </c>
+      <c r="D756" s="2">
+        <v>9</v>
+      </c>
+      <c r="F756" s="1"/>
+      <c r="G756" s="27"/>
+    </row>
+    <row r="757" spans="1:7">
+      <c r="A757" s="6">
+        <v>46123</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C757" s="5">
+        <v>9</v>
+      </c>
+      <c r="D757" s="2">
+        <v>4</v>
+      </c>
+      <c r="F757" s="1"/>
+      <c r="G757" s="27"/>
+    </row>
+    <row r="758" spans="1:7">
+      <c r="A758" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B758" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C758" s="5">
+        <v>2</v>
+      </c>
+      <c r="D758" s="2"/>
+      <c r="F758" s="1"/>
+      <c r="G758" s="27"/>
+    </row>
+    <row r="759" spans="1:7">
+      <c r="A759" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B759" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C759" s="5">
+        <v>2</v>
+      </c>
+      <c r="D759" s="2"/>
+      <c r="F759" s="1"/>
+      <c r="G759" s="27"/>
+    </row>
+    <row r="760" spans="1:7">
+      <c r="A760" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B760" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C760" s="5">
+        <v>5</v>
+      </c>
+      <c r="D760" s="2"/>
+      <c r="F760" s="1"/>
+      <c r="G760" s="27"/>
+    </row>
+    <row r="761" spans="1:7">
+      <c r="A761" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B761" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C761" s="5">
+        <v>2</v>
+      </c>
+      <c r="D761" s="2"/>
+      <c r="F761" s="1"/>
+      <c r="G761" s="27"/>
+    </row>
+    <row r="762" spans="1:7">
+      <c r="A762" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B762" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C762" s="5">
+        <v>2</v>
+      </c>
+      <c r="D762" s="2"/>
+    </row>
+    <row r="763" spans="1:7">
+      <c r="A763" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B763" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C763" s="5">
+        <v>2</v>
+      </c>
+      <c r="D763" s="2"/>
+    </row>
+    <row r="764" spans="1:7">
+      <c r="A764" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B764" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C764" s="5">
+        <v>2</v>
+      </c>
+      <c r="D764" s="2"/>
+    </row>
+    <row r="765" spans="1:7">
+      <c r="A765" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B765" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C765" s="5">
+        <v>1</v>
+      </c>
+      <c r="D765" s="2"/>
+    </row>
+    <row r="766" spans="1:7">
+      <c r="A766" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B766" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C766" s="2">
+        <v>1</v>
+      </c>
+      <c r="D766" s="2"/>
+    </row>
+    <row r="767" spans="1:7">
+      <c r="A767" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C767" s="2">
+        <v>16</v>
+      </c>
+      <c r="D767" s="2"/>
+    </row>
+    <row r="768" spans="1:7">
+      <c r="A768" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C768" s="2">
+        <v>2</v>
+      </c>
+      <c r="D768" s="2"/>
+    </row>
+    <row r="769" spans="1:4">
+      <c r="A769" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C769" s="2">
+        <v>2</v>
+      </c>
+      <c r="D769" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G769"/>
+  <dimension ref="A1:G780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -11636,9 +11636,9 @@
       <c r="C758" s="5">
         <v>2</v>
       </c>
-      <c r="D758" s="2"/>
-      <c r="F758" s="1"/>
-      <c r="G758" s="27"/>
+      <c r="D758" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="759" spans="1:7">
       <c r="A759" s="6">
@@ -11650,7 +11650,9 @@
       <c r="C759" s="5">
         <v>2</v>
       </c>
-      <c r="D759" s="2"/>
+      <c r="D759" s="2">
+        <v>2</v>
+      </c>
       <c r="F759" s="1"/>
       <c r="G759" s="27"/>
     </row>
@@ -11664,7 +11666,9 @@
       <c r="C760" s="5">
         <v>5</v>
       </c>
-      <c r="D760" s="2"/>
+      <c r="D760" s="2">
+        <v>4</v>
+      </c>
       <c r="F760" s="1"/>
       <c r="G760" s="27"/>
     </row>
@@ -11678,7 +11682,9 @@
       <c r="C761" s="5">
         <v>2</v>
       </c>
-      <c r="D761" s="2"/>
+      <c r="D761" s="2">
+        <v>0</v>
+      </c>
       <c r="F761" s="1"/>
       <c r="G761" s="27"/>
     </row>
@@ -11692,7 +11698,11 @@
       <c r="C762" s="5">
         <v>2</v>
       </c>
-      <c r="D762" s="2"/>
+      <c r="D762" s="2">
+        <v>0</v>
+      </c>
+      <c r="F762" s="1"/>
+      <c r="G762" s="27"/>
     </row>
     <row r="763" spans="1:7">
       <c r="A763" s="6">
@@ -11704,7 +11714,11 @@
       <c r="C763" s="5">
         <v>2</v>
       </c>
-      <c r="D763" s="2"/>
+      <c r="D763" s="2">
+        <v>2</v>
+      </c>
+      <c r="F763" s="1"/>
+      <c r="G763" s="27"/>
     </row>
     <row r="764" spans="1:7">
       <c r="A764" s="6">
@@ -11716,7 +11730,11 @@
       <c r="C764" s="5">
         <v>2</v>
       </c>
-      <c r="D764" s="2"/>
+      <c r="D764" s="2">
+        <v>2</v>
+      </c>
+      <c r="F764" s="1"/>
+      <c r="G764" s="27"/>
     </row>
     <row r="765" spans="1:7">
       <c r="A765" s="6">
@@ -11728,7 +11746,11 @@
       <c r="C765" s="5">
         <v>1</v>
       </c>
-      <c r="D765" s="2"/>
+      <c r="D765" s="2">
+        <v>0</v>
+      </c>
+      <c r="F765" s="1"/>
+      <c r="G765" s="27"/>
     </row>
     <row r="766" spans="1:7">
       <c r="A766" s="6">
@@ -11740,7 +11762,11 @@
       <c r="C766" s="2">
         <v>1</v>
       </c>
-      <c r="D766" s="2"/>
+      <c r="D766" s="2">
+        <v>0</v>
+      </c>
+      <c r="F766" s="1"/>
+      <c r="G766" s="27"/>
     </row>
     <row r="767" spans="1:7">
       <c r="A767" s="6">
@@ -11752,31 +11778,169 @@
       <c r="C767" s="2">
         <v>16</v>
       </c>
-      <c r="D767" s="2"/>
+      <c r="D767" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="768" spans="1:7">
       <c r="A768" s="6">
         <v>46125</v>
       </c>
-      <c r="B768" s="2" t="s">
+      <c r="B768" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C768" s="2">
         <v>2</v>
       </c>
-      <c r="D768" s="2"/>
+      <c r="D768" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="769" spans="1:4">
       <c r="A769" s="6">
         <v>46125</v>
       </c>
-      <c r="B769" s="2" t="s">
+      <c r="B769" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C769" s="2">
         <v>2</v>
       </c>
-      <c r="D769" s="2"/>
+      <c r="D769" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4">
+      <c r="A770" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B770" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C770" s="5">
+        <v>3</v>
+      </c>
+      <c r="D770" s="2"/>
+    </row>
+    <row r="771" spans="1:4">
+      <c r="A771" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B771" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C771" s="5">
+        <v>3</v>
+      </c>
+      <c r="D771" s="2"/>
+    </row>
+    <row r="772" spans="1:4">
+      <c r="A772" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B772" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C772" s="5">
+        <v>6</v>
+      </c>
+      <c r="D772" s="2"/>
+    </row>
+    <row r="773" spans="1:4">
+      <c r="A773" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B773" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C773" s="5">
+        <v>6</v>
+      </c>
+      <c r="D773" s="2"/>
+    </row>
+    <row r="774" spans="1:4">
+      <c r="A774" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B774" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C774" s="5">
+        <v>1</v>
+      </c>
+      <c r="D774" s="2"/>
+    </row>
+    <row r="775" spans="1:4">
+      <c r="A775" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B775" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C775" s="5">
+        <v>1</v>
+      </c>
+      <c r="D775" s="2"/>
+    </row>
+    <row r="776" spans="1:4">
+      <c r="A776" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B776" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C776" s="5">
+        <v>3</v>
+      </c>
+      <c r="D776" s="2"/>
+    </row>
+    <row r="777" spans="1:4">
+      <c r="A777" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B777" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C777" s="5">
+        <v>4</v>
+      </c>
+      <c r="D777" s="2"/>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B778" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C778" s="5">
+        <v>4</v>
+      </c>
+      <c r="D778" s="2"/>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B779" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C779" s="5">
+        <v>3</v>
+      </c>
+      <c r="D779" s="2"/>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B780" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C780" s="5">
+        <v>3</v>
+      </c>
+      <c r="D780" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G780"/>
+  <dimension ref="A1:G790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -11796,7 +11796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="769" spans="1:4">
+    <row r="769" spans="1:7">
       <c r="A769" s="6">
         <v>46125</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:4">
+    <row r="770" spans="1:7">
       <c r="A770" s="6">
         <v>46126</v>
       </c>
@@ -11820,9 +11820,11 @@
       <c r="C770" s="5">
         <v>3</v>
       </c>
-      <c r="D770" s="2"/>
-    </row>
-    <row r="771" spans="1:4">
+      <c r="D770" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="771" spans="1:7">
       <c r="A771" s="6">
         <v>46126</v>
       </c>
@@ -11832,9 +11834,13 @@
       <c r="C771" s="5">
         <v>3</v>
       </c>
-      <c r="D771" s="2"/>
-    </row>
-    <row r="772" spans="1:4">
+      <c r="D771" s="2">
+        <v>2</v>
+      </c>
+      <c r="F771" s="1"/>
+      <c r="G771" s="27"/>
+    </row>
+    <row r="772" spans="1:7">
       <c r="A772" s="6">
         <v>46126</v>
       </c>
@@ -11844,9 +11850,13 @@
       <c r="C772" s="5">
         <v>6</v>
       </c>
-      <c r="D772" s="2"/>
-    </row>
-    <row r="773" spans="1:4">
+      <c r="D772" s="2">
+        <v>4</v>
+      </c>
+      <c r="F772" s="1"/>
+      <c r="G772" s="27"/>
+    </row>
+    <row r="773" spans="1:7">
       <c r="A773" s="6">
         <v>46126</v>
       </c>
@@ -11856,9 +11866,13 @@
       <c r="C773" s="5">
         <v>6</v>
       </c>
-      <c r="D773" s="2"/>
-    </row>
-    <row r="774" spans="1:4">
+      <c r="D773" s="2">
+        <v>4</v>
+      </c>
+      <c r="F773" s="1"/>
+      <c r="G773" s="27"/>
+    </row>
+    <row r="774" spans="1:7">
       <c r="A774" s="6">
         <v>46126</v>
       </c>
@@ -11868,9 +11882,13 @@
       <c r="C774" s="5">
         <v>1</v>
       </c>
-      <c r="D774" s="2"/>
-    </row>
-    <row r="775" spans="1:4">
+      <c r="D774" s="2">
+        <v>5</v>
+      </c>
+      <c r="F774" s="1"/>
+      <c r="G774" s="27"/>
+    </row>
+    <row r="775" spans="1:7">
       <c r="A775" s="6">
         <v>46126</v>
       </c>
@@ -11880,9 +11898,13 @@
       <c r="C775" s="5">
         <v>1</v>
       </c>
-      <c r="D775" s="2"/>
-    </row>
-    <row r="776" spans="1:4">
+      <c r="D775" s="2">
+        <v>5</v>
+      </c>
+      <c r="F775" s="1"/>
+      <c r="G775" s="27"/>
+    </row>
+    <row r="776" spans="1:7">
       <c r="A776" s="6">
         <v>46126</v>
       </c>
@@ -11892,9 +11914,13 @@
       <c r="C776" s="5">
         <v>3</v>
       </c>
-      <c r="D776" s="2"/>
-    </row>
-    <row r="777" spans="1:4">
+      <c r="D776" s="2">
+        <v>1</v>
+      </c>
+      <c r="F776" s="1"/>
+      <c r="G776" s="27"/>
+    </row>
+    <row r="777" spans="1:7">
       <c r="A777" s="6">
         <v>46126</v>
       </c>
@@ -11904,9 +11930,13 @@
       <c r="C777" s="5">
         <v>4</v>
       </c>
-      <c r="D777" s="2"/>
-    </row>
-    <row r="778" spans="1:4">
+      <c r="D777" s="2">
+        <v>0</v>
+      </c>
+      <c r="F777" s="1"/>
+      <c r="G777" s="27"/>
+    </row>
+    <row r="778" spans="1:7">
       <c r="A778" s="6">
         <v>46126</v>
       </c>
@@ -11916,9 +11946,11 @@
       <c r="C778" s="5">
         <v>4</v>
       </c>
-      <c r="D778" s="2"/>
-    </row>
-    <row r="779" spans="1:4">
+      <c r="D778" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779" spans="1:7">
       <c r="A779" s="6">
         <v>46126</v>
       </c>
@@ -11928,9 +11960,11 @@
       <c r="C779" s="5">
         <v>3</v>
       </c>
-      <c r="D779" s="2"/>
-    </row>
-    <row r="780" spans="1:4">
+      <c r="D779" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780" spans="1:7">
       <c r="A780" s="6">
         <v>46126</v>
       </c>
@@ -11940,7 +11974,129 @@
       <c r="C780" s="5">
         <v>3</v>
       </c>
-      <c r="D780" s="2"/>
+      <c r="D780" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781" spans="1:7">
+      <c r="A781" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B781" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C781" s="5">
+        <v>2</v>
+      </c>
+      <c r="D781" s="2"/>
+    </row>
+    <row r="782" spans="1:7">
+      <c r="A782" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B782" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C782" s="2">
+        <v>2</v>
+      </c>
+      <c r="D782" s="2"/>
+    </row>
+    <row r="783" spans="1:7">
+      <c r="A783" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B783" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C783" s="2">
+        <v>7</v>
+      </c>
+      <c r="D783" s="2"/>
+    </row>
+    <row r="784" spans="1:7">
+      <c r="A784" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B784" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C784" s="2">
+        <v>7</v>
+      </c>
+      <c r="D784" s="2"/>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B785" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C785" s="2">
+        <v>1</v>
+      </c>
+      <c r="D785" s="2"/>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B786" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C786" s="2">
+        <v>1</v>
+      </c>
+      <c r="D786" s="2"/>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B787" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C787" s="2">
+        <v>9</v>
+      </c>
+      <c r="D787" s="2"/>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B788" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C788" s="2">
+        <v>9</v>
+      </c>
+      <c r="D788" s="2"/>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B789" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C789" s="2">
+        <v>7</v>
+      </c>
+      <c r="D789" s="2"/>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B790" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C790" s="2">
+        <v>7</v>
+      </c>
+      <c r="D790" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G790"/>
+  <dimension ref="A1:G816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -11988,7 +11988,9 @@
       <c r="C781" s="5">
         <v>2</v>
       </c>
-      <c r="D781" s="2"/>
+      <c r="D781" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="782" spans="1:7">
       <c r="A782" s="6">
@@ -12000,7 +12002,11 @@
       <c r="C782" s="2">
         <v>2</v>
       </c>
-      <c r="D782" s="2"/>
+      <c r="D782" s="2">
+        <v>0</v>
+      </c>
+      <c r="F782" s="1"/>
+      <c r="G782" s="27"/>
     </row>
     <row r="783" spans="1:7">
       <c r="A783" s="6">
@@ -12012,7 +12018,11 @@
       <c r="C783" s="2">
         <v>7</v>
       </c>
-      <c r="D783" s="2"/>
+      <c r="D783" s="2">
+        <v>1</v>
+      </c>
+      <c r="F783" s="1"/>
+      <c r="G783" s="27"/>
     </row>
     <row r="784" spans="1:7">
       <c r="A784" s="6">
@@ -12024,9 +12034,13 @@
       <c r="C784" s="2">
         <v>7</v>
       </c>
-      <c r="D784" s="2"/>
-    </row>
-    <row r="785" spans="1:4">
+      <c r="D784" s="2">
+        <v>1</v>
+      </c>
+      <c r="F784" s="1"/>
+      <c r="G784" s="27"/>
+    </row>
+    <row r="785" spans="1:7">
       <c r="A785" s="6">
         <v>46127</v>
       </c>
@@ -12036,9 +12050,13 @@
       <c r="C785" s="2">
         <v>1</v>
       </c>
-      <c r="D785" s="2"/>
-    </row>
-    <row r="786" spans="1:4">
+      <c r="D785" s="2">
+        <v>2</v>
+      </c>
+      <c r="F785" s="1"/>
+      <c r="G785" s="27"/>
+    </row>
+    <row r="786" spans="1:7">
       <c r="A786" s="6">
         <v>46127</v>
       </c>
@@ -12048,9 +12066,13 @@
       <c r="C786" s="2">
         <v>1</v>
       </c>
-      <c r="D786" s="2"/>
-    </row>
-    <row r="787" spans="1:4">
+      <c r="D786" s="2">
+        <v>2</v>
+      </c>
+      <c r="F786" s="1"/>
+      <c r="G786" s="27"/>
+    </row>
+    <row r="787" spans="1:7">
       <c r="A787" s="6">
         <v>46127</v>
       </c>
@@ -12060,9 +12082,13 @@
       <c r="C787" s="2">
         <v>9</v>
       </c>
-      <c r="D787" s="2"/>
-    </row>
-    <row r="788" spans="1:4">
+      <c r="D787" s="2">
+        <v>7</v>
+      </c>
+      <c r="F787" s="1"/>
+      <c r="G787" s="27"/>
+    </row>
+    <row r="788" spans="1:7">
       <c r="A788" s="6">
         <v>46127</v>
       </c>
@@ -12072,9 +12098,13 @@
       <c r="C788" s="2">
         <v>9</v>
       </c>
-      <c r="D788" s="2"/>
-    </row>
-    <row r="789" spans="1:4">
+      <c r="D788" s="2">
+        <v>7</v>
+      </c>
+      <c r="F788" s="1"/>
+      <c r="G788" s="27"/>
+    </row>
+    <row r="789" spans="1:7">
       <c r="A789" s="6">
         <v>46127</v>
       </c>
@@ -12084,9 +12114,11 @@
       <c r="C789" s="2">
         <v>7</v>
       </c>
-      <c r="D789" s="2"/>
-    </row>
-    <row r="790" spans="1:4">
+      <c r="D789" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:7">
       <c r="A790" s="6">
         <v>46127</v>
       </c>
@@ -12096,7 +12128,365 @@
       <c r="C790" s="2">
         <v>7</v>
       </c>
-      <c r="D790" s="2"/>
+      <c r="D790" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791" spans="1:7">
+      <c r="A791" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B791" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C791" s="2">
+        <v>0</v>
+      </c>
+      <c r="D791" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792" spans="1:7">
+      <c r="A792" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B792" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C792" s="2">
+        <v>0</v>
+      </c>
+      <c r="D792" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="793" spans="1:7">
+      <c r="A793" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B793" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C793" s="2">
+        <v>0</v>
+      </c>
+      <c r="D793" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="794" spans="1:7">
+      <c r="A794" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B794" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C794" s="2">
+        <v>0</v>
+      </c>
+      <c r="D794" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="795" spans="1:7">
+      <c r="A795" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B795" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C795" s="5">
+        <v>4</v>
+      </c>
+      <c r="D795" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="1:7">
+      <c r="A796" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B796" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C796" s="5">
+        <v>4</v>
+      </c>
+      <c r="D796" s="2">
+        <v>0</v>
+      </c>
+      <c r="F796" s="1"/>
+      <c r="G796" s="27"/>
+    </row>
+    <row r="797" spans="1:7">
+      <c r="A797" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B797" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C797" s="5">
+        <v>6</v>
+      </c>
+      <c r="D797" s="2">
+        <v>1</v>
+      </c>
+      <c r="F797" s="1"/>
+      <c r="G797" s="27"/>
+    </row>
+    <row r="798" spans="1:7">
+      <c r="A798" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B798" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C798" s="5">
+        <v>3</v>
+      </c>
+      <c r="D798" s="2">
+        <v>1</v>
+      </c>
+      <c r="F798" s="1"/>
+      <c r="G798" s="27"/>
+    </row>
+    <row r="799" spans="1:7">
+      <c r="A799" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B799" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C799" s="5">
+        <v>3</v>
+      </c>
+      <c r="D799" s="2">
+        <v>1</v>
+      </c>
+      <c r="F799" s="1"/>
+      <c r="G799" s="27"/>
+    </row>
+    <row r="800" spans="1:7">
+      <c r="A800" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B800" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C800" s="5">
+        <v>3</v>
+      </c>
+      <c r="D800" s="2">
+        <v>1</v>
+      </c>
+      <c r="F800" s="1"/>
+      <c r="G800" s="27"/>
+    </row>
+    <row r="801" spans="1:7">
+      <c r="A801" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B801" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C801" s="2">
+        <v>3</v>
+      </c>
+      <c r="D801" s="2">
+        <v>1</v>
+      </c>
+      <c r="F801" s="1"/>
+      <c r="G801" s="27"/>
+    </row>
+    <row r="802" spans="1:7">
+      <c r="A802" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B802" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C802" s="5">
+        <v>3</v>
+      </c>
+      <c r="D802" s="2">
+        <v>0</v>
+      </c>
+      <c r="F802" s="1"/>
+      <c r="G802" s="27"/>
+    </row>
+    <row r="803" spans="1:7">
+      <c r="A803" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B803" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C803" s="5">
+        <v>3</v>
+      </c>
+      <c r="D803" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804" spans="1:7">
+      <c r="A804" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B804" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C804" s="5">
+        <v>4</v>
+      </c>
+      <c r="D804" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:7">
+      <c r="A805" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B805" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C805" s="5">
+        <v>4</v>
+      </c>
+      <c r="D805" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="1:7">
+      <c r="A806" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B806" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C806" s="5">
+        <v>1</v>
+      </c>
+      <c r="D806" s="2"/>
+    </row>
+    <row r="807" spans="1:7">
+      <c r="A807" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B807" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C807" s="5">
+        <v>1</v>
+      </c>
+      <c r="D807" s="2"/>
+    </row>
+    <row r="808" spans="1:7">
+      <c r="A808" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B808" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C808" s="5">
+        <v>8</v>
+      </c>
+      <c r="D808" s="2"/>
+    </row>
+    <row r="809" spans="1:7">
+      <c r="A809" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B809" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C809" s="5">
+        <v>8</v>
+      </c>
+      <c r="D809" s="2"/>
+    </row>
+    <row r="810" spans="1:7">
+      <c r="A810" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C810" s="5">
+        <v>3</v>
+      </c>
+      <c r="D810" s="2"/>
+    </row>
+    <row r="811" spans="1:7">
+      <c r="A811" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B811" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C811" s="5">
+        <v>2</v>
+      </c>
+      <c r="D811" s="2"/>
+    </row>
+    <row r="812" spans="1:7">
+      <c r="A812" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B812" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C812" s="5">
+        <v>2</v>
+      </c>
+      <c r="D812" s="2"/>
+    </row>
+    <row r="813" spans="1:7">
+      <c r="A813" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B813" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C813" s="5">
+        <v>7</v>
+      </c>
+      <c r="D813" s="2"/>
+    </row>
+    <row r="814" spans="1:7">
+      <c r="A814" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B814" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C814" s="5">
+        <v>7</v>
+      </c>
+      <c r="D814" s="2"/>
+    </row>
+    <row r="815" spans="1:7">
+      <c r="A815" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B815" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C815" s="5">
+        <v>7</v>
+      </c>
+      <c r="D815" s="2"/>
+    </row>
+    <row r="816" spans="1:7">
+      <c r="A816" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B816" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C816" s="5">
+        <v>7</v>
+      </c>
+      <c r="D816" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G816"/>
+  <dimension ref="A1:G827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -12366,7 +12366,9 @@
       <c r="C806" s="5">
         <v>1</v>
       </c>
-      <c r="D806" s="2"/>
+      <c r="D806" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="807" spans="1:7">
       <c r="A807" s="6">
@@ -12378,7 +12380,11 @@
       <c r="C807" s="5">
         <v>1</v>
       </c>
-      <c r="D807" s="2"/>
+      <c r="D807" s="2">
+        <v>0</v>
+      </c>
+      <c r="F807" s="1"/>
+      <c r="G807" s="27"/>
     </row>
     <row r="808" spans="1:7">
       <c r="A808" s="6">
@@ -12390,7 +12396,11 @@
       <c r="C808" s="5">
         <v>8</v>
       </c>
-      <c r="D808" s="2"/>
+      <c r="D808" s="2">
+        <v>0</v>
+      </c>
+      <c r="F808" s="1"/>
+      <c r="G808" s="27"/>
     </row>
     <row r="809" spans="1:7">
       <c r="A809" s="6">
@@ -12402,7 +12412,11 @@
       <c r="C809" s="5">
         <v>8</v>
       </c>
-      <c r="D809" s="2"/>
+      <c r="D809" s="2">
+        <v>0</v>
+      </c>
+      <c r="F809" s="1"/>
+      <c r="G809" s="27"/>
     </row>
     <row r="810" spans="1:7">
       <c r="A810" s="6">
@@ -12414,7 +12428,11 @@
       <c r="C810" s="5">
         <v>3</v>
       </c>
-      <c r="D810" s="2"/>
+      <c r="D810" s="2">
+        <v>1</v>
+      </c>
+      <c r="F810" s="1"/>
+      <c r="G810" s="27"/>
     </row>
     <row r="811" spans="1:7">
       <c r="A811" s="6">
@@ -12426,7 +12444,11 @@
       <c r="C811" s="5">
         <v>2</v>
       </c>
-      <c r="D811" s="2"/>
+      <c r="D811" s="2">
+        <v>5</v>
+      </c>
+      <c r="F811" s="1"/>
+      <c r="G811" s="27"/>
     </row>
     <row r="812" spans="1:7">
       <c r="A812" s="6">
@@ -12438,7 +12460,11 @@
       <c r="C812" s="5">
         <v>2</v>
       </c>
-      <c r="D812" s="2"/>
+      <c r="D812" s="2">
+        <v>5</v>
+      </c>
+      <c r="F812" s="1"/>
+      <c r="G812" s="27"/>
     </row>
     <row r="813" spans="1:7">
       <c r="A813" s="6">
@@ -12450,7 +12476,9 @@
       <c r="C813" s="5">
         <v>7</v>
       </c>
-      <c r="D813" s="2"/>
+      <c r="D813" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="814" spans="1:7">
       <c r="A814" s="6">
@@ -12462,7 +12490,9 @@
       <c r="C814" s="5">
         <v>7</v>
       </c>
-      <c r="D814" s="2"/>
+      <c r="D814" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="815" spans="1:7">
       <c r="A815" s="6">
@@ -12474,7 +12504,9 @@
       <c r="C815" s="5">
         <v>7</v>
       </c>
-      <c r="D815" s="2"/>
+      <c r="D815" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="816" spans="1:7">
       <c r="A816" s="6">
@@ -12486,7 +12518,161 @@
       <c r="C816" s="5">
         <v>7</v>
       </c>
-      <c r="D816" s="2"/>
+      <c r="D816" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="1:7">
+      <c r="A817" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C817" s="5">
+        <v>9</v>
+      </c>
+      <c r="D817" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="818" spans="1:7">
+      <c r="A818" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C818" s="5">
+        <v>11</v>
+      </c>
+      <c r="D818" s="2">
+        <v>8</v>
+      </c>
+      <c r="F818" s="1"/>
+      <c r="G818" s="27"/>
+    </row>
+    <row r="819" spans="1:7">
+      <c r="A819" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B819" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C819" s="5">
+        <v>14</v>
+      </c>
+      <c r="D819" s="2">
+        <v>12</v>
+      </c>
+      <c r="F819" s="1"/>
+      <c r="G819" s="27"/>
+    </row>
+    <row r="820" spans="1:7">
+      <c r="A820" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B820" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C820" s="5">
+        <v>14</v>
+      </c>
+      <c r="D820" s="2">
+        <v>12</v>
+      </c>
+      <c r="F820" s="1"/>
+      <c r="G820" s="27"/>
+    </row>
+    <row r="821" spans="1:7">
+      <c r="A821" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C821" s="5">
+        <v>4</v>
+      </c>
+      <c r="D821" s="2"/>
+      <c r="F821" s="1"/>
+      <c r="G821" s="27"/>
+    </row>
+    <row r="822" spans="1:7">
+      <c r="A822" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B822" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C822" s="5">
+        <v>2</v>
+      </c>
+      <c r="D822" s="2"/>
+      <c r="F822" s="1"/>
+      <c r="G822" s="27"/>
+    </row>
+    <row r="823" spans="1:7">
+      <c r="A823" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B823" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C823" s="5">
+        <v>2</v>
+      </c>
+      <c r="D823" s="2"/>
+      <c r="F823" s="1"/>
+      <c r="G823" s="27"/>
+    </row>
+    <row r="824" spans="1:7">
+      <c r="A824" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B824" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C824" s="2">
+        <v>5</v>
+      </c>
+      <c r="D824" s="2"/>
+    </row>
+    <row r="825" spans="1:7">
+      <c r="A825" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B825" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C825" s="2">
+        <v>5</v>
+      </c>
+      <c r="D825" s="2"/>
+    </row>
+    <row r="826" spans="1:7">
+      <c r="A826" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B826" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C826" s="2">
+        <v>4</v>
+      </c>
+      <c r="D826" s="2"/>
+    </row>
+    <row r="827" spans="1:7">
+      <c r="A827" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B827" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C827" s="2">
+        <v>4</v>
+      </c>
+      <c r="D827" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G827"/>
+  <dimension ref="A1:G839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -12594,9 +12594,9 @@
       <c r="C821" s="5">
         <v>4</v>
       </c>
-      <c r="D821" s="2"/>
-      <c r="F821" s="1"/>
-      <c r="G821" s="27"/>
+      <c r="D821" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="822" spans="1:7">
       <c r="A822" s="6">
@@ -12608,7 +12608,9 @@
       <c r="C822" s="5">
         <v>2</v>
       </c>
-      <c r="D822" s="2"/>
+      <c r="D822" s="2">
+        <v>4</v>
+      </c>
       <c r="F822" s="1"/>
       <c r="G822" s="27"/>
     </row>
@@ -12622,7 +12624,9 @@
       <c r="C823" s="5">
         <v>2</v>
       </c>
-      <c r="D823" s="2"/>
+      <c r="D823" s="2">
+        <v>4</v>
+      </c>
       <c r="F823" s="1"/>
       <c r="G823" s="27"/>
     </row>
@@ -12636,7 +12640,11 @@
       <c r="C824" s="2">
         <v>5</v>
       </c>
-      <c r="D824" s="2"/>
+      <c r="D824" s="2">
+        <v>1</v>
+      </c>
+      <c r="F824" s="1"/>
+      <c r="G824" s="27"/>
     </row>
     <row r="825" spans="1:7">
       <c r="A825" s="6">
@@ -12648,7 +12656,11 @@
       <c r="C825" s="2">
         <v>5</v>
       </c>
-      <c r="D825" s="2"/>
+      <c r="D825" s="2">
+        <v>1</v>
+      </c>
+      <c r="F825" s="1"/>
+      <c r="G825" s="27"/>
     </row>
     <row r="826" spans="1:7">
       <c r="A826" s="6">
@@ -12660,7 +12672,11 @@
       <c r="C826" s="2">
         <v>4</v>
       </c>
-      <c r="D826" s="2"/>
+      <c r="D826" s="2">
+        <v>1</v>
+      </c>
+      <c r="F826" s="1"/>
+      <c r="G826" s="27"/>
     </row>
     <row r="827" spans="1:7">
       <c r="A827" s="6">
@@ -12672,7 +12688,155 @@
       <c r="C827" s="2">
         <v>4</v>
       </c>
-      <c r="D827" s="2"/>
+      <c r="D827" s="2">
+        <v>1</v>
+      </c>
+      <c r="F827" s="1"/>
+      <c r="G827" s="27"/>
+    </row>
+    <row r="828" spans="1:7">
+      <c r="A828" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B828" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C828" s="5">
+        <v>2</v>
+      </c>
+      <c r="D828" s="2"/>
+    </row>
+    <row r="829" spans="1:7">
+      <c r="A829" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B829" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C829" s="2">
+        <v>2</v>
+      </c>
+      <c r="D829" s="2"/>
+    </row>
+    <row r="830" spans="1:7">
+      <c r="A830" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B830" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C830" s="5">
+        <v>5</v>
+      </c>
+      <c r="D830" s="2"/>
+    </row>
+    <row r="831" spans="1:7">
+      <c r="A831" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B831" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C831" s="5">
+        <v>5</v>
+      </c>
+      <c r="D831" s="2"/>
+    </row>
+    <row r="832" spans="1:7">
+      <c r="A832" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B832" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C832" s="5">
+        <v>2</v>
+      </c>
+      <c r="D832" s="2"/>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B833" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C833" s="5">
+        <v>2</v>
+      </c>
+      <c r="D833" s="2"/>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B834" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C834" s="5">
+        <v>4</v>
+      </c>
+      <c r="D834" s="2"/>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B835" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C835" s="5">
+        <v>4</v>
+      </c>
+      <c r="D835" s="2"/>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B836" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C836" s="5">
+        <v>5</v>
+      </c>
+      <c r="D836" s="2"/>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B837" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C837" s="5">
+        <v>5</v>
+      </c>
+      <c r="D837" s="2"/>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B838" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C838" s="2">
+        <v>5</v>
+      </c>
+      <c r="D838" s="2"/>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B839" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C839" s="2">
+        <v>5</v>
+      </c>
+      <c r="D839" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G839"/>
+  <dimension ref="A1:G849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -12704,7 +12704,9 @@
       <c r="C828" s="5">
         <v>2</v>
       </c>
-      <c r="D828" s="2"/>
+      <c r="D828" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="829" spans="1:7">
       <c r="A829" s="6">
@@ -12716,7 +12718,11 @@
       <c r="C829" s="2">
         <v>2</v>
       </c>
-      <c r="D829" s="2"/>
+      <c r="D829" s="2">
+        <v>0</v>
+      </c>
+      <c r="F829" s="1"/>
+      <c r="G829" s="27"/>
     </row>
     <row r="830" spans="1:7">
       <c r="A830" s="6">
@@ -12728,7 +12734,11 @@
       <c r="C830" s="5">
         <v>5</v>
       </c>
-      <c r="D830" s="2"/>
+      <c r="D830" s="2">
+        <v>0</v>
+      </c>
+      <c r="F830" s="1"/>
+      <c r="G830" s="27"/>
     </row>
     <row r="831" spans="1:7">
       <c r="A831" s="6">
@@ -12740,7 +12750,11 @@
       <c r="C831" s="5">
         <v>5</v>
       </c>
-      <c r="D831" s="2"/>
+      <c r="D831" s="2">
+        <v>0</v>
+      </c>
+      <c r="F831" s="1"/>
+      <c r="G831" s="27"/>
     </row>
     <row r="832" spans="1:7">
       <c r="A832" s="6">
@@ -12752,9 +12766,13 @@
       <c r="C832" s="5">
         <v>2</v>
       </c>
-      <c r="D832" s="2"/>
-    </row>
-    <row r="833" spans="1:4">
+      <c r="D832" s="2">
+        <v>3</v>
+      </c>
+      <c r="F832" s="1"/>
+      <c r="G832" s="27"/>
+    </row>
+    <row r="833" spans="1:7">
       <c r="A833" s="6">
         <v>46133</v>
       </c>
@@ -12764,9 +12782,13 @@
       <c r="C833" s="5">
         <v>2</v>
       </c>
-      <c r="D833" s="2"/>
-    </row>
-    <row r="834" spans="1:4">
+      <c r="D833" s="2">
+        <v>3</v>
+      </c>
+      <c r="F833" s="1"/>
+      <c r="G833" s="27"/>
+    </row>
+    <row r="834" spans="1:7">
       <c r="A834" s="6">
         <v>46133</v>
       </c>
@@ -12776,9 +12798,13 @@
       <c r="C834" s="5">
         <v>4</v>
       </c>
-      <c r="D834" s="2"/>
-    </row>
-    <row r="835" spans="1:4">
+      <c r="D834" s="2">
+        <v>1</v>
+      </c>
+      <c r="F834" s="1"/>
+      <c r="G834" s="27"/>
+    </row>
+    <row r="835" spans="1:7">
       <c r="A835" s="6">
         <v>46133</v>
       </c>
@@ -12788,9 +12814,13 @@
       <c r="C835" s="5">
         <v>4</v>
       </c>
-      <c r="D835" s="2"/>
-    </row>
-    <row r="836" spans="1:4">
+      <c r="D835" s="2">
+        <v>1</v>
+      </c>
+      <c r="F835" s="1"/>
+      <c r="G835" s="27"/>
+    </row>
+    <row r="836" spans="1:7">
       <c r="A836" s="6">
         <v>46133</v>
       </c>
@@ -12800,9 +12830,11 @@
       <c r="C836" s="5">
         <v>5</v>
       </c>
-      <c r="D836" s="2"/>
-    </row>
-    <row r="837" spans="1:4">
+      <c r="D836" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="837" spans="1:7">
       <c r="A837" s="6">
         <v>46133</v>
       </c>
@@ -12812,9 +12844,11 @@
       <c r="C837" s="5">
         <v>5</v>
       </c>
-      <c r="D837" s="2"/>
-    </row>
-    <row r="838" spans="1:4">
+      <c r="D837" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="838" spans="1:7">
       <c r="A838" s="6">
         <v>46133</v>
       </c>
@@ -12824,9 +12858,11 @@
       <c r="C838" s="2">
         <v>5</v>
       </c>
-      <c r="D838" s="2"/>
-    </row>
-    <row r="839" spans="1:4">
+      <c r="D838" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839" spans="1:7">
       <c r="A839" s="6">
         <v>46133</v>
       </c>
@@ -12836,7 +12872,131 @@
       <c r="C839" s="2">
         <v>5</v>
       </c>
-      <c r="D839" s="2"/>
+      <c r="D839" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840" spans="1:7">
+      <c r="A840" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B840" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C840" s="2">
+        <v>0</v>
+      </c>
+      <c r="D840" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841" spans="1:7">
+      <c r="A841" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B841" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C841" s="5">
+        <v>2</v>
+      </c>
+      <c r="D841" s="2"/>
+    </row>
+    <row r="842" spans="1:7">
+      <c r="A842" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B842" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C842" s="5">
+        <v>2</v>
+      </c>
+      <c r="D842" s="2"/>
+    </row>
+    <row r="843" spans="1:7">
+      <c r="A843" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B843" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C843" s="5">
+        <v>4</v>
+      </c>
+      <c r="D843" s="2"/>
+    </row>
+    <row r="844" spans="1:7">
+      <c r="A844" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B844" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C844" s="5">
+        <v>4</v>
+      </c>
+      <c r="D844" s="2"/>
+    </row>
+    <row r="845" spans="1:7">
+      <c r="A845" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B845" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C845" s="5">
+        <v>3</v>
+      </c>
+      <c r="D845" s="2"/>
+    </row>
+    <row r="846" spans="1:7">
+      <c r="A846" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B846" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C846" s="5">
+        <v>3</v>
+      </c>
+      <c r="D846" s="2"/>
+    </row>
+    <row r="847" spans="1:7">
+      <c r="A847" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B847" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C847" s="5">
+        <v>7</v>
+      </c>
+      <c r="D847" s="2"/>
+    </row>
+    <row r="848" spans="1:7">
+      <c r="A848" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B848" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C848" s="5">
+        <v>2</v>
+      </c>
+      <c r="D848" s="2"/>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B849" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C849" s="5">
+        <v>2</v>
+      </c>
+      <c r="D849" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G849"/>
+  <dimension ref="A1:G860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -12900,7 +12900,9 @@
       <c r="C841" s="5">
         <v>2</v>
       </c>
-      <c r="D841" s="2"/>
+      <c r="D841" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="842" spans="1:7">
       <c r="A842" s="6">
@@ -12912,7 +12914,11 @@
       <c r="C842" s="5">
         <v>2</v>
       </c>
-      <c r="D842" s="2"/>
+      <c r="D842" s="2">
+        <v>0</v>
+      </c>
+      <c r="F842" s="1"/>
+      <c r="G842" s="27"/>
     </row>
     <row r="843" spans="1:7">
       <c r="A843" s="6">
@@ -12924,7 +12930,11 @@
       <c r="C843" s="5">
         <v>4</v>
       </c>
-      <c r="D843" s="2"/>
+      <c r="D843" s="2">
+        <v>2</v>
+      </c>
+      <c r="F843" s="1"/>
+      <c r="G843" s="27"/>
     </row>
     <row r="844" spans="1:7">
       <c r="A844" s="6">
@@ -12936,7 +12946,11 @@
       <c r="C844" s="5">
         <v>4</v>
       </c>
-      <c r="D844" s="2"/>
+      <c r="D844" s="2">
+        <v>2</v>
+      </c>
+      <c r="F844" s="1"/>
+      <c r="G844" s="27"/>
     </row>
     <row r="845" spans="1:7">
       <c r="A845" s="6">
@@ -12948,7 +12962,11 @@
       <c r="C845" s="5">
         <v>3</v>
       </c>
-      <c r="D845" s="2"/>
+      <c r="D845" s="2">
+        <v>0</v>
+      </c>
+      <c r="F845" s="1"/>
+      <c r="G845" s="27"/>
     </row>
     <row r="846" spans="1:7">
       <c r="A846" s="6">
@@ -12960,7 +12978,11 @@
       <c r="C846" s="5">
         <v>3</v>
       </c>
-      <c r="D846" s="2"/>
+      <c r="D846" s="2">
+        <v>0</v>
+      </c>
+      <c r="F846" s="1"/>
+      <c r="G846" s="27"/>
     </row>
     <row r="847" spans="1:7">
       <c r="A847" s="6">
@@ -12972,7 +12994,11 @@
       <c r="C847" s="5">
         <v>7</v>
       </c>
-      <c r="D847" s="2"/>
+      <c r="D847" s="2">
+        <v>6</v>
+      </c>
+      <c r="F847" s="1"/>
+      <c r="G847" s="27"/>
     </row>
     <row r="848" spans="1:7">
       <c r="A848" s="6">
@@ -12984,7 +13010,11 @@
       <c r="C848" s="5">
         <v>2</v>
       </c>
-      <c r="D848" s="2"/>
+      <c r="D848" s="2">
+        <v>3</v>
+      </c>
+      <c r="F848" s="1"/>
+      <c r="G848" s="27"/>
     </row>
     <row r="849" spans="1:4">
       <c r="A849" s="6">
@@ -12996,7 +13026,145 @@
       <c r="C849" s="5">
         <v>2</v>
       </c>
-      <c r="D849" s="2"/>
+      <c r="D849" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B850" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C850" s="5">
+        <v>0</v>
+      </c>
+      <c r="D850" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B851" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C851" s="5">
+        <v>0</v>
+      </c>
+      <c r="D851" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B852" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C852" s="5">
+        <v>3</v>
+      </c>
+      <c r="D852" s="2"/>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B853" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C853" s="5">
+        <v>3</v>
+      </c>
+      <c r="D853" s="2"/>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B854" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C854" s="5">
+        <v>3</v>
+      </c>
+      <c r="D854" s="2"/>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B855" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C855" s="5">
+        <v>3</v>
+      </c>
+      <c r="D855" s="2"/>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C856" s="5">
+        <v>6</v>
+      </c>
+      <c r="D856" s="2"/>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B857" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C857" s="5">
+        <v>1</v>
+      </c>
+      <c r="D857" s="2"/>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B858" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C858" s="2">
+        <v>1</v>
+      </c>
+      <c r="D858" s="2"/>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B859" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C859" s="2">
+        <v>8</v>
+      </c>
+      <c r="D859" s="2"/>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B860" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C860" s="2">
+        <v>8</v>
+      </c>
+      <c r="D860" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G860"/>
+  <dimension ref="A1:G871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -13016,7 +13016,7 @@
       <c r="F848" s="1"/>
       <c r="G848" s="27"/>
     </row>
-    <row r="849" spans="1:4">
+    <row r="849" spans="1:7">
       <c r="A849" s="6">
         <v>46134</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="850" spans="1:4">
+    <row r="850" spans="1:7">
       <c r="A850" s="6">
         <v>46134</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="851" spans="1:4">
+    <row r="851" spans="1:7">
       <c r="A851" s="6">
         <v>46134</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="852" spans="1:4">
+    <row r="852" spans="1:7">
       <c r="A852" s="6">
         <v>46135</v>
       </c>
@@ -13068,9 +13068,11 @@
       <c r="C852" s="5">
         <v>3</v>
       </c>
-      <c r="D852" s="2"/>
-    </row>
-    <row r="853" spans="1:4">
+      <c r="D852" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="853" spans="1:7">
       <c r="A853" s="6">
         <v>46135</v>
       </c>
@@ -13080,9 +13082,13 @@
       <c r="C853" s="5">
         <v>3</v>
       </c>
-      <c r="D853" s="2"/>
-    </row>
-    <row r="854" spans="1:4">
+      <c r="D853" s="2">
+        <v>2</v>
+      </c>
+      <c r="F853" s="1"/>
+      <c r="G853" s="27"/>
+    </row>
+    <row r="854" spans="1:7">
       <c r="A854" s="6">
         <v>46135</v>
       </c>
@@ -13092,9 +13098,13 @@
       <c r="C854" s="5">
         <v>3</v>
       </c>
-      <c r="D854" s="2"/>
-    </row>
-    <row r="855" spans="1:4">
+      <c r="D854" s="2">
+        <v>1</v>
+      </c>
+      <c r="F854" s="1"/>
+      <c r="G854" s="27"/>
+    </row>
+    <row r="855" spans="1:7">
       <c r="A855" s="6">
         <v>46135</v>
       </c>
@@ -13104,9 +13114,13 @@
       <c r="C855" s="5">
         <v>3</v>
       </c>
-      <c r="D855" s="2"/>
-    </row>
-    <row r="856" spans="1:4">
+      <c r="D855" s="2">
+        <v>1</v>
+      </c>
+      <c r="F855" s="1"/>
+      <c r="G855" s="27"/>
+    </row>
+    <row r="856" spans="1:7">
       <c r="A856" s="6">
         <v>46135</v>
       </c>
@@ -13116,9 +13130,13 @@
       <c r="C856" s="5">
         <v>6</v>
       </c>
-      <c r="D856" s="2"/>
-    </row>
-    <row r="857" spans="1:4">
+      <c r="D856" s="2">
+        <v>6</v>
+      </c>
+      <c r="F856" s="1"/>
+      <c r="G856" s="27"/>
+    </row>
+    <row r="857" spans="1:7">
       <c r="A857" s="6">
         <v>46135</v>
       </c>
@@ -13128,9 +13146,13 @@
       <c r="C857" s="5">
         <v>1</v>
       </c>
-      <c r="D857" s="2"/>
-    </row>
-    <row r="858" spans="1:4">
+      <c r="D857" s="2">
+        <v>0</v>
+      </c>
+      <c r="F857" s="1"/>
+      <c r="G857" s="27"/>
+    </row>
+    <row r="858" spans="1:7">
       <c r="A858" s="6">
         <v>46135</v>
       </c>
@@ -13140,9 +13162,13 @@
       <c r="C858" s="2">
         <v>1</v>
       </c>
-      <c r="D858" s="2"/>
-    </row>
-    <row r="859" spans="1:4">
+      <c r="D858" s="2">
+        <v>0</v>
+      </c>
+      <c r="F858" s="1"/>
+      <c r="G858" s="27"/>
+    </row>
+    <row r="859" spans="1:7">
       <c r="A859" s="6">
         <v>46135</v>
       </c>
@@ -13152,9 +13178,13 @@
       <c r="C859" s="2">
         <v>8</v>
       </c>
-      <c r="D859" s="2"/>
-    </row>
-    <row r="860" spans="1:4">
+      <c r="D859" s="2">
+        <v>5</v>
+      </c>
+      <c r="F859" s="1"/>
+      <c r="G859" s="27"/>
+    </row>
+    <row r="860" spans="1:7">
       <c r="A860" s="6">
         <v>46135</v>
       </c>
@@ -13164,7 +13194,151 @@
       <c r="C860" s="2">
         <v>8</v>
       </c>
-      <c r="D860" s="2"/>
+      <c r="D860" s="2">
+        <v>5</v>
+      </c>
+      <c r="F860" s="1"/>
+      <c r="G860" s="27"/>
+    </row>
+    <row r="861" spans="1:7">
+      <c r="A861" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B861" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C861" s="2">
+        <v>0</v>
+      </c>
+      <c r="D861" s="2">
+        <v>3</v>
+      </c>
+      <c r="F861" s="1"/>
+      <c r="G861" s="27"/>
+    </row>
+    <row r="862" spans="1:7">
+      <c r="A862" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B862" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C862" s="2">
+        <v>0</v>
+      </c>
+      <c r="D862" s="2">
+        <v>3</v>
+      </c>
+      <c r="F862" s="1"/>
+      <c r="G862" s="27"/>
+    </row>
+    <row r="863" spans="1:7">
+      <c r="A863" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B863" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C863" s="5">
+        <v>5</v>
+      </c>
+      <c r="D863" s="2"/>
+    </row>
+    <row r="864" spans="1:7">
+      <c r="A864" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B864" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C864" s="5">
+        <v>5</v>
+      </c>
+      <c r="D864" s="2"/>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C865" s="5">
+        <v>4</v>
+      </c>
+      <c r="D865" s="2"/>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B866" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C866" s="5">
+        <v>2</v>
+      </c>
+      <c r="D866" s="2"/>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B867" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C867" s="5">
+        <v>2</v>
+      </c>
+      <c r="D867" s="2"/>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B868" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C868" s="5">
+        <v>4</v>
+      </c>
+      <c r="D868" s="2"/>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B869" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C869" s="5">
+        <v>4</v>
+      </c>
+      <c r="D869" s="2"/>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B870" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C870" s="5">
+        <v>2</v>
+      </c>
+      <c r="D870" s="2"/>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B871" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C871" s="5">
+        <v>2</v>
+      </c>
+      <c r="D871" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G871"/>
+  <dimension ref="A1:G881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -13242,7 +13242,9 @@
       <c r="C863" s="5">
         <v>5</v>
       </c>
-      <c r="D863" s="2"/>
+      <c r="D863" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="864" spans="1:7">
       <c r="A864" s="6">
@@ -13254,9 +13256,13 @@
       <c r="C864" s="5">
         <v>5</v>
       </c>
-      <c r="D864" s="2"/>
-    </row>
-    <row r="865" spans="1:4">
+      <c r="D864" s="2">
+        <v>6</v>
+      </c>
+      <c r="F864" s="1"/>
+      <c r="G864" s="27"/>
+    </row>
+    <row r="865" spans="1:7">
       <c r="A865" s="6">
         <v>46136</v>
       </c>
@@ -13266,9 +13272,13 @@
       <c r="C865" s="5">
         <v>4</v>
       </c>
-      <c r="D865" s="2"/>
-    </row>
-    <row r="866" spans="1:4">
+      <c r="D865" s="2">
+        <v>3</v>
+      </c>
+      <c r="F865" s="1"/>
+      <c r="G865" s="27"/>
+    </row>
+    <row r="866" spans="1:7">
       <c r="A866" s="6">
         <v>46136</v>
       </c>
@@ -13278,9 +13288,13 @@
       <c r="C866" s="5">
         <v>2</v>
       </c>
-      <c r="D866" s="2"/>
-    </row>
-    <row r="867" spans="1:4">
+      <c r="D866" s="2">
+        <v>1</v>
+      </c>
+      <c r="F866" s="1"/>
+      <c r="G866" s="27"/>
+    </row>
+    <row r="867" spans="1:7">
       <c r="A867" s="6">
         <v>46136</v>
       </c>
@@ -13290,9 +13304,13 @@
       <c r="C867" s="5">
         <v>2</v>
       </c>
-      <c r="D867" s="2"/>
-    </row>
-    <row r="868" spans="1:4">
+      <c r="D867" s="2">
+        <v>1</v>
+      </c>
+      <c r="F867" s="1"/>
+      <c r="G867" s="27"/>
+    </row>
+    <row r="868" spans="1:7">
       <c r="A868" s="6">
         <v>46136</v>
       </c>
@@ -13302,9 +13320,13 @@
       <c r="C868" s="5">
         <v>4</v>
       </c>
-      <c r="D868" s="2"/>
-    </row>
-    <row r="869" spans="1:4">
+      <c r="D868" s="2">
+        <v>6</v>
+      </c>
+      <c r="F868" s="1"/>
+      <c r="G868" s="27"/>
+    </row>
+    <row r="869" spans="1:7">
       <c r="A869" s="6">
         <v>46136</v>
       </c>
@@ -13314,9 +13336,13 @@
       <c r="C869" s="5">
         <v>4</v>
       </c>
-      <c r="D869" s="2"/>
-    </row>
-    <row r="870" spans="1:4">
+      <c r="D869" s="2">
+        <v>6</v>
+      </c>
+      <c r="F869" s="1"/>
+      <c r="G869" s="27"/>
+    </row>
+    <row r="870" spans="1:7">
       <c r="A870" s="6">
         <v>46136</v>
       </c>
@@ -13326,9 +13352,13 @@
       <c r="C870" s="5">
         <v>2</v>
       </c>
-      <c r="D870" s="2"/>
-    </row>
-    <row r="871" spans="1:4">
+      <c r="D870" s="2">
+        <v>1</v>
+      </c>
+      <c r="F870" s="1"/>
+      <c r="G870" s="27"/>
+    </row>
+    <row r="871" spans="1:7">
       <c r="A871" s="6">
         <v>46136</v>
       </c>
@@ -13338,7 +13368,137 @@
       <c r="C871" s="5">
         <v>2</v>
       </c>
-      <c r="D871" s="2"/>
+      <c r="D871" s="2">
+        <v>1</v>
+      </c>
+      <c r="F871" s="1"/>
+      <c r="G871" s="27"/>
+    </row>
+    <row r="872" spans="1:7">
+      <c r="A872" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B872" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C872" s="5">
+        <v>0</v>
+      </c>
+      <c r="D872" s="5">
+        <v>2</v>
+      </c>
+      <c r="F872" s="1"/>
+      <c r="G872" s="27"/>
+    </row>
+    <row r="873" spans="1:7">
+      <c r="A873" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B873" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C873" s="5">
+        <v>0</v>
+      </c>
+      <c r="D873" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="874" spans="1:7">
+      <c r="A874" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B874" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C874" s="5">
+        <v>2</v>
+      </c>
+      <c r="D874" s="2"/>
+    </row>
+    <row r="875" spans="1:7">
+      <c r="A875" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B875" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C875" s="5">
+        <v>2</v>
+      </c>
+      <c r="D875" s="2"/>
+    </row>
+    <row r="876" spans="1:7">
+      <c r="A876" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B876" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C876" s="5">
+        <v>2</v>
+      </c>
+      <c r="D876" s="2"/>
+    </row>
+    <row r="877" spans="1:7">
+      <c r="A877" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B877" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C877" s="5">
+        <v>2</v>
+      </c>
+      <c r="D877" s="2"/>
+    </row>
+    <row r="878" spans="1:7">
+      <c r="A878" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B878" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C878" s="2">
+        <v>3</v>
+      </c>
+      <c r="D878" s="2"/>
+    </row>
+    <row r="879" spans="1:7">
+      <c r="A879" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B879" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C879" s="2">
+        <v>3</v>
+      </c>
+      <c r="D879" s="2"/>
+    </row>
+    <row r="880" spans="1:7">
+      <c r="A880" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B880" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C880" s="2">
+        <v>2</v>
+      </c>
+      <c r="D880" s="2"/>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B881" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C881" s="2">
+        <v>2</v>
+      </c>
+      <c r="D881" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G881"/>
+  <dimension ref="A1:G896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -13406,99 +13406,321 @@
     </row>
     <row r="874" spans="1:7">
       <c r="A874" s="6">
-        <v>46139</v>
-      </c>
-      <c r="B874" s="23" t="s">
-        <v>21</v>
+        <v>46136</v>
+      </c>
+      <c r="B874" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="C874" s="5">
-        <v>2</v>
-      </c>
-      <c r="D874" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D874" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="875" spans="1:7">
       <c r="A875" s="6">
-        <v>46139</v>
-      </c>
-      <c r="B875" s="23" t="s">
-        <v>3</v>
+        <v>46136</v>
+      </c>
+      <c r="B875" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C875" s="5">
-        <v>2</v>
-      </c>
-      <c r="D875" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D875" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="876" spans="1:7">
       <c r="A876" s="6">
-        <v>46139</v>
-      </c>
-      <c r="B876" s="21" t="s">
-        <v>15</v>
+        <v>46136</v>
+      </c>
+      <c r="B876" s="17" t="s">
+        <v>2</v>
       </c>
       <c r="C876" s="5">
-        <v>2</v>
-      </c>
-      <c r="D876" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D876" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="877" spans="1:7">
       <c r="A877" s="6">
-        <v>46139</v>
-      </c>
-      <c r="B877" s="21" t="s">
-        <v>6</v>
+        <v>46136</v>
+      </c>
+      <c r="B877" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="C877" s="5">
-        <v>2</v>
-      </c>
-      <c r="D877" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D877" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="878" spans="1:7">
       <c r="A878" s="6">
         <v>46139</v>
       </c>
-      <c r="B878" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C878" s="2">
-        <v>3</v>
-      </c>
-      <c r="D878" s="2"/>
+      <c r="B878" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C878" s="5">
+        <v>2</v>
+      </c>
+      <c r="D878" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="879" spans="1:7">
       <c r="A879" s="6">
         <v>46139</v>
       </c>
-      <c r="B879" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C879" s="2">
-        <v>3</v>
-      </c>
-      <c r="D879" s="2"/>
+      <c r="B879" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C879" s="5">
+        <v>2</v>
+      </c>
+      <c r="D879" s="2">
+        <v>1</v>
+      </c>
+      <c r="F879" s="1"/>
+      <c r="G879" s="27"/>
     </row>
     <row r="880" spans="1:7">
       <c r="A880" s="6">
         <v>46139</v>
       </c>
-      <c r="B880" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C880" s="2">
-        <v>2</v>
-      </c>
-      <c r="D880" s="2"/>
-    </row>
-    <row r="881" spans="1:4">
+      <c r="B880" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C880" s="5">
+        <v>2</v>
+      </c>
+      <c r="D880" s="2">
+        <v>1</v>
+      </c>
+      <c r="F880" s="1"/>
+      <c r="G880" s="27"/>
+    </row>
+    <row r="881" spans="1:7">
       <c r="A881" s="6">
         <v>46139</v>
       </c>
-      <c r="B881" s="20" t="s">
+      <c r="B881" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C881" s="5">
+        <v>2</v>
+      </c>
+      <c r="D881" s="2">
+        <v>1</v>
+      </c>
+      <c r="F881" s="1"/>
+      <c r="G881" s="27"/>
+    </row>
+    <row r="882" spans="1:7">
+      <c r="A882" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B882" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C882" s="2">
+        <v>3</v>
+      </c>
+      <c r="D882" s="2">
+        <v>1</v>
+      </c>
+      <c r="F882" s="1"/>
+      <c r="G882" s="27"/>
+    </row>
+    <row r="883" spans="1:7">
+      <c r="A883" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B883" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C883" s="2">
+        <v>3</v>
+      </c>
+      <c r="D883" s="2">
+        <v>1</v>
+      </c>
+      <c r="F883" s="1"/>
+      <c r="G883" s="27"/>
+    </row>
+    <row r="884" spans="1:7">
+      <c r="A884" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B884" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C884" s="2">
+        <v>2</v>
+      </c>
+      <c r="D884" s="2">
+        <v>1</v>
+      </c>
+      <c r="F884" s="1"/>
+      <c r="G884" s="27"/>
+    </row>
+    <row r="885" spans="1:7">
+      <c r="A885" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B885" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C881" s="2">
-        <v>2</v>
-      </c>
-      <c r="D881" s="2"/>
+      <c r="C885" s="2">
+        <v>2</v>
+      </c>
+      <c r="D885" s="2">
+        <v>1</v>
+      </c>
+      <c r="F885" s="1"/>
+      <c r="G885" s="27"/>
+    </row>
+    <row r="886" spans="1:7">
+      <c r="A886" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B886" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C886" s="5">
+        <v>5</v>
+      </c>
+      <c r="D886" s="2"/>
+      <c r="F886" s="1"/>
+      <c r="G886" s="27"/>
+    </row>
+    <row r="887" spans="1:7">
+      <c r="A887" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B887" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C887" s="5">
+        <v>5</v>
+      </c>
+      <c r="D887" s="2"/>
+      <c r="F887" s="1"/>
+      <c r="G887" s="27"/>
+    </row>
+    <row r="888" spans="1:7">
+      <c r="A888" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B888" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C888" s="5">
+        <v>2</v>
+      </c>
+      <c r="D888" s="2"/>
+    </row>
+    <row r="889" spans="1:7">
+      <c r="A889" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B889" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C889" s="5">
+        <v>2</v>
+      </c>
+      <c r="D889" s="2"/>
+    </row>
+    <row r="890" spans="1:7">
+      <c r="A890" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B890" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C890" s="5">
+        <v>3</v>
+      </c>
+      <c r="D890" s="2"/>
+    </row>
+    <row r="891" spans="1:7">
+      <c r="A891" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B891" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C891" s="5">
+        <v>3</v>
+      </c>
+      <c r="D891" s="2"/>
+    </row>
+    <row r="892" spans="1:7">
+      <c r="A892" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B892" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C892" s="5">
+        <v>1</v>
+      </c>
+      <c r="D892" s="2"/>
+    </row>
+    <row r="893" spans="1:7">
+      <c r="A893" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B893" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C893" s="2">
+        <v>1</v>
+      </c>
+      <c r="D893" s="2"/>
+    </row>
+    <row r="894" spans="1:7">
+      <c r="A894" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B894" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C894" s="2">
+        <v>8</v>
+      </c>
+      <c r="D894" s="2"/>
+    </row>
+    <row r="895" spans="1:7">
+      <c r="A895" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B895" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C895" s="2">
+        <v>7</v>
+      </c>
+      <c r="D895" s="2"/>
+    </row>
+    <row r="896" spans="1:7">
+      <c r="A896" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B896" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C896" s="2">
+        <v>7</v>
+      </c>
+      <c r="D896" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,16 +607,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G896"/>
+  <dimension ref="A1:H902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" customWidth="1"/>
-    <col min="8" max="9" width="22.7109375" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -13506,7 +13506,7 @@
       <c r="F880" s="1"/>
       <c r="G880" s="27"/>
     </row>
-    <row r="881" spans="1:7">
+    <row r="881" spans="1:8">
       <c r="A881" s="6">
         <v>46139</v>
       </c>
@@ -13522,7 +13522,7 @@
       <c r="F881" s="1"/>
       <c r="G881" s="27"/>
     </row>
-    <row r="882" spans="1:7">
+    <row r="882" spans="1:8">
       <c r="A882" s="6">
         <v>46139</v>
       </c>
@@ -13538,7 +13538,7 @@
       <c r="F882" s="1"/>
       <c r="G882" s="27"/>
     </row>
-    <row r="883" spans="1:7">
+    <row r="883" spans="1:8">
       <c r="A883" s="6">
         <v>46139</v>
       </c>
@@ -13554,7 +13554,7 @@
       <c r="F883" s="1"/>
       <c r="G883" s="27"/>
     </row>
-    <row r="884" spans="1:7">
+    <row r="884" spans="1:8">
       <c r="A884" s="6">
         <v>46139</v>
       </c>
@@ -13570,7 +13570,7 @@
       <c r="F884" s="1"/>
       <c r="G884" s="27"/>
     </row>
-    <row r="885" spans="1:7">
+    <row r="885" spans="1:8">
       <c r="A885" s="6">
         <v>46139</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="F885" s="1"/>
       <c r="G885" s="27"/>
     </row>
-    <row r="886" spans="1:7">
+    <row r="886" spans="1:8">
       <c r="A886" s="6">
         <v>46140</v>
       </c>
@@ -13596,11 +13596,12 @@
       <c r="C886" s="5">
         <v>5</v>
       </c>
-      <c r="D886" s="2"/>
+      <c r="D886" s="2">
+        <v>4</v>
+      </c>
       <c r="F886" s="1"/>
-      <c r="G886" s="27"/>
-    </row>
-    <row r="887" spans="1:7">
+    </row>
+    <row r="887" spans="1:8">
       <c r="A887" s="6">
         <v>46140</v>
       </c>
@@ -13610,11 +13611,14 @@
       <c r="C887" s="5">
         <v>5</v>
       </c>
-      <c r="D887" s="2"/>
+      <c r="D887" s="2">
+        <v>4</v>
+      </c>
       <c r="F887" s="1"/>
-      <c r="G887" s="27"/>
-    </row>
-    <row r="888" spans="1:7">
+      <c r="G887" s="1"/>
+      <c r="H887" s="27"/>
+    </row>
+    <row r="888" spans="1:8">
       <c r="A888" s="6">
         <v>46140</v>
       </c>
@@ -13624,9 +13628,13 @@
       <c r="C888" s="5">
         <v>2</v>
       </c>
-      <c r="D888" s="2"/>
-    </row>
-    <row r="889" spans="1:7">
+      <c r="D888" s="2">
+        <v>4</v>
+      </c>
+      <c r="G888" s="1"/>
+      <c r="H888" s="27"/>
+    </row>
+    <row r="889" spans="1:8">
       <c r="A889" s="6">
         <v>46140</v>
       </c>
@@ -13636,9 +13644,13 @@
       <c r="C889" s="5">
         <v>2</v>
       </c>
-      <c r="D889" s="2"/>
-    </row>
-    <row r="890" spans="1:7">
+      <c r="D889" s="2">
+        <v>4</v>
+      </c>
+      <c r="G889" s="1"/>
+      <c r="H889" s="27"/>
+    </row>
+    <row r="890" spans="1:8">
       <c r="A890" s="6">
         <v>46140</v>
       </c>
@@ -13648,9 +13660,13 @@
       <c r="C890" s="5">
         <v>3</v>
       </c>
-      <c r="D890" s="2"/>
-    </row>
-    <row r="891" spans="1:7">
+      <c r="D890" s="2">
+        <v>0</v>
+      </c>
+      <c r="G890" s="1"/>
+      <c r="H890" s="27"/>
+    </row>
+    <row r="891" spans="1:8">
       <c r="A891" s="6">
         <v>46140</v>
       </c>
@@ -13660,9 +13676,13 @@
       <c r="C891" s="5">
         <v>3</v>
       </c>
-      <c r="D891" s="2"/>
-    </row>
-    <row r="892" spans="1:7">
+      <c r="D891" s="2">
+        <v>0</v>
+      </c>
+      <c r="G891" s="1"/>
+      <c r="H891" s="27"/>
+    </row>
+    <row r="892" spans="1:8">
       <c r="A892" s="6">
         <v>46140</v>
       </c>
@@ -13672,9 +13692,13 @@
       <c r="C892" s="5">
         <v>1</v>
       </c>
-      <c r="D892" s="2"/>
-    </row>
-    <row r="893" spans="1:7">
+      <c r="D892" s="2">
+        <v>2</v>
+      </c>
+      <c r="G892" s="1"/>
+      <c r="H892" s="27"/>
+    </row>
+    <row r="893" spans="1:8">
       <c r="A893" s="6">
         <v>46140</v>
       </c>
@@ -13684,9 +13708,13 @@
       <c r="C893" s="2">
         <v>1</v>
       </c>
-      <c r="D893" s="2"/>
-    </row>
-    <row r="894" spans="1:7">
+      <c r="D893" s="2">
+        <v>2</v>
+      </c>
+      <c r="G893" s="1"/>
+      <c r="H893" s="27"/>
+    </row>
+    <row r="894" spans="1:8">
       <c r="A894" s="6">
         <v>46140</v>
       </c>
@@ -13696,9 +13724,13 @@
       <c r="C894" s="2">
         <v>8</v>
       </c>
-      <c r="D894" s="2"/>
-    </row>
-    <row r="895" spans="1:7">
+      <c r="D894" s="2">
+        <v>10</v>
+      </c>
+      <c r="G894" s="1"/>
+      <c r="H894" s="27"/>
+    </row>
+    <row r="895" spans="1:8">
       <c r="A895" s="6">
         <v>46140</v>
       </c>
@@ -13708,9 +13740,11 @@
       <c r="C895" s="2">
         <v>7</v>
       </c>
-      <c r="D895" s="2"/>
-    </row>
-    <row r="896" spans="1:7">
+      <c r="D895" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="896" spans="1:8">
       <c r="A896" s="6">
         <v>46140</v>
       </c>
@@ -13720,7 +13754,81 @@
       <c r="C896" s="2">
         <v>7</v>
       </c>
-      <c r="D896" s="2"/>
+      <c r="D896" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B897" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C897" s="5">
+        <v>5</v>
+      </c>
+      <c r="D897" s="2"/>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B898" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C898" s="5">
+        <v>1</v>
+      </c>
+      <c r="D898" s="2"/>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B899" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C899" s="5">
+        <v>1</v>
+      </c>
+      <c r="D899" s="2"/>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C900" s="5">
+        <v>2</v>
+      </c>
+      <c r="D900" s="2"/>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B901" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C901" s="5">
+        <v>4</v>
+      </c>
+      <c r="D901" s="2"/>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B902" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C902" s="2">
+        <v>4</v>
+      </c>
+      <c r="D902" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H902"/>
+  <dimension ref="A1:H914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -13758,77 +13758,259 @@
         <v>2</v>
       </c>
     </row>
-    <row r="897" spans="1:4">
+    <row r="897" spans="1:7">
       <c r="A897" s="6">
         <v>46141</v>
       </c>
-      <c r="B897" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C897" s="5">
-        <v>5</v>
-      </c>
-      <c r="D897" s="2"/>
-    </row>
-    <row r="898" spans="1:4">
+      <c r="B897" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C897" s="2">
+        <v>0</v>
+      </c>
+      <c r="D897" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898" spans="1:7">
       <c r="A898" s="6">
         <v>46141</v>
       </c>
-      <c r="B898" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C898" s="5">
-        <v>1</v>
-      </c>
-      <c r="D898" s="2"/>
-    </row>
-    <row r="899" spans="1:4">
+      <c r="B898" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C898" s="2">
+        <v>0</v>
+      </c>
+      <c r="D898" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899" spans="1:7">
       <c r="A899" s="6">
         <v>46141</v>
       </c>
-      <c r="B899" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C899" s="5">
-        <v>1</v>
-      </c>
-      <c r="D899" s="2"/>
-    </row>
-    <row r="900" spans="1:4">
+      <c r="B899" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C899" s="2">
+        <v>0</v>
+      </c>
+      <c r="D899" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900" spans="1:7">
       <c r="A900" s="6">
         <v>46141</v>
       </c>
-      <c r="B900" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C900" s="5">
-        <v>2</v>
-      </c>
-      <c r="D900" s="2"/>
-    </row>
-    <row r="901" spans="1:4">
+      <c r="B900" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C900" s="2">
+        <v>0</v>
+      </c>
+      <c r="D900" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901" spans="1:7">
       <c r="A901" s="6">
         <v>46141</v>
       </c>
-      <c r="B901" s="18" t="s">
-        <v>13</v>
+      <c r="B901" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C901" s="5">
-        <v>4</v>
-      </c>
-      <c r="D901" s="2"/>
-    </row>
-    <row r="902" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D901" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902" spans="1:7">
       <c r="A902" s="6">
         <v>46141</v>
       </c>
-      <c r="B902" s="18" t="s">
+      <c r="B902" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C902" s="5">
+        <v>1</v>
+      </c>
+      <c r="D902" s="2">
+        <v>1</v>
+      </c>
+      <c r="F902" s="1"/>
+      <c r="G902" s="27"/>
+    </row>
+    <row r="903" spans="1:7">
+      <c r="A903" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B903" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C903" s="5">
+        <v>1</v>
+      </c>
+      <c r="D903" s="2">
+        <v>1</v>
+      </c>
+      <c r="F903" s="1"/>
+      <c r="G903" s="27"/>
+    </row>
+    <row r="904" spans="1:7">
+      <c r="A904" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C904" s="5">
+        <v>2</v>
+      </c>
+      <c r="D904" s="2">
+        <v>2</v>
+      </c>
+      <c r="F904" s="1"/>
+      <c r="G904" s="27"/>
+    </row>
+    <row r="905" spans="1:7">
+      <c r="A905" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B905" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C905" s="5">
+        <v>4</v>
+      </c>
+      <c r="D905" s="2">
+        <v>2</v>
+      </c>
+      <c r="F905" s="1"/>
+      <c r="G905" s="27"/>
+    </row>
+    <row r="906" spans="1:7">
+      <c r="A906" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B906" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C902" s="2">
-        <v>4</v>
-      </c>
-      <c r="D902" s="2"/>
+      <c r="C906" s="2">
+        <v>4</v>
+      </c>
+      <c r="D906" s="2">
+        <v>2</v>
+      </c>
+      <c r="F906" s="1"/>
+      <c r="G906" s="27"/>
+    </row>
+    <row r="907" spans="1:7">
+      <c r="A907" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B907" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C907" s="5">
+        <v>3</v>
+      </c>
+      <c r="D907" s="2"/>
+      <c r="F907" s="1"/>
+      <c r="G907" s="27"/>
+    </row>
+    <row r="908" spans="1:7">
+      <c r="A908" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C908" s="5">
+        <v>5</v>
+      </c>
+      <c r="D908" s="2"/>
+      <c r="F908" s="1"/>
+      <c r="G908" s="27"/>
+    </row>
+    <row r="909" spans="1:7">
+      <c r="A909" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B909" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C909" s="5">
+        <v>2</v>
+      </c>
+      <c r="D909" s="2"/>
+      <c r="F909" s="1"/>
+      <c r="G909" s="27"/>
+    </row>
+    <row r="910" spans="1:7">
+      <c r="A910" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B910" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C910" s="5">
+        <v>2</v>
+      </c>
+      <c r="D910" s="2"/>
+      <c r="F910" s="1"/>
+      <c r="G910" s="27"/>
+    </row>
+    <row r="911" spans="1:7">
+      <c r="A911" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B911" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C911" s="5">
+        <v>2</v>
+      </c>
+      <c r="D911" s="2"/>
+    </row>
+    <row r="912" spans="1:7">
+      <c r="A912" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B912" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C912" s="5">
+        <v>2</v>
+      </c>
+      <c r="D912" s="2"/>
+    </row>
+    <row r="913" spans="1:4">
+      <c r="A913" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B913" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C913" s="5">
+        <v>2</v>
+      </c>
+      <c r="D913" s="2"/>
+    </row>
+    <row r="914" spans="1:4">
+      <c r="A914" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B914" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C914" s="5">
+        <v>2</v>
+      </c>
+      <c r="D914" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H914"/>
+  <dimension ref="A1:H925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -13758,7 +13758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="897" spans="1:7">
+    <row r="897" spans="1:8">
       <c r="A897" s="6">
         <v>46141</v>
       </c>
@@ -13772,7 +13772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="898" spans="1:7">
+    <row r="898" spans="1:8">
       <c r="A898" s="6">
         <v>46141</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="899" spans="1:7">
+    <row r="899" spans="1:8">
       <c r="A899" s="6">
         <v>46141</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="900" spans="1:7">
+    <row r="900" spans="1:8">
       <c r="A900" s="6">
         <v>46141</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="901" spans="1:7">
+    <row r="901" spans="1:8">
       <c r="A901" s="6">
         <v>46141</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="902" spans="1:7">
+    <row r="902" spans="1:8">
       <c r="A902" s="6">
         <v>46141</v>
       </c>
@@ -13844,7 +13844,7 @@
       <c r="F902" s="1"/>
       <c r="G902" s="27"/>
     </row>
-    <row r="903" spans="1:7">
+    <row r="903" spans="1:8">
       <c r="A903" s="6">
         <v>46141</v>
       </c>
@@ -13860,7 +13860,7 @@
       <c r="F903" s="1"/>
       <c r="G903" s="27"/>
     </row>
-    <row r="904" spans="1:7">
+    <row r="904" spans="1:8">
       <c r="A904" s="6">
         <v>46141</v>
       </c>
@@ -13876,7 +13876,7 @@
       <c r="F904" s="1"/>
       <c r="G904" s="27"/>
     </row>
-    <row r="905" spans="1:7">
+    <row r="905" spans="1:8">
       <c r="A905" s="6">
         <v>46141</v>
       </c>
@@ -13892,7 +13892,7 @@
       <c r="F905" s="1"/>
       <c r="G905" s="27"/>
     </row>
-    <row r="906" spans="1:7">
+    <row r="906" spans="1:8">
       <c r="A906" s="6">
         <v>46141</v>
       </c>
@@ -13908,7 +13908,7 @@
       <c r="F906" s="1"/>
       <c r="G906" s="27"/>
     </row>
-    <row r="907" spans="1:7">
+    <row r="907" spans="1:8">
       <c r="A907" s="6">
         <v>46142</v>
       </c>
@@ -13918,11 +13918,12 @@
       <c r="C907" s="5">
         <v>3</v>
       </c>
-      <c r="D907" s="2"/>
+      <c r="D907" s="2">
+        <v>5</v>
+      </c>
       <c r="F907" s="1"/>
-      <c r="G907" s="27"/>
-    </row>
-    <row r="908" spans="1:7">
+    </row>
+    <row r="908" spans="1:8">
       <c r="A908" s="6">
         <v>46142</v>
       </c>
@@ -13932,11 +13933,14 @@
       <c r="C908" s="5">
         <v>5</v>
       </c>
-      <c r="D908" s="2"/>
+      <c r="D908" s="2">
+        <v>4</v>
+      </c>
       <c r="F908" s="1"/>
-      <c r="G908" s="27"/>
-    </row>
-    <row r="909" spans="1:7">
+      <c r="G908" s="1"/>
+      <c r="H908" s="27"/>
+    </row>
+    <row r="909" spans="1:8">
       <c r="A909" s="6">
         <v>46142</v>
       </c>
@@ -13946,11 +13950,14 @@
       <c r="C909" s="5">
         <v>2</v>
       </c>
-      <c r="D909" s="2"/>
+      <c r="D909" s="2">
+        <v>7</v>
+      </c>
       <c r="F909" s="1"/>
-      <c r="G909" s="27"/>
-    </row>
-    <row r="910" spans="1:7">
+      <c r="G909" s="1"/>
+      <c r="H909" s="27"/>
+    </row>
+    <row r="910" spans="1:8">
       <c r="A910" s="6">
         <v>46142</v>
       </c>
@@ -13960,11 +13967,14 @@
       <c r="C910" s="5">
         <v>2</v>
       </c>
-      <c r="D910" s="2"/>
+      <c r="D910" s="2">
+        <v>7</v>
+      </c>
       <c r="F910" s="1"/>
-      <c r="G910" s="27"/>
-    </row>
-    <row r="911" spans="1:7">
+      <c r="G910" s="1"/>
+      <c r="H910" s="27"/>
+    </row>
+    <row r="911" spans="1:8">
       <c r="A911" s="6">
         <v>46142</v>
       </c>
@@ -13974,9 +13984,13 @@
       <c r="C911" s="5">
         <v>2</v>
       </c>
-      <c r="D911" s="2"/>
-    </row>
-    <row r="912" spans="1:7">
+      <c r="D911" s="2">
+        <v>0</v>
+      </c>
+      <c r="G911" s="1"/>
+      <c r="H911" s="27"/>
+    </row>
+    <row r="912" spans="1:8">
       <c r="A912" s="6">
         <v>46142</v>
       </c>
@@ -13986,9 +14000,13 @@
       <c r="C912" s="5">
         <v>2</v>
       </c>
-      <c r="D912" s="2"/>
-    </row>
-    <row r="913" spans="1:4">
+      <c r="D912" s="2">
+        <v>0</v>
+      </c>
+      <c r="G912" s="1"/>
+      <c r="H912" s="27"/>
+    </row>
+    <row r="913" spans="1:8">
       <c r="A913" s="6">
         <v>46142</v>
       </c>
@@ -13998,9 +14016,13 @@
       <c r="C913" s="5">
         <v>2</v>
       </c>
-      <c r="D913" s="2"/>
-    </row>
-    <row r="914" spans="1:4">
+      <c r="D913" s="2">
+        <v>4</v>
+      </c>
+      <c r="G913" s="1"/>
+      <c r="H913" s="27"/>
+    </row>
+    <row r="914" spans="1:8">
       <c r="A914" s="6">
         <v>46142</v>
       </c>
@@ -14010,7 +14032,167 @@
       <c r="C914" s="5">
         <v>2</v>
       </c>
-      <c r="D914" s="2"/>
+      <c r="D914" s="2">
+        <v>4</v>
+      </c>
+      <c r="G914" s="1"/>
+      <c r="H914" s="27"/>
+    </row>
+    <row r="915" spans="1:8">
+      <c r="A915" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B915" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C915" s="5">
+        <v>0</v>
+      </c>
+      <c r="D915" s="2">
+        <v>4</v>
+      </c>
+      <c r="G915" s="1"/>
+      <c r="H915" s="27"/>
+    </row>
+    <row r="916" spans="1:8">
+      <c r="A916" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B916" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C916" s="5">
+        <v>0</v>
+      </c>
+      <c r="D916" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="917" spans="1:8">
+      <c r="A917" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B917" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C917" s="5">
+        <v>1</v>
+      </c>
+      <c r="D917" s="2">
+        <v>1</v>
+      </c>
+      <c r="G917" s="1"/>
+      <c r="H917" s="27"/>
+    </row>
+    <row r="918" spans="1:8">
+      <c r="A918" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B918" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C918" s="5">
+        <v>1</v>
+      </c>
+      <c r="D918" s="2">
+        <v>1</v>
+      </c>
+      <c r="G918" s="1"/>
+      <c r="H918" s="27"/>
+    </row>
+    <row r="919" spans="1:8">
+      <c r="A919" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C919" s="5">
+        <v>4</v>
+      </c>
+      <c r="D919" s="2">
+        <v>7</v>
+      </c>
+      <c r="G919" s="1"/>
+      <c r="H919" s="27"/>
+    </row>
+    <row r="920" spans="1:8">
+      <c r="A920" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B920" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C920" s="5">
+        <v>6</v>
+      </c>
+      <c r="D920" s="2">
+        <v>8</v>
+      </c>
+      <c r="G920" s="1"/>
+      <c r="H920" s="27"/>
+    </row>
+    <row r="921" spans="1:8">
+      <c r="A921" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C921" s="5">
+        <v>2</v>
+      </c>
+      <c r="D921" s="2"/>
+      <c r="G921" s="1"/>
+      <c r="H921" s="27"/>
+    </row>
+    <row r="922" spans="1:8">
+      <c r="A922" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B922" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C922" s="5">
+        <v>3</v>
+      </c>
+      <c r="D922" s="2"/>
+    </row>
+    <row r="923" spans="1:8">
+      <c r="A923" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B923" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C923" s="5">
+        <v>3</v>
+      </c>
+      <c r="D923" s="2"/>
+    </row>
+    <row r="924" spans="1:8">
+      <c r="A924" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B924" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C924" s="5">
+        <v>1</v>
+      </c>
+      <c r="D924" s="2"/>
+    </row>
+    <row r="925" spans="1:8">
+      <c r="A925" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B925" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C925" s="5">
+        <v>1</v>
+      </c>
+      <c r="D925" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H925"/>
+  <dimension ref="A1:H940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -14136,13 +14136,15 @@
       <c r="A921" s="6">
         <v>46146</v>
       </c>
-      <c r="B921" s="2" t="s">
-        <v>21</v>
+      <c r="B921" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="C921" s="5">
-        <v>2</v>
-      </c>
-      <c r="D921" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D921" s="2">
+        <v>2</v>
+      </c>
       <c r="G921" s="1"/>
       <c r="H921" s="27"/>
     </row>
@@ -14150,49 +14152,275 @@
       <c r="A922" s="6">
         <v>46146</v>
       </c>
-      <c r="B922" s="20" t="s">
-        <v>2</v>
+      <c r="B922" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="C922" s="5">
-        <v>3</v>
-      </c>
-      <c r="D922" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D922" s="2">
+        <v>2</v>
+      </c>
+      <c r="G922" s="1"/>
+      <c r="H922" s="27"/>
     </row>
     <row r="923" spans="1:8">
       <c r="A923" s="6">
         <v>46146</v>
       </c>
       <c r="B923" s="20" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C923" s="5">
-        <v>3</v>
-      </c>
-      <c r="D923" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D923" s="2">
+        <v>2</v>
+      </c>
+      <c r="G923" s="1"/>
+      <c r="H923" s="27"/>
     </row>
     <row r="924" spans="1:8">
       <c r="A924" s="6">
         <v>46146</v>
       </c>
-      <c r="B924" s="24" t="s">
-        <v>3</v>
+      <c r="B924" s="20" t="s">
+        <v>23</v>
       </c>
       <c r="C924" s="5">
-        <v>1</v>
-      </c>
-      <c r="D924" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D924" s="2">
+        <v>2</v>
+      </c>
+      <c r="G924" s="1"/>
+      <c r="H924" s="27"/>
     </row>
     <row r="925" spans="1:8">
       <c r="A925" s="6">
         <v>46146</v>
       </c>
-      <c r="B925" s="24" t="s">
+      <c r="B925" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C925" s="5">
+        <v>0</v>
+      </c>
+      <c r="D925" s="2">
+        <v>1</v>
+      </c>
+      <c r="G925" s="1"/>
+      <c r="H925" s="27"/>
+    </row>
+    <row r="926" spans="1:8">
+      <c r="A926" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B926" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C926" s="5">
+        <v>0</v>
+      </c>
+      <c r="D926" s="2">
+        <v>1</v>
+      </c>
+      <c r="G926" s="1"/>
+      <c r="H926" s="27"/>
+    </row>
+    <row r="927" spans="1:8">
+      <c r="A927" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C927" s="5">
+        <v>2</v>
+      </c>
+      <c r="D927" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="928" spans="1:8">
+      <c r="A928" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B928" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C928" s="5">
+        <v>3</v>
+      </c>
+      <c r="D928" s="2">
+        <v>1</v>
+      </c>
+      <c r="F928" s="1"/>
+      <c r="G928" s="27"/>
+    </row>
+    <row r="929" spans="1:7">
+      <c r="A929" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B929" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C929" s="5">
+        <v>3</v>
+      </c>
+      <c r="D929" s="2">
+        <v>1</v>
+      </c>
+      <c r="F929" s="1"/>
+      <c r="G929" s="27"/>
+    </row>
+    <row r="930" spans="1:7">
+      <c r="A930" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B930" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C930" s="5">
+        <v>1</v>
+      </c>
+      <c r="D930" s="2">
+        <v>0</v>
+      </c>
+      <c r="F930" s="1"/>
+      <c r="G930" s="27"/>
+    </row>
+    <row r="931" spans="1:7">
+      <c r="A931" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B931" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C925" s="5">
-        <v>1</v>
-      </c>
-      <c r="D925" s="2"/>
+      <c r="C931" s="5">
+        <v>1</v>
+      </c>
+      <c r="D931" s="2">
+        <v>0</v>
+      </c>
+      <c r="F931" s="1"/>
+      <c r="G931" s="27"/>
+    </row>
+    <row r="932" spans="1:7">
+      <c r="A932" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B932" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C932" s="5">
+        <v>1</v>
+      </c>
+      <c r="D932" s="2"/>
+      <c r="F932" s="1"/>
+      <c r="G932" s="27"/>
+    </row>
+    <row r="933" spans="1:7">
+      <c r="A933" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B933" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C933" s="5">
+        <v>1</v>
+      </c>
+      <c r="D933" s="2"/>
+      <c r="F933" s="1"/>
+      <c r="G933" s="27"/>
+    </row>
+    <row r="934" spans="1:7">
+      <c r="A934" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C934" s="5">
+        <v>2</v>
+      </c>
+      <c r="D934" s="2"/>
+      <c r="F934" s="1"/>
+      <c r="G934" s="27"/>
+    </row>
+    <row r="935" spans="1:7">
+      <c r="A935" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B935" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C935" s="5">
+        <v>2</v>
+      </c>
+      <c r="D935" s="2"/>
+      <c r="F935" s="1"/>
+      <c r="G935" s="27"/>
+    </row>
+    <row r="936" spans="1:7">
+      <c r="A936" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B936" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C936" s="5">
+        <v>2</v>
+      </c>
+      <c r="D936" s="2"/>
+    </row>
+    <row r="937" spans="1:7">
+      <c r="A937" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B937" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C937" s="5">
+        <v>2</v>
+      </c>
+      <c r="D937" s="2"/>
+    </row>
+    <row r="938" spans="1:7">
+      <c r="A938" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B938" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C938" s="5">
+        <v>2</v>
+      </c>
+      <c r="D938" s="2"/>
+    </row>
+    <row r="939" spans="1:7">
+      <c r="A939" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B939" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C939" s="5">
+        <v>3</v>
+      </c>
+      <c r="D939" s="2"/>
+    </row>
+    <row r="940" spans="1:7">
+      <c r="A940" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B940" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C940" s="5">
+        <v>3</v>
+      </c>
+      <c r="D940" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H940"/>
+  <dimension ref="A1:H950"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -14310,13 +14310,15 @@
       <c r="A932" s="6">
         <v>46147</v>
       </c>
-      <c r="B932" s="23" t="s">
-        <v>15</v>
+      <c r="B932" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="C932" s="5">
-        <v>1</v>
-      </c>
-      <c r="D932" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D932" s="2">
+        <v>2</v>
+      </c>
       <c r="F932" s="1"/>
       <c r="G932" s="27"/>
     </row>
@@ -14324,13 +14326,15 @@
       <c r="A933" s="6">
         <v>46147</v>
       </c>
-      <c r="B933" s="23" t="s">
-        <v>6</v>
+      <c r="B933" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="C933" s="5">
-        <v>1</v>
-      </c>
-      <c r="D933" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D933" s="2">
+        <v>2</v>
+      </c>
       <c r="F933" s="1"/>
       <c r="G933" s="27"/>
     </row>
@@ -14338,27 +14342,29 @@
       <c r="A934" s="6">
         <v>46147</v>
       </c>
-      <c r="B934" s="2" t="s">
-        <v>21</v>
+      <c r="B934" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C934" s="5">
-        <v>2</v>
-      </c>
-      <c r="D934" s="2"/>
-      <c r="F934" s="1"/>
-      <c r="G934" s="27"/>
+        <v>1</v>
+      </c>
+      <c r="D934" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="935" spans="1:7">
       <c r="A935" s="6">
         <v>46147</v>
       </c>
-      <c r="B935" s="22" t="s">
-        <v>5</v>
+      <c r="B935" s="23" t="s">
+        <v>6</v>
       </c>
       <c r="C935" s="5">
-        <v>2</v>
-      </c>
-      <c r="D935" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D935" s="2">
+        <v>3</v>
+      </c>
       <c r="F935" s="1"/>
       <c r="G935" s="27"/>
     </row>
@@ -14366,61 +14372,207 @@
       <c r="A936" s="6">
         <v>46147</v>
       </c>
-      <c r="B936" s="22" t="s">
-        <v>9</v>
+      <c r="B936" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C936" s="5">
         <v>2</v>
       </c>
-      <c r="D936" s="2"/>
+      <c r="D936" s="2">
+        <v>2</v>
+      </c>
+      <c r="F936" s="1"/>
+      <c r="G936" s="27"/>
     </row>
     <row r="937" spans="1:7">
       <c r="A937" s="6">
         <v>46147</v>
       </c>
-      <c r="B937" s="20" t="s">
-        <v>4</v>
+      <c r="B937" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="C937" s="5">
         <v>2</v>
       </c>
-      <c r="D937" s="2"/>
+      <c r="D937" s="2">
+        <v>0</v>
+      </c>
+      <c r="F937" s="1"/>
+      <c r="G937" s="27"/>
     </row>
     <row r="938" spans="1:7">
       <c r="A938" s="6">
         <v>46147</v>
       </c>
-      <c r="B938" s="20" t="s">
-        <v>23</v>
+      <c r="B938" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="C938" s="5">
         <v>2</v>
       </c>
-      <c r="D938" s="2"/>
+      <c r="D938" s="2">
+        <v>0</v>
+      </c>
+      <c r="F938" s="1"/>
+      <c r="G938" s="27"/>
     </row>
     <row r="939" spans="1:7">
       <c r="A939" s="6">
         <v>46147</v>
       </c>
-      <c r="B939" s="17" t="s">
-        <v>2</v>
+      <c r="B939" s="20" t="s">
+        <v>4</v>
       </c>
       <c r="C939" s="5">
-        <v>3</v>
-      </c>
-      <c r="D939" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D939" s="2">
+        <v>0</v>
+      </c>
+      <c r="F939" s="1"/>
+      <c r="G939" s="27"/>
     </row>
     <row r="940" spans="1:7">
       <c r="A940" s="6">
         <v>46147</v>
       </c>
-      <c r="B940" s="17" t="s">
+      <c r="B940" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C940" s="5">
+        <v>2</v>
+      </c>
+      <c r="D940" s="2">
+        <v>0</v>
+      </c>
+      <c r="F940" s="1"/>
+      <c r="G940" s="27"/>
+    </row>
+    <row r="941" spans="1:7">
+      <c r="A941" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B941" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C941" s="5">
+        <v>3</v>
+      </c>
+      <c r="D941" s="2">
+        <v>1</v>
+      </c>
+      <c r="F941" s="1"/>
+      <c r="G941" s="27"/>
+    </row>
+    <row r="942" spans="1:7">
+      <c r="A942" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B942" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C940" s="5">
-        <v>3</v>
-      </c>
-      <c r="D940" s="2"/>
+      <c r="C942" s="5">
+        <v>3</v>
+      </c>
+      <c r="D942" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943" spans="1:7">
+      <c r="A943" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B943" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C943" s="5">
+        <v>5</v>
+      </c>
+      <c r="D943" s="2"/>
+    </row>
+    <row r="944" spans="1:7">
+      <c r="A944" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B944" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C944" s="5">
+        <v>5</v>
+      </c>
+      <c r="D944" s="2"/>
+    </row>
+    <row r="945" spans="1:4">
+      <c r="A945" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B945" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C945" s="5">
+        <v>4</v>
+      </c>
+      <c r="D945" s="2"/>
+    </row>
+    <row r="946" spans="1:4">
+      <c r="A946" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B946" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C946" s="5">
+        <v>4</v>
+      </c>
+      <c r="D946" s="2"/>
+    </row>
+    <row r="947" spans="1:4">
+      <c r="A947" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B947" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C947" s="5">
+        <v>5</v>
+      </c>
+      <c r="D947" s="2"/>
+    </row>
+    <row r="948" spans="1:4">
+      <c r="A948" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B948" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C948" s="5">
+        <v>5</v>
+      </c>
+      <c r="D948" s="2"/>
+    </row>
+    <row r="949" spans="1:4">
+      <c r="A949" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B949" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C949" s="5">
+        <v>2</v>
+      </c>
+      <c r="D949" s="2"/>
+    </row>
+    <row r="950" spans="1:4">
+      <c r="A950" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B950" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C950" s="5">
+        <v>2</v>
+      </c>
+      <c r="D950" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H950"/>
+  <dimension ref="A1:H960"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -14488,7 +14488,9 @@
       <c r="C943" s="5">
         <v>5</v>
       </c>
-      <c r="D943" s="2"/>
+      <c r="D943" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="944" spans="1:7">
       <c r="A944" s="6">
@@ -14500,7 +14502,9 @@
       <c r="C944" s="5">
         <v>5</v>
       </c>
-      <c r="D944" s="2"/>
+      <c r="D944" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="945" spans="1:4">
       <c r="A945" s="6">
@@ -14512,7 +14516,9 @@
       <c r="C945" s="5">
         <v>4</v>
       </c>
-      <c r="D945" s="2"/>
+      <c r="D945" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="946" spans="1:4">
       <c r="A946" s="6">
@@ -14524,7 +14530,9 @@
       <c r="C946" s="5">
         <v>4</v>
       </c>
-      <c r="D946" s="2"/>
+      <c r="D946" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="947" spans="1:4">
       <c r="A947" s="6">
@@ -14536,7 +14544,9 @@
       <c r="C947" s="5">
         <v>5</v>
       </c>
-      <c r="D947" s="2"/>
+      <c r="D947" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="948" spans="1:4">
       <c r="A948" s="6">
@@ -14548,7 +14558,9 @@
       <c r="C948" s="5">
         <v>5</v>
       </c>
-      <c r="D948" s="2"/>
+      <c r="D948" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="949" spans="1:4">
       <c r="A949" s="6">
@@ -14560,7 +14572,9 @@
       <c r="C949" s="5">
         <v>2</v>
       </c>
-      <c r="D949" s="2"/>
+      <c r="D949" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="950" spans="1:4">
       <c r="A950" s="6">
@@ -14572,7 +14586,129 @@
       <c r="C950" s="5">
         <v>2</v>
       </c>
-      <c r="D950" s="2"/>
+      <c r="D950" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4">
+      <c r="A951" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B951" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C951" s="5">
+        <v>2</v>
+      </c>
+      <c r="D951" s="2"/>
+    </row>
+    <row r="952" spans="1:4">
+      <c r="A952" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B952" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C952" s="5">
+        <v>2</v>
+      </c>
+      <c r="D952" s="2"/>
+    </row>
+    <row r="953" spans="1:4">
+      <c r="A953" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B953" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C953" s="5">
+        <v>2</v>
+      </c>
+      <c r="D953" s="2"/>
+    </row>
+    <row r="954" spans="1:4">
+      <c r="A954" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B954" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C954" s="2">
+        <v>2</v>
+      </c>
+      <c r="D954" s="2"/>
+    </row>
+    <row r="955" spans="1:4">
+      <c r="A955" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B955" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C955" s="2">
+        <v>5</v>
+      </c>
+      <c r="D955" s="2"/>
+    </row>
+    <row r="956" spans="1:4">
+      <c r="A956" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B956" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C956" s="2">
+        <v>5</v>
+      </c>
+      <c r="D956" s="2"/>
+    </row>
+    <row r="957" spans="1:4">
+      <c r="A957" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B957" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C957" s="2">
+        <v>2</v>
+      </c>
+      <c r="D957" s="2"/>
+    </row>
+    <row r="958" spans="1:4">
+      <c r="A958" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B958" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C958" s="2">
+        <v>2</v>
+      </c>
+      <c r="D958" s="2"/>
+    </row>
+    <row r="959" spans="1:4">
+      <c r="A959" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B959" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C959" s="2">
+        <v>2</v>
+      </c>
+      <c r="D959" s="2"/>
+    </row>
+    <row r="960" spans="1:4">
+      <c r="A960" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B960" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C960" s="2">
+        <v>2</v>
+      </c>
+      <c r="D960" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H960"/>
+  <dimension ref="A1:H972"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -14506,7 +14506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="945" spans="1:4">
+    <row r="945" spans="1:7">
       <c r="A945" s="6">
         <v>46148</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="946" spans="1:4">
+    <row r="946" spans="1:7">
       <c r="A946" s="6">
         <v>46148</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="947" spans="1:4">
+    <row r="947" spans="1:7">
       <c r="A947" s="6">
         <v>46148</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="948" spans="1:4">
+    <row r="948" spans="1:7">
       <c r="A948" s="6">
         <v>46148</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="949" spans="1:4">
+    <row r="949" spans="1:7">
       <c r="A949" s="6">
         <v>46148</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="950" spans="1:4">
+    <row r="950" spans="1:7">
       <c r="A950" s="6">
         <v>46148</v>
       </c>
@@ -14590,125 +14590,313 @@
         <v>0</v>
       </c>
     </row>
-    <row r="951" spans="1:4">
+    <row r="951" spans="1:7">
       <c r="A951" s="6">
         <v>46149</v>
       </c>
-      <c r="B951" s="17" t="s">
-        <v>2</v>
+      <c r="B951" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C951" s="5">
-        <v>2</v>
-      </c>
-      <c r="D951" s="2"/>
-    </row>
-    <row r="952" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D951" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="952" spans="1:7">
       <c r="A952" s="6">
         <v>46149</v>
       </c>
-      <c r="B952" s="17" t="s">
-        <v>11</v>
+      <c r="B952" s="23" t="s">
+        <v>6</v>
       </c>
       <c r="C952" s="5">
-        <v>2</v>
-      </c>
-      <c r="D952" s="2"/>
-    </row>
-    <row r="953" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D952" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="953" spans="1:7">
       <c r="A953" s="6">
         <v>46149</v>
       </c>
-      <c r="B953" s="8" t="s">
-        <v>10</v>
+      <c r="B953" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C953" s="5">
-        <v>2</v>
-      </c>
-      <c r="D953" s="2"/>
-    </row>
-    <row r="954" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D953" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="954" spans="1:7">
       <c r="A954" s="6">
         <v>46149</v>
       </c>
-      <c r="B954" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C954" s="2">
-        <v>2</v>
-      </c>
-      <c r="D954" s="2"/>
-    </row>
-    <row r="955" spans="1:4">
+      <c r="B954" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C954" s="5">
+        <v>2</v>
+      </c>
+      <c r="D954" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="955" spans="1:7">
       <c r="A955" s="6">
         <v>46149</v>
       </c>
-      <c r="B955" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C955" s="2">
-        <v>5</v>
-      </c>
-      <c r="D955" s="2"/>
-    </row>
-    <row r="956" spans="1:4">
+      <c r="B955" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C955" s="5">
+        <v>2</v>
+      </c>
+      <c r="D955" s="2">
+        <v>5</v>
+      </c>
+      <c r="F955" s="1"/>
+      <c r="G955" s="27"/>
+    </row>
+    <row r="956" spans="1:7">
       <c r="A956" s="6">
         <v>46149</v>
       </c>
-      <c r="B956" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C956" s="2">
-        <v>5</v>
-      </c>
-      <c r="D956" s="2"/>
-    </row>
-    <row r="957" spans="1:4">
+      <c r="B956" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C956" s="5">
+        <v>2</v>
+      </c>
+      <c r="D956" s="2">
+        <v>4</v>
+      </c>
+      <c r="F956" s="1"/>
+      <c r="G956" s="27"/>
+    </row>
+    <row r="957" spans="1:7">
       <c r="A957" s="6">
         <v>46149</v>
       </c>
-      <c r="B957" s="20" t="s">
-        <v>4</v>
+      <c r="B957" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C957" s="2">
         <v>2</v>
       </c>
-      <c r="D957" s="2"/>
-    </row>
-    <row r="958" spans="1:4">
+      <c r="D957" s="2">
+        <v>4</v>
+      </c>
+      <c r="F957" s="1"/>
+      <c r="G957" s="27"/>
+    </row>
+    <row r="958" spans="1:7">
       <c r="A958" s="6">
         <v>46149</v>
       </c>
-      <c r="B958" s="20" t="s">
-        <v>23</v>
+      <c r="B958" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="C958" s="2">
-        <v>2</v>
-      </c>
-      <c r="D958" s="2"/>
-    </row>
-    <row r="959" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D958" s="2">
+        <v>4</v>
+      </c>
+      <c r="F958" s="1"/>
+      <c r="G958" s="27"/>
+    </row>
+    <row r="959" spans="1:7">
       <c r="A959" s="6">
         <v>46149</v>
       </c>
-      <c r="B959" s="18" t="s">
-        <v>13</v>
+      <c r="B959" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="C959" s="2">
-        <v>2</v>
-      </c>
-      <c r="D959" s="2"/>
-    </row>
-    <row r="960" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D959" s="2">
+        <v>4</v>
+      </c>
+      <c r="F959" s="1"/>
+      <c r="G959" s="27"/>
+    </row>
+    <row r="960" spans="1:7">
       <c r="A960" s="6">
         <v>46149</v>
       </c>
-      <c r="B960" s="18" t="s">
+      <c r="B960" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C960" s="2">
+        <v>2</v>
+      </c>
+      <c r="D960" s="2">
+        <v>0</v>
+      </c>
+      <c r="F960" s="1"/>
+      <c r="G960" s="27"/>
+    </row>
+    <row r="961" spans="1:7">
+      <c r="A961" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B961" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C961" s="2">
+        <v>2</v>
+      </c>
+      <c r="D961" s="2">
+        <v>0</v>
+      </c>
+      <c r="F961" s="1"/>
+      <c r="G961" s="27"/>
+    </row>
+    <row r="962" spans="1:7">
+      <c r="A962" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B962" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C962" s="2">
+        <v>2</v>
+      </c>
+      <c r="D962" s="2">
+        <v>2</v>
+      </c>
+      <c r="F962" s="1"/>
+      <c r="G962" s="27"/>
+    </row>
+    <row r="963" spans="1:7">
+      <c r="A963" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B963" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C960" s="2">
-        <v>2</v>
-      </c>
-      <c r="D960" s="2"/>
+      <c r="C963" s="2">
+        <v>2</v>
+      </c>
+      <c r="D963" s="2">
+        <v>2</v>
+      </c>
+      <c r="F963" s="1"/>
+      <c r="G963" s="27"/>
+    </row>
+    <row r="964" spans="1:7">
+      <c r="A964" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B964" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C964" s="5">
+        <v>1</v>
+      </c>
+      <c r="D964" s="2"/>
+    </row>
+    <row r="965" spans="1:7">
+      <c r="A965" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B965" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C965" s="5">
+        <v>1</v>
+      </c>
+      <c r="D965" s="2"/>
+    </row>
+    <row r="966" spans="1:7">
+      <c r="A966" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C966" s="5">
+        <v>1</v>
+      </c>
+      <c r="D966" s="2"/>
+    </row>
+    <row r="967" spans="1:7">
+      <c r="A967" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B967" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C967" s="5">
+        <v>2</v>
+      </c>
+      <c r="D967" s="2"/>
+    </row>
+    <row r="968" spans="1:7">
+      <c r="A968" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B968" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C968" s="5">
+        <v>2</v>
+      </c>
+      <c r="D968" s="2"/>
+    </row>
+    <row r="969" spans="1:7">
+      <c r="A969" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B969" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C969" s="5">
+        <v>6</v>
+      </c>
+      <c r="D969" s="2"/>
+    </row>
+    <row r="970" spans="1:7">
+      <c r="A970" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B970" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C970" s="5">
+        <v>6</v>
+      </c>
+      <c r="D970" s="2"/>
+    </row>
+    <row r="971" spans="1:7">
+      <c r="A971" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B971" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C971" s="5">
+        <v>5</v>
+      </c>
+      <c r="D971" s="2"/>
+    </row>
+    <row r="972" spans="1:7">
+      <c r="A972" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B972" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C972" s="5">
+        <v>5</v>
+      </c>
+      <c r="D972" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H972"/>
+  <dimension ref="A1:H990"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -14794,109 +14794,379 @@
       <c r="A964" s="6">
         <v>46150</v>
       </c>
-      <c r="B964" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C964" s="5">
-        <v>1</v>
-      </c>
-      <c r="D964" s="2"/>
+      <c r="B964" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C964" s="2">
+        <v>0</v>
+      </c>
+      <c r="D964" s="2">
+        <v>1</v>
+      </c>
+      <c r="F964" s="1"/>
+      <c r="G964" s="27"/>
     </row>
     <row r="965" spans="1:7">
       <c r="A965" s="6">
         <v>46150</v>
       </c>
-      <c r="B965" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C965" s="5">
-        <v>1</v>
-      </c>
-      <c r="D965" s="2"/>
+      <c r="B965" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C965" s="2">
+        <v>0</v>
+      </c>
+      <c r="D965" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="966" spans="1:7">
       <c r="A966" s="6">
         <v>46150</v>
       </c>
-      <c r="B966" s="2" t="s">
-        <v>21</v>
+      <c r="B966" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C966" s="5">
         <v>1</v>
       </c>
-      <c r="D966" s="2"/>
+      <c r="D966" s="2">
+        <v>1</v>
+      </c>
+      <c r="F966" s="1"/>
+      <c r="G966" s="27"/>
     </row>
     <row r="967" spans="1:7">
       <c r="A967" s="6">
         <v>46150</v>
       </c>
-      <c r="B967" s="8" t="s">
-        <v>10</v>
+      <c r="B967" s="23" t="s">
+        <v>6</v>
       </c>
       <c r="C967" s="5">
-        <v>2</v>
-      </c>
-      <c r="D967" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D967" s="2">
+        <v>1</v>
+      </c>
+      <c r="F967" s="1"/>
+      <c r="G967" s="27"/>
     </row>
     <row r="968" spans="1:7">
       <c r="A968" s="6">
         <v>46150</v>
       </c>
-      <c r="B968" s="8" t="s">
-        <v>17</v>
+      <c r="B968" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C968" s="5">
-        <v>2</v>
-      </c>
-      <c r="D968" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D968" s="2">
+        <v>5</v>
+      </c>
+      <c r="F968" s="1"/>
+      <c r="G968" s="27"/>
     </row>
     <row r="969" spans="1:7">
       <c r="A969" s="6">
         <v>46150</v>
       </c>
-      <c r="B969" s="22" t="s">
-        <v>5</v>
+      <c r="B969" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C969" s="5">
-        <v>6</v>
-      </c>
-      <c r="D969" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D969" s="2">
+        <v>3</v>
+      </c>
+      <c r="F969" s="1"/>
+      <c r="G969" s="27"/>
     </row>
     <row r="970" spans="1:7">
       <c r="A970" s="6">
         <v>46150</v>
       </c>
-      <c r="B970" s="22" t="s">
-        <v>9</v>
+      <c r="B970" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="C970" s="5">
-        <v>6</v>
-      </c>
-      <c r="D970" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D970" s="2">
+        <v>2</v>
+      </c>
+      <c r="F970" s="1"/>
+      <c r="G970" s="27"/>
     </row>
     <row r="971" spans="1:7">
       <c r="A971" s="6">
         <v>46150</v>
       </c>
-      <c r="B971" s="20" t="s">
-        <v>4</v>
+      <c r="B971" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="C971" s="5">
-        <v>5</v>
-      </c>
-      <c r="D971" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D971" s="2">
+        <v>4</v>
+      </c>
+      <c r="F971" s="1"/>
+      <c r="G971" s="27"/>
     </row>
     <row r="972" spans="1:7">
       <c r="A972" s="6">
         <v>46150</v>
       </c>
-      <c r="B972" s="20" t="s">
+      <c r="B972" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C972" s="5">
+        <v>6</v>
+      </c>
+      <c r="D972" s="2">
+        <v>4</v>
+      </c>
+      <c r="F972" s="1"/>
+      <c r="G972" s="27"/>
+    </row>
+    <row r="973" spans="1:7">
+      <c r="A973" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B973" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C973" s="5">
+        <v>5</v>
+      </c>
+      <c r="D973" s="2">
+        <v>4</v>
+      </c>
+      <c r="F973" s="1"/>
+      <c r="G973" s="27"/>
+    </row>
+    <row r="974" spans="1:7">
+      <c r="A974" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B974" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C972" s="5">
-        <v>5</v>
-      </c>
-      <c r="D972" s="2"/>
+      <c r="C974" s="5">
+        <v>5</v>
+      </c>
+      <c r="D974" s="2">
+        <v>4</v>
+      </c>
+      <c r="F974" s="1"/>
+      <c r="G974" s="27"/>
+    </row>
+    <row r="975" spans="1:7">
+      <c r="A975" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B975" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C975" s="5">
+        <v>7</v>
+      </c>
+      <c r="D975" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="976" spans="1:7">
+      <c r="A976" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B976" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C976" s="5">
+        <v>0</v>
+      </c>
+      <c r="D976" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4">
+      <c r="A977" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B977" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C977" s="5">
+        <v>0</v>
+      </c>
+      <c r="D977" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4">
+      <c r="A978" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C978" s="5">
+        <v>9</v>
+      </c>
+      <c r="D978" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4">
+      <c r="A979" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B979" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C979" s="5">
+        <v>7</v>
+      </c>
+      <c r="D979" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4">
+      <c r="A980" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B980" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C980" s="5">
+        <v>7</v>
+      </c>
+      <c r="D980" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4">
+      <c r="A981" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B981" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C981" s="5">
+        <v>7</v>
+      </c>
+      <c r="D981" s="2"/>
+    </row>
+    <row r="982" spans="1:4">
+      <c r="A982" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B982" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C982" s="5">
+        <v>7</v>
+      </c>
+      <c r="D982" s="2"/>
+    </row>
+    <row r="983" spans="1:4">
+      <c r="A983" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B983" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C983" s="5">
+        <v>2</v>
+      </c>
+      <c r="D983" s="2"/>
+    </row>
+    <row r="984" spans="1:4">
+      <c r="A984" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B984" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C984" s="5">
+        <v>2</v>
+      </c>
+      <c r="D984" s="2"/>
+    </row>
+    <row r="985" spans="1:4">
+      <c r="A985" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B985" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C985" s="5">
+        <v>1</v>
+      </c>
+      <c r="D985" s="2"/>
+    </row>
+    <row r="986" spans="1:4">
+      <c r="A986" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B986" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C986" s="5">
+        <v>1</v>
+      </c>
+      <c r="D986" s="2"/>
+    </row>
+    <row r="987" spans="1:4">
+      <c r="A987" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B987" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C987" s="5">
+        <v>3</v>
+      </c>
+      <c r="D987" s="2"/>
+    </row>
+    <row r="988" spans="1:4">
+      <c r="A988" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B988" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C988" s="5">
+        <v>3</v>
+      </c>
+      <c r="D988" s="2"/>
+    </row>
+    <row r="989" spans="1:4">
+      <c r="A989" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B989" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C989" s="5">
+        <v>2</v>
+      </c>
+      <c r="D989" s="2"/>
+    </row>
+    <row r="990" spans="1:4">
+      <c r="A990" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B990" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C990" s="5">
+        <v>2</v>
+      </c>
+      <c r="D990" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -14997,7 +14997,7 @@
         <v>46151</v>
       </c>
       <c r="B977" s="21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C977" s="5">
         <v>0</v>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H990"/>
+  <dimension ref="A1:H1003"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -14992,7 +14992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="977" spans="1:4">
+    <row r="977" spans="1:7">
       <c r="A977" s="6">
         <v>46151</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="978" spans="1:4">
+    <row r="978" spans="1:7">
       <c r="A978" s="6">
         <v>46151</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="979" spans="1:4">
+    <row r="979" spans="1:7">
       <c r="A979" s="6">
         <v>46151</v>
       </c>
@@ -15034,7 +15034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="980" spans="1:4">
+    <row r="980" spans="1:7">
       <c r="A980" s="6">
         <v>46151</v>
       </c>
@@ -15048,125 +15048,323 @@
         <v>3</v>
       </c>
     </row>
-    <row r="981" spans="1:4">
+    <row r="981" spans="1:7">
       <c r="A981" s="6">
         <v>46153</v>
       </c>
       <c r="B981" s="23" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C981" s="5">
-        <v>7</v>
-      </c>
-      <c r="D981" s="2"/>
-    </row>
-    <row r="982" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D981" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982" spans="1:7">
       <c r="A982" s="6">
         <v>46153</v>
       </c>
       <c r="B982" s="23" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C982" s="5">
-        <v>7</v>
-      </c>
-      <c r="D982" s="2"/>
-    </row>
-    <row r="983" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D982" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7">
       <c r="A983" s="6">
         <v>46153</v>
       </c>
-      <c r="B983" s="21" t="s">
+      <c r="B983" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C983" s="5">
-        <v>2</v>
-      </c>
-      <c r="D983" s="2"/>
-    </row>
-    <row r="984" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D983" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984" spans="1:7">
       <c r="A984" s="6">
         <v>46153</v>
       </c>
-      <c r="B984" s="21" t="s">
-        <v>9</v>
+      <c r="B984" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C984" s="5">
-        <v>2</v>
-      </c>
-      <c r="D984" s="2"/>
-    </row>
-    <row r="985" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D984" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="1:7">
       <c r="A985" s="6">
         <v>46153</v>
       </c>
-      <c r="B985" s="18" t="s">
-        <v>13</v>
+      <c r="B985" s="23" t="s">
+        <v>6</v>
       </c>
       <c r="C985" s="5">
-        <v>1</v>
-      </c>
-      <c r="D985" s="2"/>
-    </row>
-    <row r="986" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D985" s="2">
+        <v>0</v>
+      </c>
+      <c r="F985" s="1"/>
+      <c r="G985" s="27"/>
+    </row>
+    <row r="986" spans="1:7">
       <c r="A986" s="6">
         <v>46153</v>
       </c>
-      <c r="B986" s="18" t="s">
-        <v>8</v>
+      <c r="B986" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="C986" s="5">
-        <v>1</v>
-      </c>
-      <c r="D986" s="2"/>
-    </row>
-    <row r="987" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D986" s="2">
+        <v>1</v>
+      </c>
+      <c r="F986" s="1"/>
+      <c r="G986" s="27"/>
+    </row>
+    <row r="987" spans="1:7">
       <c r="A987" s="6">
         <v>46153</v>
       </c>
-      <c r="B987" s="20" t="s">
-        <v>4</v>
+      <c r="B987" s="21" t="s">
+        <v>9</v>
       </c>
       <c r="C987" s="5">
-        <v>3</v>
-      </c>
-      <c r="D987" s="2"/>
-    </row>
-    <row r="988" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D987" s="2">
+        <v>1</v>
+      </c>
+      <c r="F987" s="1"/>
+      <c r="G987" s="27"/>
+    </row>
+    <row r="988" spans="1:7">
       <c r="A988" s="6">
         <v>46153</v>
       </c>
-      <c r="B988" s="20" t="s">
-        <v>23</v>
+      <c r="B988" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="C988" s="5">
-        <v>3</v>
-      </c>
-      <c r="D988" s="2"/>
-    </row>
-    <row r="989" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D988" s="2">
+        <v>1</v>
+      </c>
+      <c r="F988" s="1"/>
+      <c r="G988" s="27"/>
+    </row>
+    <row r="989" spans="1:7">
       <c r="A989" s="6">
         <v>46153</v>
       </c>
-      <c r="B989" s="8" t="s">
-        <v>10</v>
+      <c r="B989" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="C989" s="5">
-        <v>2</v>
-      </c>
-      <c r="D989" s="2"/>
-    </row>
-    <row r="990" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D989" s="2">
+        <v>1</v>
+      </c>
+      <c r="F989" s="1"/>
+      <c r="G989" s="27"/>
+    </row>
+    <row r="990" spans="1:7">
       <c r="A990" s="6">
         <v>46153</v>
       </c>
-      <c r="B990" s="8" t="s">
+      <c r="B990" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C990" s="5">
+        <v>3</v>
+      </c>
+      <c r="D990" s="2">
+        <v>0</v>
+      </c>
+      <c r="F990" s="1"/>
+      <c r="G990" s="27"/>
+    </row>
+    <row r="991" spans="1:7">
+      <c r="A991" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B991" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C991" s="5">
+        <v>3</v>
+      </c>
+      <c r="D991" s="2">
+        <v>0</v>
+      </c>
+      <c r="F991" s="1"/>
+      <c r="G991" s="27"/>
+    </row>
+    <row r="992" spans="1:7">
+      <c r="A992" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B992" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C992" s="5">
+        <v>2</v>
+      </c>
+      <c r="D992" s="2">
+        <v>3</v>
+      </c>
+      <c r="F992" s="1"/>
+      <c r="G992" s="27"/>
+    </row>
+    <row r="993" spans="1:4">
+      <c r="A993" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B993" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C990" s="5">
-        <v>2</v>
-      </c>
-      <c r="D990" s="2"/>
+      <c r="C993" s="5">
+        <v>2</v>
+      </c>
+      <c r="D993" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4">
+      <c r="A994" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B994" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C994" s="5">
+        <v>1</v>
+      </c>
+      <c r="D994" s="2"/>
+    </row>
+    <row r="995" spans="1:4">
+      <c r="A995" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B995" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C995" s="5">
+        <v>1</v>
+      </c>
+      <c r="D995" s="2"/>
+    </row>
+    <row r="996" spans="1:4">
+      <c r="A996" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B996" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C996" s="5">
+        <v>3</v>
+      </c>
+      <c r="D996" s="2"/>
+    </row>
+    <row r="997" spans="1:4">
+      <c r="A997" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B997" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C997" s="2">
+        <v>3</v>
+      </c>
+      <c r="D997" s="2"/>
+    </row>
+    <row r="998" spans="1:4">
+      <c r="A998" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B998" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C998" s="2">
+        <v>6</v>
+      </c>
+      <c r="D998" s="2"/>
+    </row>
+    <row r="999" spans="1:4">
+      <c r="A999" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B999" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C999" s="2">
+        <v>6</v>
+      </c>
+      <c r="D999" s="2"/>
+    </row>
+    <row r="1000" spans="1:4">
+      <c r="A1000" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B1000" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1000" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1000" s="2"/>
+    </row>
+    <row r="1001" spans="1:4">
+      <c r="A1001" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B1001" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1001" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1001" s="2"/>
+    </row>
+    <row r="1002" spans="1:4">
+      <c r="A1002" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B1002" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1002" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1002" s="2"/>
+    </row>
+    <row r="1003" spans="1:4">
+      <c r="A1003" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B1003" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1003" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1003" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1003"/>
+  <dimension ref="A1:H1010"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -15232,7 +15232,7 @@
       <c r="F992" s="1"/>
       <c r="G992" s="27"/>
     </row>
-    <row r="993" spans="1:4">
+    <row r="993" spans="1:7">
       <c r="A993" s="6">
         <v>46153</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="994" spans="1:4">
+    <row r="994" spans="1:7">
       <c r="A994" s="6">
         <v>46154</v>
       </c>
@@ -15256,9 +15256,11 @@
       <c r="C994" s="5">
         <v>1</v>
       </c>
-      <c r="D994" s="2"/>
-    </row>
-    <row r="995" spans="1:4">
+      <c r="D994" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="995" spans="1:7">
       <c r="A995" s="6">
         <v>46154</v>
       </c>
@@ -15268,9 +15270,13 @@
       <c r="C995" s="5">
         <v>1</v>
       </c>
-      <c r="D995" s="2"/>
-    </row>
-    <row r="996" spans="1:4">
+      <c r="D995" s="2">
+        <v>2</v>
+      </c>
+      <c r="F995" s="1"/>
+      <c r="G995" s="27"/>
+    </row>
+    <row r="996" spans="1:7">
       <c r="A996" s="6">
         <v>46154</v>
       </c>
@@ -15280,9 +15286,13 @@
       <c r="C996" s="5">
         <v>3</v>
       </c>
-      <c r="D996" s="2"/>
-    </row>
-    <row r="997" spans="1:4">
+      <c r="D996" s="2">
+        <v>1</v>
+      </c>
+      <c r="F996" s="1"/>
+      <c r="G996" s="27"/>
+    </row>
+    <row r="997" spans="1:7">
       <c r="A997" s="6">
         <v>46154</v>
       </c>
@@ -15292,9 +15302,13 @@
       <c r="C997" s="2">
         <v>3</v>
       </c>
-      <c r="D997" s="2"/>
-    </row>
-    <row r="998" spans="1:4">
+      <c r="D997" s="2">
+        <v>1</v>
+      </c>
+      <c r="F997" s="1"/>
+      <c r="G997" s="27"/>
+    </row>
+    <row r="998" spans="1:7">
       <c r="A998" s="6">
         <v>46154</v>
       </c>
@@ -15304,9 +15318,13 @@
       <c r="C998" s="2">
         <v>6</v>
       </c>
-      <c r="D998" s="2"/>
-    </row>
-    <row r="999" spans="1:4">
+      <c r="D998" s="2">
+        <v>0</v>
+      </c>
+      <c r="F998" s="1"/>
+      <c r="G998" s="27"/>
+    </row>
+    <row r="999" spans="1:7">
       <c r="A999" s="6">
         <v>46154</v>
       </c>
@@ -15316,9 +15334,13 @@
       <c r="C999" s="2">
         <v>6</v>
       </c>
-      <c r="D999" s="2"/>
-    </row>
-    <row r="1000" spans="1:4">
+      <c r="D999" s="2">
+        <v>0</v>
+      </c>
+      <c r="F999" s="1"/>
+      <c r="G999" s="27"/>
+    </row>
+    <row r="1000" spans="1:7">
       <c r="A1000" s="6">
         <v>46154</v>
       </c>
@@ -15328,9 +15350,13 @@
       <c r="C1000" s="2">
         <v>5</v>
       </c>
-      <c r="D1000" s="2"/>
-    </row>
-    <row r="1001" spans="1:4">
+      <c r="D1000" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1000" s="1"/>
+      <c r="G1000" s="27"/>
+    </row>
+    <row r="1001" spans="1:7">
       <c r="A1001" s="6">
         <v>46154</v>
       </c>
@@ -15340,9 +15366,11 @@
       <c r="C1001" s="2">
         <v>5</v>
       </c>
-      <c r="D1001" s="2"/>
-    </row>
-    <row r="1002" spans="1:4">
+      <c r="D1001" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:7">
       <c r="A1002" s="6">
         <v>46154</v>
       </c>
@@ -15352,9 +15380,11 @@
       <c r="C1002" s="2">
         <v>5</v>
       </c>
-      <c r="D1002" s="2"/>
-    </row>
-    <row r="1003" spans="1:4">
+      <c r="D1002" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:7">
       <c r="A1003" s="6">
         <v>46154</v>
       </c>
@@ -15364,7 +15394,93 @@
       <c r="C1003" s="2">
         <v>5</v>
       </c>
-      <c r="D1003" s="2"/>
+      <c r="D1003" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:7">
+      <c r="A1004" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1004" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1004" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1004" s="2"/>
+    </row>
+    <row r="1005" spans="1:7">
+      <c r="A1005" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1005" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1005" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1005" s="2"/>
+    </row>
+    <row r="1006" spans="1:7">
+      <c r="A1006" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1006" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1006" s="2"/>
+    </row>
+    <row r="1007" spans="1:7">
+      <c r="A1007" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1007" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1007" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1007" s="2"/>
+    </row>
+    <row r="1008" spans="1:7">
+      <c r="A1008" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1008" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1008" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1008" s="2"/>
+    </row>
+    <row r="1009" spans="1:4">
+      <c r="A1009" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1009" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1009" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1009" s="2"/>
+    </row>
+    <row r="1010" spans="1:4">
+      <c r="A1010" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1010" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1010" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1010" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -274,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -312,6 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -607,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1010"/>
+  <dimension ref="A1:H1020"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -15408,7 +15409,9 @@
       <c r="C1004" s="5">
         <v>2</v>
       </c>
-      <c r="D1004" s="2"/>
+      <c r="D1004" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1005" spans="1:7">
       <c r="A1005" s="6">
@@ -15420,7 +15423,11 @@
       <c r="C1005" s="5">
         <v>2</v>
       </c>
-      <c r="D1005" s="2"/>
+      <c r="D1005" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1005" s="1"/>
+      <c r="G1005" s="27"/>
     </row>
     <row r="1006" spans="1:7">
       <c r="A1006" s="6">
@@ -15432,7 +15439,11 @@
       <c r="C1006" s="5">
         <v>2</v>
       </c>
-      <c r="D1006" s="2"/>
+      <c r="D1006" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1006" s="1"/>
+      <c r="G1006" s="27"/>
     </row>
     <row r="1007" spans="1:7">
       <c r="A1007" s="6">
@@ -15444,7 +15455,11 @@
       <c r="C1007" s="5">
         <v>7</v>
       </c>
-      <c r="D1007" s="2"/>
+      <c r="D1007" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1007" s="1"/>
+      <c r="G1007" s="27"/>
     </row>
     <row r="1008" spans="1:7">
       <c r="A1008" s="6">
@@ -15456,9 +15471,13 @@
       <c r="C1008" s="5">
         <v>7</v>
       </c>
-      <c r="D1008" s="2"/>
-    </row>
-    <row r="1009" spans="1:4">
+      <c r="D1008" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1008" s="1"/>
+      <c r="G1008" s="27"/>
+    </row>
+    <row r="1009" spans="1:7">
       <c r="A1009" s="6">
         <v>46155</v>
       </c>
@@ -15468,9 +15487,13 @@
       <c r="C1009" s="5">
         <v>3</v>
       </c>
-      <c r="D1009" s="2"/>
-    </row>
-    <row r="1010" spans="1:4">
+      <c r="D1009" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1009" s="1"/>
+      <c r="G1009" s="27"/>
+    </row>
+    <row r="1010" spans="1:7">
       <c r="A1010" s="6">
         <v>46155</v>
       </c>
@@ -15480,7 +15503,134 @@
       <c r="C1010" s="5">
         <v>3</v>
       </c>
-      <c r="D1010" s="2"/>
+      <c r="D1010" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1010" s="1"/>
+      <c r="G1010" s="27"/>
+    </row>
+    <row r="1011" spans="1:7">
+      <c r="A1011" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1011" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1011" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1011" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1011" s="1"/>
+      <c r="G1011" s="27"/>
+    </row>
+    <row r="1012" spans="1:7">
+      <c r="A1012" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B1012" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1012" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1012" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1012" s="1"/>
+      <c r="G1012" s="27"/>
+    </row>
+    <row r="1013" spans="1:7">
+      <c r="A1013" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1013" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1013" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1013" s="2"/>
+      <c r="F1013" s="1"/>
+      <c r="G1013" s="27"/>
+    </row>
+    <row r="1014" spans="1:7">
+      <c r="A1014" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1014" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1014" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1014" s="2"/>
+      <c r="F1014" s="1"/>
+      <c r="G1014" s="27"/>
+    </row>
+    <row r="1015" spans="1:7">
+      <c r="A1015" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1015" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1015" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1015" s="2"/>
+    </row>
+    <row r="1016" spans="1:7">
+      <c r="A1016" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1016" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1016" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1016" s="2"/>
+    </row>
+    <row r="1017" spans="1:7">
+      <c r="A1017" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1017" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1017" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1017" s="2"/>
+    </row>
+    <row r="1018" spans="1:7">
+      <c r="A1018" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1018" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1018" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1018" s="2"/>
+    </row>
+    <row r="1019" spans="1:7">
+      <c r="A1019" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1019" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1019" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1019" s="2"/>
+    </row>
+    <row r="1020" spans="1:7">
+      <c r="A1020" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -274,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -312,7 +312,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -608,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1020"/>
+  <dimension ref="A1:H1034"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -15477,7 +15476,7 @@
       <c r="F1008" s="1"/>
       <c r="G1008" s="27"/>
     </row>
-    <row r="1009" spans="1:7">
+    <row r="1009" spans="1:8">
       <c r="A1009" s="6">
         <v>46155</v>
       </c>
@@ -15493,7 +15492,7 @@
       <c r="F1009" s="1"/>
       <c r="G1009" s="27"/>
     </row>
-    <row r="1010" spans="1:7">
+    <row r="1010" spans="1:8">
       <c r="A1010" s="6">
         <v>46155</v>
       </c>
@@ -15509,7 +15508,7 @@
       <c r="F1010" s="1"/>
       <c r="G1010" s="27"/>
     </row>
-    <row r="1011" spans="1:7">
+    <row r="1011" spans="1:8">
       <c r="A1011" s="6">
         <v>46155</v>
       </c>
@@ -15523,9 +15522,8 @@
         <v>2</v>
       </c>
       <c r="F1011" s="1"/>
-      <c r="G1011" s="27"/>
-    </row>
-    <row r="1012" spans="1:7">
+    </row>
+    <row r="1012" spans="1:8">
       <c r="A1012" s="6">
         <v>46155</v>
       </c>
@@ -15539,9 +15537,10 @@
         <v>2</v>
       </c>
       <c r="F1012" s="1"/>
-      <c r="G1012" s="27"/>
-    </row>
-    <row r="1013" spans="1:7">
+      <c r="G1012" s="1"/>
+      <c r="H1012" s="27"/>
+    </row>
+    <row r="1013" spans="1:8">
       <c r="A1013" s="6">
         <v>46156</v>
       </c>
@@ -15551,11 +15550,14 @@
       <c r="C1013" s="5">
         <v>9</v>
       </c>
-      <c r="D1013" s="2"/>
+      <c r="D1013" s="2">
+        <v>8</v>
+      </c>
       <c r="F1013" s="1"/>
-      <c r="G1013" s="27"/>
-    </row>
-    <row r="1014" spans="1:7">
+      <c r="G1013" s="1"/>
+      <c r="H1013" s="27"/>
+    </row>
+    <row r="1014" spans="1:8">
       <c r="A1014" s="6">
         <v>46156</v>
       </c>
@@ -15565,11 +15567,14 @@
       <c r="C1014" s="5">
         <v>4</v>
       </c>
-      <c r="D1014" s="2"/>
+      <c r="D1014" s="2">
+        <v>0</v>
+      </c>
       <c r="F1014" s="1"/>
-      <c r="G1014" s="27"/>
-    </row>
-    <row r="1015" spans="1:7">
+      <c r="G1014" s="1"/>
+      <c r="H1014" s="27"/>
+    </row>
+    <row r="1015" spans="1:8">
       <c r="A1015" s="6">
         <v>46156</v>
       </c>
@@ -15579,9 +15584,13 @@
       <c r="C1015" s="5">
         <v>4</v>
       </c>
-      <c r="D1015" s="2"/>
-    </row>
-    <row r="1016" spans="1:7">
+      <c r="D1015" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1015" s="1"/>
+      <c r="H1015" s="27"/>
+    </row>
+    <row r="1016" spans="1:8">
       <c r="A1016" s="6">
         <v>46156</v>
       </c>
@@ -15591,9 +15600,13 @@
       <c r="C1016" s="5">
         <v>5</v>
       </c>
-      <c r="D1016" s="2"/>
-    </row>
-    <row r="1017" spans="1:7">
+      <c r="D1016" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1016" s="1"/>
+      <c r="H1016" s="27"/>
+    </row>
+    <row r="1017" spans="1:8">
       <c r="A1017" s="6">
         <v>46156</v>
       </c>
@@ -15603,9 +15616,13 @@
       <c r="C1017" s="5">
         <v>5</v>
       </c>
-      <c r="D1017" s="2"/>
-    </row>
-    <row r="1018" spans="1:7">
+      <c r="D1017" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1017" s="1"/>
+      <c r="H1017" s="27"/>
+    </row>
+    <row r="1018" spans="1:8">
       <c r="A1018" s="6">
         <v>46156</v>
       </c>
@@ -15615,9 +15632,13 @@
       <c r="C1018" s="5">
         <v>2</v>
       </c>
-      <c r="D1018" s="2"/>
-    </row>
-    <row r="1019" spans="1:7">
+      <c r="D1018" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1018" s="1"/>
+      <c r="H1018" s="27"/>
+    </row>
+    <row r="1019" spans="1:8">
       <c r="A1019" s="6">
         <v>46156</v>
       </c>
@@ -15627,10 +15648,201 @@
       <c r="C1019" s="5">
         <v>2</v>
       </c>
-      <c r="D1019" s="2"/>
-    </row>
-    <row r="1020" spans="1:7">
-      <c r="A1020" s="29"/>
+      <c r="D1019" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:8">
+      <c r="A1020" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1020" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1020" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1020" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:8">
+      <c r="A1021" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1021" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1021" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1021" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:8">
+      <c r="A1022" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1022" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1022" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1022" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:8">
+      <c r="A1023" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1023" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1023" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1023" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:8">
+      <c r="A1024" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1024" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1024" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1024" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4">
+      <c r="A1025" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1025" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1025" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1025" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4">
+      <c r="A1026" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1026" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1026" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1026" s="2"/>
+    </row>
+    <row r="1027" spans="1:4">
+      <c r="A1027" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1027" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1027" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1027" s="2"/>
+    </row>
+    <row r="1028" spans="1:4">
+      <c r="A1028" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1028" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1028" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1028" s="2"/>
+    </row>
+    <row r="1029" spans="1:4">
+      <c r="A1029" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1029" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1029" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1029" s="2"/>
+    </row>
+    <row r="1030" spans="1:4">
+      <c r="A1030" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1030" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1030" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1030" s="2"/>
+    </row>
+    <row r="1031" spans="1:4">
+      <c r="A1031" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1031" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1031" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1031" s="2"/>
+    </row>
+    <row r="1032" spans="1:4">
+      <c r="A1032" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1032" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1032" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1032" s="2"/>
+    </row>
+    <row r="1033" spans="1:4">
+      <c r="A1033" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1033" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1033" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1033" s="2"/>
+    </row>
+    <row r="1034" spans="1:4">
+      <c r="A1034" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B1034" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1034" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1034" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1034"/>
+  <dimension ref="A1:H1045"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -15722,7 +15722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1025" spans="1:4">
+    <row r="1025" spans="1:7">
       <c r="A1025" s="6">
         <v>46156</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1026" spans="1:4">
+    <row r="1026" spans="1:7">
       <c r="A1026" s="6">
         <v>46157</v>
       </c>
@@ -15746,9 +15746,11 @@
       <c r="C1026" s="5">
         <v>3</v>
       </c>
-      <c r="D1026" s="2"/>
-    </row>
-    <row r="1027" spans="1:4">
+      <c r="D1026" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:7">
       <c r="A1027" s="6">
         <v>46157</v>
       </c>
@@ -15758,9 +15760,13 @@
       <c r="C1027" s="5">
         <v>3</v>
       </c>
-      <c r="D1027" s="2"/>
-    </row>
-    <row r="1028" spans="1:4">
+      <c r="D1027" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1027" s="1"/>
+      <c r="G1027" s="27"/>
+    </row>
+    <row r="1028" spans="1:7">
       <c r="A1028" s="6">
         <v>46157</v>
       </c>
@@ -15770,9 +15776,13 @@
       <c r="C1028" s="5">
         <v>4</v>
       </c>
-      <c r="D1028" s="2"/>
-    </row>
-    <row r="1029" spans="1:4">
+      <c r="D1028" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1028" s="1"/>
+      <c r="G1028" s="27"/>
+    </row>
+    <row r="1029" spans="1:7">
       <c r="A1029" s="6">
         <v>46157</v>
       </c>
@@ -15782,9 +15792,13 @@
       <c r="C1029" s="5">
         <v>4</v>
       </c>
-      <c r="D1029" s="2"/>
-    </row>
-    <row r="1030" spans="1:4">
+      <c r="D1029" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1029" s="1"/>
+      <c r="G1029" s="27"/>
+    </row>
+    <row r="1030" spans="1:7">
       <c r="A1030" s="6">
         <v>46157</v>
       </c>
@@ -15794,9 +15808,13 @@
       <c r="C1030" s="5">
         <v>9</v>
       </c>
-      <c r="D1030" s="2"/>
-    </row>
-    <row r="1031" spans="1:4">
+      <c r="D1030" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1030" s="1"/>
+      <c r="G1030" s="27"/>
+    </row>
+    <row r="1031" spans="1:7">
       <c r="A1031" s="6">
         <v>46157</v>
       </c>
@@ -15806,9 +15824,13 @@
       <c r="C1031" s="5">
         <v>9</v>
       </c>
-      <c r="D1031" s="2"/>
-    </row>
-    <row r="1032" spans="1:4">
+      <c r="D1031" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1031" s="1"/>
+      <c r="G1031" s="27"/>
+    </row>
+    <row r="1032" spans="1:7">
       <c r="A1032" s="6">
         <v>46157</v>
       </c>
@@ -15818,9 +15840,11 @@
       <c r="C1032" s="5">
         <v>5</v>
       </c>
-      <c r="D1032" s="2"/>
-    </row>
-    <row r="1033" spans="1:4">
+      <c r="D1032" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:7">
       <c r="A1033" s="6">
         <v>46157</v>
       </c>
@@ -15830,9 +15854,11 @@
       <c r="C1033" s="5">
         <v>5</v>
       </c>
-      <c r="D1033" s="2"/>
-    </row>
-    <row r="1034" spans="1:4">
+      <c r="D1033" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:7">
       <c r="A1034" s="6">
         <v>46157</v>
       </c>
@@ -15842,7 +15868,157 @@
       <c r="C1034" s="5">
         <v>4</v>
       </c>
-      <c r="D1034" s="2"/>
+      <c r="D1034" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:7">
+      <c r="A1035" s="6">
+        <v>46158</v>
+      </c>
+      <c r="B1035" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1035" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1035" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:7">
+      <c r="A1036" s="6">
+        <v>46158</v>
+      </c>
+      <c r="B1036" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1036" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1036" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1036" s="1"/>
+      <c r="G1036" s="27"/>
+    </row>
+    <row r="1037" spans="1:7">
+      <c r="A1037" s="6">
+        <v>46158</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1037" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1037" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1037" s="1"/>
+      <c r="G1037" s="27"/>
+    </row>
+    <row r="1038" spans="1:7">
+      <c r="A1038" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1038" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1038" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1038" s="2"/>
+      <c r="F1038" s="1"/>
+      <c r="G1038" s="27"/>
+    </row>
+    <row r="1039" spans="1:7">
+      <c r="A1039" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1039" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1039" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1039" s="2"/>
+      <c r="F1039" s="1"/>
+      <c r="G1039" s="27"/>
+    </row>
+    <row r="1040" spans="1:7">
+      <c r="A1040" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1040" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1040" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1040" s="2"/>
+      <c r="F1040" s="1"/>
+      <c r="G1040" s="27"/>
+    </row>
+    <row r="1041" spans="1:4">
+      <c r="A1041" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1041" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1041" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1041" s="2"/>
+    </row>
+    <row r="1042" spans="1:4">
+      <c r="A1042" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1042" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1042" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1042" s="2"/>
+    </row>
+    <row r="1043" spans="1:4">
+      <c r="A1043" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1043" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1043" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1043" s="2"/>
+    </row>
+    <row r="1044" spans="1:4">
+      <c r="A1044" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1044" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1044" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1044" s="2"/>
+    </row>
+    <row r="1045" spans="1:4">
+      <c r="A1045" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1045" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1045" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1045" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1045"/>
+  <dimension ref="A1:H1055"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -15922,13 +15922,15 @@
       <c r="A1038" s="6">
         <v>46160</v>
       </c>
-      <c r="B1038" s="17" t="s">
-        <v>5</v>
+      <c r="B1038" s="20" t="s">
+        <v>4</v>
       </c>
       <c r="C1038" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1038" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1038" s="2">
+        <v>2</v>
+      </c>
       <c r="F1038" s="1"/>
       <c r="G1038" s="27"/>
     </row>
@@ -15936,13 +15938,15 @@
       <c r="A1039" s="6">
         <v>46160</v>
       </c>
-      <c r="B1039" s="17" t="s">
-        <v>9</v>
+      <c r="B1039" s="20" t="s">
+        <v>23</v>
       </c>
       <c r="C1039" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1039" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1039" s="2">
+        <v>2</v>
+      </c>
       <c r="F1039" s="1"/>
       <c r="G1039" s="27"/>
     </row>
@@ -15950,75 +15954,234 @@
       <c r="A1040" s="6">
         <v>46160</v>
       </c>
-      <c r="B1040" s="8" t="s">
-        <v>10</v>
+      <c r="B1040" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C1040" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1040" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1040" s="2">
+        <v>1</v>
+      </c>
       <c r="F1040" s="1"/>
       <c r="G1040" s="27"/>
     </row>
-    <row r="1041" spans="1:4">
+    <row r="1041" spans="1:8">
       <c r="A1041" s="6">
         <v>46160</v>
       </c>
-      <c r="B1041" s="8" t="s">
-        <v>7</v>
+      <c r="B1041" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="C1041" s="5">
         <v>1</v>
       </c>
-      <c r="D1041" s="2"/>
-    </row>
-    <row r="1042" spans="1:4">
+      <c r="D1041" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1041" s="1"/>
+    </row>
+    <row r="1042" spans="1:8">
       <c r="A1042" s="6">
         <v>46160</v>
       </c>
-      <c r="B1042" s="13" t="s">
-        <v>13</v>
+      <c r="B1042" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="C1042" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1042" s="2"/>
-    </row>
-    <row r="1043" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D1042" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1042" s="1"/>
+      <c r="G1042" s="1"/>
+      <c r="H1042" s="27"/>
+    </row>
+    <row r="1043" spans="1:8">
       <c r="A1043" s="6">
         <v>46160</v>
       </c>
-      <c r="B1043" s="13" t="s">
-        <v>8</v>
+      <c r="B1043" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C1043" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1043" s="2"/>
-    </row>
-    <row r="1044" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D1043" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1043" s="1"/>
+      <c r="G1043" s="1"/>
+      <c r="H1043" s="27"/>
+    </row>
+    <row r="1044" spans="1:8">
       <c r="A1044" s="6">
         <v>46160</v>
       </c>
-      <c r="B1044" s="23" t="s">
-        <v>3</v>
+      <c r="B1044" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C1044" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1044" s="2"/>
-    </row>
-    <row r="1045" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D1044" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1044" s="1"/>
+      <c r="H1044" s="27"/>
+    </row>
+    <row r="1045" spans="1:8">
       <c r="A1045" s="6">
         <v>46160</v>
       </c>
-      <c r="B1045" s="23" t="s">
+      <c r="B1045" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1045" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1045" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1045" s="1"/>
+      <c r="H1045" s="27"/>
+    </row>
+    <row r="1046" spans="1:8">
+      <c r="A1046" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1046" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1046" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1046" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1046" s="1"/>
+      <c r="H1046" s="27"/>
+    </row>
+    <row r="1047" spans="1:8">
+      <c r="A1047" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1047" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1047" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1047" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1047" s="1"/>
+      <c r="H1047" s="27"/>
+    </row>
+    <row r="1048" spans="1:8">
+      <c r="A1048" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B1048" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C1045" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1045" s="2"/>
+      <c r="C1048" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1048" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1048" s="1"/>
+      <c r="H1048" s="27"/>
+    </row>
+    <row r="1049" spans="1:8">
+      <c r="A1049" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1049" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1049" s="2"/>
+      <c r="G1049" s="1"/>
+      <c r="H1049" s="27"/>
+    </row>
+    <row r="1050" spans="1:8">
+      <c r="A1050" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1050" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1050" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1050" s="2"/>
+      <c r="G1050" s="1"/>
+      <c r="H1050" s="27"/>
+    </row>
+    <row r="1051" spans="1:8">
+      <c r="A1051" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1051" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1051" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1051" s="2"/>
+    </row>
+    <row r="1052" spans="1:8">
+      <c r="A1052" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1052" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1052" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1052" s="2"/>
+    </row>
+    <row r="1053" spans="1:8">
+      <c r="A1053" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1053" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1053" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1053" s="2"/>
+    </row>
+    <row r="1054" spans="1:8">
+      <c r="A1054" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1054" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1054" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1054" s="2"/>
+    </row>
+    <row r="1055" spans="1:8">
+      <c r="A1055" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B1055" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1055" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1055" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,15 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1055"/>
+  <dimension ref="A1:H1065"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -16105,9 +16105,9 @@
       <c r="C1049" s="5">
         <v>3</v>
       </c>
-      <c r="D1049" s="2"/>
-      <c r="G1049" s="1"/>
-      <c r="H1049" s="27"/>
+      <c r="D1049" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1050" spans="1:8">
       <c r="A1050" s="6">
@@ -16119,9 +16119,11 @@
       <c r="C1050" s="5">
         <v>3</v>
       </c>
-      <c r="D1050" s="2"/>
-      <c r="G1050" s="1"/>
-      <c r="H1050" s="27"/>
+      <c r="D1050" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1050" s="1"/>
+      <c r="G1050" s="27"/>
     </row>
     <row r="1051" spans="1:8">
       <c r="A1051" s="6">
@@ -16133,7 +16135,11 @@
       <c r="C1051" s="5">
         <v>3</v>
       </c>
-      <c r="D1051" s="2"/>
+      <c r="D1051" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1051" s="1"/>
+      <c r="G1051" s="27"/>
     </row>
     <row r="1052" spans="1:8">
       <c r="A1052" s="6">
@@ -16145,7 +16151,11 @@
       <c r="C1052" s="5">
         <v>1</v>
       </c>
-      <c r="D1052" s="2"/>
+      <c r="D1052" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1052" s="1"/>
+      <c r="G1052" s="27"/>
     </row>
     <row r="1053" spans="1:8">
       <c r="A1053" s="6">
@@ -16157,7 +16167,11 @@
       <c r="C1053" s="5">
         <v>1</v>
       </c>
-      <c r="D1053" s="2"/>
+      <c r="D1053" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1053" s="1"/>
+      <c r="G1053" s="27"/>
     </row>
     <row r="1054" spans="1:8">
       <c r="A1054" s="6">
@@ -16169,7 +16183,11 @@
       <c r="C1054" s="5">
         <v>2</v>
       </c>
-      <c r="D1054" s="2"/>
+      <c r="D1054" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1054" s="1"/>
+      <c r="G1054" s="27"/>
     </row>
     <row r="1055" spans="1:8">
       <c r="A1055" s="6">
@@ -16181,7 +16199,131 @@
       <c r="C1055" s="5">
         <v>2</v>
       </c>
-      <c r="D1055" s="2"/>
+      <c r="D1055" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1055" s="1"/>
+      <c r="G1055" s="27"/>
+    </row>
+    <row r="1056" spans="1:8">
+      <c r="A1056" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1056" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1056" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1056" s="2"/>
+    </row>
+    <row r="1057" spans="1:4">
+      <c r="A1057" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1057" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1057" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1057" s="2"/>
+    </row>
+    <row r="1058" spans="1:4">
+      <c r="A1058" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1058" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1058" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1058" s="2"/>
+    </row>
+    <row r="1059" spans="1:4">
+      <c r="A1059" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1059" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1059" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1059" s="2"/>
+    </row>
+    <row r="1060" spans="1:4">
+      <c r="A1060" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1060" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1060" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1060" s="2"/>
+    </row>
+    <row r="1061" spans="1:4">
+      <c r="A1061" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1061" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1061" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1061" s="2"/>
+    </row>
+    <row r="1062" spans="1:4">
+      <c r="A1062" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1062" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1062" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1062" s="2"/>
+    </row>
+    <row r="1063" spans="1:4">
+      <c r="A1063" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1063" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1063" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1063" s="2"/>
+    </row>
+    <row r="1064" spans="1:4">
+      <c r="A1064" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1064" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1064" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1064" s="2"/>
+    </row>
+    <row r="1065" spans="1:4">
+      <c r="A1065" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B1065" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1065" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1065" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1065"/>
+  <dimension ref="A1:H1073"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -16215,7 +16215,9 @@
       <c r="C1056" s="5">
         <v>2</v>
       </c>
-      <c r="D1056" s="2"/>
+      <c r="D1056" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1057" spans="1:4">
       <c r="A1057" s="6">
@@ -16227,7 +16229,9 @@
       <c r="C1057" s="5">
         <v>2</v>
       </c>
-      <c r="D1057" s="2"/>
+      <c r="D1057" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1058" spans="1:4">
       <c r="A1058" s="6">
@@ -16239,7 +16243,9 @@
       <c r="C1058" s="5">
         <v>4</v>
       </c>
-      <c r="D1058" s="2"/>
+      <c r="D1058" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1059" spans="1:4">
       <c r="A1059" s="6">
@@ -16251,7 +16257,9 @@
       <c r="C1059" s="5">
         <v>4</v>
       </c>
-      <c r="D1059" s="2"/>
+      <c r="D1059" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1060" spans="1:4">
       <c r="A1060" s="6">
@@ -16263,7 +16271,9 @@
       <c r="C1060" s="5">
         <v>5</v>
       </c>
-      <c r="D1060" s="2"/>
+      <c r="D1060" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1061" spans="1:4">
       <c r="A1061" s="6">
@@ -16275,7 +16285,9 @@
       <c r="C1061" s="2">
         <v>5</v>
       </c>
-      <c r="D1061" s="2"/>
+      <c r="D1061" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1062" spans="1:4">
       <c r="A1062" s="6">
@@ -16287,7 +16299,9 @@
       <c r="C1062" s="2">
         <v>4</v>
       </c>
-      <c r="D1062" s="2"/>
+      <c r="D1062" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1063" spans="1:4">
       <c r="A1063" s="6">
@@ -16299,7 +16313,9 @@
       <c r="C1063" s="2">
         <v>4</v>
       </c>
-      <c r="D1063" s="2"/>
+      <c r="D1063" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1064" spans="1:4">
       <c r="A1064" s="6">
@@ -16311,7 +16327,9 @@
       <c r="C1064" s="2">
         <v>4</v>
       </c>
-      <c r="D1064" s="2"/>
+      <c r="D1064" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1065" spans="1:4">
       <c r="A1065" s="6">
@@ -16323,7 +16341,105 @@
       <c r="C1065" s="2">
         <v>4</v>
       </c>
-      <c r="D1065" s="2"/>
+      <c r="D1065" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4">
+      <c r="A1066" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1066" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1066" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1066" s="2"/>
+    </row>
+    <row r="1067" spans="1:4">
+      <c r="A1067" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1067" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1067" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1067" s="2"/>
+    </row>
+    <row r="1068" spans="1:4">
+      <c r="A1068" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1068" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1068" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1068" s="2"/>
+    </row>
+    <row r="1069" spans="1:4">
+      <c r="A1069" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1069" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1069" s="5">
+        <v>11</v>
+      </c>
+      <c r="D1069" s="2"/>
+    </row>
+    <row r="1070" spans="1:4">
+      <c r="A1070" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1070" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1070" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1070" s="2"/>
+    </row>
+    <row r="1071" spans="1:4">
+      <c r="A1071" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1071" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1071" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1071" s="2"/>
+    </row>
+    <row r="1072" spans="1:4">
+      <c r="A1072" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1072" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1072" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1072" s="2"/>
+    </row>
+    <row r="1073" spans="1:4">
+      <c r="A1073" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1073" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1073" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1073" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1073"/>
+  <dimension ref="A1:H1099"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -16219,7 +16219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1057" spans="1:4">
+    <row r="1057" spans="1:8">
       <c r="A1057" s="6">
         <v>46162</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1058" spans="1:4">
+    <row r="1058" spans="1:8">
       <c r="A1058" s="6">
         <v>46162</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1059" spans="1:4">
+    <row r="1059" spans="1:8">
       <c r="A1059" s="6">
         <v>46162</v>
       </c>
@@ -16261,7 +16261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1060" spans="1:4">
+    <row r="1060" spans="1:8">
       <c r="A1060" s="6">
         <v>46162</v>
       </c>
@@ -16275,7 +16275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1061" spans="1:4">
+    <row r="1061" spans="1:8">
       <c r="A1061" s="6">
         <v>46162</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1062" spans="1:4">
+    <row r="1062" spans="1:8">
       <c r="A1062" s="6">
         <v>46162</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1063" spans="1:4">
+    <row r="1063" spans="1:8">
       <c r="A1063" s="6">
         <v>46162</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1064" spans="1:4">
+    <row r="1064" spans="1:8">
       <c r="A1064" s="6">
         <v>46162</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1065" spans="1:4">
+    <row r="1065" spans="1:8">
       <c r="A1065" s="6">
         <v>46162</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1066" spans="1:4">
+    <row r="1066" spans="1:8">
       <c r="A1066" s="6">
         <v>46163</v>
       </c>
@@ -16355,9 +16355,11 @@
       <c r="C1066" s="5">
         <v>9</v>
       </c>
-      <c r="D1066" s="2"/>
-    </row>
-    <row r="1067" spans="1:4">
+      <c r="D1066" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:8">
       <c r="A1067" s="6">
         <v>46163</v>
       </c>
@@ -16367,9 +16369,13 @@
       <c r="C1067" s="5">
         <v>2</v>
       </c>
-      <c r="D1067" s="2"/>
-    </row>
-    <row r="1068" spans="1:4">
+      <c r="D1067" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1067" s="1"/>
+      <c r="H1067" s="27"/>
+    </row>
+    <row r="1068" spans="1:8">
       <c r="A1068" s="6">
         <v>46163</v>
       </c>
@@ -16379,9 +16385,13 @@
       <c r="C1068" s="5">
         <v>2</v>
       </c>
-      <c r="D1068" s="2"/>
-    </row>
-    <row r="1069" spans="1:4">
+      <c r="D1068" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1068" s="1"/>
+      <c r="H1068" s="27"/>
+    </row>
+    <row r="1069" spans="1:8">
       <c r="A1069" s="6">
         <v>46163</v>
       </c>
@@ -16391,9 +16401,13 @@
       <c r="C1069" s="5">
         <v>11</v>
       </c>
-      <c r="D1069" s="2"/>
-    </row>
-    <row r="1070" spans="1:4">
+      <c r="D1069" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1069" s="1"/>
+      <c r="H1069" s="27"/>
+    </row>
+    <row r="1070" spans="1:8">
       <c r="A1070" s="6">
         <v>46163</v>
       </c>
@@ -16403,9 +16417,13 @@
       <c r="C1070" s="5">
         <v>5</v>
       </c>
-      <c r="D1070" s="2"/>
-    </row>
-    <row r="1071" spans="1:4">
+      <c r="D1070" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1070" s="1"/>
+      <c r="H1070" s="27"/>
+    </row>
+    <row r="1071" spans="1:8">
       <c r="A1071" s="6">
         <v>46163</v>
       </c>
@@ -16415,9 +16433,13 @@
       <c r="C1071" s="5">
         <v>5</v>
       </c>
-      <c r="D1071" s="2"/>
-    </row>
-    <row r="1072" spans="1:4">
+      <c r="D1071" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1071" s="1"/>
+      <c r="H1071" s="27"/>
+    </row>
+    <row r="1072" spans="1:8">
       <c r="A1072" s="6">
         <v>46163</v>
       </c>
@@ -16427,9 +16449,13 @@
       <c r="C1072" s="5">
         <v>7</v>
       </c>
-      <c r="D1072" s="2"/>
-    </row>
-    <row r="1073" spans="1:4">
+      <c r="D1072" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1072" s="1"/>
+      <c r="H1072" s="27"/>
+    </row>
+    <row r="1073" spans="1:8">
       <c r="A1073" s="6">
         <v>46163</v>
       </c>
@@ -16439,7 +16465,391 @@
       <c r="C1073" s="5">
         <v>7</v>
       </c>
-      <c r="D1073" s="2"/>
+      <c r="D1073" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1073" s="1"/>
+      <c r="H1073" s="27"/>
+    </row>
+    <row r="1074" spans="1:8">
+      <c r="A1074" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1074" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1074" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1074" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1074" s="1"/>
+      <c r="H1074" s="27"/>
+    </row>
+    <row r="1075" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A1075" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B1075" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1075" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1075" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1075" s="1"/>
+      <c r="H1075" s="27"/>
+    </row>
+    <row r="1076" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A1076" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1076" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1076" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1076" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1076" s="1"/>
+      <c r="H1076" s="27"/>
+    </row>
+    <row r="1077" spans="1:8">
+      <c r="A1077" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1077" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1077" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1077" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1077" s="1"/>
+      <c r="H1077" s="27"/>
+    </row>
+    <row r="1078" spans="1:8">
+      <c r="A1078" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1078" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1078" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1078" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:8">
+      <c r="A1079" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1079" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1079" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1079" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1079" s="1"/>
+      <c r="G1079" s="27"/>
+    </row>
+    <row r="1080" spans="1:8">
+      <c r="A1080" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1080" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1080" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1080" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1080" s="1"/>
+      <c r="G1080" s="27"/>
+    </row>
+    <row r="1081" spans="1:8">
+      <c r="A1081" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1081" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1081" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1081" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1081" s="1"/>
+      <c r="G1081" s="27"/>
+    </row>
+    <row r="1082" spans="1:8">
+      <c r="A1082" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1082" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1082" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1082" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1082" s="1"/>
+      <c r="G1082" s="27"/>
+    </row>
+    <row r="1083" spans="1:8">
+      <c r="A1083" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1083" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1083" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1083" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1083" s="1"/>
+      <c r="G1083" s="27"/>
+    </row>
+    <row r="1084" spans="1:8">
+      <c r="A1084" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1084" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1084" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1084" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1084" s="1"/>
+      <c r="G1084" s="27"/>
+    </row>
+    <row r="1085" spans="1:8">
+      <c r="A1085" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1085" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1085" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1085" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1085" s="1"/>
+      <c r="G1085" s="27"/>
+    </row>
+    <row r="1086" spans="1:8">
+      <c r="A1086" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B1086" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1086" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1086" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1086" s="1"/>
+      <c r="G1086" s="27"/>
+    </row>
+    <row r="1087" spans="1:8">
+      <c r="A1087" s="6">
+        <v>46165</v>
+      </c>
+      <c r="B1087" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1087" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1087" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:8">
+      <c r="A1088" s="6">
+        <v>46165</v>
+      </c>
+      <c r="B1088" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1088" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1088" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1088" s="1"/>
+      <c r="G1088" s="27"/>
+    </row>
+    <row r="1089" spans="1:7">
+      <c r="A1089" s="6">
+        <v>46165</v>
+      </c>
+      <c r="B1089" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1089" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1089" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1089" s="1"/>
+      <c r="G1089" s="27"/>
+    </row>
+    <row r="1090" spans="1:7">
+      <c r="A1090" s="6">
+        <v>46165</v>
+      </c>
+      <c r="B1090" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1090" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1090" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1090" s="1"/>
+      <c r="G1090" s="27"/>
+    </row>
+    <row r="1091" spans="1:7">
+      <c r="A1091" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1091" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1091" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1091" s="2"/>
+      <c r="F1091" s="1"/>
+      <c r="G1091" s="27"/>
+    </row>
+    <row r="1092" spans="1:7">
+      <c r="A1092" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1092" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1092" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1092" s="2"/>
+      <c r="F1092" s="1"/>
+      <c r="G1092" s="27"/>
+    </row>
+    <row r="1093" spans="1:7">
+      <c r="A1093" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1093" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1093" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1093" s="2"/>
+    </row>
+    <row r="1094" spans="1:7">
+      <c r="A1094" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1094" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1094" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1094" s="2"/>
+    </row>
+    <row r="1095" spans="1:7">
+      <c r="A1095" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1095" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1095" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1095" s="2"/>
+    </row>
+    <row r="1096" spans="1:7">
+      <c r="A1096" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1096" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1096" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1096" s="2"/>
+    </row>
+    <row r="1097" spans="1:7">
+      <c r="A1097" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1097" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1097" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1097" s="2"/>
+    </row>
+    <row r="1098" spans="1:7">
+      <c r="A1098" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1098" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1098" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1098" s="2"/>
+    </row>
+    <row r="1099" spans="1:7">
+      <c r="A1099" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B1099" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1099" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1099" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="28">
   <si>
     <t>Data</t>
   </si>
@@ -607,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1099"/>
+  <dimension ref="A1:H1109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -16749,9 +16749,9 @@
       <c r="C1091" s="5">
         <v>8</v>
       </c>
-      <c r="D1091" s="2"/>
-      <c r="F1091" s="1"/>
-      <c r="G1091" s="27"/>
+      <c r="D1091" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="1092" spans="1:7">
       <c r="A1092" s="6">
@@ -16763,7 +16763,9 @@
       <c r="C1092" s="5">
         <v>5</v>
       </c>
-      <c r="D1092" s="2"/>
+      <c r="D1092" s="2">
+        <v>1</v>
+      </c>
       <c r="F1092" s="1"/>
       <c r="G1092" s="27"/>
     </row>
@@ -16777,7 +16779,11 @@
       <c r="C1093" s="5">
         <v>5</v>
       </c>
-      <c r="D1093" s="2"/>
+      <c r="D1093" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1093" s="1"/>
+      <c r="G1093" s="27"/>
     </row>
     <row r="1094" spans="1:7">
       <c r="A1094" s="6">
@@ -16789,7 +16795,11 @@
       <c r="C1094" s="5">
         <v>2</v>
       </c>
-      <c r="D1094" s="2"/>
+      <c r="D1094" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1094" s="1"/>
+      <c r="G1094" s="27"/>
     </row>
     <row r="1095" spans="1:7">
       <c r="A1095" s="6">
@@ -16801,7 +16811,11 @@
       <c r="C1095" s="5">
         <v>2</v>
       </c>
-      <c r="D1095" s="2"/>
+      <c r="D1095" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1095" s="1"/>
+      <c r="G1095" s="27"/>
     </row>
     <row r="1096" spans="1:7">
       <c r="A1096" s="6">
@@ -16813,7 +16827,11 @@
       <c r="C1096" s="5">
         <v>4</v>
       </c>
-      <c r="D1096" s="2"/>
+      <c r="D1096" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1096" s="1"/>
+      <c r="G1096" s="27"/>
     </row>
     <row r="1097" spans="1:7">
       <c r="A1097" s="6">
@@ -16825,7 +16843,11 @@
       <c r="C1097" s="5">
         <v>4</v>
       </c>
-      <c r="D1097" s="2"/>
+      <c r="D1097" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1097" s="1"/>
+      <c r="G1097" s="27"/>
     </row>
     <row r="1098" spans="1:7">
       <c r="A1098" s="6">
@@ -16837,7 +16859,9 @@
       <c r="C1098" s="5">
         <v>4</v>
       </c>
-      <c r="D1098" s="2"/>
+      <c r="D1098" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1099" spans="1:7">
       <c r="A1099" s="6">
@@ -16849,7 +16873,129 @@
       <c r="C1099" s="5">
         <v>4</v>
       </c>
-      <c r="D1099" s="2"/>
+      <c r="D1099" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:7">
+      <c r="A1100" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1100" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1100" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1100" s="2"/>
+    </row>
+    <row r="1101" spans="1:7">
+      <c r="A1101" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1101" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1101" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1101" s="2"/>
+    </row>
+    <row r="1102" spans="1:7">
+      <c r="A1102" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1102" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1102" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1102" s="2"/>
+    </row>
+    <row r="1103" spans="1:7">
+      <c r="A1103" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1103" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1103" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1103" s="2"/>
+    </row>
+    <row r="1104" spans="1:7">
+      <c r="A1104" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1104" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1104" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1104" s="2"/>
+    </row>
+    <row r="1105" spans="1:4">
+      <c r="A1105" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1105" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1105" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1105" s="2"/>
+    </row>
+    <row r="1106" spans="1:4">
+      <c r="A1106" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1106" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1106" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1106" s="2"/>
+    </row>
+    <row r="1107" spans="1:4">
+      <c r="A1107" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1107" s="5">
+        <v>13</v>
+      </c>
+      <c r="D1107" s="2"/>
+    </row>
+    <row r="1108" spans="1:4">
+      <c r="A1108" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1108" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1108" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1108" s="2"/>
+    </row>
+    <row r="1109" spans="1:4">
+      <c r="A1109" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1109" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1109" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1109" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="29">
   <si>
     <t>Data</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>LITTERI DANIELE</t>
+  </si>
+  <si>
+    <t>BOTTARO ANDREA</t>
   </si>
 </sst>
 </file>
@@ -607,15 +610,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1109"/>
+  <dimension ref="A1:H1123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -16707,7 +16710,7 @@
       <c r="F1088" s="1"/>
       <c r="G1088" s="27"/>
     </row>
-    <row r="1089" spans="1:7">
+    <row r="1089" spans="1:8">
       <c r="A1089" s="6">
         <v>46165</v>
       </c>
@@ -16723,7 +16726,7 @@
       <c r="F1089" s="1"/>
       <c r="G1089" s="27"/>
     </row>
-    <row r="1090" spans="1:7">
+    <row r="1090" spans="1:8">
       <c r="A1090" s="6">
         <v>46165</v>
       </c>
@@ -16739,7 +16742,7 @@
       <c r="F1090" s="1"/>
       <c r="G1090" s="27"/>
     </row>
-    <row r="1091" spans="1:7">
+    <row r="1091" spans="1:8">
       <c r="A1091" s="6">
         <v>46167</v>
       </c>
@@ -16753,7 +16756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1092" spans="1:7">
+    <row r="1092" spans="1:8">
       <c r="A1092" s="6">
         <v>46167</v>
       </c>
@@ -16769,7 +16772,7 @@
       <c r="F1092" s="1"/>
       <c r="G1092" s="27"/>
     </row>
-    <row r="1093" spans="1:7">
+    <row r="1093" spans="1:8">
       <c r="A1093" s="6">
         <v>46167</v>
       </c>
@@ -16785,7 +16788,7 @@
       <c r="F1093" s="1"/>
       <c r="G1093" s="27"/>
     </row>
-    <row r="1094" spans="1:7">
+    <row r="1094" spans="1:8">
       <c r="A1094" s="6">
         <v>46167</v>
       </c>
@@ -16801,7 +16804,7 @@
       <c r="F1094" s="1"/>
       <c r="G1094" s="27"/>
     </row>
-    <row r="1095" spans="1:7">
+    <row r="1095" spans="1:8">
       <c r="A1095" s="6">
         <v>46167</v>
       </c>
@@ -16817,7 +16820,7 @@
       <c r="F1095" s="1"/>
       <c r="G1095" s="27"/>
     </row>
-    <row r="1096" spans="1:7">
+    <row r="1096" spans="1:8">
       <c r="A1096" s="6">
         <v>46167</v>
       </c>
@@ -16833,7 +16836,7 @@
       <c r="F1096" s="1"/>
       <c r="G1096" s="27"/>
     </row>
-    <row r="1097" spans="1:7">
+    <row r="1097" spans="1:8">
       <c r="A1097" s="6">
         <v>46167</v>
       </c>
@@ -16849,7 +16852,7 @@
       <c r="F1097" s="1"/>
       <c r="G1097" s="27"/>
     </row>
-    <row r="1098" spans="1:7">
+    <row r="1098" spans="1:8">
       <c r="A1098" s="6">
         <v>46167</v>
       </c>
@@ -16863,7 +16866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1099" spans="1:7">
+    <row r="1099" spans="1:8">
       <c r="A1099" s="6">
         <v>46167</v>
       </c>
@@ -16877,7 +16880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1100" spans="1:7">
+    <row r="1100" spans="1:8">
       <c r="A1100" s="6">
         <v>46168</v>
       </c>
@@ -16887,9 +16890,11 @@
       <c r="C1100" s="5">
         <v>5</v>
       </c>
-      <c r="D1100" s="2"/>
-    </row>
-    <row r="1101" spans="1:7">
+      <c r="D1100" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:8">
       <c r="A1101" s="6">
         <v>46168</v>
       </c>
@@ -16899,9 +16904,11 @@
       <c r="C1101" s="5">
         <v>5</v>
       </c>
-      <c r="D1101" s="2"/>
-    </row>
-    <row r="1102" spans="1:7">
+      <c r="D1101" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:8">
       <c r="A1102" s="6">
         <v>46168</v>
       </c>
@@ -16911,9 +16918,13 @@
       <c r="C1102" s="5">
         <v>1</v>
       </c>
-      <c r="D1102" s="2"/>
-    </row>
-    <row r="1103" spans="1:7">
+      <c r="D1102" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1102" s="1"/>
+      <c r="H1102" s="27"/>
+    </row>
+    <row r="1103" spans="1:8">
       <c r="A1103" s="6">
         <v>46168</v>
       </c>
@@ -16923,9 +16934,13 @@
       <c r="C1103" s="5">
         <v>5</v>
       </c>
-      <c r="D1103" s="2"/>
-    </row>
-    <row r="1104" spans="1:7">
+      <c r="D1103" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1103" s="1"/>
+      <c r="H1103" s="27"/>
+    </row>
+    <row r="1104" spans="1:8">
       <c r="A1104" s="6">
         <v>46168</v>
       </c>
@@ -16935,9 +16950,13 @@
       <c r="C1104" s="5">
         <v>5</v>
       </c>
-      <c r="D1104" s="2"/>
-    </row>
-    <row r="1105" spans="1:4">
+      <c r="D1104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1104" s="1"/>
+      <c r="H1104" s="27"/>
+    </row>
+    <row r="1105" spans="1:8">
       <c r="A1105" s="6">
         <v>46168</v>
       </c>
@@ -16947,9 +16966,13 @@
       <c r="C1105" s="5">
         <v>4</v>
       </c>
-      <c r="D1105" s="2"/>
-    </row>
-    <row r="1106" spans="1:4">
+      <c r="D1105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1105" s="1"/>
+      <c r="H1105" s="27"/>
+    </row>
+    <row r="1106" spans="1:8">
       <c r="A1106" s="6">
         <v>46168</v>
       </c>
@@ -16959,9 +16982,13 @@
       <c r="C1106" s="5">
         <v>4</v>
       </c>
-      <c r="D1106" s="2"/>
-    </row>
-    <row r="1107" spans="1:4">
+      <c r="D1106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1106" s="1"/>
+      <c r="H1106" s="27"/>
+    </row>
+    <row r="1107" spans="1:8">
       <c r="A1107" s="6">
         <v>46168</v>
       </c>
@@ -16971,9 +16998,13 @@
       <c r="C1107" s="5">
         <v>13</v>
       </c>
-      <c r="D1107" s="2"/>
-    </row>
-    <row r="1108" spans="1:4">
+      <c r="D1107" s="2">
+        <v>9</v>
+      </c>
+      <c r="G1107" s="1"/>
+      <c r="H1107" s="27"/>
+    </row>
+    <row r="1108" spans="1:8">
       <c r="A1108" s="6">
         <v>46168</v>
       </c>
@@ -16983,9 +17014,13 @@
       <c r="C1108" s="5">
         <v>5</v>
       </c>
-      <c r="D1108" s="2"/>
-    </row>
-    <row r="1109" spans="1:4">
+      <c r="D1108" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1108" s="1"/>
+      <c r="H1108" s="27"/>
+    </row>
+    <row r="1109" spans="1:8">
       <c r="A1109" s="6">
         <v>46168</v>
       </c>
@@ -16995,7 +17030,185 @@
       <c r="C1109" s="5">
         <v>5</v>
       </c>
-      <c r="D1109" s="2"/>
+      <c r="D1109" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:8">
+      <c r="A1110" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1110" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1110" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1110" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:8">
+      <c r="A1111" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1111" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1111" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1111" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:8">
+      <c r="A1112" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1112" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1112" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1112" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:8">
+      <c r="A1113" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B1113" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1113" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1113" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:8">
+      <c r="A1114" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1114" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1114" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1114" s="2"/>
+    </row>
+    <row r="1115" spans="1:8">
+      <c r="A1115" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1115" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1115" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1115" s="2"/>
+    </row>
+    <row r="1116" spans="1:8">
+      <c r="A1116" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1116" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1116" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1116" s="2"/>
+    </row>
+    <row r="1117" spans="1:8">
+      <c r="A1117" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1117" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1117" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1117" s="2"/>
+    </row>
+    <row r="1118" spans="1:8">
+      <c r="A1118" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1118" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1118" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1118" s="2"/>
+    </row>
+    <row r="1119" spans="1:8">
+      <c r="A1119" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1119" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1119" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1119" s="2"/>
+    </row>
+    <row r="1120" spans="1:8">
+      <c r="A1120" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1120" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1120" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1120" s="2"/>
+    </row>
+    <row r="1121" spans="1:4">
+      <c r="A1121" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1121" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1121" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1121" s="2"/>
+    </row>
+    <row r="1122" spans="1:4">
+      <c r="A1122" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1122" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1122" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1122" s="2"/>
+    </row>
+    <row r="1123" spans="1:4">
+      <c r="A1123" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1123" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1123" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>BOTTARO ANDREA</t>
+  </si>
+  <si>
+    <t>VITTORIO FRANCESCO</t>
   </si>
 </sst>
 </file>
@@ -610,15 +613,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1123"/>
+  <dimension ref="A1:H1148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -17094,121 +17097,493 @@
       <c r="A1114" s="6">
         <v>46169</v>
       </c>
-      <c r="B1114" s="17" t="s">
-        <v>15</v>
+      <c r="B1114" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="C1114" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1114" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1114" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1115" spans="1:8">
       <c r="A1115" s="6">
         <v>46169</v>
       </c>
-      <c r="B1115" s="17" t="s">
-        <v>6</v>
+      <c r="B1115" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="C1115" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1115" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1115" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1116" spans="1:8">
       <c r="A1116" s="6">
         <v>46169</v>
       </c>
-      <c r="B1116" s="20" t="s">
-        <v>21</v>
+      <c r="B1116" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="C1116" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1116" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D1116" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1117" spans="1:8">
       <c r="A1117" s="6">
         <v>46169</v>
       </c>
-      <c r="B1117" s="20" t="s">
-        <v>11</v>
+      <c r="B1117" s="17" t="s">
+        <v>6</v>
       </c>
       <c r="C1117" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1117" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D1117" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1117" s="1"/>
+      <c r="H1117" s="27"/>
     </row>
     <row r="1118" spans="1:8">
       <c r="A1118" s="6">
         <v>46169</v>
       </c>
-      <c r="B1118" s="18" t="s">
-        <v>13</v>
+      <c r="B1118" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C1118" s="5">
-        <v>9</v>
-      </c>
-      <c r="D1118" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D1118" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1118" s="1"/>
+      <c r="H1118" s="27"/>
     </row>
     <row r="1119" spans="1:8">
       <c r="A1119" s="6">
         <v>46169</v>
       </c>
-      <c r="B1119" s="18" t="s">
-        <v>8</v>
+      <c r="B1119" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="C1119" s="5">
-        <v>9</v>
-      </c>
-      <c r="D1119" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D1119" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1119" s="1"/>
+      <c r="H1119" s="27"/>
     </row>
     <row r="1120" spans="1:8">
       <c r="A1120" s="6">
         <v>46169</v>
       </c>
-      <c r="B1120" s="13" t="s">
-        <v>4</v>
+      <c r="B1120" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="C1120" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1120" s="2"/>
-    </row>
-    <row r="1121" spans="1:4">
+        <v>9</v>
+      </c>
+      <c r="D1120" s="2">
+        <v>7</v>
+      </c>
+      <c r="G1120" s="1"/>
+      <c r="H1120" s="27"/>
+    </row>
+    <row r="1121" spans="1:8">
       <c r="A1121" s="6">
         <v>46169</v>
       </c>
-      <c r="B1121" s="13" t="s">
-        <v>23</v>
+      <c r="B1121" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="C1121" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1121" s="2"/>
-    </row>
-    <row r="1122" spans="1:4">
+        <v>9</v>
+      </c>
+      <c r="D1121" s="2">
+        <v>7</v>
+      </c>
+      <c r="G1121" s="1"/>
+      <c r="H1121" s="27"/>
+    </row>
+    <row r="1122" spans="1:8">
       <c r="A1122" s="6">
         <v>46169</v>
       </c>
-      <c r="B1122" s="24" t="s">
-        <v>10</v>
+      <c r="B1122" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="C1122" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1122" s="2"/>
-    </row>
-    <row r="1123" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="D1122" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1122" s="1"/>
+      <c r="H1122" s="27"/>
+    </row>
+    <row r="1123" spans="1:8">
       <c r="A1123" s="6">
         <v>46169</v>
       </c>
-      <c r="B1123" s="24" t="s">
+      <c r="B1123" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1123" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1123" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1123" s="1"/>
+      <c r="H1123" s="27"/>
+    </row>
+    <row r="1124" spans="1:8">
+      <c r="A1124" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1124" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1124" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1124" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:8">
+      <c r="A1125" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B1125" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C1123" s="2">
-        <v>1</v>
-      </c>
-      <c r="D1123" s="2"/>
+      <c r="C1125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1125" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:8">
+      <c r="A1126" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1126" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1126" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1126" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:8">
+      <c r="A1127" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1127" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1127" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1127" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1127" s="1"/>
+      <c r="G1127" s="27"/>
+    </row>
+    <row r="1128" spans="1:8">
+      <c r="A1128" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1128" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1128" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1128" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1128" s="1"/>
+      <c r="G1128" s="27"/>
+    </row>
+    <row r="1129" spans="1:8">
+      <c r="A1129" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1129" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1129" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1129" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1129" s="1"/>
+      <c r="G1129" s="27"/>
+    </row>
+    <row r="1130" spans="1:8">
+      <c r="A1130" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1130" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1130" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1130" s="1"/>
+      <c r="G1130" s="27"/>
+    </row>
+    <row r="1131" spans="1:8">
+      <c r="A1131" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1131" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1131" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1131" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1131" s="1"/>
+      <c r="G1131" s="27"/>
+    </row>
+    <row r="1132" spans="1:8">
+      <c r="A1132" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1132" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1132" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1132" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1132" s="1"/>
+      <c r="G1132" s="27"/>
+    </row>
+    <row r="1133" spans="1:8">
+      <c r="A1133" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1133" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1133" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1133" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:8">
+      <c r="A1134" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1134" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1134" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1134" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:8">
+      <c r="A1135" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1135" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1135" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1135" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:8">
+      <c r="A1136" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B1136" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1136" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1136" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4">
+      <c r="A1137" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1137" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1137" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1137" s="2"/>
+    </row>
+    <row r="1138" spans="1:4">
+      <c r="A1138" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1138" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1138" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1138" s="2"/>
+    </row>
+    <row r="1139" spans="1:4">
+      <c r="A1139" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1139" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1139" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1139" s="2"/>
+    </row>
+    <row r="1140" spans="1:4">
+      <c r="A1140" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1140" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1140" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1140" s="2"/>
+    </row>
+    <row r="1141" spans="1:4">
+      <c r="A1141" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1141" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1141" s="2"/>
+    </row>
+    <row r="1142" spans="1:4">
+      <c r="A1142" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1142" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1142" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1142" s="2"/>
+    </row>
+    <row r="1143" spans="1:4">
+      <c r="A1143" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1143" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1143" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1143" s="2"/>
+    </row>
+    <row r="1144" spans="1:4">
+      <c r="A1144" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1144" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1144" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1144" s="2"/>
+    </row>
+    <row r="1145" spans="1:4">
+      <c r="A1145" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1145" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1145" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1145" s="2"/>
+    </row>
+    <row r="1146" spans="1:4">
+      <c r="A1146" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1146" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1146" s="2"/>
+    </row>
+    <row r="1147" spans="1:4">
+      <c r="A1147" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1147" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1147" s="2"/>
+    </row>
+    <row r="1148" spans="1:4">
+      <c r="A1148" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B1148" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1148" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1148"/>
+  <dimension ref="A1:H1164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -17441,7 +17441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1137" spans="1:4">
+    <row r="1137" spans="1:7">
       <c r="A1137" s="6">
         <v>46171</v>
       </c>
@@ -17451,9 +17451,11 @@
       <c r="C1137" s="2">
         <v>2</v>
       </c>
-      <c r="D1137" s="2"/>
-    </row>
-    <row r="1138" spans="1:4">
+      <c r="D1137" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7">
       <c r="A1138" s="6">
         <v>46171</v>
       </c>
@@ -17463,9 +17465,11 @@
       <c r="C1138" s="2">
         <v>2</v>
       </c>
-      <c r="D1138" s="2"/>
-    </row>
-    <row r="1139" spans="1:4">
+      <c r="D1138" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7">
       <c r="A1139" s="6">
         <v>46171</v>
       </c>
@@ -17475,9 +17479,13 @@
       <c r="C1139" s="2">
         <v>5</v>
       </c>
-      <c r="D1139" s="2"/>
-    </row>
-    <row r="1140" spans="1:4">
+      <c r="D1139" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1139" s="1"/>
+      <c r="G1139" s="27"/>
+    </row>
+    <row r="1140" spans="1:7">
       <c r="A1140" s="6">
         <v>46171</v>
       </c>
@@ -17487,9 +17495,13 @@
       <c r="C1140" s="2">
         <v>5</v>
       </c>
-      <c r="D1140" s="2"/>
-    </row>
-    <row r="1141" spans="1:4">
+      <c r="D1140" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1140" s="1"/>
+      <c r="G1140" s="27"/>
+    </row>
+    <row r="1141" spans="1:7">
       <c r="A1141" s="6">
         <v>46171</v>
       </c>
@@ -17499,9 +17511,13 @@
       <c r="C1141" s="2">
         <v>1</v>
       </c>
-      <c r="D1141" s="2"/>
-    </row>
-    <row r="1142" spans="1:4">
+      <c r="D1141" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1141" s="1"/>
+      <c r="G1141" s="27"/>
+    </row>
+    <row r="1142" spans="1:7">
       <c r="A1142" s="6">
         <v>46171</v>
       </c>
@@ -17511,9 +17527,13 @@
       <c r="C1142" s="2">
         <v>2</v>
       </c>
-      <c r="D1142" s="2"/>
-    </row>
-    <row r="1143" spans="1:4">
+      <c r="D1142" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1142" s="1"/>
+      <c r="G1142" s="27"/>
+    </row>
+    <row r="1143" spans="1:7">
       <c r="A1143" s="6">
         <v>46171</v>
       </c>
@@ -17523,9 +17543,13 @@
       <c r="C1143" s="2">
         <v>2</v>
       </c>
-      <c r="D1143" s="2"/>
-    </row>
-    <row r="1144" spans="1:4">
+      <c r="D1143" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1143" s="1"/>
+      <c r="G1143" s="27"/>
+    </row>
+    <row r="1144" spans="1:7">
       <c r="A1144" s="6">
         <v>46171</v>
       </c>
@@ -17535,9 +17559,13 @@
       <c r="C1144" s="2">
         <v>4</v>
       </c>
-      <c r="D1144" s="2"/>
-    </row>
-    <row r="1145" spans="1:4">
+      <c r="D1144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1144" s="1"/>
+      <c r="G1144" s="27"/>
+    </row>
+    <row r="1145" spans="1:7">
       <c r="A1145" s="6">
         <v>46171</v>
       </c>
@@ -17547,9 +17575,13 @@
       <c r="C1145" s="2">
         <v>4</v>
       </c>
-      <c r="D1145" s="2"/>
-    </row>
-    <row r="1146" spans="1:4">
+      <c r="D1145" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1145" s="1"/>
+      <c r="G1145" s="27"/>
+    </row>
+    <row r="1146" spans="1:7">
       <c r="A1146" s="6">
         <v>46171</v>
       </c>
@@ -17559,9 +17591,11 @@
       <c r="C1146" s="2">
         <v>13</v>
       </c>
-      <c r="D1146" s="2"/>
-    </row>
-    <row r="1147" spans="1:4">
+      <c r="D1146" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:7">
       <c r="A1147" s="6">
         <v>46171</v>
       </c>
@@ -17571,9 +17605,11 @@
       <c r="C1147" s="2">
         <v>1</v>
       </c>
-      <c r="D1147" s="2"/>
-    </row>
-    <row r="1148" spans="1:4">
+      <c r="D1147" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:7">
       <c r="A1148" s="6">
         <v>46171</v>
       </c>
@@ -17583,7 +17619,223 @@
       <c r="C1148" s="2">
         <v>1</v>
       </c>
-      <c r="D1148" s="2"/>
+      <c r="D1148" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:7">
+      <c r="A1149" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B1149" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1149" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1149" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:7">
+      <c r="A1150" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B1150" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1150" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1150" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1150" s="1"/>
+      <c r="G1150" s="27"/>
+    </row>
+    <row r="1151" spans="1:7">
+      <c r="A1151" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B1151" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1151" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1151" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1151" s="1"/>
+      <c r="G1151" s="27"/>
+    </row>
+    <row r="1152" spans="1:7">
+      <c r="A1152" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B1152" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1152" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1152" s="2">
+        <v>18</v>
+      </c>
+      <c r="F1152" s="1"/>
+      <c r="G1152" s="27"/>
+    </row>
+    <row r="1153" spans="1:7">
+      <c r="A1153" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B1153" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1153" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1153" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1153" s="1"/>
+      <c r="G1153" s="27"/>
+    </row>
+    <row r="1154" spans="1:7">
+      <c r="A1154" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1154" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1154" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1154" s="2"/>
+      <c r="F1154" s="1"/>
+      <c r="G1154" s="27"/>
+    </row>
+    <row r="1155" spans="1:7">
+      <c r="A1155" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1155" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1155" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1155" s="2"/>
+      <c r="F1155" s="1"/>
+      <c r="G1155" s="27"/>
+    </row>
+    <row r="1156" spans="1:7">
+      <c r="A1156" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1156" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1156" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1156" s="2"/>
+    </row>
+    <row r="1157" spans="1:7">
+      <c r="A1157" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1157" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1157" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1157" s="2"/>
+    </row>
+    <row r="1158" spans="1:7">
+      <c r="A1158" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1158" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1158" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1158" s="2"/>
+    </row>
+    <row r="1159" spans="1:7">
+      <c r="A1159" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1159" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1159" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1159" s="2"/>
+    </row>
+    <row r="1160" spans="1:7">
+      <c r="A1160" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1160" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1160" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1160" s="2"/>
+    </row>
+    <row r="1161" spans="1:7">
+      <c r="A1161" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1161" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1161" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1161" s="2"/>
+    </row>
+    <row r="1162" spans="1:7">
+      <c r="A1162" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1162" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1162" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1162" s="2"/>
+    </row>
+    <row r="1163" spans="1:7">
+      <c r="A1163" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1163" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1163" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1163" s="2"/>
+    </row>
+    <row r="1164" spans="1:7">
+      <c r="A1164" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1164" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1164" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1164" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -280,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -318,6 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -613,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1164"/>
+  <dimension ref="A1:H1178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -621,7 +622,8 @@
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -17685,7 +17687,7 @@
       <c r="F1152" s="1"/>
       <c r="G1152" s="27"/>
     </row>
-    <row r="1153" spans="1:7">
+    <row r="1153" spans="1:8">
       <c r="A1153" s="6">
         <v>46172</v>
       </c>
@@ -17701,7 +17703,7 @@
       <c r="F1153" s="1"/>
       <c r="G1153" s="27"/>
     </row>
-    <row r="1154" spans="1:7">
+    <row r="1154" spans="1:8">
       <c r="A1154" s="6">
         <v>46174</v>
       </c>
@@ -17711,11 +17713,12 @@
       <c r="C1154" s="5">
         <v>3</v>
       </c>
-      <c r="D1154" s="2"/>
+      <c r="D1154" s="2">
+        <v>3</v>
+      </c>
       <c r="F1154" s="1"/>
-      <c r="G1154" s="27"/>
-    </row>
-    <row r="1155" spans="1:7">
+    </row>
+    <row r="1155" spans="1:8">
       <c r="A1155" s="6">
         <v>46174</v>
       </c>
@@ -17725,11 +17728,14 @@
       <c r="C1155" s="5">
         <v>3</v>
       </c>
-      <c r="D1155" s="2"/>
+      <c r="D1155" s="2">
+        <v>2</v>
+      </c>
       <c r="F1155" s="1"/>
-      <c r="G1155" s="27"/>
-    </row>
-    <row r="1156" spans="1:7">
+      <c r="G1155" s="1"/>
+      <c r="H1155" s="27"/>
+    </row>
+    <row r="1156" spans="1:8">
       <c r="A1156" s="6">
         <v>46174</v>
       </c>
@@ -17739,9 +17745,13 @@
       <c r="C1156" s="5">
         <v>3</v>
       </c>
-      <c r="D1156" s="2"/>
-    </row>
-    <row r="1157" spans="1:7">
+      <c r="D1156" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1156" s="1"/>
+      <c r="H1156" s="27"/>
+    </row>
+    <row r="1157" spans="1:8">
       <c r="A1157" s="6">
         <v>46174</v>
       </c>
@@ -17751,9 +17761,13 @@
       <c r="C1157" s="5">
         <v>4</v>
       </c>
-      <c r="D1157" s="2"/>
-    </row>
-    <row r="1158" spans="1:7">
+      <c r="D1157" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1157" s="1"/>
+      <c r="H1157" s="27"/>
+    </row>
+    <row r="1158" spans="1:8">
       <c r="A1158" s="6">
         <v>46174</v>
       </c>
@@ -17763,9 +17777,13 @@
       <c r="C1158" s="5">
         <v>4</v>
       </c>
-      <c r="D1158" s="2"/>
-    </row>
-    <row r="1159" spans="1:7">
+      <c r="D1158" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1158" s="1"/>
+      <c r="H1158" s="27"/>
+    </row>
+    <row r="1159" spans="1:8">
       <c r="A1159" s="6">
         <v>46174</v>
       </c>
@@ -17775,9 +17793,13 @@
       <c r="C1159" s="5">
         <v>3</v>
       </c>
-      <c r="D1159" s="2"/>
-    </row>
-    <row r="1160" spans="1:7">
+      <c r="D1159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1159" s="1"/>
+      <c r="H1159" s="27"/>
+    </row>
+    <row r="1160" spans="1:8">
       <c r="A1160" s="6">
         <v>46174</v>
       </c>
@@ -17787,9 +17809,13 @@
       <c r="C1160" s="5">
         <v>3</v>
       </c>
-      <c r="D1160" s="2"/>
-    </row>
-    <row r="1161" spans="1:7">
+      <c r="D1160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1160" s="1"/>
+      <c r="H1160" s="27"/>
+    </row>
+    <row r="1161" spans="1:8">
       <c r="A1161" s="6">
         <v>46174</v>
       </c>
@@ -17799,9 +17825,13 @@
       <c r="C1161" s="5">
         <v>3</v>
       </c>
-      <c r="D1161" s="2"/>
-    </row>
-    <row r="1162" spans="1:7">
+      <c r="D1161" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1161" s="1"/>
+      <c r="H1161" s="27"/>
+    </row>
+    <row r="1162" spans="1:8">
       <c r="A1162" s="6">
         <v>46174</v>
       </c>
@@ -17811,9 +17841,13 @@
       <c r="C1162" s="5">
         <v>3</v>
       </c>
-      <c r="D1162" s="2"/>
-    </row>
-    <row r="1163" spans="1:7">
+      <c r="D1162" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1162" s="1"/>
+      <c r="H1162" s="27"/>
+    </row>
+    <row r="1163" spans="1:8">
       <c r="A1163" s="6">
         <v>46174</v>
       </c>
@@ -17823,9 +17857,11 @@
       <c r="C1163" s="5">
         <v>2</v>
       </c>
-      <c r="D1163" s="2"/>
-    </row>
-    <row r="1164" spans="1:7">
+      <c r="D1163" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:8">
       <c r="A1164" s="6">
         <v>46174</v>
       </c>
@@ -17835,7 +17871,172 @@
       <c r="C1164" s="5">
         <v>2</v>
       </c>
-      <c r="D1164" s="2"/>
+      <c r="D1164" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:8">
+      <c r="A1165" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1165" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1165" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1165" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:8">
+      <c r="A1166" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1166" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1166" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1166" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:8">
+      <c r="A1167" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1167" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1167" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1167" s="2"/>
+    </row>
+    <row r="1168" spans="1:8">
+      <c r="A1168" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1168" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1168" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1168" s="2"/>
+    </row>
+    <row r="1169" spans="1:4">
+      <c r="A1169" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1169" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1169" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1169" s="2"/>
+    </row>
+    <row r="1170" spans="1:4">
+      <c r="A1170" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1170" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1170" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1170" s="2"/>
+    </row>
+    <row r="1171" spans="1:4">
+      <c r="A1171" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1171" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1171" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1171" s="2"/>
+    </row>
+    <row r="1172" spans="1:4">
+      <c r="A1172" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1172" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1172" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1172" s="2"/>
+    </row>
+    <row r="1173" spans="1:4">
+      <c r="A1173" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1173" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1173" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1173" s="2"/>
+    </row>
+    <row r="1174" spans="1:4">
+      <c r="A1174" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1174" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1174" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1174" s="2"/>
+    </row>
+    <row r="1175" spans="1:4">
+      <c r="A1175" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1175" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1175" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1175" s="2"/>
+    </row>
+    <row r="1176" spans="1:4">
+      <c r="A1176" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1176" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1176" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1176" s="2"/>
+    </row>
+    <row r="1177" spans="1:4">
+      <c r="A1177" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1177" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1177" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1177" s="2"/>
+    </row>
+    <row r="1178" spans="1:4">
+      <c r="A1178" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -280,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -318,7 +318,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -614,16 +613,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1178"/>
+  <dimension ref="A1:H1187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -17913,7 +17911,9 @@
       <c r="C1167" s="5">
         <v>1</v>
       </c>
-      <c r="D1167" s="2"/>
+      <c r="D1167" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1168" spans="1:8">
       <c r="A1168" s="6">
@@ -17925,9 +17925,13 @@
       <c r="C1168" s="5">
         <v>1</v>
       </c>
-      <c r="D1168" s="2"/>
-    </row>
-    <row r="1169" spans="1:4">
+      <c r="D1168" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1168" s="1"/>
+      <c r="G1168" s="27"/>
+    </row>
+    <row r="1169" spans="1:7">
       <c r="A1169" s="6">
         <v>46176</v>
       </c>
@@ -17937,9 +17941,13 @@
       <c r="C1169" s="5">
         <v>5</v>
       </c>
-      <c r="D1169" s="2"/>
-    </row>
-    <row r="1170" spans="1:4">
+      <c r="D1169" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1169" s="1"/>
+      <c r="G1169" s="27"/>
+    </row>
+    <row r="1170" spans="1:7">
       <c r="A1170" s="6">
         <v>46176</v>
       </c>
@@ -17949,9 +17957,13 @@
       <c r="C1170" s="5">
         <v>4</v>
       </c>
-      <c r="D1170" s="2"/>
-    </row>
-    <row r="1171" spans="1:4">
+      <c r="D1170" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1170" s="1"/>
+      <c r="G1170" s="27"/>
+    </row>
+    <row r="1171" spans="1:7">
       <c r="A1171" s="6">
         <v>46176</v>
       </c>
@@ -17961,9 +17973,13 @@
       <c r="C1171" s="5">
         <v>4</v>
       </c>
-      <c r="D1171" s="2"/>
-    </row>
-    <row r="1172" spans="1:4">
+      <c r="D1171" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1171" s="1"/>
+      <c r="G1171" s="27"/>
+    </row>
+    <row r="1172" spans="1:7">
       <c r="A1172" s="6">
         <v>46176</v>
       </c>
@@ -17973,9 +17989,13 @@
       <c r="C1172" s="5">
         <v>4</v>
       </c>
-      <c r="D1172" s="2"/>
-    </row>
-    <row r="1173" spans="1:4">
+      <c r="D1172" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1172" s="1"/>
+      <c r="G1172" s="27"/>
+    </row>
+    <row r="1173" spans="1:7">
       <c r="A1173" s="6">
         <v>46176</v>
       </c>
@@ -17985,9 +18005,13 @@
       <c r="C1173" s="5">
         <v>4</v>
       </c>
-      <c r="D1173" s="2"/>
-    </row>
-    <row r="1174" spans="1:4">
+      <c r="D1173" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1173" s="1"/>
+      <c r="G1173" s="27"/>
+    </row>
+    <row r="1174" spans="1:7">
       <c r="A1174" s="6">
         <v>46176</v>
       </c>
@@ -17997,9 +18021,13 @@
       <c r="C1174" s="5">
         <v>2</v>
       </c>
-      <c r="D1174" s="2"/>
-    </row>
-    <row r="1175" spans="1:4">
+      <c r="D1174" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1174" s="1"/>
+      <c r="G1174" s="27"/>
+    </row>
+    <row r="1175" spans="1:7">
       <c r="A1175" s="6">
         <v>46176</v>
       </c>
@@ -18009,9 +18037,13 @@
       <c r="C1175" s="5">
         <v>2</v>
       </c>
-      <c r="D1175" s="2"/>
-    </row>
-    <row r="1176" spans="1:4">
+      <c r="D1175" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1175" s="1"/>
+      <c r="G1175" s="27"/>
+    </row>
+    <row r="1176" spans="1:7">
       <c r="A1176" s="6">
         <v>46176</v>
       </c>
@@ -18021,9 +18053,13 @@
       <c r="C1176" s="5">
         <v>2</v>
       </c>
-      <c r="D1176" s="2"/>
-    </row>
-    <row r="1177" spans="1:4">
+      <c r="D1176" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1176" s="1"/>
+      <c r="G1176" s="27"/>
+    </row>
+    <row r="1177" spans="1:7">
       <c r="A1177" s="6">
         <v>46176</v>
       </c>
@@ -18031,12 +18067,135 @@
         <v>11</v>
       </c>
       <c r="C1177" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1177" s="2"/>
-    </row>
-    <row r="1178" spans="1:4">
-      <c r="A1178" s="29"/>
+        <v>2</v>
+      </c>
+      <c r="D1177" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:7">
+      <c r="A1178" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1178" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1178" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1178" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:7">
+      <c r="A1179" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B1179" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1179" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1179" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:7">
+      <c r="A1180" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1180" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1180" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1180" s="2"/>
+    </row>
+    <row r="1181" spans="1:7">
+      <c r="A1181" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1181" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1181" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1181" s="2"/>
+    </row>
+    <row r="1182" spans="1:7">
+      <c r="A1182" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1182" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1182" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1182" s="2"/>
+    </row>
+    <row r="1183" spans="1:7">
+      <c r="A1183" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1183" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1183" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1183" s="2"/>
+    </row>
+    <row r="1184" spans="1:7">
+      <c r="A1184" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1184" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1184" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1184" s="2"/>
+    </row>
+    <row r="1185" spans="1:4">
+      <c r="A1185" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1185" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1185" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1185" s="2"/>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1186" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1186" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1186" s="2"/>
+    </row>
+    <row r="1187" spans="1:4">
+      <c r="A1187" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1187" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1187" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1187" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1187"/>
+  <dimension ref="A1:H1201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -18111,7 +18111,9 @@
       <c r="C1180" s="5">
         <v>3</v>
       </c>
-      <c r="D1180" s="2"/>
+      <c r="D1180" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1181" spans="1:7">
       <c r="A1181" s="6">
@@ -18123,7 +18125,11 @@
       <c r="C1181" s="5">
         <v>3</v>
       </c>
-      <c r="D1181" s="2"/>
+      <c r="D1181" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1181" s="1"/>
+      <c r="G1181" s="27"/>
     </row>
     <row r="1182" spans="1:7">
       <c r="A1182" s="6">
@@ -18135,7 +18141,11 @@
       <c r="C1182" s="2">
         <v>3</v>
       </c>
-      <c r="D1182" s="2"/>
+      <c r="D1182" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1182" s="1"/>
+      <c r="G1182" s="27"/>
     </row>
     <row r="1183" spans="1:7">
       <c r="A1183" s="6">
@@ -18147,7 +18157,11 @@
       <c r="C1183" s="2">
         <v>3</v>
       </c>
-      <c r="D1183" s="2"/>
+      <c r="D1183" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1183" s="1"/>
+      <c r="G1183" s="27"/>
     </row>
     <row r="1184" spans="1:7">
       <c r="A1184" s="6">
@@ -18159,9 +18173,13 @@
       <c r="C1184" s="2">
         <v>4</v>
       </c>
-      <c r="D1184" s="2"/>
-    </row>
-    <row r="1185" spans="1:4">
+      <c r="D1184" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1184" s="1"/>
+      <c r="G1184" s="27"/>
+    </row>
+    <row r="1185" spans="1:7">
       <c r="A1185" s="6">
         <v>46177</v>
       </c>
@@ -18171,9 +18189,13 @@
       <c r="C1185" s="2">
         <v>4</v>
       </c>
-      <c r="D1185" s="2"/>
-    </row>
-    <row r="1186" spans="1:4">
+      <c r="D1185" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1185" s="1"/>
+      <c r="G1185" s="27"/>
+    </row>
+    <row r="1186" spans="1:7">
       <c r="A1186" s="6">
         <v>46177</v>
       </c>
@@ -18183,9 +18205,13 @@
       <c r="C1186" s="2">
         <v>7</v>
       </c>
-      <c r="D1186" s="2"/>
-    </row>
-    <row r="1187" spans="1:4">
+      <c r="D1186" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1186" s="1"/>
+      <c r="G1186" s="27"/>
+    </row>
+    <row r="1187" spans="1:7">
       <c r="A1187" s="6">
         <v>46177</v>
       </c>
@@ -18195,7 +18221,187 @@
       <c r="C1187" s="2">
         <v>7</v>
       </c>
-      <c r="D1187" s="2"/>
+      <c r="D1187" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1187" s="1"/>
+      <c r="G1187" s="27"/>
+    </row>
+    <row r="1188" spans="1:7">
+      <c r="A1188" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1188" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1188" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1188" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:7">
+      <c r="A1189" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1189" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1189" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1189" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:7">
+      <c r="A1190" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1190" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1190" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1190" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:7">
+      <c r="A1191" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B1191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1191" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1191" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:7">
+      <c r="A1192" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1192" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1192" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1192" s="2"/>
+    </row>
+    <row r="1193" spans="1:7">
+      <c r="A1193" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1193" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1193" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1193" s="2"/>
+    </row>
+    <row r="1194" spans="1:7">
+      <c r="A1194" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1194" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1194" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1194" s="2"/>
+    </row>
+    <row r="1195" spans="1:7">
+      <c r="A1195" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1195" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1195" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1195" s="2"/>
+    </row>
+    <row r="1196" spans="1:7">
+      <c r="A1196" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1196" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1196" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1196" s="2"/>
+    </row>
+    <row r="1197" spans="1:7">
+      <c r="A1197" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1197" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1197" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1197" s="2"/>
+    </row>
+    <row r="1198" spans="1:7">
+      <c r="A1198" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1198" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1198" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1198" s="2"/>
+    </row>
+    <row r="1199" spans="1:7">
+      <c r="A1199" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1199" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1199" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1199" s="2"/>
+    </row>
+    <row r="1200" spans="1:7">
+      <c r="A1200" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1200" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1200" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1200" s="2"/>
+    </row>
+    <row r="1201" spans="1:4">
+      <c r="A1201" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1201" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1201" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1201" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1201"/>
+  <dimension ref="A1:H1215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -18293,7 +18293,9 @@
       <c r="C1192" s="5">
         <v>3</v>
       </c>
-      <c r="D1192" s="2"/>
+      <c r="D1192" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1193" spans="1:7">
       <c r="A1193" s="6">
@@ -18305,7 +18307,11 @@
       <c r="C1193" s="5">
         <v>3</v>
       </c>
-      <c r="D1193" s="2"/>
+      <c r="D1193" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1193" s="1"/>
+      <c r="G1193" s="27"/>
     </row>
     <row r="1194" spans="1:7">
       <c r="A1194" s="6">
@@ -18317,7 +18323,11 @@
       <c r="C1194" s="5">
         <v>6</v>
       </c>
-      <c r="D1194" s="2"/>
+      <c r="D1194" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1194" s="1"/>
+      <c r="G1194" s="27"/>
     </row>
     <row r="1195" spans="1:7">
       <c r="A1195" s="6">
@@ -18329,7 +18339,11 @@
       <c r="C1195" s="5">
         <v>6</v>
       </c>
-      <c r="D1195" s="2"/>
+      <c r="D1195" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1195" s="1"/>
+      <c r="G1195" s="27"/>
     </row>
     <row r="1196" spans="1:7">
       <c r="A1196" s="6">
@@ -18341,7 +18355,11 @@
       <c r="C1196" s="5">
         <v>2</v>
       </c>
-      <c r="D1196" s="2"/>
+      <c r="D1196" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1196" s="1"/>
+      <c r="G1196" s="27"/>
     </row>
     <row r="1197" spans="1:7">
       <c r="A1197" s="6">
@@ -18353,7 +18371,11 @@
       <c r="C1197" s="5">
         <v>2</v>
       </c>
-      <c r="D1197" s="2"/>
+      <c r="D1197" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1197" s="1"/>
+      <c r="G1197" s="27"/>
     </row>
     <row r="1198" spans="1:7">
       <c r="A1198" s="6">
@@ -18365,7 +18387,11 @@
       <c r="C1198" s="5">
         <v>5</v>
       </c>
-      <c r="D1198" s="2"/>
+      <c r="D1198" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1198" s="1"/>
+      <c r="G1198" s="27"/>
     </row>
     <row r="1199" spans="1:7">
       <c r="A1199" s="6">
@@ -18377,7 +18403,11 @@
       <c r="C1199" s="5">
         <v>5</v>
       </c>
-      <c r="D1199" s="2"/>
+      <c r="D1199" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1199" s="1"/>
+      <c r="G1199" s="27"/>
     </row>
     <row r="1200" spans="1:7">
       <c r="A1200" s="6">
@@ -18389,9 +18419,13 @@
       <c r="C1200" s="5">
         <v>2</v>
       </c>
-      <c r="D1200" s="2"/>
-    </row>
-    <row r="1201" spans="1:4">
+      <c r="D1200" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1200" s="1"/>
+      <c r="G1200" s="27"/>
+    </row>
+    <row r="1201" spans="1:7">
       <c r="A1201" s="6">
         <v>46178</v>
       </c>
@@ -18401,7 +18435,203 @@
       <c r="C1201" s="5">
         <v>2</v>
       </c>
-      <c r="D1201" s="2"/>
+      <c r="D1201" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:7">
+      <c r="A1202" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1202" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1202" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1202" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:7">
+      <c r="A1203" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B1203" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1203" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1203" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:7">
+      <c r="A1204" s="6">
+        <v>46179</v>
+      </c>
+      <c r="B1204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1204" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1204" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:7">
+      <c r="A1205" s="6">
+        <v>46179</v>
+      </c>
+      <c r="B1205" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1205" s="5">
+        <v>11</v>
+      </c>
+      <c r="D1205" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:7">
+      <c r="A1206" s="6">
+        <v>46179</v>
+      </c>
+      <c r="B1206" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1206" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1206" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1206" s="1"/>
+      <c r="G1206" s="27"/>
+    </row>
+    <row r="1207" spans="1:7">
+      <c r="A1207" s="6">
+        <v>46179</v>
+      </c>
+      <c r="B1207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1207" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1207" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1207" s="1"/>
+      <c r="G1207" s="27"/>
+    </row>
+    <row r="1208" spans="1:7">
+      <c r="A1208" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1208" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1208" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1208" s="2"/>
+      <c r="F1208" s="1"/>
+      <c r="G1208" s="27"/>
+    </row>
+    <row r="1209" spans="1:7">
+      <c r="A1209" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1209" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1209" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1209" s="2"/>
+      <c r="F1209" s="1"/>
+      <c r="G1209" s="27"/>
+    </row>
+    <row r="1210" spans="1:7">
+      <c r="A1210" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1210" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1210" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1210" s="2"/>
+      <c r="F1210" s="1"/>
+      <c r="G1210" s="27"/>
+    </row>
+    <row r="1211" spans="1:7">
+      <c r="A1211" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1211" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1211" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1211" s="2"/>
+      <c r="F1211" s="1"/>
+      <c r="G1211" s="27"/>
+    </row>
+    <row r="1212" spans="1:7">
+      <c r="A1212" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1212" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1212" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1212" s="2"/>
+      <c r="F1212" s="1"/>
+      <c r="G1212" s="27"/>
+    </row>
+    <row r="1213" spans="1:7">
+      <c r="A1213" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1213" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1213" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1213" s="2"/>
+    </row>
+    <row r="1214" spans="1:7">
+      <c r="A1214" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1214" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1214" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1214" s="2"/>
+    </row>
+    <row r="1215" spans="1:7">
+      <c r="A1215" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1215" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1215" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1215" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1215"/>
+  <dimension ref="A1:H1228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -18537,7 +18537,9 @@
       <c r="C1208" s="5">
         <v>2</v>
       </c>
-      <c r="D1208" s="2"/>
+      <c r="D1208" s="2">
+        <v>0</v>
+      </c>
       <c r="F1208" s="1"/>
       <c r="G1208" s="27"/>
     </row>
@@ -18551,7 +18553,9 @@
       <c r="C1209" s="5">
         <v>2</v>
       </c>
-      <c r="D1209" s="2"/>
+      <c r="D1209" s="2">
+        <v>0</v>
+      </c>
       <c r="F1209" s="1"/>
       <c r="G1209" s="27"/>
     </row>
@@ -18565,7 +18569,9 @@
       <c r="C1210" s="5">
         <v>5</v>
       </c>
-      <c r="D1210" s="2"/>
+      <c r="D1210" s="2">
+        <v>1</v>
+      </c>
       <c r="F1210" s="1"/>
       <c r="G1210" s="27"/>
     </row>
@@ -18579,7 +18585,9 @@
       <c r="C1211" s="5">
         <v>5</v>
       </c>
-      <c r="D1211" s="2"/>
+      <c r="D1211" s="2">
+        <v>1</v>
+      </c>
       <c r="F1211" s="1"/>
       <c r="G1211" s="27"/>
     </row>
@@ -18593,7 +18601,9 @@
       <c r="C1212" s="5">
         <v>1</v>
       </c>
-      <c r="D1212" s="2"/>
+      <c r="D1212" s="2">
+        <v>0</v>
+      </c>
       <c r="F1212" s="1"/>
       <c r="G1212" s="27"/>
     </row>
@@ -18607,7 +18617,9 @@
       <c r="C1213" s="5">
         <v>1</v>
       </c>
-      <c r="D1213" s="2"/>
+      <c r="D1213" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1214" spans="1:7">
       <c r="A1214" s="6">
@@ -18619,7 +18631,9 @@
       <c r="C1214" s="5">
         <v>2</v>
       </c>
-      <c r="D1214" s="2"/>
+      <c r="D1214" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1215" spans="1:7">
       <c r="A1215" s="6">
@@ -18631,7 +18645,169 @@
       <c r="C1215" s="5">
         <v>2</v>
       </c>
-      <c r="D1215" s="2"/>
+      <c r="D1215" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:7">
+      <c r="A1216" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1216" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1216" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4">
+      <c r="A1217" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B1217" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1217" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1217" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4">
+      <c r="A1218" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1218" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1218" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1218" s="2"/>
+    </row>
+    <row r="1219" spans="1:4">
+      <c r="A1219" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1219" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1219" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1219" s="2"/>
+    </row>
+    <row r="1220" spans="1:4">
+      <c r="A1220" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1220" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1220" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1220" s="2"/>
+    </row>
+    <row r="1221" spans="1:4">
+      <c r="A1221" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1221" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1221" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1221" s="2"/>
+    </row>
+    <row r="1222" spans="1:4">
+      <c r="A1222" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1222" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1222" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1222" s="2"/>
+    </row>
+    <row r="1223" spans="1:4">
+      <c r="A1223" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1223" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1223" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1223" s="2"/>
+    </row>
+    <row r="1224" spans="1:4">
+      <c r="A1224" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1224" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1224" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1224" s="2"/>
+    </row>
+    <row r="1225" spans="1:4">
+      <c r="A1225" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1225" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1225" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1225" s="2"/>
+    </row>
+    <row r="1226" spans="1:4">
+      <c r="A1226" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1226" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1226" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1226" s="2"/>
+    </row>
+    <row r="1227" spans="1:4">
+      <c r="A1227" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1227" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1227" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1227" s="2"/>
+    </row>
+    <row r="1228" spans="1:4">
+      <c r="A1228" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B1228" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1228" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1228" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1228"/>
+  <dimension ref="A1:H1232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -18663,7 +18663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1217" spans="1:4">
+    <row r="1217" spans="1:7">
       <c r="A1217" s="6">
         <v>46181</v>
       </c>
@@ -18677,7 +18677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1218" spans="1:4">
+    <row r="1218" spans="1:7">
       <c r="A1218" s="6">
         <v>46182</v>
       </c>
@@ -18687,9 +18687,11 @@
       <c r="C1218" s="5">
         <v>7</v>
       </c>
-      <c r="D1218" s="2"/>
-    </row>
-    <row r="1219" spans="1:4">
+      <c r="D1218" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:7">
       <c r="A1219" s="6">
         <v>46182</v>
       </c>
@@ -18699,9 +18701,13 @@
       <c r="C1219" s="5">
         <v>6</v>
       </c>
-      <c r="D1219" s="2"/>
-    </row>
-    <row r="1220" spans="1:4">
+      <c r="D1219" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1219" s="1"/>
+      <c r="G1219" s="27"/>
+    </row>
+    <row r="1220" spans="1:7">
       <c r="A1220" s="6">
         <v>46182</v>
       </c>
@@ -18711,9 +18717,13 @@
       <c r="C1220" s="5">
         <v>6</v>
       </c>
-      <c r="D1220" s="2"/>
-    </row>
-    <row r="1221" spans="1:4">
+      <c r="D1220" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1220" s="1"/>
+      <c r="G1220" s="27"/>
+    </row>
+    <row r="1221" spans="1:7">
       <c r="A1221" s="6">
         <v>46182</v>
       </c>
@@ -18723,9 +18733,13 @@
       <c r="C1221" s="5">
         <v>4</v>
       </c>
-      <c r="D1221" s="2"/>
-    </row>
-    <row r="1222" spans="1:4">
+      <c r="D1221" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1221" s="1"/>
+      <c r="G1221" s="27"/>
+    </row>
+    <row r="1222" spans="1:7">
       <c r="A1222" s="6">
         <v>46182</v>
       </c>
@@ -18735,9 +18749,13 @@
       <c r="C1222" s="5">
         <v>4</v>
       </c>
-      <c r="D1222" s="2"/>
-    </row>
-    <row r="1223" spans="1:4">
+      <c r="D1222" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1222" s="1"/>
+      <c r="G1222" s="27"/>
+    </row>
+    <row r="1223" spans="1:7">
       <c r="A1223" s="6">
         <v>46182</v>
       </c>
@@ -18747,9 +18765,13 @@
       <c r="C1223" s="5">
         <v>1</v>
       </c>
-      <c r="D1223" s="2"/>
-    </row>
-    <row r="1224" spans="1:4">
+      <c r="D1223" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1223" s="1"/>
+      <c r="G1223" s="27"/>
+    </row>
+    <row r="1224" spans="1:7">
       <c r="A1224" s="6">
         <v>46182</v>
       </c>
@@ -18759,9 +18781,13 @@
       <c r="C1224" s="5">
         <v>1</v>
       </c>
-      <c r="D1224" s="2"/>
-    </row>
-    <row r="1225" spans="1:4">
+      <c r="D1224" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1224" s="1"/>
+      <c r="G1224" s="27"/>
+    </row>
+    <row r="1225" spans="1:7">
       <c r="A1225" s="6">
         <v>46182</v>
       </c>
@@ -18771,9 +18797,13 @@
       <c r="C1225" s="5">
         <v>7</v>
       </c>
-      <c r="D1225" s="2"/>
-    </row>
-    <row r="1226" spans="1:4">
+      <c r="D1225" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1225" s="1"/>
+      <c r="G1225" s="27"/>
+    </row>
+    <row r="1226" spans="1:7">
       <c r="A1226" s="6">
         <v>46182</v>
       </c>
@@ -18783,31 +18813,87 @@
       <c r="C1226" s="5">
         <v>7</v>
       </c>
-      <c r="D1226" s="2"/>
-    </row>
-    <row r="1227" spans="1:4">
+      <c r="D1226" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1226" s="1"/>
+      <c r="G1226" s="27"/>
+    </row>
+    <row r="1227" spans="1:7">
       <c r="A1227" s="6">
         <v>46182</v>
       </c>
-      <c r="B1227" s="2" t="s">
+      <c r="B1227" s="20" t="s">
         <v>3</v>
       </c>
       <c r="C1227" s="2">
         <v>4</v>
       </c>
-      <c r="D1227" s="2"/>
-    </row>
-    <row r="1228" spans="1:4">
+      <c r="D1227" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:7">
       <c r="A1228" s="6">
         <v>46182</v>
       </c>
-      <c r="B1228" s="2" t="s">
+      <c r="B1228" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C1228" s="2">
         <v>4</v>
       </c>
-      <c r="D1228" s="2"/>
+      <c r="D1228" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:7">
+      <c r="A1229" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1229" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1229" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1229" s="2"/>
+    </row>
+    <row r="1230" spans="1:7">
+      <c r="A1230" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1230" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1230" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1230" s="2"/>
+    </row>
+    <row r="1231" spans="1:7">
+      <c r="A1231" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1231" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1231" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1231" s="2"/>
+    </row>
+    <row r="1232" spans="1:7">
+      <c r="A1232" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1232" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1232" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1232" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1232"/>
+  <dimension ref="A1:H1244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -18851,49 +18851,219 @@
       <c r="A1229" s="6">
         <v>46183</v>
       </c>
-      <c r="B1229" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1229" s="5">
-        <v>8</v>
-      </c>
-      <c r="D1229" s="2"/>
+      <c r="B1229" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1229" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1229" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1230" spans="1:7">
       <c r="A1230" s="6">
         <v>46183</v>
       </c>
-      <c r="B1230" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1230" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1230" s="2"/>
+      <c r="B1230" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1230" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1230" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1231" spans="1:7">
       <c r="A1231" s="6">
         <v>46183</v>
       </c>
-      <c r="B1231" s="23" t="s">
-        <v>9</v>
+      <c r="B1231" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C1231" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1231" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D1231" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="1232" spans="1:7">
       <c r="A1232" s="6">
         <v>46183</v>
       </c>
-      <c r="B1232" s="2" t="s">
-        <v>4</v>
+      <c r="B1232" s="23" t="s">
+        <v>5</v>
       </c>
       <c r="C1232" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1232" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1232" s="1"/>
+      <c r="G1232" s="27"/>
+    </row>
+    <row r="1233" spans="1:7">
+      <c r="A1233" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1233" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1233" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1233" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1233" s="1"/>
+      <c r="G1233" s="27"/>
+    </row>
+    <row r="1234" spans="1:7">
+      <c r="A1234" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B1234" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1234" s="5">
         <v>10</v>
       </c>
-      <c r="D1232" s="2"/>
+      <c r="D1234" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1234" s="1"/>
+      <c r="G1234" s="27"/>
+    </row>
+    <row r="1235" spans="1:7">
+      <c r="A1235" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1235" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1235" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1235" s="2"/>
+      <c r="F1235" s="1"/>
+      <c r="G1235" s="27"/>
+    </row>
+    <row r="1236" spans="1:7">
+      <c r="A1236" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1236" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1236" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1236" s="2"/>
+      <c r="F1236" s="1"/>
+      <c r="G1236" s="27"/>
+    </row>
+    <row r="1237" spans="1:7">
+      <c r="A1237" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1237" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1237" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1237" s="2"/>
+      <c r="F1237" s="1"/>
+      <c r="G1237" s="27"/>
+    </row>
+    <row r="1238" spans="1:7">
+      <c r="A1238" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1238" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1238" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1238" s="2"/>
+      <c r="F1238" s="1"/>
+      <c r="G1238" s="27"/>
+    </row>
+    <row r="1239" spans="1:7">
+      <c r="A1239" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1239" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1239" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1239" s="2"/>
+    </row>
+    <row r="1240" spans="1:7">
+      <c r="A1240" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1240" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1240" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1240" s="2"/>
+    </row>
+    <row r="1241" spans="1:7">
+      <c r="A1241" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1241" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1241" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1241" s="2"/>
+    </row>
+    <row r="1242" spans="1:7">
+      <c r="A1242" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1242" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1242" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1242" s="2"/>
+    </row>
+    <row r="1243" spans="1:7">
+      <c r="A1243" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1243" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1243" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1243" s="2"/>
+    </row>
+    <row r="1244" spans="1:7">
+      <c r="A1244" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1244" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1244" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1244" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -613,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1244"/>
+  <dimension ref="A1:H1255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -18941,13 +18941,15 @@
       <c r="A1235" s="6">
         <v>46184</v>
       </c>
-      <c r="B1235" s="17" t="s">
-        <v>15</v>
+      <c r="B1235" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="C1235" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1235" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1235" s="2">
+        <v>1</v>
+      </c>
       <c r="F1235" s="1"/>
       <c r="G1235" s="27"/>
     </row>
@@ -18955,13 +18957,15 @@
       <c r="A1236" s="6">
         <v>46184</v>
       </c>
-      <c r="B1236" s="17" t="s">
-        <v>6</v>
+      <c r="B1236" s="22" t="s">
+        <v>19</v>
       </c>
       <c r="C1236" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1236" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1236" s="2">
+        <v>1</v>
+      </c>
       <c r="F1236" s="1"/>
       <c r="G1236" s="27"/>
     </row>
@@ -18969,27 +18973,29 @@
       <c r="A1237" s="6">
         <v>46184</v>
       </c>
-      <c r="B1237" s="2" t="s">
-        <v>13</v>
+      <c r="B1237" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="C1237" s="5">
-        <v>7</v>
-      </c>
-      <c r="D1237" s="2"/>
-      <c r="F1237" s="1"/>
-      <c r="G1237" s="27"/>
+        <v>6</v>
+      </c>
+      <c r="D1237" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1238" spans="1:7">
       <c r="A1238" s="6">
         <v>46184</v>
       </c>
-      <c r="B1238" s="2" t="s">
-        <v>5</v>
+      <c r="B1238" s="17" t="s">
+        <v>6</v>
       </c>
       <c r="C1238" s="5">
-        <v>7</v>
-      </c>
-      <c r="D1238" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D1238" s="2">
+        <v>2</v>
+      </c>
       <c r="F1238" s="1"/>
       <c r="G1238" s="27"/>
     </row>
@@ -18997,73 +19003,239 @@
       <c r="A1239" s="6">
         <v>46184</v>
       </c>
-      <c r="B1239" s="8" t="s">
-        <v>10</v>
+      <c r="B1239" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C1239" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1239" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="D1239" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1239" s="1"/>
+      <c r="G1239" s="27"/>
     </row>
     <row r="1240" spans="1:7">
       <c r="A1240" s="6">
         <v>46184</v>
       </c>
-      <c r="B1240" s="8" t="s">
+      <c r="B1240" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1240" s="5">
         <v>7</v>
       </c>
-      <c r="C1240" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1240" s="2"/>
+      <c r="D1240" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1240" s="1"/>
+      <c r="G1240" s="27"/>
     </row>
     <row r="1241" spans="1:7">
       <c r="A1241" s="6">
         <v>46184</v>
       </c>
-      <c r="B1241" s="13" t="s">
-        <v>4</v>
+      <c r="B1241" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C1241" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1241" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D1241" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1241" s="1"/>
+      <c r="G1241" s="27"/>
     </row>
     <row r="1242" spans="1:7">
       <c r="A1242" s="6">
         <v>46184</v>
       </c>
-      <c r="B1242" s="13" t="s">
-        <v>23</v>
+      <c r="B1242" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C1242" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1242" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D1242" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1242" s="1"/>
+      <c r="G1242" s="27"/>
     </row>
     <row r="1243" spans="1:7">
       <c r="A1243" s="6">
         <v>46184</v>
       </c>
-      <c r="B1243" s="18" t="s">
-        <v>2</v>
+      <c r="B1243" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="C1243" s="5">
         <v>6</v>
       </c>
-      <c r="D1243" s="2"/>
+      <c r="D1243" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1243" s="1"/>
+      <c r="G1243" s="27"/>
     </row>
     <row r="1244" spans="1:7">
       <c r="A1244" s="6">
         <v>46184</v>
       </c>
-      <c r="B1244" s="18" t="s">
+      <c r="B1244" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1244" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1244" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1244" s="1"/>
+      <c r="G1244" s="27"/>
+    </row>
+    <row r="1245" spans="1:7">
+      <c r="A1245" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1245" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1245" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1245" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1245" s="1"/>
+      <c r="G1245" s="27"/>
+    </row>
+    <row r="1246" spans="1:7">
+      <c r="A1246" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B1246" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C1244" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1244" s="2"/>
+      <c r="C1246" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1246" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1246" s="1"/>
+      <c r="G1246" s="27"/>
+    </row>
+    <row r="1247" spans="1:7">
+      <c r="A1247" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1247" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1247" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1247" s="2"/>
+      <c r="F1247" s="1"/>
+      <c r="G1247" s="27"/>
+    </row>
+    <row r="1248" spans="1:7">
+      <c r="A1248" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1248" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1248" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1248" s="2"/>
+    </row>
+    <row r="1249" spans="1:4">
+      <c r="A1249" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1249" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1249" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1249" s="2"/>
+    </row>
+    <row r="1250" spans="1:4">
+      <c r="A1250" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1250" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1250" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1250" s="2"/>
+    </row>
+    <row r="1251" spans="1:4">
+      <c r="A1251" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1251" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1251" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1251" s="2"/>
+    </row>
+    <row r="1252" spans="1:4">
+      <c r="A1252" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1252" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1252" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1252" s="2"/>
+    </row>
+    <row r="1253" spans="1:4">
+      <c r="A1253" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1253" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1253" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1253" s="2"/>
+    </row>
+    <row r="1254" spans="1:4">
+      <c r="A1254" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1254" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1254" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1254" s="2"/>
+    </row>
+    <row r="1255" spans="1:4">
+      <c r="A1255" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1255" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1255" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1255" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>VITTORIO FRANCESCO</t>
+  </si>
+  <si>
+    <t>AMENTA SONNY</t>
   </si>
 </sst>
 </file>
@@ -613,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1255"/>
+  <dimension ref="A1:H1287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -19131,13 +19134,15 @@
       <c r="A1247" s="6">
         <v>46185</v>
       </c>
-      <c r="B1247" s="2" t="s">
-        <v>15</v>
+      <c r="B1247" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="C1247" s="5">
-        <v>9</v>
-      </c>
-      <c r="D1247" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1247" s="2">
+        <v>10</v>
+      </c>
       <c r="F1247" s="1"/>
       <c r="G1247" s="27"/>
     </row>
@@ -19146,96 +19151,588 @@
         <v>46185</v>
       </c>
       <c r="B1248" s="17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C1248" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1248" s="2"/>
-    </row>
-    <row r="1249" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1248" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1248" s="1"/>
+      <c r="G1248" s="27"/>
+    </row>
+    <row r="1249" spans="1:7">
       <c r="A1249" s="6">
         <v>46185</v>
       </c>
-      <c r="B1249" s="17" t="s">
+      <c r="B1249" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1249" s="5">
         <v>9</v>
       </c>
-      <c r="C1249" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1249" s="2"/>
-    </row>
-    <row r="1250" spans="1:4">
+      <c r="D1249" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7">
       <c r="A1250" s="6">
         <v>46185</v>
       </c>
-      <c r="B1250" s="18" t="s">
-        <v>2</v>
+      <c r="B1250" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="C1250" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1250" s="2"/>
-    </row>
-    <row r="1251" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="D1250" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1250" s="1"/>
+      <c r="G1250" s="27"/>
+    </row>
+    <row r="1251" spans="1:7">
       <c r="A1251" s="6">
         <v>46185</v>
       </c>
-      <c r="B1251" s="18" t="s">
-        <v>3</v>
+      <c r="B1251" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="C1251" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1251" s="2"/>
-    </row>
-    <row r="1252" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="D1251" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1251" s="1"/>
+      <c r="G1251" s="27"/>
+    </row>
+    <row r="1252" spans="1:7">
       <c r="A1252" s="6">
         <v>46185</v>
       </c>
-      <c r="B1252" s="13" t="s">
-        <v>4</v>
+      <c r="B1252" s="18" t="s">
+        <v>2</v>
       </c>
       <c r="C1252" s="5">
-        <v>12</v>
-      </c>
-      <c r="D1252" s="2"/>
-    </row>
-    <row r="1253" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="D1252" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1252" s="1"/>
+      <c r="G1252" s="27"/>
+    </row>
+    <row r="1253" spans="1:7">
       <c r="A1253" s="6">
         <v>46185</v>
       </c>
-      <c r="B1253" s="13" t="s">
-        <v>23</v>
+      <c r="B1253" s="18" t="s">
+        <v>3</v>
       </c>
       <c r="C1253" s="5">
-        <v>12</v>
-      </c>
-      <c r="D1253" s="2"/>
-    </row>
-    <row r="1254" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="D1253" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1253" s="1"/>
+      <c r="G1253" s="27"/>
+    </row>
+    <row r="1254" spans="1:7">
       <c r="A1254" s="6">
         <v>46185</v>
       </c>
-      <c r="B1254" s="8" t="s">
-        <v>10</v>
+      <c r="B1254" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="C1254" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1254" s="2"/>
-    </row>
-    <row r="1255" spans="1:4">
+        <v>12</v>
+      </c>
+      <c r="D1254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1254" s="1"/>
+      <c r="G1254" s="27"/>
+    </row>
+    <row r="1255" spans="1:7">
       <c r="A1255" s="6">
         <v>46185</v>
       </c>
-      <c r="B1255" s="8" t="s">
+      <c r="B1255" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1255" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1255" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1255" s="1"/>
+      <c r="G1255" s="27"/>
+    </row>
+    <row r="1256" spans="1:7">
+      <c r="A1256" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1256" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1256" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1256" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1256" s="1"/>
+      <c r="G1256" s="27"/>
+    </row>
+    <row r="1257" spans="1:7">
+      <c r="A1257" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B1257" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C1255" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1255" s="2"/>
+      <c r="C1257" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1257" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1257" s="1"/>
+      <c r="G1257" s="27"/>
+    </row>
+    <row r="1258" spans="1:7">
+      <c r="A1258" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B1258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1258" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1258" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:7">
+      <c r="A1259" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B1259" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1259" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1259" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1259" s="1"/>
+      <c r="G1259" s="27"/>
+    </row>
+    <row r="1260" spans="1:7">
+      <c r="A1260" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B1260" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1260" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1260" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1260" s="1"/>
+      <c r="G1260" s="27"/>
+    </row>
+    <row r="1261" spans="1:7">
+      <c r="A1261" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B1261" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1261" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1261" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1261" s="1"/>
+      <c r="G1261" s="27"/>
+    </row>
+    <row r="1262" spans="1:7">
+      <c r="A1262" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B1262" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1262" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1262" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1262" s="1"/>
+      <c r="G1262" s="27"/>
+    </row>
+    <row r="1263" spans="1:7">
+      <c r="A1263" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1263" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1263" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1263" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:7">
+      <c r="A1264" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1264" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1264" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1264" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1264" s="1"/>
+      <c r="G1264" s="27"/>
+    </row>
+    <row r="1265" spans="1:7">
+      <c r="A1265" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1265" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1265" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1265" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1265" s="1"/>
+      <c r="G1265" s="27"/>
+    </row>
+    <row r="1266" spans="1:7">
+      <c r="A1266" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1266" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1266" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1266" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1266" s="1"/>
+      <c r="G1266" s="27"/>
+    </row>
+    <row r="1267" spans="1:7">
+      <c r="A1267" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1267" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1267" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1267" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1267" s="1"/>
+      <c r="G1267" s="27"/>
+    </row>
+    <row r="1268" spans="1:7">
+      <c r="A1268" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1268" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1268" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1268" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1268" s="1"/>
+      <c r="G1268" s="27"/>
+    </row>
+    <row r="1269" spans="1:7">
+      <c r="A1269" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B1269" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1269" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1269" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:7">
+      <c r="A1270" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1270" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1270" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1270" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:7">
+      <c r="A1271" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1271" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1271" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1271" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:7">
+      <c r="A1272" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1272" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1272" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1272" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:7">
+      <c r="A1273" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1273" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1273" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1273" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1273" s="1"/>
+      <c r="G1273" s="27"/>
+    </row>
+    <row r="1274" spans="1:7">
+      <c r="A1274" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1274" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1274" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1274" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1274" s="1"/>
+      <c r="G1274" s="27"/>
+    </row>
+    <row r="1275" spans="1:7">
+      <c r="A1275" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1275" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1275" s="5">
+        <v>13</v>
+      </c>
+      <c r="D1275" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1275" s="1"/>
+      <c r="G1275" s="27"/>
+    </row>
+    <row r="1276" spans="1:7">
+      <c r="A1276" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1276" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1276" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1276" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1276" s="1"/>
+      <c r="G1276" s="27"/>
+    </row>
+    <row r="1277" spans="1:7">
+      <c r="A1277" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1277" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1277" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1277" s="2"/>
+      <c r="F1277" s="1"/>
+      <c r="G1277" s="27"/>
+    </row>
+    <row r="1278" spans="1:7">
+      <c r="A1278" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1278" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1278" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1278" s="2"/>
+      <c r="F1278" s="1"/>
+      <c r="G1278" s="27"/>
+    </row>
+    <row r="1279" spans="1:7">
+      <c r="A1279" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1279" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1279" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1279" s="2"/>
+      <c r="F1279" s="1"/>
+      <c r="G1279" s="27"/>
+    </row>
+    <row r="1280" spans="1:7">
+      <c r="A1280" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1280" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1280" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1280" s="2"/>
+    </row>
+    <row r="1281" spans="1:4">
+      <c r="A1281" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1281" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1281" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1281" s="2"/>
+    </row>
+    <row r="1282" spans="1:4">
+      <c r="A1282" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1282" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1282" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1282" s="2"/>
+    </row>
+    <row r="1283" spans="1:4">
+      <c r="A1283" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1283" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1283" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1283" s="2"/>
+    </row>
+    <row r="1284" spans="1:4">
+      <c r="A1284" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1284" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1284" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1284" s="2"/>
+    </row>
+    <row r="1285" spans="1:4">
+      <c r="A1285" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1285" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1285" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1285" s="2"/>
+    </row>
+    <row r="1286" spans="1:4">
+      <c r="A1286" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1286" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1286" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1286" s="2"/>
+    </row>
+    <row r="1287" spans="1:4">
+      <c r="A1287" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1287" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1287" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1287" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1287"/>
+  <dimension ref="A1:H1302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -19606,9 +19606,9 @@
       <c r="C1277" s="5">
         <v>3</v>
       </c>
-      <c r="D1277" s="2"/>
-      <c r="F1277" s="1"/>
-      <c r="G1277" s="27"/>
+      <c r="D1277" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1278" spans="1:7">
       <c r="A1278" s="6">
@@ -19620,7 +19620,9 @@
       <c r="C1278" s="5">
         <v>2</v>
       </c>
-      <c r="D1278" s="2"/>
+      <c r="D1278" s="2">
+        <v>0</v>
+      </c>
       <c r="F1278" s="1"/>
       <c r="G1278" s="27"/>
     </row>
@@ -19634,7 +19636,9 @@
       <c r="C1279" s="5">
         <v>2</v>
       </c>
-      <c r="D1279" s="2"/>
+      <c r="D1279" s="2">
+        <v>0</v>
+      </c>
       <c r="F1279" s="1"/>
       <c r="G1279" s="27"/>
     </row>
@@ -19648,9 +19652,13 @@
       <c r="C1280" s="5">
         <v>5</v>
       </c>
-      <c r="D1280" s="2"/>
-    </row>
-    <row r="1281" spans="1:4">
+      <c r="D1280" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1280" s="1"/>
+      <c r="G1280" s="27"/>
+    </row>
+    <row r="1281" spans="1:7">
       <c r="A1281" s="6">
         <v>46190</v>
       </c>
@@ -19660,9 +19668,13 @@
       <c r="C1281" s="5">
         <v>5</v>
       </c>
-      <c r="D1281" s="2"/>
-    </row>
-    <row r="1282" spans="1:4">
+      <c r="D1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1281" s="1"/>
+      <c r="G1281" s="27"/>
+    </row>
+    <row r="1282" spans="1:7">
       <c r="A1282" s="6">
         <v>46190</v>
       </c>
@@ -19672,9 +19684,13 @@
       <c r="C1282" s="5">
         <v>2</v>
       </c>
-      <c r="D1282" s="2"/>
-    </row>
-    <row r="1283" spans="1:4">
+      <c r="D1282" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1282" s="1"/>
+      <c r="G1282" s="27"/>
+    </row>
+    <row r="1283" spans="1:7">
       <c r="A1283" s="6">
         <v>46190</v>
       </c>
@@ -19684,9 +19700,13 @@
       <c r="C1283" s="2">
         <v>2</v>
       </c>
-      <c r="D1283" s="2"/>
-    </row>
-    <row r="1284" spans="1:4">
+      <c r="D1283" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1283" s="1"/>
+      <c r="G1283" s="27"/>
+    </row>
+    <row r="1284" spans="1:7">
       <c r="A1284" s="6">
         <v>46190</v>
       </c>
@@ -19696,9 +19716,13 @@
       <c r="C1284" s="2">
         <v>4</v>
       </c>
-      <c r="D1284" s="2"/>
-    </row>
-    <row r="1285" spans="1:4">
+      <c r="D1284" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1284" s="1"/>
+      <c r="G1284" s="27"/>
+    </row>
+    <row r="1285" spans="1:7">
       <c r="A1285" s="6">
         <v>46190</v>
       </c>
@@ -19708,9 +19732,11 @@
       <c r="C1285" s="2">
         <v>4</v>
       </c>
-      <c r="D1285" s="2"/>
-    </row>
-    <row r="1286" spans="1:4">
+      <c r="D1285" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:7">
       <c r="A1286" s="6">
         <v>46190</v>
       </c>
@@ -19720,9 +19746,11 @@
       <c r="C1286" s="2">
         <v>4</v>
       </c>
-      <c r="D1286" s="2"/>
-    </row>
-    <row r="1287" spans="1:4">
+      <c r="D1286" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7">
       <c r="A1287" s="6">
         <v>46190</v>
       </c>
@@ -19732,7 +19760,193 @@
       <c r="C1287" s="2">
         <v>4</v>
       </c>
-      <c r="D1287" s="2"/>
+      <c r="D1287" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:7">
+      <c r="A1288" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1288" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1288" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1288" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:7">
+      <c r="A1289" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B1289" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1289" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1289" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:7">
+      <c r="A1290" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1290" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1290" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1290" s="2"/>
+    </row>
+    <row r="1291" spans="1:7">
+      <c r="A1291" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1291" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1291" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1291" s="2"/>
+    </row>
+    <row r="1292" spans="1:7">
+      <c r="A1292" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1292" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1292" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1292" s="2"/>
+    </row>
+    <row r="1293" spans="1:7">
+      <c r="A1293" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1293" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1293" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1293" s="2"/>
+    </row>
+    <row r="1294" spans="1:7">
+      <c r="A1294" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1294" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1294" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1294" s="2"/>
+    </row>
+    <row r="1295" spans="1:7">
+      <c r="A1295" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1295" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1295" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1295" s="2"/>
+    </row>
+    <row r="1296" spans="1:7">
+      <c r="A1296" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1296" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1296" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1296" s="2"/>
+    </row>
+    <row r="1297" spans="1:4">
+      <c r="A1297" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1297" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1297" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1297" s="2"/>
+    </row>
+    <row r="1298" spans="1:4">
+      <c r="A1298" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1298" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1298" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1298" s="2"/>
+    </row>
+    <row r="1299" spans="1:4">
+      <c r="A1299" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1299" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1299" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1299" s="2"/>
+    </row>
+    <row r="1300" spans="1:4">
+      <c r="A1300" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1300" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1300" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1300" s="2"/>
+    </row>
+    <row r="1301" spans="1:4">
+      <c r="A1301" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1301" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1301" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1301" s="2"/>
+    </row>
+    <row r="1302" spans="1:4">
+      <c r="A1302" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B1302" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1302" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1302" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1302"/>
+  <dimension ref="A1:H1311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -19802,7 +19802,9 @@
       <c r="C1290" s="5">
         <v>4</v>
       </c>
-      <c r="D1290" s="2"/>
+      <c r="D1290" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1291" spans="1:7">
       <c r="A1291" s="6">
@@ -19814,7 +19816,9 @@
       <c r="C1291" s="5">
         <v>12</v>
       </c>
-      <c r="D1291" s="2"/>
+      <c r="D1291" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1292" spans="1:7">
       <c r="A1292" s="6">
@@ -19826,7 +19830,9 @@
       <c r="C1292" s="5">
         <v>12</v>
       </c>
-      <c r="D1292" s="2"/>
+      <c r="D1292" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1293" spans="1:7">
       <c r="A1293" s="6">
@@ -19838,7 +19844,9 @@
       <c r="C1293" s="2">
         <v>3</v>
       </c>
-      <c r="D1293" s="2"/>
+      <c r="D1293" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1294" spans="1:7">
       <c r="A1294" s="6">
@@ -19850,7 +19858,9 @@
       <c r="C1294" s="2">
         <v>3</v>
       </c>
-      <c r="D1294" s="2"/>
+      <c r="D1294" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1295" spans="1:7">
       <c r="A1295" s="6">
@@ -19862,7 +19872,9 @@
       <c r="C1295" s="5">
         <v>3</v>
       </c>
-      <c r="D1295" s="2"/>
+      <c r="D1295" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1296" spans="1:7">
       <c r="A1296" s="6">
@@ -19874,7 +19886,9 @@
       <c r="C1296" s="5">
         <v>3</v>
       </c>
-      <c r="D1296" s="2"/>
+      <c r="D1296" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1297" spans="1:4">
       <c r="A1297" s="6">
@@ -19886,7 +19900,9 @@
       <c r="C1297" s="5">
         <v>5</v>
       </c>
-      <c r="D1297" s="2"/>
+      <c r="D1297" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1298" spans="1:4">
       <c r="A1298" s="6">
@@ -19898,7 +19914,9 @@
       <c r="C1298" s="5">
         <v>5</v>
       </c>
-      <c r="D1298" s="2"/>
+      <c r="D1298" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1299" spans="1:4">
       <c r="A1299" s="6">
@@ -19910,7 +19928,9 @@
       <c r="C1299" s="5">
         <v>5</v>
       </c>
-      <c r="D1299" s="2"/>
+      <c r="D1299" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1300" spans="1:4">
       <c r="A1300" s="6">
@@ -19922,7 +19942,9 @@
       <c r="C1300" s="5">
         <v>5</v>
       </c>
-      <c r="D1300" s="2"/>
+      <c r="D1300" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1301" spans="1:4">
       <c r="A1301" s="6">
@@ -19934,7 +19956,9 @@
       <c r="C1301" s="5">
         <v>8</v>
       </c>
-      <c r="D1301" s="2"/>
+      <c r="D1301" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1302" spans="1:4">
       <c r="A1302" s="6">
@@ -19946,7 +19970,117 @@
       <c r="C1302" s="5">
         <v>8</v>
       </c>
-      <c r="D1302" s="2"/>
+      <c r="D1302" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4">
+      <c r="A1303" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1303" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1303" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1303" s="2"/>
+    </row>
+    <row r="1304" spans="1:4">
+      <c r="A1304" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1304" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1304" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1304" s="2"/>
+    </row>
+    <row r="1305" spans="1:4">
+      <c r="A1305" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1305" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1305" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1305" s="2"/>
+    </row>
+    <row r="1306" spans="1:4">
+      <c r="A1306" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1306" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1306" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1306" s="2"/>
+    </row>
+    <row r="1307" spans="1:4">
+      <c r="A1307" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1307" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1307" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1307" s="2"/>
+    </row>
+    <row r="1308" spans="1:4">
+      <c r="A1308" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1308" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1308" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1308" s="2"/>
+    </row>
+    <row r="1309" spans="1:4">
+      <c r="A1309" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1309" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1309" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1309" s="2"/>
+    </row>
+    <row r="1310" spans="1:4">
+      <c r="A1310" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1310" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1310" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1310" s="2"/>
+    </row>
+    <row r="1311" spans="1:4">
+      <c r="A1311" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1311" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1311" s="2">
+        <v>16</v>
+      </c>
+      <c r="D1311" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1311"/>
+  <dimension ref="A1:H1325"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -19890,7 +19890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1297" spans="1:4">
+    <row r="1297" spans="1:7">
       <c r="A1297" s="6">
         <v>46191</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1298" spans="1:4">
+    <row r="1298" spans="1:7">
       <c r="A1298" s="6">
         <v>46191</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1299" spans="1:4">
+    <row r="1299" spans="1:7">
       <c r="A1299" s="6">
         <v>46191</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1300" spans="1:4">
+    <row r="1300" spans="1:7">
       <c r="A1300" s="6">
         <v>46191</v>
       </c>
@@ -19946,7 +19946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1301" spans="1:4">
+    <row r="1301" spans="1:7">
       <c r="A1301" s="6">
         <v>46191</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1302" spans="1:4">
+    <row r="1302" spans="1:7">
       <c r="A1302" s="6">
         <v>46191</v>
       </c>
@@ -19974,113 +19974,339 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1303" spans="1:4">
+    <row r="1303" spans="1:7">
       <c r="A1303" s="6">
         <v>46192</v>
       </c>
-      <c r="B1303" s="8" t="s">
-        <v>3</v>
+      <c r="B1303" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="C1303" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1303" s="2"/>
-    </row>
-    <row r="1304" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1303" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:7">
       <c r="A1304" s="6">
         <v>46192</v>
       </c>
-      <c r="B1304" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1304" s="2">
-        <v>3</v>
-      </c>
-      <c r="D1304" s="2"/>
-    </row>
-    <row r="1305" spans="1:4">
+      <c r="B1304" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1304" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1304" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:7">
       <c r="A1305" s="6">
         <v>46192</v>
       </c>
-      <c r="B1305" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1305" s="2">
-        <v>13</v>
-      </c>
-      <c r="D1305" s="2"/>
-    </row>
-    <row r="1306" spans="1:4">
+      <c r="B1305" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1305" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1305" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:7">
       <c r="A1306" s="6">
         <v>46192</v>
       </c>
-      <c r="B1306" s="2" t="s">
-        <v>15</v>
+      <c r="B1306" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="C1306" s="2">
-        <v>11</v>
-      </c>
-      <c r="D1306" s="2"/>
-    </row>
-    <row r="1307" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="D1306" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1306" s="1"/>
+      <c r="G1306" s="27"/>
+    </row>
+    <row r="1307" spans="1:7">
       <c r="A1307" s="6">
         <v>46192</v>
       </c>
-      <c r="B1307" s="13" t="s">
-        <v>2</v>
+      <c r="B1307" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1307" s="2">
-        <v>4</v>
-      </c>
-      <c r="D1307" s="2"/>
-    </row>
-    <row r="1308" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="D1307" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1307" s="1"/>
+      <c r="G1307" s="27"/>
+    </row>
+    <row r="1308" spans="1:7">
       <c r="A1308" s="6">
         <v>46192</v>
       </c>
-      <c r="B1308" s="13" t="s">
+      <c r="B1308" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1308" s="2">
         <v>11</v>
       </c>
-      <c r="C1308" s="2">
-        <v>4</v>
-      </c>
-      <c r="D1308" s="2"/>
-    </row>
-    <row r="1309" spans="1:4">
+      <c r="D1308" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1308" s="1"/>
+      <c r="G1308" s="27"/>
+    </row>
+    <row r="1309" spans="1:7">
       <c r="A1309" s="6">
         <v>46192</v>
       </c>
-      <c r="B1309" s="12" t="s">
-        <v>21</v>
+      <c r="B1309" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="C1309" s="2">
-        <v>8</v>
-      </c>
-      <c r="D1309" s="2"/>
-    </row>
-    <row r="1310" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="D1309" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1309" s="1"/>
+      <c r="G1309" s="27"/>
+    </row>
+    <row r="1310" spans="1:7">
       <c r="A1310" s="6">
         <v>46192</v>
       </c>
-      <c r="B1310" s="12" t="s">
-        <v>9</v>
+      <c r="B1310" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="C1310" s="2">
-        <v>8</v>
-      </c>
-      <c r="D1310" s="2"/>
-    </row>
-    <row r="1311" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="D1310" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1310" s="1"/>
+      <c r="G1310" s="27"/>
+    </row>
+    <row r="1311" spans="1:7">
       <c r="A1311" s="6">
         <v>46192</v>
       </c>
-      <c r="B1311" s="2" t="s">
-        <v>4</v>
+      <c r="B1311" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="C1311" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1311" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1311" s="1"/>
+      <c r="G1311" s="27"/>
+    </row>
+    <row r="1312" spans="1:7">
+      <c r="A1312" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1312" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1312" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1312" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1312" s="1"/>
+      <c r="G1312" s="27"/>
+    </row>
+    <row r="1313" spans="1:7">
+      <c r="A1313" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B1313" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1313" s="2">
         <v>16</v>
       </c>
-      <c r="D1311" s="2"/>
+      <c r="D1313" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1313" s="1"/>
+      <c r="G1313" s="27"/>
+    </row>
+    <row r="1314" spans="1:7">
+      <c r="A1314" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B1314" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1314" s="5">
+        <v>14</v>
+      </c>
+      <c r="D1314" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:7">
+      <c r="A1315" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B1315" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1315" s="5">
+        <v>11</v>
+      </c>
+      <c r="D1315" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1315" s="1"/>
+      <c r="G1315" s="27"/>
+    </row>
+    <row r="1316" spans="1:7">
+      <c r="A1316" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B1316" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1316" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1316" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1316" s="1"/>
+      <c r="G1316" s="27"/>
+    </row>
+    <row r="1317" spans="1:7">
+      <c r="A1317" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B1317" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1317" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1317" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1317" s="1"/>
+      <c r="G1317" s="27"/>
+    </row>
+    <row r="1318" spans="1:7">
+      <c r="A1318" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1318" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1318" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1318" s="2"/>
+      <c r="F1318" s="1"/>
+      <c r="G1318" s="27"/>
+    </row>
+    <row r="1319" spans="1:7">
+      <c r="A1319" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1319" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1319" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1319" s="2"/>
+      <c r="F1319" s="1"/>
+      <c r="G1319" s="27"/>
+    </row>
+    <row r="1320" spans="1:7">
+      <c r="A1320" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1320" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1320" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1320" s="2"/>
+      <c r="F1320" s="1"/>
+      <c r="G1320" s="27"/>
+    </row>
+    <row r="1321" spans="1:7">
+      <c r="A1321" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1321" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1321" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1321" s="2"/>
+    </row>
+    <row r="1322" spans="1:7">
+      <c r="A1322" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1322" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1322" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1322" s="2"/>
+    </row>
+    <row r="1323" spans="1:7">
+      <c r="A1323" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1323" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1323" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1323" s="2"/>
+    </row>
+    <row r="1324" spans="1:7">
+      <c r="A1324" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1324" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1324" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1324" s="2"/>
+    </row>
+    <row r="1325" spans="1:7">
+      <c r="A1325" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B1325" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1325" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1325" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1325"/>
+  <dimension ref="A1:H1331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -20216,9 +20216,9 @@
       <c r="C1318" s="5">
         <v>1</v>
       </c>
-      <c r="D1318" s="2"/>
-      <c r="F1318" s="1"/>
-      <c r="G1318" s="27"/>
+      <c r="D1318" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1319" spans="1:7">
       <c r="A1319" s="6">
@@ -20230,7 +20230,9 @@
       <c r="C1319" s="5">
         <v>1</v>
       </c>
-      <c r="D1319" s="2"/>
+      <c r="D1319" s="2">
+        <v>4</v>
+      </c>
       <c r="F1319" s="1"/>
       <c r="G1319" s="27"/>
     </row>
@@ -20244,7 +20246,9 @@
       <c r="C1320" s="5">
         <v>1</v>
       </c>
-      <c r="D1320" s="2"/>
+      <c r="D1320" s="2">
+        <v>4</v>
+      </c>
       <c r="F1320" s="1"/>
       <c r="G1320" s="27"/>
     </row>
@@ -20258,7 +20262,11 @@
       <c r="C1321" s="5">
         <v>4</v>
       </c>
-      <c r="D1321" s="2"/>
+      <c r="D1321" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1321" s="1"/>
+      <c r="G1321" s="27"/>
     </row>
     <row r="1322" spans="1:7">
       <c r="A1322" s="6">
@@ -20270,7 +20278,11 @@
       <c r="C1322" s="5">
         <v>4</v>
       </c>
-      <c r="D1322" s="2"/>
+      <c r="D1322" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1322" s="1"/>
+      <c r="G1322" s="27"/>
     </row>
     <row r="1323" spans="1:7">
       <c r="A1323" s="6">
@@ -20282,7 +20294,11 @@
       <c r="C1323" s="5">
         <v>2</v>
       </c>
-      <c r="D1323" s="2"/>
+      <c r="D1323" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1323" s="1"/>
+      <c r="G1323" s="27"/>
     </row>
     <row r="1324" spans="1:7">
       <c r="A1324" s="6">
@@ -20294,19 +20310,97 @@
       <c r="C1324" s="5">
         <v>2</v>
       </c>
-      <c r="D1324" s="2"/>
+      <c r="D1324" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1324" s="1"/>
+      <c r="G1324" s="27"/>
     </row>
     <row r="1325" spans="1:7">
       <c r="A1325" s="6">
         <v>46195</v>
       </c>
-      <c r="B1325" s="8" t="s">
+      <c r="B1325" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C1325" s="5">
         <v>3</v>
       </c>
-      <c r="D1325" s="2"/>
+      <c r="D1325" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:7">
+      <c r="A1326" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1326" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1326" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1326" s="2"/>
+    </row>
+    <row r="1327" spans="1:7">
+      <c r="A1327" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1327" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1327" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1327" s="2"/>
+    </row>
+    <row r="1328" spans="1:7">
+      <c r="A1328" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1328" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1328" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1328" s="2"/>
+    </row>
+    <row r="1329" spans="1:4">
+      <c r="A1329" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1329" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1329" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1329" s="2"/>
+    </row>
+    <row r="1330" spans="1:4">
+      <c r="A1330" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1330" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1330" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1330" s="2"/>
+    </row>
+    <row r="1331" spans="1:4">
+      <c r="A1331" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1331" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1331" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1331"/>
+  <dimension ref="A1:H1345"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -20334,73 +20334,279 @@
       <c r="A1326" s="6">
         <v>46196</v>
       </c>
-      <c r="B1326" s="9" t="s">
-        <v>15</v>
+      <c r="B1326" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="C1326" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1326" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1326" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1327" spans="1:7">
       <c r="A1327" s="6">
         <v>46196</v>
       </c>
-      <c r="B1327" s="9" t="s">
-        <v>6</v>
+      <c r="B1327" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C1327" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1327" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1327" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1328" spans="1:7">
       <c r="A1328" s="6">
         <v>46196</v>
       </c>
-      <c r="B1328" s="13" t="s">
-        <v>2</v>
+      <c r="B1328" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="C1328" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1328" s="2"/>
-    </row>
-    <row r="1329" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1328" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:7">
       <c r="A1329" s="6">
         <v>46196</v>
       </c>
-      <c r="B1329" s="13" t="s">
-        <v>11</v>
+      <c r="B1329" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C1329" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1329" s="2"/>
-    </row>
-    <row r="1330" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1329" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:7">
       <c r="A1330" s="6">
         <v>46196</v>
       </c>
-      <c r="B1330" s="2" t="s">
-        <v>13</v>
+      <c r="B1330" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="C1330" s="5">
-        <v>9</v>
-      </c>
-      <c r="D1330" s="2"/>
-    </row>
-    <row r="1331" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D1330" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:7">
       <c r="A1331" s="6">
         <v>46196</v>
       </c>
-      <c r="B1331" s="2" t="s">
-        <v>4</v>
+      <c r="B1331" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="C1331" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1331" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1331" s="1"/>
+      <c r="G1331" s="27"/>
+    </row>
+    <row r="1332" spans="1:7">
+      <c r="A1332" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1332" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1332" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1332" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1332" s="1"/>
+      <c r="G1332" s="27"/>
+    </row>
+    <row r="1333" spans="1:7">
+      <c r="A1333" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1333" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1333" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1333" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1333" s="1"/>
+      <c r="G1333" s="27"/>
+    </row>
+    <row r="1334" spans="1:7">
+      <c r="A1334" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1334" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1334" s="5">
         <v>9</v>
       </c>
-      <c r="D1331" s="2"/>
+      <c r="D1334" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1334" s="1"/>
+      <c r="G1334" s="27"/>
+    </row>
+    <row r="1335" spans="1:7">
+      <c r="A1335" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B1335" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1335" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1335" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1335" s="1"/>
+      <c r="G1335" s="27"/>
+    </row>
+    <row r="1336" spans="1:7">
+      <c r="A1336" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1336" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1336" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1336" s="2"/>
+      <c r="F1336" s="1"/>
+      <c r="G1336" s="27"/>
+    </row>
+    <row r="1337" spans="1:7">
+      <c r="A1337" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1337" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1337" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1337" s="2"/>
+      <c r="F1337" s="1"/>
+      <c r="G1337" s="27"/>
+    </row>
+    <row r="1338" spans="1:7">
+      <c r="A1338" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1338" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1338" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1338" s="2"/>
+      <c r="F1338" s="1"/>
+      <c r="G1338" s="27"/>
+    </row>
+    <row r="1339" spans="1:7">
+      <c r="A1339" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1339" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1339" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1339" s="2"/>
+      <c r="F1339" s="1"/>
+      <c r="G1339" s="27"/>
+    </row>
+    <row r="1340" spans="1:7">
+      <c r="A1340" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1340" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1340" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1340" s="2"/>
+    </row>
+    <row r="1341" spans="1:7">
+      <c r="A1341" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1341" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1341" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1341" s="2"/>
+    </row>
+    <row r="1342" spans="1:7">
+      <c r="A1342" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1342" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1342" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1342" s="2"/>
+    </row>
+    <row r="1343" spans="1:7">
+      <c r="A1343" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1343" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1343" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1343" s="2"/>
+    </row>
+    <row r="1344" spans="1:7">
+      <c r="A1344" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1344" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1344" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1344" s="2"/>
+    </row>
+    <row r="1345" spans="1:4">
+      <c r="A1345" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B1345" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1345" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1345" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1345"/>
+  <dimension ref="A1:H1351"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -20490,9 +20490,9 @@
       <c r="C1336" s="5">
         <v>1</v>
       </c>
-      <c r="D1336" s="2"/>
-      <c r="F1336" s="1"/>
-      <c r="G1336" s="27"/>
+      <c r="D1336" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1337" spans="1:7">
       <c r="A1337" s="6">
@@ -20504,7 +20504,9 @@
       <c r="C1337" s="5">
         <v>1</v>
       </c>
-      <c r="D1337" s="2"/>
+      <c r="D1337" s="2">
+        <v>3</v>
+      </c>
       <c r="F1337" s="1"/>
       <c r="G1337" s="27"/>
     </row>
@@ -20518,7 +20520,9 @@
       <c r="C1338" s="5">
         <v>2</v>
       </c>
-      <c r="D1338" s="2"/>
+      <c r="D1338" s="2">
+        <v>0</v>
+      </c>
       <c r="F1338" s="1"/>
       <c r="G1338" s="27"/>
     </row>
@@ -20532,7 +20536,9 @@
       <c r="C1339" s="5">
         <v>2</v>
       </c>
-      <c r="D1339" s="2"/>
+      <c r="D1339" s="2">
+        <v>0</v>
+      </c>
       <c r="F1339" s="1"/>
       <c r="G1339" s="27"/>
     </row>
@@ -20546,7 +20552,11 @@
       <c r="C1340" s="5">
         <v>3</v>
       </c>
-      <c r="D1340" s="2"/>
+      <c r="D1340" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1340" s="1"/>
+      <c r="G1340" s="27"/>
     </row>
     <row r="1341" spans="1:7">
       <c r="A1341" s="6">
@@ -20558,7 +20568,11 @@
       <c r="C1341" s="5">
         <v>7</v>
       </c>
-      <c r="D1341" s="2"/>
+      <c r="D1341" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1341" s="1"/>
+      <c r="G1341" s="27"/>
     </row>
     <row r="1342" spans="1:7">
       <c r="A1342" s="6">
@@ -20570,7 +20584,11 @@
       <c r="C1342" s="5">
         <v>2</v>
       </c>
-      <c r="D1342" s="2"/>
+      <c r="D1342" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1342" s="1"/>
+      <c r="G1342" s="27"/>
     </row>
     <row r="1343" spans="1:7">
       <c r="A1343" s="6">
@@ -20582,7 +20600,11 @@
       <c r="C1343" s="5">
         <v>2</v>
       </c>
-      <c r="D1343" s="2"/>
+      <c r="D1343" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1343" s="1"/>
+      <c r="G1343" s="27"/>
     </row>
     <row r="1344" spans="1:7">
       <c r="A1344" s="6">
@@ -20594,7 +20616,9 @@
       <c r="C1344" s="5">
         <v>4</v>
       </c>
-      <c r="D1344" s="2"/>
+      <c r="D1344" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1345" spans="1:4">
       <c r="A1345" s="6">
@@ -20606,7 +20630,85 @@
       <c r="C1345" s="2">
         <v>4</v>
       </c>
-      <c r="D1345" s="2"/>
+      <c r="D1345" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4">
+      <c r="A1346" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1346" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1346" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1346" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4">
+      <c r="A1347" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1347" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1347" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1347" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4">
+      <c r="A1348" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1348" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1348" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1348" s="2"/>
+    </row>
+    <row r="1349" spans="1:4">
+      <c r="A1349" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1349" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1349" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1349" s="2"/>
+    </row>
+    <row r="1350" spans="1:4">
+      <c r="A1350" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1350" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1350" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1350" s="2"/>
+    </row>
+    <row r="1351" spans="1:4">
+      <c r="A1351" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1351" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1351" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1351" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,14 +616,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1351"/>
+  <dimension ref="A1:H1362"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -20620,7 +20620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1345" spans="1:4">
+    <row r="1345" spans="1:7">
       <c r="A1345" s="6">
         <v>46197</v>
       </c>
@@ -20634,7 +20634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1346" spans="1:4">
+    <row r="1346" spans="1:7">
       <c r="A1346" s="6">
         <v>46198</v>
       </c>
@@ -20648,7 +20648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1347" spans="1:4">
+    <row r="1347" spans="1:7">
       <c r="A1347" s="6">
         <v>46198</v>
       </c>
@@ -20662,7 +20662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1348" spans="1:4">
+    <row r="1348" spans="1:7">
       <c r="A1348" s="6">
         <v>46198</v>
       </c>
@@ -20672,9 +20672,11 @@
       <c r="C1348" s="5">
         <v>6</v>
       </c>
-      <c r="D1348" s="2"/>
-    </row>
-    <row r="1349" spans="1:4">
+      <c r="D1348" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:7">
       <c r="A1349" s="6">
         <v>46198</v>
       </c>
@@ -20684,9 +20686,11 @@
       <c r="C1349" s="5">
         <v>6</v>
       </c>
-      <c r="D1349" s="2"/>
-    </row>
-    <row r="1350" spans="1:4">
+      <c r="D1349" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:7">
       <c r="A1350" s="6">
         <v>46198</v>
       </c>
@@ -20696,9 +20700,11 @@
       <c r="C1350" s="5">
         <v>3</v>
       </c>
-      <c r="D1350" s="2"/>
-    </row>
-    <row r="1351" spans="1:4">
+      <c r="D1350" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:7">
       <c r="A1351" s="6">
         <v>46198</v>
       </c>
@@ -20708,7 +20714,165 @@
       <c r="C1351" s="5">
         <v>3</v>
       </c>
-      <c r="D1351" s="2"/>
+      <c r="D1351" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:7">
+      <c r="A1352" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1352" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1352" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1352" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:7">
+      <c r="A1353" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1353" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1353" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1353" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1353" s="1"/>
+      <c r="G1353" s="27"/>
+    </row>
+    <row r="1354" spans="1:7">
+      <c r="A1354" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1354" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1354" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1354" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1354" s="1"/>
+      <c r="G1354" s="27"/>
+    </row>
+    <row r="1355" spans="1:7">
+      <c r="A1355" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1355" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1355" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1355" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1355" s="1"/>
+      <c r="G1355" s="27"/>
+    </row>
+    <row r="1356" spans="1:7">
+      <c r="A1356" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B1356" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1356" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1356" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1356" s="1"/>
+      <c r="G1356" s="27"/>
+    </row>
+    <row r="1357" spans="1:7">
+      <c r="A1357" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1357" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1357" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1357" s="2"/>
+      <c r="F1357" s="1"/>
+      <c r="G1357" s="27"/>
+    </row>
+    <row r="1358" spans="1:7">
+      <c r="A1358" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1358" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1358" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1358" s="2"/>
+      <c r="F1358" s="1"/>
+      <c r="G1358" s="27"/>
+    </row>
+    <row r="1359" spans="1:7">
+      <c r="A1359" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1359" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1359" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1359" s="2"/>
+      <c r="F1359" s="1"/>
+      <c r="G1359" s="27"/>
+    </row>
+    <row r="1360" spans="1:7">
+      <c r="A1360" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1360" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1360" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1360" s="2"/>
+    </row>
+    <row r="1361" spans="1:4">
+      <c r="A1361" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1361" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1361" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1361" s="2"/>
+    </row>
+    <row r="1362" spans="1:4">
+      <c r="A1362" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1362" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1362" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1362" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,14 +616,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1362"/>
+  <dimension ref="A1:H1384"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -20800,13 +20800,15 @@
       <c r="A1357" s="6">
         <v>46199</v>
       </c>
-      <c r="B1357" s="9" t="s">
-        <v>15</v>
+      <c r="B1357" s="20" t="s">
+        <v>5</v>
       </c>
       <c r="C1357" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1357" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1357" s="2">
+        <v>1</v>
+      </c>
       <c r="F1357" s="1"/>
       <c r="G1357" s="27"/>
     </row>
@@ -20814,13 +20816,15 @@
       <c r="A1358" s="6">
         <v>46199</v>
       </c>
-      <c r="B1358" s="9" t="s">
-        <v>6</v>
+      <c r="B1358" s="20" t="s">
+        <v>9</v>
       </c>
       <c r="C1358" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1358" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1358" s="2">
+        <v>1</v>
+      </c>
       <c r="F1358" s="1"/>
       <c r="G1358" s="27"/>
     </row>
@@ -20828,13 +20832,15 @@
       <c r="A1359" s="6">
         <v>46199</v>
       </c>
-      <c r="B1359" s="2" t="s">
-        <v>2</v>
+      <c r="B1359" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="C1359" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1359" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1359" s="2">
+        <v>1</v>
+      </c>
       <c r="F1359" s="1"/>
       <c r="G1359" s="27"/>
     </row>
@@ -20842,37 +20848,363 @@
       <c r="A1360" s="6">
         <v>46199</v>
       </c>
-      <c r="B1360" s="8" t="s">
-        <v>4</v>
+      <c r="B1360" s="22" t="s">
+        <v>11</v>
       </c>
       <c r="C1360" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1360" s="2"/>
-    </row>
-    <row r="1361" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1360" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1360" s="1"/>
+      <c r="G1360" s="27"/>
+    </row>
+    <row r="1361" spans="1:7">
       <c r="A1361" s="6">
         <v>46199</v>
       </c>
-      <c r="B1361" s="8" t="s">
-        <v>23</v>
+      <c r="B1361" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C1361" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1361" s="2"/>
-    </row>
-    <row r="1362" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="D1361" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1361" s="1"/>
+      <c r="G1361" s="27"/>
+    </row>
+    <row r="1362" spans="1:7">
       <c r="A1362" s="6">
         <v>46199</v>
       </c>
-      <c r="B1362" s="2" t="s">
+      <c r="B1362" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1362" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1362" s="1"/>
+      <c r="G1362" s="27"/>
+    </row>
+    <row r="1363" spans="1:7">
+      <c r="A1363" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1363" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1363" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1363" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:7">
+      <c r="A1364" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1364" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1364" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1364" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1364" s="1"/>
+      <c r="G1364" s="27"/>
+    </row>
+    <row r="1365" spans="1:7">
+      <c r="A1365" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1365" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1365" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1365" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1365" s="1"/>
+      <c r="G1365" s="27"/>
+    </row>
+    <row r="1366" spans="1:7">
+      <c r="A1366" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1366" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1366" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1366" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1366" s="1"/>
+      <c r="G1366" s="27"/>
+    </row>
+    <row r="1367" spans="1:7">
+      <c r="A1367" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1367" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1367" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1367" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1367" s="1"/>
+      <c r="G1367" s="27"/>
+    </row>
+    <row r="1368" spans="1:7">
+      <c r="A1368" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B1368" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1362" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1362" s="2"/>
+      <c r="C1368" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1368" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1368" s="1"/>
+      <c r="G1368" s="27"/>
+    </row>
+    <row r="1369" spans="1:7">
+      <c r="A1369" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1369" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1369" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1369" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1369" s="1"/>
+      <c r="G1369" s="27"/>
+    </row>
+    <row r="1370" spans="1:7">
+      <c r="A1370" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1370" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1370" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1370" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1370" s="1"/>
+      <c r="G1370" s="27"/>
+    </row>
+    <row r="1371" spans="1:7">
+      <c r="A1371" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1371" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1371" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1371" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:7">
+      <c r="A1372" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1372" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1372" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1372" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1372" s="1"/>
+      <c r="G1372" s="27"/>
+    </row>
+    <row r="1373" spans="1:7">
+      <c r="A1373" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1373" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1373" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1373" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1373" s="1"/>
+      <c r="G1373" s="27"/>
+    </row>
+    <row r="1374" spans="1:7">
+      <c r="A1374" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B1374" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1374" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1374" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1374" s="1"/>
+      <c r="G1374" s="27"/>
+    </row>
+    <row r="1375" spans="1:7">
+      <c r="A1375" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1375" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1375" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1375" s="2"/>
+      <c r="F1375" s="1"/>
+      <c r="G1375" s="27"/>
+    </row>
+    <row r="1376" spans="1:7">
+      <c r="A1376" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1376" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1376" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1376" s="2"/>
+      <c r="F1376" s="1"/>
+      <c r="G1376" s="27"/>
+    </row>
+    <row r="1377" spans="1:7">
+      <c r="A1377" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1377" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1377" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1377" s="2"/>
+      <c r="F1377" s="1"/>
+      <c r="G1377" s="27"/>
+    </row>
+    <row r="1378" spans="1:7">
+      <c r="A1378" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1378" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1378" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1378" s="2"/>
+    </row>
+    <row r="1379" spans="1:7">
+      <c r="A1379" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1379" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1379" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1379" s="2"/>
+    </row>
+    <row r="1380" spans="1:7">
+      <c r="A1380" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1380" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1380" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1380" s="2"/>
+    </row>
+    <row r="1381" spans="1:7">
+      <c r="A1381" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1381" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1381" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1381" s="2"/>
+    </row>
+    <row r="1382" spans="1:7">
+      <c r="A1382" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1382" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1382" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1382" s="2"/>
+    </row>
+    <row r="1383" spans="1:7">
+      <c r="A1383" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1383" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1383" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1383" s="2"/>
+    </row>
+    <row r="1384" spans="1:7">
+      <c r="A1384" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1384" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1384" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1384" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,14 +616,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1384"/>
+  <dimension ref="A1:H1392"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -21090,9 +21090,9 @@
       <c r="C1375" s="5">
         <v>4</v>
       </c>
-      <c r="D1375" s="2"/>
-      <c r="F1375" s="1"/>
-      <c r="G1375" s="27"/>
+      <c r="D1375" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1376" spans="1:7">
       <c r="A1376" s="6">
@@ -21104,7 +21104,9 @@
       <c r="C1376" s="5">
         <v>4</v>
       </c>
-      <c r="D1376" s="2"/>
+      <c r="D1376" s="2">
+        <v>3</v>
+      </c>
       <c r="F1376" s="1"/>
       <c r="G1376" s="27"/>
     </row>
@@ -21118,7 +21120,9 @@
       <c r="C1377" s="5">
         <v>3</v>
       </c>
-      <c r="D1377" s="2"/>
+      <c r="D1377" s="2">
+        <v>2</v>
+      </c>
       <c r="F1377" s="1"/>
       <c r="G1377" s="27"/>
     </row>
@@ -21132,7 +21136,11 @@
       <c r="C1378" s="5">
         <v>3</v>
       </c>
-      <c r="D1378" s="2"/>
+      <c r="D1378" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1378" s="1"/>
+      <c r="G1378" s="27"/>
     </row>
     <row r="1379" spans="1:7">
       <c r="A1379" s="6">
@@ -21144,7 +21152,11 @@
       <c r="C1379" s="5">
         <v>3</v>
       </c>
-      <c r="D1379" s="2"/>
+      <c r="D1379" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1379" s="1"/>
+      <c r="G1379" s="27"/>
     </row>
     <row r="1380" spans="1:7">
       <c r="A1380" s="6">
@@ -21156,7 +21168,11 @@
       <c r="C1380" s="2">
         <v>3</v>
       </c>
-      <c r="D1380" s="2"/>
+      <c r="D1380" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1380" s="1"/>
+      <c r="G1380" s="27"/>
     </row>
     <row r="1381" spans="1:7">
       <c r="A1381" s="6">
@@ -21168,7 +21184,11 @@
       <c r="C1381" s="2">
         <v>2</v>
       </c>
-      <c r="D1381" s="2"/>
+      <c r="D1381" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1381" s="1"/>
+      <c r="G1381" s="27"/>
     </row>
     <row r="1382" spans="1:7">
       <c r="A1382" s="6">
@@ -21180,7 +21200,11 @@
       <c r="C1382" s="2">
         <v>2</v>
       </c>
-      <c r="D1382" s="2"/>
+      <c r="D1382" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1382" s="1"/>
+      <c r="G1382" s="27"/>
     </row>
     <row r="1383" spans="1:7">
       <c r="A1383" s="6">
@@ -21192,7 +21216,11 @@
       <c r="C1383" s="2">
         <v>4</v>
       </c>
-      <c r="D1383" s="2"/>
+      <c r="D1383" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1383" s="1"/>
+      <c r="G1383" s="27"/>
     </row>
     <row r="1384" spans="1:7">
       <c r="A1384" s="6">
@@ -21204,7 +21232,109 @@
       <c r="C1384" s="2">
         <v>4</v>
       </c>
-      <c r="D1384" s="2"/>
+      <c r="D1384" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:7">
+      <c r="A1385" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1385" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1385" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1385" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:7">
+      <c r="A1386" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B1386" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1386" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1386" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:7">
+      <c r="A1387" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1387" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1387" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1387" s="2"/>
+    </row>
+    <row r="1388" spans="1:7">
+      <c r="A1388" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1388" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1388" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1388" s="2"/>
+    </row>
+    <row r="1389" spans="1:7">
+      <c r="A1389" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1389" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1389" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1389" s="2"/>
+    </row>
+    <row r="1390" spans="1:7">
+      <c r="A1390" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1390" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1390" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1390" s="2"/>
+    </row>
+    <row r="1391" spans="1:7">
+      <c r="A1391" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1391" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1391" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1391" s="2"/>
+    </row>
+    <row r="1392" spans="1:7">
+      <c r="A1392" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1392" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1392" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1392" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1392"/>
+  <dimension ref="A1:H1409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -21268,73 +21268,317 @@
       <c r="A1387" s="6">
         <v>46203</v>
       </c>
-      <c r="B1387" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1387" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1387" s="2"/>
+      <c r="B1387" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1387" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1387" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1388" spans="1:7">
       <c r="A1388" s="6">
         <v>46203</v>
       </c>
-      <c r="B1388" s="8" t="s">
-        <v>27</v>
+      <c r="B1388" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C1388" s="2">
-        <v>3</v>
-      </c>
-      <c r="D1388" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1388" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1389" spans="1:7">
       <c r="A1389" s="6">
         <v>46203</v>
       </c>
-      <c r="B1389" s="13" t="s">
-        <v>2</v>
+      <c r="B1389" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C1389" s="2">
-        <v>1</v>
-      </c>
-      <c r="D1389" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1389" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1390" spans="1:7">
       <c r="A1390" s="6">
         <v>46203</v>
       </c>
-      <c r="B1390" s="13" t="s">
-        <v>11</v>
+      <c r="B1390" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C1390" s="2">
-        <v>1</v>
-      </c>
-      <c r="D1390" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1390" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1391" spans="1:7">
       <c r="A1391" s="6">
         <v>46203</v>
       </c>
-      <c r="B1391" s="24" t="s">
-        <v>13</v>
+      <c r="B1391" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1391" s="2">
-        <v>5</v>
-      </c>
-      <c r="D1391" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1391" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1392" spans="1:7">
       <c r="A1392" s="6">
         <v>46203</v>
       </c>
-      <c r="B1392" s="24" t="s">
+      <c r="B1392" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1392" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1392" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:7">
+      <c r="A1393" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1393" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1393" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1393" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:7">
+      <c r="A1394" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1394" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1394" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1394" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1394" s="1"/>
+      <c r="G1394" s="27"/>
+    </row>
+    <row r="1395" spans="1:7">
+      <c r="A1395" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1395" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1395" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1395" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1395" s="1"/>
+      <c r="G1395" s="27"/>
+    </row>
+    <row r="1396" spans="1:7">
+      <c r="A1396" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1396" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1396" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1396" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1396" s="1"/>
+      <c r="G1396" s="27"/>
+    </row>
+    <row r="1397" spans="1:7">
+      <c r="A1397" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1397" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1397" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1397" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1397" s="1"/>
+      <c r="G1397" s="27"/>
+    </row>
+    <row r="1398" spans="1:7">
+      <c r="A1398" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B1398" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C1392" s="2">
-        <v>5</v>
-      </c>
-      <c r="D1392" s="2"/>
+      <c r="C1398" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1398" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1398" s="1"/>
+      <c r="G1398" s="27"/>
+    </row>
+    <row r="1399" spans="1:7">
+      <c r="A1399" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1399" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1399" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1399" s="2"/>
+      <c r="F1399" s="1"/>
+      <c r="G1399" s="27"/>
+    </row>
+    <row r="1400" spans="1:7">
+      <c r="A1400" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1400" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1400" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1400" s="2"/>
+      <c r="F1400" s="1"/>
+      <c r="G1400" s="27"/>
+    </row>
+    <row r="1401" spans="1:7">
+      <c r="A1401" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1401" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1401" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1401" s="2"/>
+      <c r="F1401" s="1"/>
+      <c r="G1401" s="27"/>
+    </row>
+    <row r="1402" spans="1:7">
+      <c r="A1402" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1402" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1402" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1402" s="2"/>
+    </row>
+    <row r="1403" spans="1:7">
+      <c r="A1403" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1403" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1403" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1403" s="2"/>
+    </row>
+    <row r="1404" spans="1:7">
+      <c r="A1404" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1404" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1404" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1404" s="2"/>
+    </row>
+    <row r="1405" spans="1:7">
+      <c r="A1405" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1405" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1405" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1405" s="2"/>
+    </row>
+    <row r="1406" spans="1:7">
+      <c r="A1406" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1406" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1406" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1406" s="2"/>
+    </row>
+    <row r="1407" spans="1:7">
+      <c r="A1407" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1407" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1407" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1407" s="2"/>
+    </row>
+    <row r="1408" spans="1:7">
+      <c r="A1408" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1408" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1408" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1408" s="2"/>
+    </row>
+    <row r="1409" spans="1:4">
+      <c r="A1409" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1409" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1409" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1409" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1409"/>
+  <dimension ref="A1:H1417"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -21452,9 +21452,9 @@
       <c r="C1399" s="5">
         <v>3</v>
       </c>
-      <c r="D1399" s="2"/>
-      <c r="F1399" s="1"/>
-      <c r="G1399" s="27"/>
+      <c r="D1399" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1400" spans="1:7">
       <c r="A1400" s="6">
@@ -21466,7 +21466,9 @@
       <c r="C1400" s="5">
         <v>3</v>
       </c>
-      <c r="D1400" s="2"/>
+      <c r="D1400" s="2">
+        <v>1</v>
+      </c>
       <c r="F1400" s="1"/>
       <c r="G1400" s="27"/>
     </row>
@@ -21480,7 +21482,9 @@
       <c r="C1401" s="5">
         <v>2</v>
       </c>
-      <c r="D1401" s="2"/>
+      <c r="D1401" s="2">
+        <v>2</v>
+      </c>
       <c r="F1401" s="1"/>
       <c r="G1401" s="27"/>
     </row>
@@ -21494,7 +21498,11 @@
       <c r="C1402" s="5">
         <v>1</v>
       </c>
-      <c r="D1402" s="2"/>
+      <c r="D1402" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1402" s="1"/>
+      <c r="G1402" s="27"/>
     </row>
     <row r="1403" spans="1:7">
       <c r="A1403" s="6">
@@ -21506,7 +21514,11 @@
       <c r="C1403" s="5">
         <v>1</v>
       </c>
-      <c r="D1403" s="2"/>
+      <c r="D1403" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1403" s="1"/>
+      <c r="G1403" s="27"/>
     </row>
     <row r="1404" spans="1:7">
       <c r="A1404" s="6">
@@ -21518,7 +21530,11 @@
       <c r="C1404" s="5">
         <v>3</v>
       </c>
-      <c r="D1404" s="2"/>
+      <c r="D1404" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1404" s="1"/>
+      <c r="G1404" s="27"/>
     </row>
     <row r="1405" spans="1:7">
       <c r="A1405" s="6">
@@ -21530,7 +21546,11 @@
       <c r="C1405" s="5">
         <v>3</v>
       </c>
-      <c r="D1405" s="2"/>
+      <c r="D1405" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1405" s="1"/>
+      <c r="G1405" s="27"/>
     </row>
     <row r="1406" spans="1:7">
       <c r="A1406" s="6">
@@ -21542,7 +21562,11 @@
       <c r="C1406" s="5">
         <v>1</v>
       </c>
-      <c r="D1406" s="2"/>
+      <c r="D1406" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1406" s="1"/>
+      <c r="G1406" s="27"/>
     </row>
     <row r="1407" spans="1:7">
       <c r="A1407" s="6">
@@ -21554,7 +21578,9 @@
       <c r="C1407" s="5">
         <v>1</v>
       </c>
-      <c r="D1407" s="2"/>
+      <c r="D1407" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1408" spans="1:7">
       <c r="A1408" s="6">
@@ -21566,7 +21592,9 @@
       <c r="C1408" s="5">
         <v>4</v>
       </c>
-      <c r="D1408" s="2"/>
+      <c r="D1408" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1409" spans="1:4">
       <c r="A1409" s="6">
@@ -21578,7 +21606,105 @@
       <c r="C1409" s="5">
         <v>4</v>
       </c>
-      <c r="D1409" s="2"/>
+      <c r="D1409" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4">
+      <c r="A1410" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1410" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1410" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1410" s="2"/>
+    </row>
+    <row r="1411" spans="1:4">
+      <c r="A1411" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1411" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1411" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1411" s="2"/>
+    </row>
+    <row r="1412" spans="1:4">
+      <c r="A1412" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1412" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1412" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1412" s="2"/>
+    </row>
+    <row r="1413" spans="1:4">
+      <c r="A1413" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1413" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1413" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1413" s="2"/>
+    </row>
+    <row r="1414" spans="1:4">
+      <c r="A1414" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1414" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1414" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1414" s="2"/>
+    </row>
+    <row r="1415" spans="1:4">
+      <c r="A1415" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1415" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1415" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1415" s="2"/>
+    </row>
+    <row r="1416" spans="1:4">
+      <c r="A1416" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1416" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1416" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1416" s="2"/>
+    </row>
+    <row r="1417" spans="1:4">
+      <c r="A1417" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B1417" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1417" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1417" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -283,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -319,7 +319,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -616,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1417"/>
+  <dimension ref="A1:F1492"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -624,13 +623,12 @@
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="8" width="29.42578125" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" customWidth="1"/>
-    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -11281,7 +11279,7 @@
       <c r="A735" s="6">
         <v>46121</v>
       </c>
-      <c r="B735" s="28" t="s">
+      <c r="B735" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C735" s="5">
@@ -11295,7 +11293,7 @@
       <c r="A736" s="6">
         <v>46121</v>
       </c>
-      <c r="B736" s="28" t="s">
+      <c r="B736" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C736" s="5">
@@ -11305,7 +11303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="737" spans="1:7">
+    <row r="737" spans="1:6">
       <c r="A737" s="6">
         <v>46121</v>
       </c>
@@ -11319,7 +11317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="738" spans="1:7">
+    <row r="738" spans="1:6">
       <c r="A738" s="6">
         <v>46121</v>
       </c>
@@ -11333,9 +11331,8 @@
         <v>1</v>
       </c>
       <c r="F738" s="1"/>
-      <c r="G738" s="27"/>
-    </row>
-    <row r="739" spans="1:7">
+    </row>
+    <row r="739" spans="1:6">
       <c r="A739" s="6">
         <v>46121</v>
       </c>
@@ -11349,9 +11346,8 @@
         <v>1</v>
       </c>
       <c r="F739" s="1"/>
-      <c r="G739" s="27"/>
-    </row>
-    <row r="740" spans="1:7">
+    </row>
+    <row r="740" spans="1:6">
       <c r="A740" s="6">
         <v>46121</v>
       </c>
@@ -11365,9 +11361,8 @@
         <v>0</v>
       </c>
       <c r="F740" s="1"/>
-      <c r="G740" s="27"/>
-    </row>
-    <row r="741" spans="1:7">
+    </row>
+    <row r="741" spans="1:6">
       <c r="A741" s="6">
         <v>46121</v>
       </c>
@@ -11381,9 +11376,8 @@
         <v>0</v>
       </c>
       <c r="F741" s="1"/>
-      <c r="G741" s="27"/>
-    </row>
-    <row r="742" spans="1:7">
+    </row>
+    <row r="742" spans="1:6">
       <c r="A742" s="6">
         <v>46121</v>
       </c>
@@ -11397,9 +11391,8 @@
         <v>2</v>
       </c>
       <c r="F742" s="1"/>
-      <c r="G742" s="27"/>
-    </row>
-    <row r="743" spans="1:7">
+    </row>
+    <row r="743" spans="1:6">
       <c r="A743" s="6">
         <v>46122</v>
       </c>
@@ -11413,9 +11406,8 @@
         <v>1</v>
       </c>
       <c r="F743" s="1"/>
-      <c r="G743" s="27"/>
-    </row>
-    <row r="744" spans="1:7">
+    </row>
+    <row r="744" spans="1:6">
       <c r="A744" s="6">
         <v>46122</v>
       </c>
@@ -11429,9 +11421,8 @@
         <v>1</v>
       </c>
       <c r="F744" s="1"/>
-      <c r="G744" s="27"/>
-    </row>
-    <row r="745" spans="1:7">
+    </row>
+    <row r="745" spans="1:6">
       <c r="A745" s="6">
         <v>46122</v>
       </c>
@@ -11445,9 +11436,8 @@
         <v>1</v>
       </c>
       <c r="F745" s="1"/>
-      <c r="G745" s="27"/>
-    </row>
-    <row r="746" spans="1:7">
+    </row>
+    <row r="746" spans="1:6">
       <c r="A746" s="6">
         <v>46122</v>
       </c>
@@ -11461,9 +11451,8 @@
         <v>1</v>
       </c>
       <c r="F746" s="1"/>
-      <c r="G746" s="27"/>
-    </row>
-    <row r="747" spans="1:7">
+    </row>
+    <row r="747" spans="1:6">
       <c r="A747" s="6">
         <v>46122</v>
       </c>
@@ -11477,9 +11466,8 @@
         <v>2</v>
       </c>
       <c r="F747" s="1"/>
-      <c r="G747" s="27"/>
-    </row>
-    <row r="748" spans="1:7">
+    </row>
+    <row r="748" spans="1:6">
       <c r="A748" s="6">
         <v>46122</v>
       </c>
@@ -11493,9 +11481,8 @@
         <v>2</v>
       </c>
       <c r="F748" s="1"/>
-      <c r="G748" s="27"/>
-    </row>
-    <row r="749" spans="1:7">
+    </row>
+    <row r="749" spans="1:6">
       <c r="A749" s="6">
         <v>46122</v>
       </c>
@@ -11509,7 +11496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="750" spans="1:7">
+    <row r="750" spans="1:6">
       <c r="A750" s="6">
         <v>46122</v>
       </c>
@@ -11523,9 +11510,8 @@
         <v>3</v>
       </c>
       <c r="F750" s="1"/>
-      <c r="G750" s="27"/>
-    </row>
-    <row r="751" spans="1:7">
+    </row>
+    <row r="751" spans="1:6">
       <c r="A751" s="6">
         <v>46122</v>
       </c>
@@ -11539,9 +11525,8 @@
         <v>2</v>
       </c>
       <c r="F751" s="1"/>
-      <c r="G751" s="27"/>
-    </row>
-    <row r="752" spans="1:7">
+    </row>
+    <row r="752" spans="1:6">
       <c r="A752" s="6">
         <v>46122</v>
       </c>
@@ -11555,9 +11540,8 @@
         <v>2</v>
       </c>
       <c r="F752" s="1"/>
-      <c r="G752" s="27"/>
-    </row>
-    <row r="753" spans="1:7">
+    </row>
+    <row r="753" spans="1:6">
       <c r="A753" s="6">
         <v>46122</v>
       </c>
@@ -11571,9 +11555,8 @@
         <v>0</v>
       </c>
       <c r="F753" s="1"/>
-      <c r="G753" s="27"/>
-    </row>
-    <row r="754" spans="1:7">
+    </row>
+    <row r="754" spans="1:6">
       <c r="A754" s="6">
         <v>46122</v>
       </c>
@@ -11587,9 +11570,8 @@
         <v>0</v>
       </c>
       <c r="F754" s="1"/>
-      <c r="G754" s="27"/>
-    </row>
-    <row r="755" spans="1:7">
+    </row>
+    <row r="755" spans="1:6">
       <c r="A755" s="6">
         <v>46123</v>
       </c>
@@ -11603,7 +11585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="756" spans="1:7">
+    <row r="756" spans="1:6">
       <c r="A756" s="6">
         <v>46123</v>
       </c>
@@ -11617,9 +11599,8 @@
         <v>9</v>
       </c>
       <c r="F756" s="1"/>
-      <c r="G756" s="27"/>
-    </row>
-    <row r="757" spans="1:7">
+    </row>
+    <row r="757" spans="1:6">
       <c r="A757" s="6">
         <v>46123</v>
       </c>
@@ -11633,9 +11614,8 @@
         <v>4</v>
       </c>
       <c r="F757" s="1"/>
-      <c r="G757" s="27"/>
-    </row>
-    <row r="758" spans="1:7">
+    </row>
+    <row r="758" spans="1:6">
       <c r="A758" s="6">
         <v>46125</v>
       </c>
@@ -11649,7 +11629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="759" spans="1:7">
+    <row r="759" spans="1:6">
       <c r="A759" s="6">
         <v>46125</v>
       </c>
@@ -11663,9 +11643,8 @@
         <v>2</v>
       </c>
       <c r="F759" s="1"/>
-      <c r="G759" s="27"/>
-    </row>
-    <row r="760" spans="1:7">
+    </row>
+    <row r="760" spans="1:6">
       <c r="A760" s="6">
         <v>46125</v>
       </c>
@@ -11679,9 +11658,8 @@
         <v>4</v>
       </c>
       <c r="F760" s="1"/>
-      <c r="G760" s="27"/>
-    </row>
-    <row r="761" spans="1:7">
+    </row>
+    <row r="761" spans="1:6">
       <c r="A761" s="6">
         <v>46125</v>
       </c>
@@ -11695,9 +11673,8 @@
         <v>0</v>
       </c>
       <c r="F761" s="1"/>
-      <c r="G761" s="27"/>
-    </row>
-    <row r="762" spans="1:7">
+    </row>
+    <row r="762" spans="1:6">
       <c r="A762" s="6">
         <v>46125</v>
       </c>
@@ -11711,9 +11688,8 @@
         <v>0</v>
       </c>
       <c r="F762" s="1"/>
-      <c r="G762" s="27"/>
-    </row>
-    <row r="763" spans="1:7">
+    </row>
+    <row r="763" spans="1:6">
       <c r="A763" s="6">
         <v>46125</v>
       </c>
@@ -11727,9 +11703,8 @@
         <v>2</v>
       </c>
       <c r="F763" s="1"/>
-      <c r="G763" s="27"/>
-    </row>
-    <row r="764" spans="1:7">
+    </row>
+    <row r="764" spans="1:6">
       <c r="A764" s="6">
         <v>46125</v>
       </c>
@@ -11743,9 +11718,8 @@
         <v>2</v>
       </c>
       <c r="F764" s="1"/>
-      <c r="G764" s="27"/>
-    </row>
-    <row r="765" spans="1:7">
+    </row>
+    <row r="765" spans="1:6">
       <c r="A765" s="6">
         <v>46125</v>
       </c>
@@ -11759,9 +11733,8 @@
         <v>0</v>
       </c>
       <c r="F765" s="1"/>
-      <c r="G765" s="27"/>
-    </row>
-    <row r="766" spans="1:7">
+    </row>
+    <row r="766" spans="1:6">
       <c r="A766" s="6">
         <v>46125</v>
       </c>
@@ -11775,9 +11748,8 @@
         <v>0</v>
       </c>
       <c r="F766" s="1"/>
-      <c r="G766" s="27"/>
-    </row>
-    <row r="767" spans="1:7">
+    </row>
+    <row r="767" spans="1:6">
       <c r="A767" s="6">
         <v>46125</v>
       </c>
@@ -11791,11 +11763,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="768" spans="1:7">
+    <row r="768" spans="1:6">
       <c r="A768" s="6">
         <v>46125</v>
       </c>
-      <c r="B768" s="28" t="s">
+      <c r="B768" s="27" t="s">
         <v>4</v>
       </c>
       <c r="C768" s="2">
@@ -11805,11 +11777,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="769" spans="1:7">
+    <row r="769" spans="1:6">
       <c r="A769" s="6">
         <v>46125</v>
       </c>
-      <c r="B769" s="28" t="s">
+      <c r="B769" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C769" s="2">
@@ -11819,7 +11791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:7">
+    <row r="770" spans="1:6">
       <c r="A770" s="6">
         <v>46126</v>
       </c>
@@ -11833,7 +11805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="771" spans="1:7">
+    <row r="771" spans="1:6">
       <c r="A771" s="6">
         <v>46126</v>
       </c>
@@ -11847,9 +11819,8 @@
         <v>2</v>
       </c>
       <c r="F771" s="1"/>
-      <c r="G771" s="27"/>
-    </row>
-    <row r="772" spans="1:7">
+    </row>
+    <row r="772" spans="1:6">
       <c r="A772" s="6">
         <v>46126</v>
       </c>
@@ -11863,9 +11834,8 @@
         <v>4</v>
       </c>
       <c r="F772" s="1"/>
-      <c r="G772" s="27"/>
-    </row>
-    <row r="773" spans="1:7">
+    </row>
+    <row r="773" spans="1:6">
       <c r="A773" s="6">
         <v>46126</v>
       </c>
@@ -11879,9 +11849,8 @@
         <v>4</v>
       </c>
       <c r="F773" s="1"/>
-      <c r="G773" s="27"/>
-    </row>
-    <row r="774" spans="1:7">
+    </row>
+    <row r="774" spans="1:6">
       <c r="A774" s="6">
         <v>46126</v>
       </c>
@@ -11895,9 +11864,8 @@
         <v>5</v>
       </c>
       <c r="F774" s="1"/>
-      <c r="G774" s="27"/>
-    </row>
-    <row r="775" spans="1:7">
+    </row>
+    <row r="775" spans="1:6">
       <c r="A775" s="6">
         <v>46126</v>
       </c>
@@ -11911,9 +11879,8 @@
         <v>5</v>
       </c>
       <c r="F775" s="1"/>
-      <c r="G775" s="27"/>
-    </row>
-    <row r="776" spans="1:7">
+    </row>
+    <row r="776" spans="1:6">
       <c r="A776" s="6">
         <v>46126</v>
       </c>
@@ -11927,9 +11894,8 @@
         <v>1</v>
       </c>
       <c r="F776" s="1"/>
-      <c r="G776" s="27"/>
-    </row>
-    <row r="777" spans="1:7">
+    </row>
+    <row r="777" spans="1:6">
       <c r="A777" s="6">
         <v>46126</v>
       </c>
@@ -11943,9 +11909,8 @@
         <v>0</v>
       </c>
       <c r="F777" s="1"/>
-      <c r="G777" s="27"/>
-    </row>
-    <row r="778" spans="1:7">
+    </row>
+    <row r="778" spans="1:6">
       <c r="A778" s="6">
         <v>46126</v>
       </c>
@@ -11959,7 +11924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:7">
+    <row r="779" spans="1:6">
       <c r="A779" s="6">
         <v>46126</v>
       </c>
@@ -11973,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:7">
+    <row r="780" spans="1:6">
       <c r="A780" s="6">
         <v>46126</v>
       </c>
@@ -11987,7 +11952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:7">
+    <row r="781" spans="1:6">
       <c r="A781" s="6">
         <v>46127</v>
       </c>
@@ -12001,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:7">
+    <row r="782" spans="1:6">
       <c r="A782" s="6">
         <v>46127</v>
       </c>
@@ -12015,9 +11980,8 @@
         <v>0</v>
       </c>
       <c r="F782" s="1"/>
-      <c r="G782" s="27"/>
-    </row>
-    <row r="783" spans="1:7">
+    </row>
+    <row r="783" spans="1:6">
       <c r="A783" s="6">
         <v>46127</v>
       </c>
@@ -12031,9 +11995,8 @@
         <v>1</v>
       </c>
       <c r="F783" s="1"/>
-      <c r="G783" s="27"/>
-    </row>
-    <row r="784" spans="1:7">
+    </row>
+    <row r="784" spans="1:6">
       <c r="A784" s="6">
         <v>46127</v>
       </c>
@@ -12047,9 +12010,8 @@
         <v>1</v>
       </c>
       <c r="F784" s="1"/>
-      <c r="G784" s="27"/>
-    </row>
-    <row r="785" spans="1:7">
+    </row>
+    <row r="785" spans="1:6">
       <c r="A785" s="6">
         <v>46127</v>
       </c>
@@ -12063,9 +12025,8 @@
         <v>2</v>
       </c>
       <c r="F785" s="1"/>
-      <c r="G785" s="27"/>
-    </row>
-    <row r="786" spans="1:7">
+    </row>
+    <row r="786" spans="1:6">
       <c r="A786" s="6">
         <v>46127</v>
       </c>
@@ -12079,9 +12040,8 @@
         <v>2</v>
       </c>
       <c r="F786" s="1"/>
-      <c r="G786" s="27"/>
-    </row>
-    <row r="787" spans="1:7">
+    </row>
+    <row r="787" spans="1:6">
       <c r="A787" s="6">
         <v>46127</v>
       </c>
@@ -12095,9 +12055,8 @@
         <v>7</v>
       </c>
       <c r="F787" s="1"/>
-      <c r="G787" s="27"/>
-    </row>
-    <row r="788" spans="1:7">
+    </row>
+    <row r="788" spans="1:6">
       <c r="A788" s="6">
         <v>46127</v>
       </c>
@@ -12111,9 +12070,8 @@
         <v>7</v>
       </c>
       <c r="F788" s="1"/>
-      <c r="G788" s="27"/>
-    </row>
-    <row r="789" spans="1:7">
+    </row>
+    <row r="789" spans="1:6">
       <c r="A789" s="6">
         <v>46127</v>
       </c>
@@ -12127,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="790" spans="1:7">
+    <row r="790" spans="1:6">
       <c r="A790" s="6">
         <v>46127</v>
       </c>
@@ -12141,7 +12099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="1:7">
+    <row r="791" spans="1:6">
       <c r="A791" s="6">
         <v>46127</v>
       </c>
@@ -12155,7 +12113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="792" spans="1:7">
+    <row r="792" spans="1:6">
       <c r="A792" s="6">
         <v>46127</v>
       </c>
@@ -12169,7 +12127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="793" spans="1:7">
+    <row r="793" spans="1:6">
       <c r="A793" s="6">
         <v>46128</v>
       </c>
@@ -12183,7 +12141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:7">
+    <row r="794" spans="1:6">
       <c r="A794" s="6">
         <v>46128</v>
       </c>
@@ -12197,7 +12155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="795" spans="1:7">
+    <row r="795" spans="1:6">
       <c r="A795" s="6">
         <v>46128</v>
       </c>
@@ -12211,7 +12169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:7">
+    <row r="796" spans="1:6">
       <c r="A796" s="6">
         <v>46128</v>
       </c>
@@ -12225,9 +12183,8 @@
         <v>0</v>
       </c>
       <c r="F796" s="1"/>
-      <c r="G796" s="27"/>
-    </row>
-    <row r="797" spans="1:7">
+    </row>
+    <row r="797" spans="1:6">
       <c r="A797" s="6">
         <v>46128</v>
       </c>
@@ -12241,9 +12198,8 @@
         <v>1</v>
       </c>
       <c r="F797" s="1"/>
-      <c r="G797" s="27"/>
-    </row>
-    <row r="798" spans="1:7">
+    </row>
+    <row r="798" spans="1:6">
       <c r="A798" s="6">
         <v>46128</v>
       </c>
@@ -12257,9 +12213,8 @@
         <v>1</v>
       </c>
       <c r="F798" s="1"/>
-      <c r="G798" s="27"/>
-    </row>
-    <row r="799" spans="1:7">
+    </row>
+    <row r="799" spans="1:6">
       <c r="A799" s="6">
         <v>46128</v>
       </c>
@@ -12273,9 +12228,8 @@
         <v>1</v>
       </c>
       <c r="F799" s="1"/>
-      <c r="G799" s="27"/>
-    </row>
-    <row r="800" spans="1:7">
+    </row>
+    <row r="800" spans="1:6">
       <c r="A800" s="6">
         <v>46128</v>
       </c>
@@ -12289,9 +12243,8 @@
         <v>1</v>
       </c>
       <c r="F800" s="1"/>
-      <c r="G800" s="27"/>
-    </row>
-    <row r="801" spans="1:7">
+    </row>
+    <row r="801" spans="1:6">
       <c r="A801" s="6">
         <v>46128</v>
       </c>
@@ -12305,9 +12258,8 @@
         <v>1</v>
       </c>
       <c r="F801" s="1"/>
-      <c r="G801" s="27"/>
-    </row>
-    <row r="802" spans="1:7">
+    </row>
+    <row r="802" spans="1:6">
       <c r="A802" s="6">
         <v>46128</v>
       </c>
@@ -12321,9 +12273,8 @@
         <v>0</v>
       </c>
       <c r="F802" s="1"/>
-      <c r="G802" s="27"/>
-    </row>
-    <row r="803" spans="1:7">
+    </row>
+    <row r="803" spans="1:6">
       <c r="A803" s="6">
         <v>46128</v>
       </c>
@@ -12337,7 +12288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:7">
+    <row r="804" spans="1:6">
       <c r="A804" s="6">
         <v>46128</v>
       </c>
@@ -12351,7 +12302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:7">
+    <row r="805" spans="1:6">
       <c r="A805" s="6">
         <v>46128</v>
       </c>
@@ -12365,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:7">
+    <row r="806" spans="1:6">
       <c r="A806" s="6">
         <v>46129</v>
       </c>
@@ -12379,7 +12330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:7">
+    <row r="807" spans="1:6">
       <c r="A807" s="6">
         <v>46129</v>
       </c>
@@ -12393,9 +12344,8 @@
         <v>0</v>
       </c>
       <c r="F807" s="1"/>
-      <c r="G807" s="27"/>
-    </row>
-    <row r="808" spans="1:7">
+    </row>
+    <row r="808" spans="1:6">
       <c r="A808" s="6">
         <v>46129</v>
       </c>
@@ -12409,9 +12359,8 @@
         <v>0</v>
       </c>
       <c r="F808" s="1"/>
-      <c r="G808" s="27"/>
-    </row>
-    <row r="809" spans="1:7">
+    </row>
+    <row r="809" spans="1:6">
       <c r="A809" s="6">
         <v>46129</v>
       </c>
@@ -12425,9 +12374,8 @@
         <v>0</v>
       </c>
       <c r="F809" s="1"/>
-      <c r="G809" s="27"/>
-    </row>
-    <row r="810" spans="1:7">
+    </row>
+    <row r="810" spans="1:6">
       <c r="A810" s="6">
         <v>46129</v>
       </c>
@@ -12441,9 +12389,8 @@
         <v>1</v>
       </c>
       <c r="F810" s="1"/>
-      <c r="G810" s="27"/>
-    </row>
-    <row r="811" spans="1:7">
+    </row>
+    <row r="811" spans="1:6">
       <c r="A811" s="6">
         <v>46129</v>
       </c>
@@ -12457,9 +12404,8 @@
         <v>5</v>
       </c>
       <c r="F811" s="1"/>
-      <c r="G811" s="27"/>
-    </row>
-    <row r="812" spans="1:7">
+    </row>
+    <row r="812" spans="1:6">
       <c r="A812" s="6">
         <v>46129</v>
       </c>
@@ -12473,9 +12419,8 @@
         <v>5</v>
       </c>
       <c r="F812" s="1"/>
-      <c r="G812" s="27"/>
-    </row>
-    <row r="813" spans="1:7">
+    </row>
+    <row r="813" spans="1:6">
       <c r="A813" s="6">
         <v>46129</v>
       </c>
@@ -12489,7 +12434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="814" spans="1:7">
+    <row r="814" spans="1:6">
       <c r="A814" s="6">
         <v>46129</v>
       </c>
@@ -12503,7 +12448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="815" spans="1:7">
+    <row r="815" spans="1:6">
       <c r="A815" s="6">
         <v>46129</v>
       </c>
@@ -12517,7 +12462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:7">
+    <row r="816" spans="1:6">
       <c r="A816" s="6">
         <v>46129</v>
       </c>
@@ -12531,7 +12476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:7">
+    <row r="817" spans="1:6">
       <c r="A817" s="6">
         <v>46130</v>
       </c>
@@ -12545,7 +12490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="818" spans="1:7">
+    <row r="818" spans="1:6">
       <c r="A818" s="6">
         <v>46130</v>
       </c>
@@ -12559,9 +12504,8 @@
         <v>8</v>
       </c>
       <c r="F818" s="1"/>
-      <c r="G818" s="27"/>
-    </row>
-    <row r="819" spans="1:7">
+    </row>
+    <row r="819" spans="1:6">
       <c r="A819" s="6">
         <v>46130</v>
       </c>
@@ -12575,9 +12519,8 @@
         <v>12</v>
       </c>
       <c r="F819" s="1"/>
-      <c r="G819" s="27"/>
-    </row>
-    <row r="820" spans="1:7">
+    </row>
+    <row r="820" spans="1:6">
       <c r="A820" s="6">
         <v>46130</v>
       </c>
@@ -12591,9 +12534,8 @@
         <v>12</v>
       </c>
       <c r="F820" s="1"/>
-      <c r="G820" s="27"/>
-    </row>
-    <row r="821" spans="1:7">
+    </row>
+    <row r="821" spans="1:6">
       <c r="A821" s="6">
         <v>46132</v>
       </c>
@@ -12607,7 +12549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="822" spans="1:7">
+    <row r="822" spans="1:6">
       <c r="A822" s="6">
         <v>46132</v>
       </c>
@@ -12621,9 +12563,8 @@
         <v>4</v>
       </c>
       <c r="F822" s="1"/>
-      <c r="G822" s="27"/>
-    </row>
-    <row r="823" spans="1:7">
+    </row>
+    <row r="823" spans="1:6">
       <c r="A823" s="6">
         <v>46132</v>
       </c>
@@ -12637,9 +12578,8 @@
         <v>4</v>
       </c>
       <c r="F823" s="1"/>
-      <c r="G823" s="27"/>
-    </row>
-    <row r="824" spans="1:7">
+    </row>
+    <row r="824" spans="1:6">
       <c r="A824" s="6">
         <v>46132</v>
       </c>
@@ -12653,9 +12593,8 @@
         <v>1</v>
       </c>
       <c r="F824" s="1"/>
-      <c r="G824" s="27"/>
-    </row>
-    <row r="825" spans="1:7">
+    </row>
+    <row r="825" spans="1:6">
       <c r="A825" s="6">
         <v>46132</v>
       </c>
@@ -12669,9 +12608,8 @@
         <v>1</v>
       </c>
       <c r="F825" s="1"/>
-      <c r="G825" s="27"/>
-    </row>
-    <row r="826" spans="1:7">
+    </row>
+    <row r="826" spans="1:6">
       <c r="A826" s="6">
         <v>46132</v>
       </c>
@@ -12685,9 +12623,8 @@
         <v>1</v>
       </c>
       <c r="F826" s="1"/>
-      <c r="G826" s="27"/>
-    </row>
-    <row r="827" spans="1:7">
+    </row>
+    <row r="827" spans="1:6">
       <c r="A827" s="6">
         <v>46132</v>
       </c>
@@ -12701,9 +12638,8 @@
         <v>1</v>
       </c>
       <c r="F827" s="1"/>
-      <c r="G827" s="27"/>
-    </row>
-    <row r="828" spans="1:7">
+    </row>
+    <row r="828" spans="1:6">
       <c r="A828" s="6">
         <v>46133</v>
       </c>
@@ -12717,7 +12653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:7">
+    <row r="829" spans="1:6">
       <c r="A829" s="6">
         <v>46133</v>
       </c>
@@ -12731,9 +12667,8 @@
         <v>0</v>
       </c>
       <c r="F829" s="1"/>
-      <c r="G829" s="27"/>
-    </row>
-    <row r="830" spans="1:7">
+    </row>
+    <row r="830" spans="1:6">
       <c r="A830" s="6">
         <v>46133</v>
       </c>
@@ -12747,9 +12682,8 @@
         <v>0</v>
       </c>
       <c r="F830" s="1"/>
-      <c r="G830" s="27"/>
-    </row>
-    <row r="831" spans="1:7">
+    </row>
+    <row r="831" spans="1:6">
       <c r="A831" s="6">
         <v>46133</v>
       </c>
@@ -12763,9 +12697,8 @@
         <v>0</v>
       </c>
       <c r="F831" s="1"/>
-      <c r="G831" s="27"/>
-    </row>
-    <row r="832" spans="1:7">
+    </row>
+    <row r="832" spans="1:6">
       <c r="A832" s="6">
         <v>46133</v>
       </c>
@@ -12779,9 +12712,8 @@
         <v>3</v>
       </c>
       <c r="F832" s="1"/>
-      <c r="G832" s="27"/>
-    </row>
-    <row r="833" spans="1:7">
+    </row>
+    <row r="833" spans="1:6">
       <c r="A833" s="6">
         <v>46133</v>
       </c>
@@ -12795,9 +12727,8 @@
         <v>3</v>
       </c>
       <c r="F833" s="1"/>
-      <c r="G833" s="27"/>
-    </row>
-    <row r="834" spans="1:7">
+    </row>
+    <row r="834" spans="1:6">
       <c r="A834" s="6">
         <v>46133</v>
       </c>
@@ -12811,9 +12742,8 @@
         <v>1</v>
       </c>
       <c r="F834" s="1"/>
-      <c r="G834" s="27"/>
-    </row>
-    <row r="835" spans="1:7">
+    </row>
+    <row r="835" spans="1:6">
       <c r="A835" s="6">
         <v>46133</v>
       </c>
@@ -12827,9 +12757,8 @@
         <v>1</v>
       </c>
       <c r="F835" s="1"/>
-      <c r="G835" s="27"/>
-    </row>
-    <row r="836" spans="1:7">
+    </row>
+    <row r="836" spans="1:6">
       <c r="A836" s="6">
         <v>46133</v>
       </c>
@@ -12843,7 +12772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="837" spans="1:7">
+    <row r="837" spans="1:6">
       <c r="A837" s="6">
         <v>46133</v>
       </c>
@@ -12857,7 +12786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="838" spans="1:7">
+    <row r="838" spans="1:6">
       <c r="A838" s="6">
         <v>46133</v>
       </c>
@@ -12871,7 +12800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:7">
+    <row r="839" spans="1:6">
       <c r="A839" s="6">
         <v>46133</v>
       </c>
@@ -12885,7 +12814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:7">
+    <row r="840" spans="1:6">
       <c r="A840" s="6">
         <v>46133</v>
       </c>
@@ -12899,7 +12828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="841" spans="1:7">
+    <row r="841" spans="1:6">
       <c r="A841" s="6">
         <v>46134</v>
       </c>
@@ -12913,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:7">
+    <row r="842" spans="1:6">
       <c r="A842" s="6">
         <v>46134</v>
       </c>
@@ -12927,9 +12856,8 @@
         <v>0</v>
       </c>
       <c r="F842" s="1"/>
-      <c r="G842" s="27"/>
-    </row>
-    <row r="843" spans="1:7">
+    </row>
+    <row r="843" spans="1:6">
       <c r="A843" s="6">
         <v>46134</v>
       </c>
@@ -12943,9 +12871,8 @@
         <v>2</v>
       </c>
       <c r="F843" s="1"/>
-      <c r="G843" s="27"/>
-    </row>
-    <row r="844" spans="1:7">
+    </row>
+    <row r="844" spans="1:6">
       <c r="A844" s="6">
         <v>46134</v>
       </c>
@@ -12959,9 +12886,8 @@
         <v>2</v>
       </c>
       <c r="F844" s="1"/>
-      <c r="G844" s="27"/>
-    </row>
-    <row r="845" spans="1:7">
+    </row>
+    <row r="845" spans="1:6">
       <c r="A845" s="6">
         <v>46134</v>
       </c>
@@ -12975,9 +12901,8 @@
         <v>0</v>
       </c>
       <c r="F845" s="1"/>
-      <c r="G845" s="27"/>
-    </row>
-    <row r="846" spans="1:7">
+    </row>
+    <row r="846" spans="1:6">
       <c r="A846" s="6">
         <v>46134</v>
       </c>
@@ -12991,9 +12916,8 @@
         <v>0</v>
       </c>
       <c r="F846" s="1"/>
-      <c r="G846" s="27"/>
-    </row>
-    <row r="847" spans="1:7">
+    </row>
+    <row r="847" spans="1:6">
       <c r="A847" s="6">
         <v>46134</v>
       </c>
@@ -13007,9 +12931,8 @@
         <v>6</v>
       </c>
       <c r="F847" s="1"/>
-      <c r="G847" s="27"/>
-    </row>
-    <row r="848" spans="1:7">
+    </row>
+    <row r="848" spans="1:6">
       <c r="A848" s="6">
         <v>46134</v>
       </c>
@@ -13023,9 +12946,8 @@
         <v>3</v>
       </c>
       <c r="F848" s="1"/>
-      <c r="G848" s="27"/>
-    </row>
-    <row r="849" spans="1:7">
+    </row>
+    <row r="849" spans="1:6">
       <c r="A849" s="6">
         <v>46134</v>
       </c>
@@ -13039,7 +12961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="850" spans="1:7">
+    <row r="850" spans="1:6">
       <c r="A850" s="6">
         <v>46134</v>
       </c>
@@ -13053,7 +12975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="851" spans="1:7">
+    <row r="851" spans="1:6">
       <c r="A851" s="6">
         <v>46134</v>
       </c>
@@ -13067,7 +12989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="852" spans="1:7">
+    <row r="852" spans="1:6">
       <c r="A852" s="6">
         <v>46135</v>
       </c>
@@ -13081,7 +13003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="853" spans="1:7">
+    <row r="853" spans="1:6">
       <c r="A853" s="6">
         <v>46135</v>
       </c>
@@ -13095,9 +13017,8 @@
         <v>2</v>
       </c>
       <c r="F853" s="1"/>
-      <c r="G853" s="27"/>
-    </row>
-    <row r="854" spans="1:7">
+    </row>
+    <row r="854" spans="1:6">
       <c r="A854" s="6">
         <v>46135</v>
       </c>
@@ -13111,9 +13032,8 @@
         <v>1</v>
       </c>
       <c r="F854" s="1"/>
-      <c r="G854" s="27"/>
-    </row>
-    <row r="855" spans="1:7">
+    </row>
+    <row r="855" spans="1:6">
       <c r="A855" s="6">
         <v>46135</v>
       </c>
@@ -13127,9 +13047,8 @@
         <v>1</v>
       </c>
       <c r="F855" s="1"/>
-      <c r="G855" s="27"/>
-    </row>
-    <row r="856" spans="1:7">
+    </row>
+    <row r="856" spans="1:6">
       <c r="A856" s="6">
         <v>46135</v>
       </c>
@@ -13143,9 +13062,8 @@
         <v>6</v>
       </c>
       <c r="F856" s="1"/>
-      <c r="G856" s="27"/>
-    </row>
-    <row r="857" spans="1:7">
+    </row>
+    <row r="857" spans="1:6">
       <c r="A857" s="6">
         <v>46135</v>
       </c>
@@ -13159,9 +13077,8 @@
         <v>0</v>
       </c>
       <c r="F857" s="1"/>
-      <c r="G857" s="27"/>
-    </row>
-    <row r="858" spans="1:7">
+    </row>
+    <row r="858" spans="1:6">
       <c r="A858" s="6">
         <v>46135</v>
       </c>
@@ -13175,9 +13092,8 @@
         <v>0</v>
       </c>
       <c r="F858" s="1"/>
-      <c r="G858" s="27"/>
-    </row>
-    <row r="859" spans="1:7">
+    </row>
+    <row r="859" spans="1:6">
       <c r="A859" s="6">
         <v>46135</v>
       </c>
@@ -13191,9 +13107,8 @@
         <v>5</v>
       </c>
       <c r="F859" s="1"/>
-      <c r="G859" s="27"/>
-    </row>
-    <row r="860" spans="1:7">
+    </row>
+    <row r="860" spans="1:6">
       <c r="A860" s="6">
         <v>46135</v>
       </c>
@@ -13207,9 +13122,8 @@
         <v>5</v>
       </c>
       <c r="F860" s="1"/>
-      <c r="G860" s="27"/>
-    </row>
-    <row r="861" spans="1:7">
+    </row>
+    <row r="861" spans="1:6">
       <c r="A861" s="6">
         <v>46135</v>
       </c>
@@ -13223,9 +13137,8 @@
         <v>3</v>
       </c>
       <c r="F861" s="1"/>
-      <c r="G861" s="27"/>
-    </row>
-    <row r="862" spans="1:7">
+    </row>
+    <row r="862" spans="1:6">
       <c r="A862" s="6">
         <v>46135</v>
       </c>
@@ -13239,9 +13152,8 @@
         <v>3</v>
       </c>
       <c r="F862" s="1"/>
-      <c r="G862" s="27"/>
-    </row>
-    <row r="863" spans="1:7">
+    </row>
+    <row r="863" spans="1:6">
       <c r="A863" s="6">
         <v>46136</v>
       </c>
@@ -13255,7 +13167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="864" spans="1:7">
+    <row r="864" spans="1:6">
       <c r="A864" s="6">
         <v>46136</v>
       </c>
@@ -13269,9 +13181,8 @@
         <v>6</v>
       </c>
       <c r="F864" s="1"/>
-      <c r="G864" s="27"/>
-    </row>
-    <row r="865" spans="1:7">
+    </row>
+    <row r="865" spans="1:6">
       <c r="A865" s="6">
         <v>46136</v>
       </c>
@@ -13285,9 +13196,8 @@
         <v>3</v>
       </c>
       <c r="F865" s="1"/>
-      <c r="G865" s="27"/>
-    </row>
-    <row r="866" spans="1:7">
+    </row>
+    <row r="866" spans="1:6">
       <c r="A866" s="6">
         <v>46136</v>
       </c>
@@ -13301,9 +13211,8 @@
         <v>1</v>
       </c>
       <c r="F866" s="1"/>
-      <c r="G866" s="27"/>
-    </row>
-    <row r="867" spans="1:7">
+    </row>
+    <row r="867" spans="1:6">
       <c r="A867" s="6">
         <v>46136</v>
       </c>
@@ -13317,9 +13226,8 @@
         <v>1</v>
       </c>
       <c r="F867" s="1"/>
-      <c r="G867" s="27"/>
-    </row>
-    <row r="868" spans="1:7">
+    </row>
+    <row r="868" spans="1:6">
       <c r="A868" s="6">
         <v>46136</v>
       </c>
@@ -13333,9 +13241,8 @@
         <v>6</v>
       </c>
       <c r="F868" s="1"/>
-      <c r="G868" s="27"/>
-    </row>
-    <row r="869" spans="1:7">
+    </row>
+    <row r="869" spans="1:6">
       <c r="A869" s="6">
         <v>46136</v>
       </c>
@@ -13349,9 +13256,8 @@
         <v>6</v>
       </c>
       <c r="F869" s="1"/>
-      <c r="G869" s="27"/>
-    </row>
-    <row r="870" spans="1:7">
+    </row>
+    <row r="870" spans="1:6">
       <c r="A870" s="6">
         <v>46136</v>
       </c>
@@ -13365,9 +13271,8 @@
         <v>1</v>
       </c>
       <c r="F870" s="1"/>
-      <c r="G870" s="27"/>
-    </row>
-    <row r="871" spans="1:7">
+    </row>
+    <row r="871" spans="1:6">
       <c r="A871" s="6">
         <v>46136</v>
       </c>
@@ -13381,9 +13286,8 @@
         <v>1</v>
       </c>
       <c r="F871" s="1"/>
-      <c r="G871" s="27"/>
-    </row>
-    <row r="872" spans="1:7">
+    </row>
+    <row r="872" spans="1:6">
       <c r="A872" s="6">
         <v>46136</v>
       </c>
@@ -13397,9 +13301,8 @@
         <v>2</v>
       </c>
       <c r="F872" s="1"/>
-      <c r="G872" s="27"/>
-    </row>
-    <row r="873" spans="1:7">
+    </row>
+    <row r="873" spans="1:6">
       <c r="A873" s="6">
         <v>46136</v>
       </c>
@@ -13413,7 +13316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="874" spans="1:7">
+    <row r="874" spans="1:6">
       <c r="A874" s="6">
         <v>46136</v>
       </c>
@@ -13427,7 +13330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="875" spans="1:7">
+    <row r="875" spans="1:6">
       <c r="A875" s="6">
         <v>46136</v>
       </c>
@@ -13441,7 +13344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="876" spans="1:7">
+    <row r="876" spans="1:6">
       <c r="A876" s="6">
         <v>46136</v>
       </c>
@@ -13455,7 +13358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="877" spans="1:7">
+    <row r="877" spans="1:6">
       <c r="A877" s="6">
         <v>46136</v>
       </c>
@@ -13469,7 +13372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="878" spans="1:7">
+    <row r="878" spans="1:6">
       <c r="A878" s="6">
         <v>46139</v>
       </c>
@@ -13483,7 +13386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="879" spans="1:7">
+    <row r="879" spans="1:6">
       <c r="A879" s="6">
         <v>46139</v>
       </c>
@@ -13497,9 +13400,8 @@
         <v>1</v>
       </c>
       <c r="F879" s="1"/>
-      <c r="G879" s="27"/>
-    </row>
-    <row r="880" spans="1:7">
+    </row>
+    <row r="880" spans="1:6">
       <c r="A880" s="6">
         <v>46139</v>
       </c>
@@ -13513,9 +13415,8 @@
         <v>1</v>
       </c>
       <c r="F880" s="1"/>
-      <c r="G880" s="27"/>
-    </row>
-    <row r="881" spans="1:8">
+    </row>
+    <row r="881" spans="1:6">
       <c r="A881" s="6">
         <v>46139</v>
       </c>
@@ -13529,9 +13430,8 @@
         <v>1</v>
       </c>
       <c r="F881" s="1"/>
-      <c r="G881" s="27"/>
-    </row>
-    <row r="882" spans="1:8">
+    </row>
+    <row r="882" spans="1:6">
       <c r="A882" s="6">
         <v>46139</v>
       </c>
@@ -13545,9 +13445,8 @@
         <v>1</v>
       </c>
       <c r="F882" s="1"/>
-      <c r="G882" s="27"/>
-    </row>
-    <row r="883" spans="1:8">
+    </row>
+    <row r="883" spans="1:6">
       <c r="A883" s="6">
         <v>46139</v>
       </c>
@@ -13561,9 +13460,8 @@
         <v>1</v>
       </c>
       <c r="F883" s="1"/>
-      <c r="G883" s="27"/>
-    </row>
-    <row r="884" spans="1:8">
+    </row>
+    <row r="884" spans="1:6">
       <c r="A884" s="6">
         <v>46139</v>
       </c>
@@ -13577,9 +13475,8 @@
         <v>1</v>
       </c>
       <c r="F884" s="1"/>
-      <c r="G884" s="27"/>
-    </row>
-    <row r="885" spans="1:8">
+    </row>
+    <row r="885" spans="1:6">
       <c r="A885" s="6">
         <v>46139</v>
       </c>
@@ -13593,9 +13490,8 @@
         <v>1</v>
       </c>
       <c r="F885" s="1"/>
-      <c r="G885" s="27"/>
-    </row>
-    <row r="886" spans="1:8">
+    </row>
+    <row r="886" spans="1:6">
       <c r="A886" s="6">
         <v>46140</v>
       </c>
@@ -13610,7 +13506,7 @@
       </c>
       <c r="F886" s="1"/>
     </row>
-    <row r="887" spans="1:8">
+    <row r="887" spans="1:6">
       <c r="A887" s="6">
         <v>46140</v>
       </c>
@@ -13624,10 +13520,8 @@
         <v>4</v>
       </c>
       <c r="F887" s="1"/>
-      <c r="G887" s="1"/>
-      <c r="H887" s="27"/>
-    </row>
-    <row r="888" spans="1:8">
+    </row>
+    <row r="888" spans="1:6">
       <c r="A888" s="6">
         <v>46140</v>
       </c>
@@ -13640,10 +13534,8 @@
       <c r="D888" s="2">
         <v>4</v>
       </c>
-      <c r="G888" s="1"/>
-      <c r="H888" s="27"/>
-    </row>
-    <row r="889" spans="1:8">
+    </row>
+    <row r="889" spans="1:6">
       <c r="A889" s="6">
         <v>46140</v>
       </c>
@@ -13656,10 +13548,8 @@
       <c r="D889" s="2">
         <v>4</v>
       </c>
-      <c r="G889" s="1"/>
-      <c r="H889" s="27"/>
-    </row>
-    <row r="890" spans="1:8">
+    </row>
+    <row r="890" spans="1:6">
       <c r="A890" s="6">
         <v>46140</v>
       </c>
@@ -13672,10 +13562,8 @@
       <c r="D890" s="2">
         <v>0</v>
       </c>
-      <c r="G890" s="1"/>
-      <c r="H890" s="27"/>
-    </row>
-    <row r="891" spans="1:8">
+    </row>
+    <row r="891" spans="1:6">
       <c r="A891" s="6">
         <v>46140</v>
       </c>
@@ -13688,10 +13576,8 @@
       <c r="D891" s="2">
         <v>0</v>
       </c>
-      <c r="G891" s="1"/>
-      <c r="H891" s="27"/>
-    </row>
-    <row r="892" spans="1:8">
+    </row>
+    <row r="892" spans="1:6">
       <c r="A892" s="6">
         <v>46140</v>
       </c>
@@ -13704,10 +13590,8 @@
       <c r="D892" s="2">
         <v>2</v>
       </c>
-      <c r="G892" s="1"/>
-      <c r="H892" s="27"/>
-    </row>
-    <row r="893" spans="1:8">
+    </row>
+    <row r="893" spans="1:6">
       <c r="A893" s="6">
         <v>46140</v>
       </c>
@@ -13720,10 +13604,8 @@
       <c r="D893" s="2">
         <v>2</v>
       </c>
-      <c r="G893" s="1"/>
-      <c r="H893" s="27"/>
-    </row>
-    <row r="894" spans="1:8">
+    </row>
+    <row r="894" spans="1:6">
       <c r="A894" s="6">
         <v>46140</v>
       </c>
@@ -13736,10 +13618,8 @@
       <c r="D894" s="2">
         <v>10</v>
       </c>
-      <c r="G894" s="1"/>
-      <c r="H894" s="27"/>
-    </row>
-    <row r="895" spans="1:8">
+    </row>
+    <row r="895" spans="1:6">
       <c r="A895" s="6">
         <v>46140</v>
       </c>
@@ -13753,7 +13633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="896" spans="1:8">
+    <row r="896" spans="1:6">
       <c r="A896" s="6">
         <v>46140</v>
       </c>
@@ -13767,7 +13647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="897" spans="1:8">
+    <row r="897" spans="1:6">
       <c r="A897" s="6">
         <v>46141</v>
       </c>
@@ -13781,7 +13661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="898" spans="1:8">
+    <row r="898" spans="1:6">
       <c r="A898" s="6">
         <v>46141</v>
       </c>
@@ -13795,7 +13675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="899" spans="1:8">
+    <row r="899" spans="1:6">
       <c r="A899" s="6">
         <v>46141</v>
       </c>
@@ -13809,7 +13689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="900" spans="1:8">
+    <row r="900" spans="1:6">
       <c r="A900" s="6">
         <v>46141</v>
       </c>
@@ -13823,7 +13703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="901" spans="1:8">
+    <row r="901" spans="1:6">
       <c r="A901" s="6">
         <v>46141</v>
       </c>
@@ -13837,7 +13717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="902" spans="1:8">
+    <row r="902" spans="1:6">
       <c r="A902" s="6">
         <v>46141</v>
       </c>
@@ -13851,9 +13731,8 @@
         <v>1</v>
       </c>
       <c r="F902" s="1"/>
-      <c r="G902" s="27"/>
-    </row>
-    <row r="903" spans="1:8">
+    </row>
+    <row r="903" spans="1:6">
       <c r="A903" s="6">
         <v>46141</v>
       </c>
@@ -13867,9 +13746,8 @@
         <v>1</v>
       </c>
       <c r="F903" s="1"/>
-      <c r="G903" s="27"/>
-    </row>
-    <row r="904" spans="1:8">
+    </row>
+    <row r="904" spans="1:6">
       <c r="A904" s="6">
         <v>46141</v>
       </c>
@@ -13883,9 +13761,8 @@
         <v>2</v>
       </c>
       <c r="F904" s="1"/>
-      <c r="G904" s="27"/>
-    </row>
-    <row r="905" spans="1:8">
+    </row>
+    <row r="905" spans="1:6">
       <c r="A905" s="6">
         <v>46141</v>
       </c>
@@ -13899,9 +13776,8 @@
         <v>2</v>
       </c>
       <c r="F905" s="1"/>
-      <c r="G905" s="27"/>
-    </row>
-    <row r="906" spans="1:8">
+    </row>
+    <row r="906" spans="1:6">
       <c r="A906" s="6">
         <v>46141</v>
       </c>
@@ -13915,9 +13791,8 @@
         <v>2</v>
       </c>
       <c r="F906" s="1"/>
-      <c r="G906" s="27"/>
-    </row>
-    <row r="907" spans="1:8">
+    </row>
+    <row r="907" spans="1:6">
       <c r="A907" s="6">
         <v>46142</v>
       </c>
@@ -13932,7 +13807,7 @@
       </c>
       <c r="F907" s="1"/>
     </row>
-    <row r="908" spans="1:8">
+    <row r="908" spans="1:6">
       <c r="A908" s="6">
         <v>46142</v>
       </c>
@@ -13946,10 +13821,8 @@
         <v>4</v>
       </c>
       <c r="F908" s="1"/>
-      <c r="G908" s="1"/>
-      <c r="H908" s="27"/>
-    </row>
-    <row r="909" spans="1:8">
+    </row>
+    <row r="909" spans="1:6">
       <c r="A909" s="6">
         <v>46142</v>
       </c>
@@ -13963,10 +13836,8 @@
         <v>7</v>
       </c>
       <c r="F909" s="1"/>
-      <c r="G909" s="1"/>
-      <c r="H909" s="27"/>
-    </row>
-    <row r="910" spans="1:8">
+    </row>
+    <row r="910" spans="1:6">
       <c r="A910" s="6">
         <v>46142</v>
       </c>
@@ -13980,10 +13851,8 @@
         <v>7</v>
       </c>
       <c r="F910" s="1"/>
-      <c r="G910" s="1"/>
-      <c r="H910" s="27"/>
-    </row>
-    <row r="911" spans="1:8">
+    </row>
+    <row r="911" spans="1:6">
       <c r="A911" s="6">
         <v>46142</v>
       </c>
@@ -13996,10 +13865,8 @@
       <c r="D911" s="2">
         <v>0</v>
       </c>
-      <c r="G911" s="1"/>
-      <c r="H911" s="27"/>
-    </row>
-    <row r="912" spans="1:8">
+    </row>
+    <row r="912" spans="1:6">
       <c r="A912" s="6">
         <v>46142</v>
       </c>
@@ -14012,10 +13879,8 @@
       <c r="D912" s="2">
         <v>0</v>
       </c>
-      <c r="G912" s="1"/>
-      <c r="H912" s="27"/>
-    </row>
-    <row r="913" spans="1:8">
+    </row>
+    <row r="913" spans="1:6">
       <c r="A913" s="6">
         <v>46142</v>
       </c>
@@ -14028,10 +13893,8 @@
       <c r="D913" s="2">
         <v>4</v>
       </c>
-      <c r="G913" s="1"/>
-      <c r="H913" s="27"/>
-    </row>
-    <row r="914" spans="1:8">
+    </row>
+    <row r="914" spans="1:6">
       <c r="A914" s="6">
         <v>46142</v>
       </c>
@@ -14044,10 +13907,8 @@
       <c r="D914" s="2">
         <v>4</v>
       </c>
-      <c r="G914" s="1"/>
-      <c r="H914" s="27"/>
-    </row>
-    <row r="915" spans="1:8">
+    </row>
+    <row r="915" spans="1:6">
       <c r="A915" s="6">
         <v>46142</v>
       </c>
@@ -14060,10 +13921,8 @@
       <c r="D915" s="2">
         <v>4</v>
       </c>
-      <c r="G915" s="1"/>
-      <c r="H915" s="27"/>
-    </row>
-    <row r="916" spans="1:8">
+    </row>
+    <row r="916" spans="1:6">
       <c r="A916" s="6">
         <v>46142</v>
       </c>
@@ -14077,7 +13936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="917" spans="1:8">
+    <row r="917" spans="1:6">
       <c r="A917" s="6">
         <v>46144</v>
       </c>
@@ -14090,10 +13949,8 @@
       <c r="D917" s="2">
         <v>1</v>
       </c>
-      <c r="G917" s="1"/>
-      <c r="H917" s="27"/>
-    </row>
-    <row r="918" spans="1:8">
+    </row>
+    <row r="918" spans="1:6">
       <c r="A918" s="6">
         <v>46144</v>
       </c>
@@ -14106,10 +13963,8 @@
       <c r="D918" s="2">
         <v>1</v>
       </c>
-      <c r="G918" s="1"/>
-      <c r="H918" s="27"/>
-    </row>
-    <row r="919" spans="1:8">
+    </row>
+    <row r="919" spans="1:6">
       <c r="A919" s="6">
         <v>46144</v>
       </c>
@@ -14122,10 +13977,8 @@
       <c r="D919" s="2">
         <v>7</v>
       </c>
-      <c r="G919" s="1"/>
-      <c r="H919" s="27"/>
-    </row>
-    <row r="920" spans="1:8">
+    </row>
+    <row r="920" spans="1:6">
       <c r="A920" s="6">
         <v>46144</v>
       </c>
@@ -14138,10 +13991,8 @@
       <c r="D920" s="2">
         <v>8</v>
       </c>
-      <c r="G920" s="1"/>
-      <c r="H920" s="27"/>
-    </row>
-    <row r="921" spans="1:8">
+    </row>
+    <row r="921" spans="1:6">
       <c r="A921" s="6">
         <v>46146</v>
       </c>
@@ -14154,10 +14005,8 @@
       <c r="D921" s="2">
         <v>2</v>
       </c>
-      <c r="G921" s="1"/>
-      <c r="H921" s="27"/>
-    </row>
-    <row r="922" spans="1:8">
+    </row>
+    <row r="922" spans="1:6">
       <c r="A922" s="6">
         <v>46146</v>
       </c>
@@ -14170,10 +14019,8 @@
       <c r="D922" s="2">
         <v>2</v>
       </c>
-      <c r="G922" s="1"/>
-      <c r="H922" s="27"/>
-    </row>
-    <row r="923" spans="1:8">
+    </row>
+    <row r="923" spans="1:6">
       <c r="A923" s="6">
         <v>46146</v>
       </c>
@@ -14186,10 +14033,8 @@
       <c r="D923" s="2">
         <v>2</v>
       </c>
-      <c r="G923" s="1"/>
-      <c r="H923" s="27"/>
-    </row>
-    <row r="924" spans="1:8">
+    </row>
+    <row r="924" spans="1:6">
       <c r="A924" s="6">
         <v>46146</v>
       </c>
@@ -14202,10 +14047,8 @@
       <c r="D924" s="2">
         <v>2</v>
       </c>
-      <c r="G924" s="1"/>
-      <c r="H924" s="27"/>
-    </row>
-    <row r="925" spans="1:8">
+    </row>
+    <row r="925" spans="1:6">
       <c r="A925" s="6">
         <v>46146</v>
       </c>
@@ -14218,10 +14061,8 @@
       <c r="D925" s="2">
         <v>1</v>
       </c>
-      <c r="G925" s="1"/>
-      <c r="H925" s="27"/>
-    </row>
-    <row r="926" spans="1:8">
+    </row>
+    <row r="926" spans="1:6">
       <c r="A926" s="6">
         <v>46146</v>
       </c>
@@ -14234,10 +14075,8 @@
       <c r="D926" s="2">
         <v>1</v>
       </c>
-      <c r="G926" s="1"/>
-      <c r="H926" s="27"/>
-    </row>
-    <row r="927" spans="1:8">
+    </row>
+    <row r="927" spans="1:6">
       <c r="A927" s="6">
         <v>46146</v>
       </c>
@@ -14251,7 +14090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="928" spans="1:8">
+    <row r="928" spans="1:6">
       <c r="A928" s="6">
         <v>46146</v>
       </c>
@@ -14265,9 +14104,8 @@
         <v>1</v>
       </c>
       <c r="F928" s="1"/>
-      <c r="G928" s="27"/>
-    </row>
-    <row r="929" spans="1:7">
+    </row>
+    <row r="929" spans="1:6">
       <c r="A929" s="6">
         <v>46146</v>
       </c>
@@ -14281,9 +14119,8 @@
         <v>1</v>
       </c>
       <c r="F929" s="1"/>
-      <c r="G929" s="27"/>
-    </row>
-    <row r="930" spans="1:7">
+    </row>
+    <row r="930" spans="1:6">
       <c r="A930" s="6">
         <v>46146</v>
       </c>
@@ -14297,9 +14134,8 @@
         <v>0</v>
       </c>
       <c r="F930" s="1"/>
-      <c r="G930" s="27"/>
-    </row>
-    <row r="931" spans="1:7">
+    </row>
+    <row r="931" spans="1:6">
       <c r="A931" s="6">
         <v>46146</v>
       </c>
@@ -14313,9 +14149,8 @@
         <v>0</v>
       </c>
       <c r="F931" s="1"/>
-      <c r="G931" s="27"/>
-    </row>
-    <row r="932" spans="1:7">
+    </row>
+    <row r="932" spans="1:6">
       <c r="A932" s="6">
         <v>46147</v>
       </c>
@@ -14329,9 +14164,8 @@
         <v>2</v>
       </c>
       <c r="F932" s="1"/>
-      <c r="G932" s="27"/>
-    </row>
-    <row r="933" spans="1:7">
+    </row>
+    <row r="933" spans="1:6">
       <c r="A933" s="6">
         <v>46147</v>
       </c>
@@ -14345,9 +14179,8 @@
         <v>2</v>
       </c>
       <c r="F933" s="1"/>
-      <c r="G933" s="27"/>
-    </row>
-    <row r="934" spans="1:7">
+    </row>
+    <row r="934" spans="1:6">
       <c r="A934" s="6">
         <v>46147</v>
       </c>
@@ -14361,7 +14194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="935" spans="1:7">
+    <row r="935" spans="1:6">
       <c r="A935" s="6">
         <v>46147</v>
       </c>
@@ -14375,9 +14208,8 @@
         <v>3</v>
       </c>
       <c r="F935" s="1"/>
-      <c r="G935" s="27"/>
-    </row>
-    <row r="936" spans="1:7">
+    </row>
+    <row r="936" spans="1:6">
       <c r="A936" s="6">
         <v>46147</v>
       </c>
@@ -14391,9 +14223,8 @@
         <v>2</v>
       </c>
       <c r="F936" s="1"/>
-      <c r="G936" s="27"/>
-    </row>
-    <row r="937" spans="1:7">
+    </row>
+    <row r="937" spans="1:6">
       <c r="A937" s="6">
         <v>46147</v>
       </c>
@@ -14407,9 +14238,8 @@
         <v>0</v>
       </c>
       <c r="F937" s="1"/>
-      <c r="G937" s="27"/>
-    </row>
-    <row r="938" spans="1:7">
+    </row>
+    <row r="938" spans="1:6">
       <c r="A938" s="6">
         <v>46147</v>
       </c>
@@ -14423,9 +14253,8 @@
         <v>0</v>
       </c>
       <c r="F938" s="1"/>
-      <c r="G938" s="27"/>
-    </row>
-    <row r="939" spans="1:7">
+    </row>
+    <row r="939" spans="1:6">
       <c r="A939" s="6">
         <v>46147</v>
       </c>
@@ -14439,9 +14268,8 @@
         <v>0</v>
       </c>
       <c r="F939" s="1"/>
-      <c r="G939" s="27"/>
-    </row>
-    <row r="940" spans="1:7">
+    </row>
+    <row r="940" spans="1:6">
       <c r="A940" s="6">
         <v>46147</v>
       </c>
@@ -14455,9 +14283,8 @@
         <v>0</v>
       </c>
       <c r="F940" s="1"/>
-      <c r="G940" s="27"/>
-    </row>
-    <row r="941" spans="1:7">
+    </row>
+    <row r="941" spans="1:6">
       <c r="A941" s="6">
         <v>46147</v>
       </c>
@@ -14471,9 +14298,8 @@
         <v>1</v>
       </c>
       <c r="F941" s="1"/>
-      <c r="G941" s="27"/>
-    </row>
-    <row r="942" spans="1:7">
+    </row>
+    <row r="942" spans="1:6">
       <c r="A942" s="6">
         <v>46147</v>
       </c>
@@ -14487,7 +14313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="943" spans="1:7">
+    <row r="943" spans="1:6">
       <c r="A943" s="6">
         <v>46148</v>
       </c>
@@ -14501,7 +14327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="944" spans="1:7">
+    <row r="944" spans="1:6">
       <c r="A944" s="6">
         <v>46148</v>
       </c>
@@ -14515,7 +14341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="945" spans="1:7">
+    <row r="945" spans="1:6">
       <c r="A945" s="6">
         <v>46148</v>
       </c>
@@ -14529,7 +14355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="946" spans="1:7">
+    <row r="946" spans="1:6">
       <c r="A946" s="6">
         <v>46148</v>
       </c>
@@ -14543,7 +14369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="947" spans="1:7">
+    <row r="947" spans="1:6">
       <c r="A947" s="6">
         <v>46148</v>
       </c>
@@ -14557,7 +14383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="948" spans="1:7">
+    <row r="948" spans="1:6">
       <c r="A948" s="6">
         <v>46148</v>
       </c>
@@ -14571,7 +14397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="949" spans="1:7">
+    <row r="949" spans="1:6">
       <c r="A949" s="6">
         <v>46148</v>
       </c>
@@ -14585,7 +14411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="950" spans="1:7">
+    <row r="950" spans="1:6">
       <c r="A950" s="6">
         <v>46148</v>
       </c>
@@ -14599,7 +14425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="951" spans="1:7">
+    <row r="951" spans="1:6">
       <c r="A951" s="6">
         <v>46149</v>
       </c>
@@ -14613,7 +14439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="952" spans="1:7">
+    <row r="952" spans="1:6">
       <c r="A952" s="6">
         <v>46149</v>
       </c>
@@ -14627,7 +14453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="953" spans="1:7">
+    <row r="953" spans="1:6">
       <c r="A953" s="6">
         <v>46149</v>
       </c>
@@ -14641,7 +14467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="954" spans="1:7">
+    <row r="954" spans="1:6">
       <c r="A954" s="6">
         <v>46149</v>
       </c>
@@ -14655,7 +14481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="955" spans="1:7">
+    <row r="955" spans="1:6">
       <c r="A955" s="6">
         <v>46149</v>
       </c>
@@ -14669,9 +14495,8 @@
         <v>5</v>
       </c>
       <c r="F955" s="1"/>
-      <c r="G955" s="27"/>
-    </row>
-    <row r="956" spans="1:7">
+    </row>
+    <row r="956" spans="1:6">
       <c r="A956" s="6">
         <v>46149</v>
       </c>
@@ -14685,9 +14510,8 @@
         <v>4</v>
       </c>
       <c r="F956" s="1"/>
-      <c r="G956" s="27"/>
-    </row>
-    <row r="957" spans="1:7">
+    </row>
+    <row r="957" spans="1:6">
       <c r="A957" s="6">
         <v>46149</v>
       </c>
@@ -14701,9 +14525,8 @@
         <v>4</v>
       </c>
       <c r="F957" s="1"/>
-      <c r="G957" s="27"/>
-    </row>
-    <row r="958" spans="1:7">
+    </row>
+    <row r="958" spans="1:6">
       <c r="A958" s="6">
         <v>46149</v>
       </c>
@@ -14717,9 +14540,8 @@
         <v>4</v>
       </c>
       <c r="F958" s="1"/>
-      <c r="G958" s="27"/>
-    </row>
-    <row r="959" spans="1:7">
+    </row>
+    <row r="959" spans="1:6">
       <c r="A959" s="6">
         <v>46149</v>
       </c>
@@ -14733,9 +14555,8 @@
         <v>4</v>
       </c>
       <c r="F959" s="1"/>
-      <c r="G959" s="27"/>
-    </row>
-    <row r="960" spans="1:7">
+    </row>
+    <row r="960" spans="1:6">
       <c r="A960" s="6">
         <v>46149</v>
       </c>
@@ -14749,9 +14570,8 @@
         <v>0</v>
       </c>
       <c r="F960" s="1"/>
-      <c r="G960" s="27"/>
-    </row>
-    <row r="961" spans="1:7">
+    </row>
+    <row r="961" spans="1:6">
       <c r="A961" s="6">
         <v>46149</v>
       </c>
@@ -14765,9 +14585,8 @@
         <v>0</v>
       </c>
       <c r="F961" s="1"/>
-      <c r="G961" s="27"/>
-    </row>
-    <row r="962" spans="1:7">
+    </row>
+    <row r="962" spans="1:6">
       <c r="A962" s="6">
         <v>46149</v>
       </c>
@@ -14781,9 +14600,8 @@
         <v>2</v>
       </c>
       <c r="F962" s="1"/>
-      <c r="G962" s="27"/>
-    </row>
-    <row r="963" spans="1:7">
+    </row>
+    <row r="963" spans="1:6">
       <c r="A963" s="6">
         <v>46149</v>
       </c>
@@ -14797,9 +14615,8 @@
         <v>2</v>
       </c>
       <c r="F963" s="1"/>
-      <c r="G963" s="27"/>
-    </row>
-    <row r="964" spans="1:7">
+    </row>
+    <row r="964" spans="1:6">
       <c r="A964" s="6">
         <v>46150</v>
       </c>
@@ -14813,9 +14630,8 @@
         <v>1</v>
       </c>
       <c r="F964" s="1"/>
-      <c r="G964" s="27"/>
-    </row>
-    <row r="965" spans="1:7">
+    </row>
+    <row r="965" spans="1:6">
       <c r="A965" s="6">
         <v>46150</v>
       </c>
@@ -14829,7 +14645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="966" spans="1:7">
+    <row r="966" spans="1:6">
       <c r="A966" s="6">
         <v>46150</v>
       </c>
@@ -14843,9 +14659,8 @@
         <v>1</v>
       </c>
       <c r="F966" s="1"/>
-      <c r="G966" s="27"/>
-    </row>
-    <row r="967" spans="1:7">
+    </row>
+    <row r="967" spans="1:6">
       <c r="A967" s="6">
         <v>46150</v>
       </c>
@@ -14859,9 +14674,8 @@
         <v>1</v>
       </c>
       <c r="F967" s="1"/>
-      <c r="G967" s="27"/>
-    </row>
-    <row r="968" spans="1:7">
+    </row>
+    <row r="968" spans="1:6">
       <c r="A968" s="6">
         <v>46150</v>
       </c>
@@ -14875,9 +14689,8 @@
         <v>5</v>
       </c>
       <c r="F968" s="1"/>
-      <c r="G968" s="27"/>
-    </row>
-    <row r="969" spans="1:7">
+    </row>
+    <row r="969" spans="1:6">
       <c r="A969" s="6">
         <v>46150</v>
       </c>
@@ -14891,9 +14704,8 @@
         <v>3</v>
       </c>
       <c r="F969" s="1"/>
-      <c r="G969" s="27"/>
-    </row>
-    <row r="970" spans="1:7">
+    </row>
+    <row r="970" spans="1:6">
       <c r="A970" s="6">
         <v>46150</v>
       </c>
@@ -14907,9 +14719,8 @@
         <v>2</v>
       </c>
       <c r="F970" s="1"/>
-      <c r="G970" s="27"/>
-    </row>
-    <row r="971" spans="1:7">
+    </row>
+    <row r="971" spans="1:6">
       <c r="A971" s="6">
         <v>46150</v>
       </c>
@@ -14923,9 +14734,8 @@
         <v>4</v>
       </c>
       <c r="F971" s="1"/>
-      <c r="G971" s="27"/>
-    </row>
-    <row r="972" spans="1:7">
+    </row>
+    <row r="972" spans="1:6">
       <c r="A972" s="6">
         <v>46150</v>
       </c>
@@ -14939,9 +14749,8 @@
         <v>4</v>
       </c>
       <c r="F972" s="1"/>
-      <c r="G972" s="27"/>
-    </row>
-    <row r="973" spans="1:7">
+    </row>
+    <row r="973" spans="1:6">
       <c r="A973" s="6">
         <v>46150</v>
       </c>
@@ -14955,9 +14764,8 @@
         <v>4</v>
       </c>
       <c r="F973" s="1"/>
-      <c r="G973" s="27"/>
-    </row>
-    <row r="974" spans="1:7">
+    </row>
+    <row r="974" spans="1:6">
       <c r="A974" s="6">
         <v>46150</v>
       </c>
@@ -14971,9 +14779,8 @@
         <v>4</v>
       </c>
       <c r="F974" s="1"/>
-      <c r="G974" s="27"/>
-    </row>
-    <row r="975" spans="1:7">
+    </row>
+    <row r="975" spans="1:6">
       <c r="A975" s="6">
         <v>46151</v>
       </c>
@@ -14987,7 +14794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="976" spans="1:7">
+    <row r="976" spans="1:6">
       <c r="A976" s="6">
         <v>46151</v>
       </c>
@@ -15001,7 +14808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="977" spans="1:7">
+    <row r="977" spans="1:6">
       <c r="A977" s="6">
         <v>46151</v>
       </c>
@@ -15015,7 +14822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="978" spans="1:7">
+    <row r="978" spans="1:6">
       <c r="A978" s="6">
         <v>46151</v>
       </c>
@@ -15029,7 +14836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="979" spans="1:7">
+    <row r="979" spans="1:6">
       <c r="A979" s="6">
         <v>46151</v>
       </c>
@@ -15043,7 +14850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="980" spans="1:7">
+    <row r="980" spans="1:6">
       <c r="A980" s="6">
         <v>46151</v>
       </c>
@@ -15057,7 +14864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="981" spans="1:7">
+    <row r="981" spans="1:6">
       <c r="A981" s="6">
         <v>46153</v>
       </c>
@@ -15071,7 +14878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="982" spans="1:7">
+    <row r="982" spans="1:6">
       <c r="A982" s="6">
         <v>46153</v>
       </c>
@@ -15085,7 +14892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="983" spans="1:7">
+    <row r="983" spans="1:6">
       <c r="A983" s="6">
         <v>46153</v>
       </c>
@@ -15099,7 +14906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="984" spans="1:7">
+    <row r="984" spans="1:6">
       <c r="A984" s="6">
         <v>46153</v>
       </c>
@@ -15113,7 +14920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="985" spans="1:7">
+    <row r="985" spans="1:6">
       <c r="A985" s="6">
         <v>46153</v>
       </c>
@@ -15127,9 +14934,8 @@
         <v>0</v>
       </c>
       <c r="F985" s="1"/>
-      <c r="G985" s="27"/>
-    </row>
-    <row r="986" spans="1:7">
+    </row>
+    <row r="986" spans="1:6">
       <c r="A986" s="6">
         <v>46153</v>
       </c>
@@ -15143,9 +14949,8 @@
         <v>1</v>
       </c>
       <c r="F986" s="1"/>
-      <c r="G986" s="27"/>
-    </row>
-    <row r="987" spans="1:7">
+    </row>
+    <row r="987" spans="1:6">
       <c r="A987" s="6">
         <v>46153</v>
       </c>
@@ -15159,9 +14964,8 @@
         <v>1</v>
       </c>
       <c r="F987" s="1"/>
-      <c r="G987" s="27"/>
-    </row>
-    <row r="988" spans="1:7">
+    </row>
+    <row r="988" spans="1:6">
       <c r="A988" s="6">
         <v>46153</v>
       </c>
@@ -15175,9 +14979,8 @@
         <v>1</v>
       </c>
       <c r="F988" s="1"/>
-      <c r="G988" s="27"/>
-    </row>
-    <row r="989" spans="1:7">
+    </row>
+    <row r="989" spans="1:6">
       <c r="A989" s="6">
         <v>46153</v>
       </c>
@@ -15191,9 +14994,8 @@
         <v>1</v>
       </c>
       <c r="F989" s="1"/>
-      <c r="G989" s="27"/>
-    </row>
-    <row r="990" spans="1:7">
+    </row>
+    <row r="990" spans="1:6">
       <c r="A990" s="6">
         <v>46153</v>
       </c>
@@ -15207,9 +15009,8 @@
         <v>0</v>
       </c>
       <c r="F990" s="1"/>
-      <c r="G990" s="27"/>
-    </row>
-    <row r="991" spans="1:7">
+    </row>
+    <row r="991" spans="1:6">
       <c r="A991" s="6">
         <v>46153</v>
       </c>
@@ -15223,9 +15024,8 @@
         <v>0</v>
       </c>
       <c r="F991" s="1"/>
-      <c r="G991" s="27"/>
-    </row>
-    <row r="992" spans="1:7">
+    </row>
+    <row r="992" spans="1:6">
       <c r="A992" s="6">
         <v>46153</v>
       </c>
@@ -15239,9 +15039,8 @@
         <v>3</v>
       </c>
       <c r="F992" s="1"/>
-      <c r="G992" s="27"/>
-    </row>
-    <row r="993" spans="1:7">
+    </row>
+    <row r="993" spans="1:6">
       <c r="A993" s="6">
         <v>46153</v>
       </c>
@@ -15255,7 +15054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="994" spans="1:7">
+    <row r="994" spans="1:6">
       <c r="A994" s="6">
         <v>46154</v>
       </c>
@@ -15269,7 +15068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="995" spans="1:7">
+    <row r="995" spans="1:6">
       <c r="A995" s="6">
         <v>46154</v>
       </c>
@@ -15283,9 +15082,8 @@
         <v>2</v>
       </c>
       <c r="F995" s="1"/>
-      <c r="G995" s="27"/>
-    </row>
-    <row r="996" spans="1:7">
+    </row>
+    <row r="996" spans="1:6">
       <c r="A996" s="6">
         <v>46154</v>
       </c>
@@ -15299,9 +15097,8 @@
         <v>1</v>
       </c>
       <c r="F996" s="1"/>
-      <c r="G996" s="27"/>
-    </row>
-    <row r="997" spans="1:7">
+    </row>
+    <row r="997" spans="1:6">
       <c r="A997" s="6">
         <v>46154</v>
       </c>
@@ -15315,9 +15112,8 @@
         <v>1</v>
       </c>
       <c r="F997" s="1"/>
-      <c r="G997" s="27"/>
-    </row>
-    <row r="998" spans="1:7">
+    </row>
+    <row r="998" spans="1:6">
       <c r="A998" s="6">
         <v>46154</v>
       </c>
@@ -15331,9 +15127,8 @@
         <v>0</v>
       </c>
       <c r="F998" s="1"/>
-      <c r="G998" s="27"/>
-    </row>
-    <row r="999" spans="1:7">
+    </row>
+    <row r="999" spans="1:6">
       <c r="A999" s="6">
         <v>46154</v>
       </c>
@@ -15347,9 +15142,8 @@
         <v>0</v>
       </c>
       <c r="F999" s="1"/>
-      <c r="G999" s="27"/>
-    </row>
-    <row r="1000" spans="1:7">
+    </row>
+    <row r="1000" spans="1:6">
       <c r="A1000" s="6">
         <v>46154</v>
       </c>
@@ -15363,9 +15157,8 @@
         <v>3</v>
       </c>
       <c r="F1000" s="1"/>
-      <c r="G1000" s="27"/>
-    </row>
-    <row r="1001" spans="1:7">
+    </row>
+    <row r="1001" spans="1:6">
       <c r="A1001" s="6">
         <v>46154</v>
       </c>
@@ -15379,7 +15172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1002" spans="1:7">
+    <row r="1002" spans="1:6">
       <c r="A1002" s="6">
         <v>46154</v>
       </c>
@@ -15393,7 +15186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1003" spans="1:7">
+    <row r="1003" spans="1:6">
       <c r="A1003" s="6">
         <v>46154</v>
       </c>
@@ -15407,7 +15200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1004" spans="1:7">
+    <row r="1004" spans="1:6">
       <c r="A1004" s="6">
         <v>46155</v>
       </c>
@@ -15421,7 +15214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1005" spans="1:7">
+    <row r="1005" spans="1:6">
       <c r="A1005" s="6">
         <v>46155</v>
       </c>
@@ -15435,9 +15228,8 @@
         <v>1</v>
       </c>
       <c r="F1005" s="1"/>
-      <c r="G1005" s="27"/>
-    </row>
-    <row r="1006" spans="1:7">
+    </row>
+    <row r="1006" spans="1:6">
       <c r="A1006" s="6">
         <v>46155</v>
       </c>
@@ -15451,9 +15243,8 @@
         <v>2</v>
       </c>
       <c r="F1006" s="1"/>
-      <c r="G1006" s="27"/>
-    </row>
-    <row r="1007" spans="1:7">
+    </row>
+    <row r="1007" spans="1:6">
       <c r="A1007" s="6">
         <v>46155</v>
       </c>
@@ -15467,9 +15258,8 @@
         <v>1</v>
       </c>
       <c r="F1007" s="1"/>
-      <c r="G1007" s="27"/>
-    </row>
-    <row r="1008" spans="1:7">
+    </row>
+    <row r="1008" spans="1:6">
       <c r="A1008" s="6">
         <v>46155</v>
       </c>
@@ -15483,9 +15273,8 @@
         <v>1</v>
       </c>
       <c r="F1008" s="1"/>
-      <c r="G1008" s="27"/>
-    </row>
-    <row r="1009" spans="1:8">
+    </row>
+    <row r="1009" spans="1:6">
       <c r="A1009" s="6">
         <v>46155</v>
       </c>
@@ -15499,9 +15288,8 @@
         <v>3</v>
       </c>
       <c r="F1009" s="1"/>
-      <c r="G1009" s="27"/>
-    </row>
-    <row r="1010" spans="1:8">
+    </row>
+    <row r="1010" spans="1:6">
       <c r="A1010" s="6">
         <v>46155</v>
       </c>
@@ -15515,9 +15303,8 @@
         <v>3</v>
       </c>
       <c r="F1010" s="1"/>
-      <c r="G1010" s="27"/>
-    </row>
-    <row r="1011" spans="1:8">
+    </row>
+    <row r="1011" spans="1:6">
       <c r="A1011" s="6">
         <v>46155</v>
       </c>
@@ -15532,7 +15319,7 @@
       </c>
       <c r="F1011" s="1"/>
     </row>
-    <row r="1012" spans="1:8">
+    <row r="1012" spans="1:6">
       <c r="A1012" s="6">
         <v>46155</v>
       </c>
@@ -15546,10 +15333,8 @@
         <v>2</v>
       </c>
       <c r="F1012" s="1"/>
-      <c r="G1012" s="1"/>
-      <c r="H1012" s="27"/>
-    </row>
-    <row r="1013" spans="1:8">
+    </row>
+    <row r="1013" spans="1:6">
       <c r="A1013" s="6">
         <v>46156</v>
       </c>
@@ -15563,10 +15348,8 @@
         <v>8</v>
       </c>
       <c r="F1013" s="1"/>
-      <c r="G1013" s="1"/>
-      <c r="H1013" s="27"/>
-    </row>
-    <row r="1014" spans="1:8">
+    </row>
+    <row r="1014" spans="1:6">
       <c r="A1014" s="6">
         <v>46156</v>
       </c>
@@ -15580,10 +15363,8 @@
         <v>0</v>
       </c>
       <c r="F1014" s="1"/>
-      <c r="G1014" s="1"/>
-      <c r="H1014" s="27"/>
-    </row>
-    <row r="1015" spans="1:8">
+    </row>
+    <row r="1015" spans="1:6">
       <c r="A1015" s="6">
         <v>46156</v>
       </c>
@@ -15596,10 +15377,8 @@
       <c r="D1015" s="2">
         <v>0</v>
       </c>
-      <c r="G1015" s="1"/>
-      <c r="H1015" s="27"/>
-    </row>
-    <row r="1016" spans="1:8">
+    </row>
+    <row r="1016" spans="1:6">
       <c r="A1016" s="6">
         <v>46156</v>
       </c>
@@ -15612,10 +15391,8 @@
       <c r="D1016" s="2">
         <v>0</v>
       </c>
-      <c r="G1016" s="1"/>
-      <c r="H1016" s="27"/>
-    </row>
-    <row r="1017" spans="1:8">
+    </row>
+    <row r="1017" spans="1:6">
       <c r="A1017" s="6">
         <v>46156</v>
       </c>
@@ -15628,10 +15405,8 @@
       <c r="D1017" s="2">
         <v>0</v>
       </c>
-      <c r="G1017" s="1"/>
-      <c r="H1017" s="27"/>
-    </row>
-    <row r="1018" spans="1:8">
+    </row>
+    <row r="1018" spans="1:6">
       <c r="A1018" s="6">
         <v>46156</v>
       </c>
@@ -15644,10 +15419,8 @@
       <c r="D1018" s="2">
         <v>4</v>
       </c>
-      <c r="G1018" s="1"/>
-      <c r="H1018" s="27"/>
-    </row>
-    <row r="1019" spans="1:8">
+    </row>
+    <row r="1019" spans="1:6">
       <c r="A1019" s="6">
         <v>46156</v>
       </c>
@@ -15661,7 +15434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1020" spans="1:8">
+    <row r="1020" spans="1:6">
       <c r="A1020" s="6">
         <v>46156</v>
       </c>
@@ -15675,7 +15448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1021" spans="1:8">
+    <row r="1021" spans="1:6">
       <c r="A1021" s="6">
         <v>46156</v>
       </c>
@@ -15689,7 +15462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1022" spans="1:8">
+    <row r="1022" spans="1:6">
       <c r="A1022" s="6">
         <v>46156</v>
       </c>
@@ -15703,7 +15476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1023" spans="1:8">
+    <row r="1023" spans="1:6">
       <c r="A1023" s="6">
         <v>46156</v>
       </c>
@@ -15717,7 +15490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1024" spans="1:8">
+    <row r="1024" spans="1:6">
       <c r="A1024" s="6">
         <v>46156</v>
       </c>
@@ -15731,7 +15504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1025" spans="1:7">
+    <row r="1025" spans="1:6">
       <c r="A1025" s="6">
         <v>46156</v>
       </c>
@@ -15745,7 +15518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1026" spans="1:7">
+    <row r="1026" spans="1:6">
       <c r="A1026" s="6">
         <v>46157</v>
       </c>
@@ -15759,7 +15532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1027" spans="1:7">
+    <row r="1027" spans="1:6">
       <c r="A1027" s="6">
         <v>46157</v>
       </c>
@@ -15773,9 +15546,8 @@
         <v>1</v>
       </c>
       <c r="F1027" s="1"/>
-      <c r="G1027" s="27"/>
-    </row>
-    <row r="1028" spans="1:7">
+    </row>
+    <row r="1028" spans="1:6">
       <c r="A1028" s="6">
         <v>46157</v>
       </c>
@@ -15789,9 +15561,8 @@
         <v>0</v>
       </c>
       <c r="F1028" s="1"/>
-      <c r="G1028" s="27"/>
-    </row>
-    <row r="1029" spans="1:7">
+    </row>
+    <row r="1029" spans="1:6">
       <c r="A1029" s="6">
         <v>46157</v>
       </c>
@@ -15805,9 +15576,8 @@
         <v>0</v>
       </c>
       <c r="F1029" s="1"/>
-      <c r="G1029" s="27"/>
-    </row>
-    <row r="1030" spans="1:7">
+    </row>
+    <row r="1030" spans="1:6">
       <c r="A1030" s="6">
         <v>46157</v>
       </c>
@@ -15821,9 +15591,8 @@
         <v>6</v>
       </c>
       <c r="F1030" s="1"/>
-      <c r="G1030" s="27"/>
-    </row>
-    <row r="1031" spans="1:7">
+    </row>
+    <row r="1031" spans="1:6">
       <c r="A1031" s="6">
         <v>46157</v>
       </c>
@@ -15837,9 +15606,8 @@
         <v>6</v>
       </c>
       <c r="F1031" s="1"/>
-      <c r="G1031" s="27"/>
-    </row>
-    <row r="1032" spans="1:7">
+    </row>
+    <row r="1032" spans="1:6">
       <c r="A1032" s="6">
         <v>46157</v>
       </c>
@@ -15853,7 +15621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1033" spans="1:7">
+    <row r="1033" spans="1:6">
       <c r="A1033" s="6">
         <v>46157</v>
       </c>
@@ -15867,7 +15635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1034" spans="1:7">
+    <row r="1034" spans="1:6">
       <c r="A1034" s="6">
         <v>46157</v>
       </c>
@@ -15881,7 +15649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1035" spans="1:7">
+    <row r="1035" spans="1:6">
       <c r="A1035" s="6">
         <v>46158</v>
       </c>
@@ -15895,7 +15663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1036" spans="1:7">
+    <row r="1036" spans="1:6">
       <c r="A1036" s="6">
         <v>46158</v>
       </c>
@@ -15909,9 +15677,8 @@
         <v>5</v>
       </c>
       <c r="F1036" s="1"/>
-      <c r="G1036" s="27"/>
-    </row>
-    <row r="1037" spans="1:7">
+    </row>
+    <row r="1037" spans="1:6">
       <c r="A1037" s="6">
         <v>46158</v>
       </c>
@@ -15925,9 +15692,8 @@
         <v>10</v>
       </c>
       <c r="F1037" s="1"/>
-      <c r="G1037" s="27"/>
-    </row>
-    <row r="1038" spans="1:7">
+    </row>
+    <row r="1038" spans="1:6">
       <c r="A1038" s="6">
         <v>46160</v>
       </c>
@@ -15941,9 +15707,8 @@
         <v>2</v>
       </c>
       <c r="F1038" s="1"/>
-      <c r="G1038" s="27"/>
-    </row>
-    <row r="1039" spans="1:7">
+    </row>
+    <row r="1039" spans="1:6">
       <c r="A1039" s="6">
         <v>46160</v>
       </c>
@@ -15957,9 +15722,8 @@
         <v>2</v>
       </c>
       <c r="F1039" s="1"/>
-      <c r="G1039" s="27"/>
-    </row>
-    <row r="1040" spans="1:7">
+    </row>
+    <row r="1040" spans="1:6">
       <c r="A1040" s="6">
         <v>46160</v>
       </c>
@@ -15973,9 +15737,8 @@
         <v>1</v>
       </c>
       <c r="F1040" s="1"/>
-      <c r="G1040" s="27"/>
-    </row>
-    <row r="1041" spans="1:8">
+    </row>
+    <row r="1041" spans="1:6">
       <c r="A1041" s="6">
         <v>46160</v>
       </c>
@@ -15990,7 +15753,7 @@
       </c>
       <c r="F1041" s="1"/>
     </row>
-    <row r="1042" spans="1:8">
+    <row r="1042" spans="1:6">
       <c r="A1042" s="6">
         <v>46160</v>
       </c>
@@ -16004,10 +15767,8 @@
         <v>1</v>
       </c>
       <c r="F1042" s="1"/>
-      <c r="G1042" s="1"/>
-      <c r="H1042" s="27"/>
-    </row>
-    <row r="1043" spans="1:8">
+    </row>
+    <row r="1043" spans="1:6">
       <c r="A1043" s="6">
         <v>46160</v>
       </c>
@@ -16021,10 +15782,8 @@
         <v>1</v>
       </c>
       <c r="F1043" s="1"/>
-      <c r="G1043" s="1"/>
-      <c r="H1043" s="27"/>
-    </row>
-    <row r="1044" spans="1:8">
+    </row>
+    <row r="1044" spans="1:6">
       <c r="A1044" s="6">
         <v>46160</v>
       </c>
@@ -16037,10 +15796,8 @@
       <c r="D1044" s="2">
         <v>1</v>
       </c>
-      <c r="G1044" s="1"/>
-      <c r="H1044" s="27"/>
-    </row>
-    <row r="1045" spans="1:8">
+    </row>
+    <row r="1045" spans="1:6">
       <c r="A1045" s="6">
         <v>46160</v>
       </c>
@@ -16053,10 +15810,8 @@
       <c r="D1045" s="2">
         <v>4</v>
       </c>
-      <c r="G1045" s="1"/>
-      <c r="H1045" s="27"/>
-    </row>
-    <row r="1046" spans="1:8">
+    </row>
+    <row r="1046" spans="1:6">
       <c r="A1046" s="6">
         <v>46160</v>
       </c>
@@ -16069,10 +15824,8 @@
       <c r="D1046" s="2">
         <v>4</v>
       </c>
-      <c r="G1046" s="1"/>
-      <c r="H1046" s="27"/>
-    </row>
-    <row r="1047" spans="1:8">
+    </row>
+    <row r="1047" spans="1:6">
       <c r="A1047" s="6">
         <v>46160</v>
       </c>
@@ -16085,10 +15838,8 @@
       <c r="D1047" s="2">
         <v>4</v>
       </c>
-      <c r="G1047" s="1"/>
-      <c r="H1047" s="27"/>
-    </row>
-    <row r="1048" spans="1:8">
+    </row>
+    <row r="1048" spans="1:6">
       <c r="A1048" s="6">
         <v>46160</v>
       </c>
@@ -16101,10 +15852,8 @@
       <c r="D1048" s="2">
         <v>4</v>
       </c>
-      <c r="G1048" s="1"/>
-      <c r="H1048" s="27"/>
-    </row>
-    <row r="1049" spans="1:8">
+    </row>
+    <row r="1049" spans="1:6">
       <c r="A1049" s="6">
         <v>46161</v>
       </c>
@@ -16118,7 +15867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1050" spans="1:8">
+    <row r="1050" spans="1:6">
       <c r="A1050" s="6">
         <v>46161</v>
       </c>
@@ -16132,9 +15881,8 @@
         <v>0</v>
       </c>
       <c r="F1050" s="1"/>
-      <c r="G1050" s="27"/>
-    </row>
-    <row r="1051" spans="1:8">
+    </row>
+    <row r="1051" spans="1:6">
       <c r="A1051" s="6">
         <v>46161</v>
       </c>
@@ -16148,9 +15896,8 @@
         <v>0</v>
       </c>
       <c r="F1051" s="1"/>
-      <c r="G1051" s="27"/>
-    </row>
-    <row r="1052" spans="1:8">
+    </row>
+    <row r="1052" spans="1:6">
       <c r="A1052" s="6">
         <v>46161</v>
       </c>
@@ -16164,9 +15911,8 @@
         <v>1</v>
       </c>
       <c r="F1052" s="1"/>
-      <c r="G1052" s="27"/>
-    </row>
-    <row r="1053" spans="1:8">
+    </row>
+    <row r="1053" spans="1:6">
       <c r="A1053" s="6">
         <v>46161</v>
       </c>
@@ -16180,9 +15926,8 @@
         <v>1</v>
       </c>
       <c r="F1053" s="1"/>
-      <c r="G1053" s="27"/>
-    </row>
-    <row r="1054" spans="1:8">
+    </row>
+    <row r="1054" spans="1:6">
       <c r="A1054" s="6">
         <v>46161</v>
       </c>
@@ -16196,9 +15941,8 @@
         <v>1</v>
       </c>
       <c r="F1054" s="1"/>
-      <c r="G1054" s="27"/>
-    </row>
-    <row r="1055" spans="1:8">
+    </row>
+    <row r="1055" spans="1:6">
       <c r="A1055" s="6">
         <v>46161</v>
       </c>
@@ -16212,9 +15956,8 @@
         <v>1</v>
       </c>
       <c r="F1055" s="1"/>
-      <c r="G1055" s="27"/>
-    </row>
-    <row r="1056" spans="1:8">
+    </row>
+    <row r="1056" spans="1:6">
       <c r="A1056" s="6">
         <v>46162</v>
       </c>
@@ -16228,7 +15971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1057" spans="1:8">
+    <row r="1057" spans="1:4">
       <c r="A1057" s="6">
         <v>46162</v>
       </c>
@@ -16242,7 +15985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1058" spans="1:8">
+    <row r="1058" spans="1:4">
       <c r="A1058" s="6">
         <v>46162</v>
       </c>
@@ -16256,7 +15999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1059" spans="1:8">
+    <row r="1059" spans="1:4">
       <c r="A1059" s="6">
         <v>46162</v>
       </c>
@@ -16270,7 +16013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1060" spans="1:8">
+    <row r="1060" spans="1:4">
       <c r="A1060" s="6">
         <v>46162</v>
       </c>
@@ -16284,7 +16027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1061" spans="1:8">
+    <row r="1061" spans="1:4">
       <c r="A1061" s="6">
         <v>46162</v>
       </c>
@@ -16298,7 +16041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1062" spans="1:8">
+    <row r="1062" spans="1:4">
       <c r="A1062" s="6">
         <v>46162</v>
       </c>
@@ -16312,7 +16055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1063" spans="1:8">
+    <row r="1063" spans="1:4">
       <c r="A1063" s="6">
         <v>46162</v>
       </c>
@@ -16326,7 +16069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1064" spans="1:8">
+    <row r="1064" spans="1:4">
       <c r="A1064" s="6">
         <v>46162</v>
       </c>
@@ -16340,7 +16083,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1065" spans="1:8">
+    <row r="1065" spans="1:4">
       <c r="A1065" s="6">
         <v>46162</v>
       </c>
@@ -16354,7 +16097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1066" spans="1:8">
+    <row r="1066" spans="1:4">
       <c r="A1066" s="6">
         <v>46163</v>
       </c>
@@ -16368,7 +16111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1067" spans="1:8">
+    <row r="1067" spans="1:4">
       <c r="A1067" s="6">
         <v>46163</v>
       </c>
@@ -16381,10 +16124,8 @@
       <c r="D1067" s="2">
         <v>0</v>
       </c>
-      <c r="G1067" s="1"/>
-      <c r="H1067" s="27"/>
-    </row>
-    <row r="1068" spans="1:8">
+    </row>
+    <row r="1068" spans="1:4">
       <c r="A1068" s="6">
         <v>46163</v>
       </c>
@@ -16397,10 +16138,8 @@
       <c r="D1068" s="2">
         <v>0</v>
       </c>
-      <c r="G1068" s="1"/>
-      <c r="H1068" s="27"/>
-    </row>
-    <row r="1069" spans="1:8">
+    </row>
+    <row r="1069" spans="1:4">
       <c r="A1069" s="6">
         <v>46163</v>
       </c>
@@ -16413,10 +16152,8 @@
       <c r="D1069" s="2">
         <v>6</v>
       </c>
-      <c r="G1069" s="1"/>
-      <c r="H1069" s="27"/>
-    </row>
-    <row r="1070" spans="1:8">
+    </row>
+    <row r="1070" spans="1:4">
       <c r="A1070" s="6">
         <v>46163</v>
       </c>
@@ -16429,10 +16166,8 @@
       <c r="D1070" s="2">
         <v>2</v>
       </c>
-      <c r="G1070" s="1"/>
-      <c r="H1070" s="27"/>
-    </row>
-    <row r="1071" spans="1:8">
+    </row>
+    <row r="1071" spans="1:4">
       <c r="A1071" s="6">
         <v>46163</v>
       </c>
@@ -16445,10 +16180,8 @@
       <c r="D1071" s="2">
         <v>2</v>
       </c>
-      <c r="G1071" s="1"/>
-      <c r="H1071" s="27"/>
-    </row>
-    <row r="1072" spans="1:8">
+    </row>
+    <row r="1072" spans="1:4">
       <c r="A1072" s="6">
         <v>46163</v>
       </c>
@@ -16461,10 +16194,8 @@
       <c r="D1072" s="2">
         <v>2</v>
       </c>
-      <c r="G1072" s="1"/>
-      <c r="H1072" s="27"/>
-    </row>
-    <row r="1073" spans="1:8">
+    </row>
+    <row r="1073" spans="1:6">
       <c r="A1073" s="6">
         <v>46163</v>
       </c>
@@ -16477,10 +16208,8 @@
       <c r="D1073" s="2">
         <v>2</v>
       </c>
-      <c r="G1073" s="1"/>
-      <c r="H1073" s="27"/>
-    </row>
-    <row r="1074" spans="1:8">
+    </row>
+    <row r="1074" spans="1:6">
       <c r="A1074" s="6">
         <v>46163</v>
       </c>
@@ -16493,10 +16222,8 @@
       <c r="D1074" s="2">
         <v>1</v>
       </c>
-      <c r="G1074" s="1"/>
-      <c r="H1074" s="27"/>
-    </row>
-    <row r="1075" spans="1:8" ht="16.5" customHeight="1">
+    </row>
+    <row r="1075" spans="1:6" ht="16.5" customHeight="1">
       <c r="A1075" s="6">
         <v>46163</v>
       </c>
@@ -16509,10 +16236,8 @@
       <c r="D1075" s="2">
         <v>1</v>
       </c>
-      <c r="G1075" s="1"/>
-      <c r="H1075" s="27"/>
-    </row>
-    <row r="1076" spans="1:8" ht="16.5" customHeight="1">
+    </row>
+    <row r="1076" spans="1:6" ht="16.5" customHeight="1">
       <c r="A1076" s="6">
         <v>46164</v>
       </c>
@@ -16525,10 +16250,8 @@
       <c r="D1076" s="2">
         <v>1</v>
       </c>
-      <c r="G1076" s="1"/>
-      <c r="H1076" s="27"/>
-    </row>
-    <row r="1077" spans="1:8">
+    </row>
+    <row r="1077" spans="1:6">
       <c r="A1077" s="6">
         <v>46164</v>
       </c>
@@ -16541,10 +16264,8 @@
       <c r="D1077" s="2">
         <v>1</v>
       </c>
-      <c r="G1077" s="1"/>
-      <c r="H1077" s="27"/>
-    </row>
-    <row r="1078" spans="1:8">
+    </row>
+    <row r="1078" spans="1:6">
       <c r="A1078" s="6">
         <v>46164</v>
       </c>
@@ -16558,7 +16279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1079" spans="1:8">
+    <row r="1079" spans="1:6">
       <c r="A1079" s="6">
         <v>46164</v>
       </c>
@@ -16572,9 +16293,8 @@
         <v>0</v>
       </c>
       <c r="F1079" s="1"/>
-      <c r="G1079" s="27"/>
-    </row>
-    <row r="1080" spans="1:8">
+    </row>
+    <row r="1080" spans="1:6">
       <c r="A1080" s="6">
         <v>46164</v>
       </c>
@@ -16588,9 +16308,8 @@
         <v>0</v>
       </c>
       <c r="F1080" s="1"/>
-      <c r="G1080" s="27"/>
-    </row>
-    <row r="1081" spans="1:8">
+    </row>
+    <row r="1081" spans="1:6">
       <c r="A1081" s="6">
         <v>46164</v>
       </c>
@@ -16604,9 +16323,8 @@
         <v>0</v>
       </c>
       <c r="F1081" s="1"/>
-      <c r="G1081" s="27"/>
-    </row>
-    <row r="1082" spans="1:8">
+    </row>
+    <row r="1082" spans="1:6">
       <c r="A1082" s="6">
         <v>46164</v>
       </c>
@@ -16620,9 +16338,8 @@
         <v>0</v>
       </c>
       <c r="F1082" s="1"/>
-      <c r="G1082" s="27"/>
-    </row>
-    <row r="1083" spans="1:8">
+    </row>
+    <row r="1083" spans="1:6">
       <c r="A1083" s="6">
         <v>46164</v>
       </c>
@@ -16636,9 +16353,8 @@
         <v>2</v>
       </c>
       <c r="F1083" s="1"/>
-      <c r="G1083" s="27"/>
-    </row>
-    <row r="1084" spans="1:8">
+    </row>
+    <row r="1084" spans="1:6">
       <c r="A1084" s="6">
         <v>46164</v>
       </c>
@@ -16652,9 +16368,8 @@
         <v>2</v>
       </c>
       <c r="F1084" s="1"/>
-      <c r="G1084" s="27"/>
-    </row>
-    <row r="1085" spans="1:8">
+    </row>
+    <row r="1085" spans="1:6">
       <c r="A1085" s="6">
         <v>46164</v>
       </c>
@@ -16668,9 +16383,8 @@
         <v>1</v>
       </c>
       <c r="F1085" s="1"/>
-      <c r="G1085" s="27"/>
-    </row>
-    <row r="1086" spans="1:8">
+    </row>
+    <row r="1086" spans="1:6">
       <c r="A1086" s="6">
         <v>46164</v>
       </c>
@@ -16684,9 +16398,8 @@
         <v>1</v>
       </c>
       <c r="F1086" s="1"/>
-      <c r="G1086" s="27"/>
-    </row>
-    <row r="1087" spans="1:8">
+    </row>
+    <row r="1087" spans="1:6">
       <c r="A1087" s="6">
         <v>46165</v>
       </c>
@@ -16700,7 +16413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1088" spans="1:8">
+    <row r="1088" spans="1:6">
       <c r="A1088" s="6">
         <v>46165</v>
       </c>
@@ -16714,9 +16427,8 @@
         <v>9</v>
       </c>
       <c r="F1088" s="1"/>
-      <c r="G1088" s="27"/>
-    </row>
-    <row r="1089" spans="1:8">
+    </row>
+    <row r="1089" spans="1:6">
       <c r="A1089" s="6">
         <v>46165</v>
       </c>
@@ -16730,9 +16442,8 @@
         <v>3</v>
       </c>
       <c r="F1089" s="1"/>
-      <c r="G1089" s="27"/>
-    </row>
-    <row r="1090" spans="1:8">
+    </row>
+    <row r="1090" spans="1:6">
       <c r="A1090" s="6">
         <v>46165</v>
       </c>
@@ -16746,9 +16457,8 @@
         <v>3</v>
       </c>
       <c r="F1090" s="1"/>
-      <c r="G1090" s="27"/>
-    </row>
-    <row r="1091" spans="1:8">
+    </row>
+    <row r="1091" spans="1:6">
       <c r="A1091" s="6">
         <v>46167</v>
       </c>
@@ -16762,7 +16472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1092" spans="1:8">
+    <row r="1092" spans="1:6">
       <c r="A1092" s="6">
         <v>46167</v>
       </c>
@@ -16776,9 +16486,8 @@
         <v>1</v>
       </c>
       <c r="F1092" s="1"/>
-      <c r="G1092" s="27"/>
-    </row>
-    <row r="1093" spans="1:8">
+    </row>
+    <row r="1093" spans="1:6">
       <c r="A1093" s="6">
         <v>46167</v>
       </c>
@@ -16792,9 +16501,8 @@
         <v>1</v>
       </c>
       <c r="F1093" s="1"/>
-      <c r="G1093" s="27"/>
-    </row>
-    <row r="1094" spans="1:8">
+    </row>
+    <row r="1094" spans="1:6">
       <c r="A1094" s="6">
         <v>46167</v>
       </c>
@@ -16808,9 +16516,8 @@
         <v>2</v>
       </c>
       <c r="F1094" s="1"/>
-      <c r="G1094" s="27"/>
-    </row>
-    <row r="1095" spans="1:8">
+    </row>
+    <row r="1095" spans="1:6">
       <c r="A1095" s="6">
         <v>46167</v>
       </c>
@@ -16824,9 +16531,8 @@
         <v>2</v>
       </c>
       <c r="F1095" s="1"/>
-      <c r="G1095" s="27"/>
-    </row>
-    <row r="1096" spans="1:8">
+    </row>
+    <row r="1096" spans="1:6">
       <c r="A1096" s="6">
         <v>46167</v>
       </c>
@@ -16840,9 +16546,8 @@
         <v>5</v>
       </c>
       <c r="F1096" s="1"/>
-      <c r="G1096" s="27"/>
-    </row>
-    <row r="1097" spans="1:8">
+    </row>
+    <row r="1097" spans="1:6">
       <c r="A1097" s="6">
         <v>46167</v>
       </c>
@@ -16856,9 +16561,8 @@
         <v>5</v>
       </c>
       <c r="F1097" s="1"/>
-      <c r="G1097" s="27"/>
-    </row>
-    <row r="1098" spans="1:8">
+    </row>
+    <row r="1098" spans="1:6">
       <c r="A1098" s="6">
         <v>46167</v>
       </c>
@@ -16872,7 +16576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1099" spans="1:8">
+    <row r="1099" spans="1:6">
       <c r="A1099" s="6">
         <v>46167</v>
       </c>
@@ -16886,7 +16590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1100" spans="1:8">
+    <row r="1100" spans="1:6">
       <c r="A1100" s="6">
         <v>46168</v>
       </c>
@@ -16900,7 +16604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1101" spans="1:8">
+    <row r="1101" spans="1:6">
       <c r="A1101" s="6">
         <v>46168</v>
       </c>
@@ -16914,7 +16618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1102" spans="1:8">
+    <row r="1102" spans="1:6">
       <c r="A1102" s="6">
         <v>46168</v>
       </c>
@@ -16927,10 +16631,8 @@
       <c r="D1102" s="2">
         <v>2</v>
       </c>
-      <c r="G1102" s="1"/>
-      <c r="H1102" s="27"/>
-    </row>
-    <row r="1103" spans="1:8">
+    </row>
+    <row r="1103" spans="1:6">
       <c r="A1103" s="6">
         <v>46168</v>
       </c>
@@ -16943,10 +16645,8 @@
       <c r="D1103" s="2">
         <v>0</v>
       </c>
-      <c r="G1103" s="1"/>
-      <c r="H1103" s="27"/>
-    </row>
-    <row r="1104" spans="1:8">
+    </row>
+    <row r="1104" spans="1:6">
       <c r="A1104" s="6">
         <v>46168</v>
       </c>
@@ -16959,10 +16659,8 @@
       <c r="D1104" s="2">
         <v>0</v>
       </c>
-      <c r="G1104" s="1"/>
-      <c r="H1104" s="27"/>
-    </row>
-    <row r="1105" spans="1:8">
+    </row>
+    <row r="1105" spans="1:4">
       <c r="A1105" s="6">
         <v>46168</v>
       </c>
@@ -16975,10 +16673,8 @@
       <c r="D1105" s="2">
         <v>0</v>
       </c>
-      <c r="G1105" s="1"/>
-      <c r="H1105" s="27"/>
-    </row>
-    <row r="1106" spans="1:8">
+    </row>
+    <row r="1106" spans="1:4">
       <c r="A1106" s="6">
         <v>46168</v>
       </c>
@@ -16991,10 +16687,8 @@
       <c r="D1106" s="2">
         <v>0</v>
       </c>
-      <c r="G1106" s="1"/>
-      <c r="H1106" s="27"/>
-    </row>
-    <row r="1107" spans="1:8">
+    </row>
+    <row r="1107" spans="1:4">
       <c r="A1107" s="6">
         <v>46168</v>
       </c>
@@ -17007,10 +16701,8 @@
       <c r="D1107" s="2">
         <v>9</v>
       </c>
-      <c r="G1107" s="1"/>
-      <c r="H1107" s="27"/>
-    </row>
-    <row r="1108" spans="1:8">
+    </row>
+    <row r="1108" spans="1:4">
       <c r="A1108" s="6">
         <v>46168</v>
       </c>
@@ -17023,10 +16715,8 @@
       <c r="D1108" s="2">
         <v>1</v>
       </c>
-      <c r="G1108" s="1"/>
-      <c r="H1108" s="27"/>
-    </row>
-    <row r="1109" spans="1:8">
+    </row>
+    <row r="1109" spans="1:4">
       <c r="A1109" s="6">
         <v>46168</v>
       </c>
@@ -17040,7 +16730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1110" spans="1:8">
+    <row r="1110" spans="1:4">
       <c r="A1110" s="6">
         <v>46168</v>
       </c>
@@ -17054,7 +16744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1111" spans="1:8">
+    <row r="1111" spans="1:4">
       <c r="A1111" s="6">
         <v>46168</v>
       </c>
@@ -17068,7 +16758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1112" spans="1:8">
+    <row r="1112" spans="1:4">
       <c r="A1112" s="6">
         <v>46168</v>
       </c>
@@ -17082,7 +16772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1113" spans="1:8">
+    <row r="1113" spans="1:4">
       <c r="A1113" s="6">
         <v>46168</v>
       </c>
@@ -17096,7 +16786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1114" spans="1:8">
+    <row r="1114" spans="1:4">
       <c r="A1114" s="6">
         <v>46169</v>
       </c>
@@ -17110,7 +16800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1115" spans="1:8">
+    <row r="1115" spans="1:4">
       <c r="A1115" s="6">
         <v>46169</v>
       </c>
@@ -17124,7 +16814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1116" spans="1:8">
+    <row r="1116" spans="1:4">
       <c r="A1116" s="6">
         <v>46169</v>
       </c>
@@ -17138,7 +16828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1117" spans="1:8">
+    <row r="1117" spans="1:4">
       <c r="A1117" s="6">
         <v>46169</v>
       </c>
@@ -17151,10 +16841,8 @@
       <c r="D1117" s="2">
         <v>2</v>
       </c>
-      <c r="G1117" s="1"/>
-      <c r="H1117" s="27"/>
-    </row>
-    <row r="1118" spans="1:8">
+    </row>
+    <row r="1118" spans="1:4">
       <c r="A1118" s="6">
         <v>46169</v>
       </c>
@@ -17167,10 +16855,8 @@
       <c r="D1118" s="2">
         <v>5</v>
       </c>
-      <c r="G1118" s="1"/>
-      <c r="H1118" s="27"/>
-    </row>
-    <row r="1119" spans="1:8">
+    </row>
+    <row r="1119" spans="1:4">
       <c r="A1119" s="6">
         <v>46169</v>
       </c>
@@ -17183,10 +16869,8 @@
       <c r="D1119" s="2">
         <v>5</v>
       </c>
-      <c r="G1119" s="1"/>
-      <c r="H1119" s="27"/>
-    </row>
-    <row r="1120" spans="1:8">
+    </row>
+    <row r="1120" spans="1:4">
       <c r="A1120" s="6">
         <v>46169</v>
       </c>
@@ -17199,10 +16883,8 @@
       <c r="D1120" s="2">
         <v>7</v>
       </c>
-      <c r="G1120" s="1"/>
-      <c r="H1120" s="27"/>
-    </row>
-    <row r="1121" spans="1:8">
+    </row>
+    <row r="1121" spans="1:6">
       <c r="A1121" s="6">
         <v>46169</v>
       </c>
@@ -17215,10 +16897,8 @@
       <c r="D1121" s="2">
         <v>7</v>
       </c>
-      <c r="G1121" s="1"/>
-      <c r="H1121" s="27"/>
-    </row>
-    <row r="1122" spans="1:8">
+    </row>
+    <row r="1122" spans="1:6">
       <c r="A1122" s="6">
         <v>46169</v>
       </c>
@@ -17231,10 +16911,8 @@
       <c r="D1122" s="2">
         <v>1</v>
       </c>
-      <c r="G1122" s="1"/>
-      <c r="H1122" s="27"/>
-    </row>
-    <row r="1123" spans="1:8">
+    </row>
+    <row r="1123" spans="1:6">
       <c r="A1123" s="6">
         <v>46169</v>
       </c>
@@ -17247,10 +16925,8 @@
       <c r="D1123" s="2">
         <v>1</v>
       </c>
-      <c r="G1123" s="1"/>
-      <c r="H1123" s="27"/>
-    </row>
-    <row r="1124" spans="1:8">
+    </row>
+    <row r="1124" spans="1:6">
       <c r="A1124" s="6">
         <v>46169</v>
       </c>
@@ -17264,7 +16940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1125" spans="1:8">
+    <row r="1125" spans="1:6">
       <c r="A1125" s="6">
         <v>46169</v>
       </c>
@@ -17278,7 +16954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1126" spans="1:8">
+    <row r="1126" spans="1:6">
       <c r="A1126" s="6">
         <v>46170</v>
       </c>
@@ -17292,7 +16968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1127" spans="1:8">
+    <row r="1127" spans="1:6">
       <c r="A1127" s="6">
         <v>46170</v>
       </c>
@@ -17306,9 +16982,8 @@
         <v>3</v>
       </c>
       <c r="F1127" s="1"/>
-      <c r="G1127" s="27"/>
-    </row>
-    <row r="1128" spans="1:8">
+    </row>
+    <row r="1128" spans="1:6">
       <c r="A1128" s="6">
         <v>46170</v>
       </c>
@@ -17322,9 +16997,8 @@
         <v>3</v>
       </c>
       <c r="F1128" s="1"/>
-      <c r="G1128" s="27"/>
-    </row>
-    <row r="1129" spans="1:8">
+    </row>
+    <row r="1129" spans="1:6">
       <c r="A1129" s="6">
         <v>46170</v>
       </c>
@@ -17338,9 +17012,8 @@
         <v>0</v>
       </c>
       <c r="F1129" s="1"/>
-      <c r="G1129" s="27"/>
-    </row>
-    <row r="1130" spans="1:8">
+    </row>
+    <row r="1130" spans="1:6">
       <c r="A1130" s="6">
         <v>46170</v>
       </c>
@@ -17354,9 +17027,8 @@
         <v>0</v>
       </c>
       <c r="F1130" s="1"/>
-      <c r="G1130" s="27"/>
-    </row>
-    <row r="1131" spans="1:8">
+    </row>
+    <row r="1131" spans="1:6">
       <c r="A1131" s="6">
         <v>46170</v>
       </c>
@@ -17370,9 +17042,8 @@
         <v>3</v>
       </c>
       <c r="F1131" s="1"/>
-      <c r="G1131" s="27"/>
-    </row>
-    <row r="1132" spans="1:8">
+    </row>
+    <row r="1132" spans="1:6">
       <c r="A1132" s="6">
         <v>46170</v>
       </c>
@@ -17386,9 +17057,8 @@
         <v>3</v>
       </c>
       <c r="F1132" s="1"/>
-      <c r="G1132" s="27"/>
-    </row>
-    <row r="1133" spans="1:8">
+    </row>
+    <row r="1133" spans="1:6">
       <c r="A1133" s="6">
         <v>46170</v>
       </c>
@@ -17402,7 +17072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1134" spans="1:8">
+    <row r="1134" spans="1:6">
       <c r="A1134" s="6">
         <v>46170</v>
       </c>
@@ -17416,7 +17086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1135" spans="1:8">
+    <row r="1135" spans="1:6">
       <c r="A1135" s="6">
         <v>46170</v>
       </c>
@@ -17430,7 +17100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1136" spans="1:8">
+    <row r="1136" spans="1:6">
       <c r="A1136" s="6">
         <v>46170</v>
       </c>
@@ -17444,7 +17114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1137" spans="1:7">
+    <row r="1137" spans="1:6">
       <c r="A1137" s="6">
         <v>46171</v>
       </c>
@@ -17458,7 +17128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1138" spans="1:7">
+    <row r="1138" spans="1:6">
       <c r="A1138" s="6">
         <v>46171</v>
       </c>
@@ -17472,7 +17142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1139" spans="1:7">
+    <row r="1139" spans="1:6">
       <c r="A1139" s="6">
         <v>46171</v>
       </c>
@@ -17486,9 +17156,8 @@
         <v>2</v>
       </c>
       <c r="F1139" s="1"/>
-      <c r="G1139" s="27"/>
-    </row>
-    <row r="1140" spans="1:7">
+    </row>
+    <row r="1140" spans="1:6">
       <c r="A1140" s="6">
         <v>46171</v>
       </c>
@@ -17502,9 +17171,8 @@
         <v>2</v>
       </c>
       <c r="F1140" s="1"/>
-      <c r="G1140" s="27"/>
-    </row>
-    <row r="1141" spans="1:7">
+    </row>
+    <row r="1141" spans="1:6">
       <c r="A1141" s="6">
         <v>46171</v>
       </c>
@@ -17518,9 +17186,8 @@
         <v>4</v>
       </c>
       <c r="F1141" s="1"/>
-      <c r="G1141" s="27"/>
-    </row>
-    <row r="1142" spans="1:7">
+    </row>
+    <row r="1142" spans="1:6">
       <c r="A1142" s="6">
         <v>46171</v>
       </c>
@@ -17534,9 +17201,8 @@
         <v>0</v>
       </c>
       <c r="F1142" s="1"/>
-      <c r="G1142" s="27"/>
-    </row>
-    <row r="1143" spans="1:7">
+    </row>
+    <row r="1143" spans="1:6">
       <c r="A1143" s="6">
         <v>46171</v>
       </c>
@@ -17550,9 +17216,8 @@
         <v>0</v>
       </c>
       <c r="F1143" s="1"/>
-      <c r="G1143" s="27"/>
-    </row>
-    <row r="1144" spans="1:7">
+    </row>
+    <row r="1144" spans="1:6">
       <c r="A1144" s="6">
         <v>46171</v>
       </c>
@@ -17566,9 +17231,8 @@
         <v>2</v>
       </c>
       <c r="F1144" s="1"/>
-      <c r="G1144" s="27"/>
-    </row>
-    <row r="1145" spans="1:7">
+    </row>
+    <row r="1145" spans="1:6">
       <c r="A1145" s="6">
         <v>46171</v>
       </c>
@@ -17582,9 +17246,8 @@
         <v>2</v>
       </c>
       <c r="F1145" s="1"/>
-      <c r="G1145" s="27"/>
-    </row>
-    <row r="1146" spans="1:7">
+    </row>
+    <row r="1146" spans="1:6">
       <c r="A1146" s="6">
         <v>46171</v>
       </c>
@@ -17598,7 +17261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1147" spans="1:7">
+    <row r="1147" spans="1:6">
       <c r="A1147" s="6">
         <v>46171</v>
       </c>
@@ -17612,7 +17275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1148" spans="1:7">
+    <row r="1148" spans="1:6">
       <c r="A1148" s="6">
         <v>46171</v>
       </c>
@@ -17626,7 +17289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1149" spans="1:7">
+    <row r="1149" spans="1:6">
       <c r="A1149" s="6">
         <v>46172</v>
       </c>
@@ -17640,7 +17303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1150" spans="1:7">
+    <row r="1150" spans="1:6">
       <c r="A1150" s="6">
         <v>46172</v>
       </c>
@@ -17654,9 +17317,8 @@
         <v>3</v>
       </c>
       <c r="F1150" s="1"/>
-      <c r="G1150" s="27"/>
-    </row>
-    <row r="1151" spans="1:7">
+    </row>
+    <row r="1151" spans="1:6">
       <c r="A1151" s="6">
         <v>46172</v>
       </c>
@@ -17670,9 +17332,8 @@
         <v>5</v>
       </c>
       <c r="F1151" s="1"/>
-      <c r="G1151" s="27"/>
-    </row>
-    <row r="1152" spans="1:7">
+    </row>
+    <row r="1152" spans="1:6">
       <c r="A1152" s="6">
         <v>46172</v>
       </c>
@@ -17686,9 +17347,8 @@
         <v>18</v>
       </c>
       <c r="F1152" s="1"/>
-      <c r="G1152" s="27"/>
-    </row>
-    <row r="1153" spans="1:8">
+    </row>
+    <row r="1153" spans="1:6">
       <c r="A1153" s="6">
         <v>46172</v>
       </c>
@@ -17702,9 +17362,8 @@
         <v>0</v>
       </c>
       <c r="F1153" s="1"/>
-      <c r="G1153" s="27"/>
-    </row>
-    <row r="1154" spans="1:8">
+    </row>
+    <row r="1154" spans="1:6">
       <c r="A1154" s="6">
         <v>46174</v>
       </c>
@@ -17719,7 +17378,7 @@
       </c>
       <c r="F1154" s="1"/>
     </row>
-    <row r="1155" spans="1:8">
+    <row r="1155" spans="1:6">
       <c r="A1155" s="6">
         <v>46174</v>
       </c>
@@ -17733,10 +17392,8 @@
         <v>2</v>
       </c>
       <c r="F1155" s="1"/>
-      <c r="G1155" s="1"/>
-      <c r="H1155" s="27"/>
-    </row>
-    <row r="1156" spans="1:8">
+    </row>
+    <row r="1156" spans="1:6">
       <c r="A1156" s="6">
         <v>46174</v>
       </c>
@@ -17749,10 +17406,8 @@
       <c r="D1156" s="2">
         <v>2</v>
       </c>
-      <c r="G1156" s="1"/>
-      <c r="H1156" s="27"/>
-    </row>
-    <row r="1157" spans="1:8">
+    </row>
+    <row r="1157" spans="1:6">
       <c r="A1157" s="6">
         <v>46174</v>
       </c>
@@ -17765,10 +17420,8 @@
       <c r="D1157" s="2">
         <v>2</v>
       </c>
-      <c r="G1157" s="1"/>
-      <c r="H1157" s="27"/>
-    </row>
-    <row r="1158" spans="1:8">
+    </row>
+    <row r="1158" spans="1:6">
       <c r="A1158" s="6">
         <v>46174</v>
       </c>
@@ -17781,10 +17434,8 @@
       <c r="D1158" s="2">
         <v>2</v>
       </c>
-      <c r="G1158" s="1"/>
-      <c r="H1158" s="27"/>
-    </row>
-    <row r="1159" spans="1:8">
+    </row>
+    <row r="1159" spans="1:6">
       <c r="A1159" s="6">
         <v>46174</v>
       </c>
@@ -17797,10 +17448,8 @@
       <c r="D1159" s="2">
         <v>0</v>
       </c>
-      <c r="G1159" s="1"/>
-      <c r="H1159" s="27"/>
-    </row>
-    <row r="1160" spans="1:8">
+    </row>
+    <row r="1160" spans="1:6">
       <c r="A1160" s="6">
         <v>46174</v>
       </c>
@@ -17813,10 +17462,8 @@
       <c r="D1160" s="2">
         <v>0</v>
       </c>
-      <c r="G1160" s="1"/>
-      <c r="H1160" s="27"/>
-    </row>
-    <row r="1161" spans="1:8">
+    </row>
+    <row r="1161" spans="1:6">
       <c r="A1161" s="6">
         <v>46174</v>
       </c>
@@ -17829,10 +17476,8 @@
       <c r="D1161" s="2">
         <v>5</v>
       </c>
-      <c r="G1161" s="1"/>
-      <c r="H1161" s="27"/>
-    </row>
-    <row r="1162" spans="1:8">
+    </row>
+    <row r="1162" spans="1:6">
       <c r="A1162" s="6">
         <v>46174</v>
       </c>
@@ -17845,10 +17490,8 @@
       <c r="D1162" s="2">
         <v>5</v>
       </c>
-      <c r="G1162" s="1"/>
-      <c r="H1162" s="27"/>
-    </row>
-    <row r="1163" spans="1:8">
+    </row>
+    <row r="1163" spans="1:6">
       <c r="A1163" s="6">
         <v>46174</v>
       </c>
@@ -17862,7 +17505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1164" spans="1:8">
+    <row r="1164" spans="1:6">
       <c r="A1164" s="6">
         <v>46174</v>
       </c>
@@ -17876,7 +17519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1165" spans="1:8">
+    <row r="1165" spans="1:6">
       <c r="A1165" s="6">
         <v>46174</v>
       </c>
@@ -17890,7 +17533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1166" spans="1:8">
+    <row r="1166" spans="1:6">
       <c r="A1166" s="6">
         <v>46174</v>
       </c>
@@ -17904,7 +17547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1167" spans="1:8">
+    <row r="1167" spans="1:6">
       <c r="A1167" s="6">
         <v>46176</v>
       </c>
@@ -17918,7 +17561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1168" spans="1:8">
+    <row r="1168" spans="1:6">
       <c r="A1168" s="6">
         <v>46176</v>
       </c>
@@ -17932,9 +17575,8 @@
         <v>1</v>
       </c>
       <c r="F1168" s="1"/>
-      <c r="G1168" s="27"/>
-    </row>
-    <row r="1169" spans="1:7">
+    </row>
+    <row r="1169" spans="1:6">
       <c r="A1169" s="6">
         <v>46176</v>
       </c>
@@ -17948,9 +17590,8 @@
         <v>3</v>
       </c>
       <c r="F1169" s="1"/>
-      <c r="G1169" s="27"/>
-    </row>
-    <row r="1170" spans="1:7">
+    </row>
+    <row r="1170" spans="1:6">
       <c r="A1170" s="6">
         <v>46176</v>
       </c>
@@ -17964,9 +17605,8 @@
         <v>4</v>
       </c>
       <c r="F1170" s="1"/>
-      <c r="G1170" s="27"/>
-    </row>
-    <row r="1171" spans="1:7">
+    </row>
+    <row r="1171" spans="1:6">
       <c r="A1171" s="6">
         <v>46176</v>
       </c>
@@ -17980,9 +17620,8 @@
         <v>4</v>
       </c>
       <c r="F1171" s="1"/>
-      <c r="G1171" s="27"/>
-    </row>
-    <row r="1172" spans="1:7">
+    </row>
+    <row r="1172" spans="1:6">
       <c r="A1172" s="6">
         <v>46176</v>
       </c>
@@ -17996,9 +17635,8 @@
         <v>2</v>
       </c>
       <c r="F1172" s="1"/>
-      <c r="G1172" s="27"/>
-    </row>
-    <row r="1173" spans="1:7">
+    </row>
+    <row r="1173" spans="1:6">
       <c r="A1173" s="6">
         <v>46176</v>
       </c>
@@ -18012,9 +17650,8 @@
         <v>2</v>
       </c>
       <c r="F1173" s="1"/>
-      <c r="G1173" s="27"/>
-    </row>
-    <row r="1174" spans="1:7">
+    </row>
+    <row r="1174" spans="1:6">
       <c r="A1174" s="6">
         <v>46176</v>
       </c>
@@ -18028,9 +17665,8 @@
         <v>2</v>
       </c>
       <c r="F1174" s="1"/>
-      <c r="G1174" s="27"/>
-    </row>
-    <row r="1175" spans="1:7">
+    </row>
+    <row r="1175" spans="1:6">
       <c r="A1175" s="6">
         <v>46176</v>
       </c>
@@ -18044,9 +17680,8 @@
         <v>2</v>
       </c>
       <c r="F1175" s="1"/>
-      <c r="G1175" s="27"/>
-    </row>
-    <row r="1176" spans="1:7">
+    </row>
+    <row r="1176" spans="1:6">
       <c r="A1176" s="6">
         <v>46176</v>
       </c>
@@ -18060,9 +17695,8 @@
         <v>2</v>
       </c>
       <c r="F1176" s="1"/>
-      <c r="G1176" s="27"/>
-    </row>
-    <row r="1177" spans="1:7">
+    </row>
+    <row r="1177" spans="1:6">
       <c r="A1177" s="6">
         <v>46176</v>
       </c>
@@ -18076,7 +17710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1178" spans="1:7">
+    <row r="1178" spans="1:6">
       <c r="A1178" s="6">
         <v>46176</v>
       </c>
@@ -18090,7 +17724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1179" spans="1:7">
+    <row r="1179" spans="1:6">
       <c r="A1179" s="6">
         <v>46176</v>
       </c>
@@ -18104,7 +17738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1180" spans="1:7">
+    <row r="1180" spans="1:6">
       <c r="A1180" s="6">
         <v>46177</v>
       </c>
@@ -18118,7 +17752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1181" spans="1:7">
+    <row r="1181" spans="1:6">
       <c r="A1181" s="6">
         <v>46177</v>
       </c>
@@ -18132,9 +17766,8 @@
         <v>4</v>
       </c>
       <c r="F1181" s="1"/>
-      <c r="G1181" s="27"/>
-    </row>
-    <row r="1182" spans="1:7">
+    </row>
+    <row r="1182" spans="1:6">
       <c r="A1182" s="6">
         <v>46177</v>
       </c>
@@ -18148,9 +17781,8 @@
         <v>4</v>
       </c>
       <c r="F1182" s="1"/>
-      <c r="G1182" s="27"/>
-    </row>
-    <row r="1183" spans="1:7">
+    </row>
+    <row r="1183" spans="1:6">
       <c r="A1183" s="6">
         <v>46177</v>
       </c>
@@ -18164,9 +17796,8 @@
         <v>4</v>
       </c>
       <c r="F1183" s="1"/>
-      <c r="G1183" s="27"/>
-    </row>
-    <row r="1184" spans="1:7">
+    </row>
+    <row r="1184" spans="1:6">
       <c r="A1184" s="6">
         <v>46177</v>
       </c>
@@ -18180,9 +17811,8 @@
         <v>0</v>
       </c>
       <c r="F1184" s="1"/>
-      <c r="G1184" s="27"/>
-    </row>
-    <row r="1185" spans="1:7">
+    </row>
+    <row r="1185" spans="1:6">
       <c r="A1185" s="6">
         <v>46177</v>
       </c>
@@ -18196,9 +17826,8 @@
         <v>0</v>
       </c>
       <c r="F1185" s="1"/>
-      <c r="G1185" s="27"/>
-    </row>
-    <row r="1186" spans="1:7">
+    </row>
+    <row r="1186" spans="1:6">
       <c r="A1186" s="6">
         <v>46177</v>
       </c>
@@ -18212,9 +17841,8 @@
         <v>3</v>
       </c>
       <c r="F1186" s="1"/>
-      <c r="G1186" s="27"/>
-    </row>
-    <row r="1187" spans="1:7">
+    </row>
+    <row r="1187" spans="1:6">
       <c r="A1187" s="6">
         <v>46177</v>
       </c>
@@ -18228,9 +17856,8 @@
         <v>3</v>
       </c>
       <c r="F1187" s="1"/>
-      <c r="G1187" s="27"/>
-    </row>
-    <row r="1188" spans="1:7">
+    </row>
+    <row r="1188" spans="1:6">
       <c r="A1188" s="6">
         <v>46177</v>
       </c>
@@ -18244,7 +17871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1189" spans="1:7">
+    <row r="1189" spans="1:6">
       <c r="A1189" s="6">
         <v>46177</v>
       </c>
@@ -18258,7 +17885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1190" spans="1:7">
+    <row r="1190" spans="1:6">
       <c r="A1190" s="6">
         <v>46177</v>
       </c>
@@ -18272,7 +17899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1191" spans="1:7">
+    <row r="1191" spans="1:6">
       <c r="A1191" s="6">
         <v>46177</v>
       </c>
@@ -18286,7 +17913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1192" spans="1:7">
+    <row r="1192" spans="1:6">
       <c r="A1192" s="6">
         <v>46178</v>
       </c>
@@ -18300,7 +17927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1193" spans="1:7">
+    <row r="1193" spans="1:6">
       <c r="A1193" s="6">
         <v>46178</v>
       </c>
@@ -18314,9 +17941,8 @@
         <v>2</v>
       </c>
       <c r="F1193" s="1"/>
-      <c r="G1193" s="27"/>
-    </row>
-    <row r="1194" spans="1:7">
+    </row>
+    <row r="1194" spans="1:6">
       <c r="A1194" s="6">
         <v>46178</v>
       </c>
@@ -18330,9 +17956,8 @@
         <v>0</v>
       </c>
       <c r="F1194" s="1"/>
-      <c r="G1194" s="27"/>
-    </row>
-    <row r="1195" spans="1:7">
+    </row>
+    <row r="1195" spans="1:6">
       <c r="A1195" s="6">
         <v>46178</v>
       </c>
@@ -18346,9 +17971,8 @@
         <v>0</v>
       </c>
       <c r="F1195" s="1"/>
-      <c r="G1195" s="27"/>
-    </row>
-    <row r="1196" spans="1:7">
+    </row>
+    <row r="1196" spans="1:6">
       <c r="A1196" s="6">
         <v>46178</v>
       </c>
@@ -18362,9 +17986,8 @@
         <v>2</v>
       </c>
       <c r="F1196" s="1"/>
-      <c r="G1196" s="27"/>
-    </row>
-    <row r="1197" spans="1:7">
+    </row>
+    <row r="1197" spans="1:6">
       <c r="A1197" s="6">
         <v>46178</v>
       </c>
@@ -18378,9 +18001,8 @@
         <v>2</v>
       </c>
       <c r="F1197" s="1"/>
-      <c r="G1197" s="27"/>
-    </row>
-    <row r="1198" spans="1:7">
+    </row>
+    <row r="1198" spans="1:6">
       <c r="A1198" s="6">
         <v>46178</v>
       </c>
@@ -18394,9 +18016,8 @@
         <v>3</v>
       </c>
       <c r="F1198" s="1"/>
-      <c r="G1198" s="27"/>
-    </row>
-    <row r="1199" spans="1:7">
+    </row>
+    <row r="1199" spans="1:6">
       <c r="A1199" s="6">
         <v>46178</v>
       </c>
@@ -18410,9 +18031,8 @@
         <v>3</v>
       </c>
       <c r="F1199" s="1"/>
-      <c r="G1199" s="27"/>
-    </row>
-    <row r="1200" spans="1:7">
+    </row>
+    <row r="1200" spans="1:6">
       <c r="A1200" s="6">
         <v>46178</v>
       </c>
@@ -18426,9 +18046,8 @@
         <v>1</v>
       </c>
       <c r="F1200" s="1"/>
-      <c r="G1200" s="27"/>
-    </row>
-    <row r="1201" spans="1:7">
+    </row>
+    <row r="1201" spans="1:6">
       <c r="A1201" s="6">
         <v>46178</v>
       </c>
@@ -18442,7 +18061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1202" spans="1:7">
+    <row r="1202" spans="1:6">
       <c r="A1202" s="6">
         <v>46178</v>
       </c>
@@ -18456,7 +18075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1203" spans="1:7">
+    <row r="1203" spans="1:6">
       <c r="A1203" s="6">
         <v>46178</v>
       </c>
@@ -18470,7 +18089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1204" spans="1:7">
+    <row r="1204" spans="1:6">
       <c r="A1204" s="6">
         <v>46179</v>
       </c>
@@ -18484,7 +18103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1205" spans="1:7">
+    <row r="1205" spans="1:6">
       <c r="A1205" s="6">
         <v>46179</v>
       </c>
@@ -18498,7 +18117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1206" spans="1:7">
+    <row r="1206" spans="1:6">
       <c r="A1206" s="6">
         <v>46179</v>
       </c>
@@ -18512,9 +18131,8 @@
         <v>5</v>
       </c>
       <c r="F1206" s="1"/>
-      <c r="G1206" s="27"/>
-    </row>
-    <row r="1207" spans="1:7">
+    </row>
+    <row r="1207" spans="1:6">
       <c r="A1207" s="6">
         <v>46179</v>
       </c>
@@ -18528,9 +18146,8 @@
         <v>5</v>
       </c>
       <c r="F1207" s="1"/>
-      <c r="G1207" s="27"/>
-    </row>
-    <row r="1208" spans="1:7">
+    </row>
+    <row r="1208" spans="1:6">
       <c r="A1208" s="6">
         <v>46181</v>
       </c>
@@ -18544,9 +18161,8 @@
         <v>0</v>
       </c>
       <c r="F1208" s="1"/>
-      <c r="G1208" s="27"/>
-    </row>
-    <row r="1209" spans="1:7">
+    </row>
+    <row r="1209" spans="1:6">
       <c r="A1209" s="6">
         <v>46181</v>
       </c>
@@ -18560,9 +18176,8 @@
         <v>0</v>
       </c>
       <c r="F1209" s="1"/>
-      <c r="G1209" s="27"/>
-    </row>
-    <row r="1210" spans="1:7">
+    </row>
+    <row r="1210" spans="1:6">
       <c r="A1210" s="6">
         <v>46181</v>
       </c>
@@ -18576,9 +18191,8 @@
         <v>1</v>
       </c>
       <c r="F1210" s="1"/>
-      <c r="G1210" s="27"/>
-    </row>
-    <row r="1211" spans="1:7">
+    </row>
+    <row r="1211" spans="1:6">
       <c r="A1211" s="6">
         <v>46181</v>
       </c>
@@ -18592,9 +18206,8 @@
         <v>1</v>
       </c>
       <c r="F1211" s="1"/>
-      <c r="G1211" s="27"/>
-    </row>
-    <row r="1212" spans="1:7">
+    </row>
+    <row r="1212" spans="1:6">
       <c r="A1212" s="6">
         <v>46181</v>
       </c>
@@ -18608,9 +18221,8 @@
         <v>0</v>
       </c>
       <c r="F1212" s="1"/>
-      <c r="G1212" s="27"/>
-    </row>
-    <row r="1213" spans="1:7">
+    </row>
+    <row r="1213" spans="1:6">
       <c r="A1213" s="6">
         <v>46181</v>
       </c>
@@ -18624,7 +18236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1214" spans="1:7">
+    <row r="1214" spans="1:6">
       <c r="A1214" s="6">
         <v>46181</v>
       </c>
@@ -18638,7 +18250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1215" spans="1:7">
+    <row r="1215" spans="1:6">
       <c r="A1215" s="6">
         <v>46181</v>
       </c>
@@ -18652,7 +18264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1216" spans="1:7">
+    <row r="1216" spans="1:6">
       <c r="A1216" s="6">
         <v>46181</v>
       </c>
@@ -18666,7 +18278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1217" spans="1:7">
+    <row r="1217" spans="1:6">
       <c r="A1217" s="6">
         <v>46181</v>
       </c>
@@ -18680,7 +18292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1218" spans="1:7">
+    <row r="1218" spans="1:6">
       <c r="A1218" s="6">
         <v>46182</v>
       </c>
@@ -18694,7 +18306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1219" spans="1:7">
+    <row r="1219" spans="1:6">
       <c r="A1219" s="6">
         <v>46182</v>
       </c>
@@ -18708,9 +18320,8 @@
         <v>3</v>
       </c>
       <c r="F1219" s="1"/>
-      <c r="G1219" s="27"/>
-    </row>
-    <row r="1220" spans="1:7">
+    </row>
+    <row r="1220" spans="1:6">
       <c r="A1220" s="6">
         <v>46182</v>
       </c>
@@ -18724,9 +18335,8 @@
         <v>3</v>
       </c>
       <c r="F1220" s="1"/>
-      <c r="G1220" s="27"/>
-    </row>
-    <row r="1221" spans="1:7">
+    </row>
+    <row r="1221" spans="1:6">
       <c r="A1221" s="6">
         <v>46182</v>
       </c>
@@ -18740,9 +18350,8 @@
         <v>3</v>
       </c>
       <c r="F1221" s="1"/>
-      <c r="G1221" s="27"/>
-    </row>
-    <row r="1222" spans="1:7">
+    </row>
+    <row r="1222" spans="1:6">
       <c r="A1222" s="6">
         <v>46182</v>
       </c>
@@ -18756,9 +18365,8 @@
         <v>3</v>
       </c>
       <c r="F1222" s="1"/>
-      <c r="G1222" s="27"/>
-    </row>
-    <row r="1223" spans="1:7">
+    </row>
+    <row r="1223" spans="1:6">
       <c r="A1223" s="6">
         <v>46182</v>
       </c>
@@ -18772,9 +18380,8 @@
         <v>2</v>
       </c>
       <c r="F1223" s="1"/>
-      <c r="G1223" s="27"/>
-    </row>
-    <row r="1224" spans="1:7">
+    </row>
+    <row r="1224" spans="1:6">
       <c r="A1224" s="6">
         <v>46182</v>
       </c>
@@ -18788,9 +18395,8 @@
         <v>2</v>
       </c>
       <c r="F1224" s="1"/>
-      <c r="G1224" s="27"/>
-    </row>
-    <row r="1225" spans="1:7">
+    </row>
+    <row r="1225" spans="1:6">
       <c r="A1225" s="6">
         <v>46182</v>
       </c>
@@ -18804,9 +18410,8 @@
         <v>0</v>
       </c>
       <c r="F1225" s="1"/>
-      <c r="G1225" s="27"/>
-    </row>
-    <row r="1226" spans="1:7">
+    </row>
+    <row r="1226" spans="1:6">
       <c r="A1226" s="6">
         <v>46182</v>
       </c>
@@ -18820,9 +18425,8 @@
         <v>0</v>
       </c>
       <c r="F1226" s="1"/>
-      <c r="G1226" s="27"/>
-    </row>
-    <row r="1227" spans="1:7">
+    </row>
+    <row r="1227" spans="1:6">
       <c r="A1227" s="6">
         <v>46182</v>
       </c>
@@ -18836,7 +18440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1228" spans="1:7">
+    <row r="1228" spans="1:6">
       <c r="A1228" s="6">
         <v>46182</v>
       </c>
@@ -18850,7 +18454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1229" spans="1:7">
+    <row r="1229" spans="1:6">
       <c r="A1229" s="6">
         <v>46183</v>
       </c>
@@ -18864,7 +18468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1230" spans="1:7">
+    <row r="1230" spans="1:6">
       <c r="A1230" s="6">
         <v>46183</v>
       </c>
@@ -18878,7 +18482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1231" spans="1:7">
+    <row r="1231" spans="1:6">
       <c r="A1231" s="6">
         <v>46183</v>
       </c>
@@ -18892,7 +18496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1232" spans="1:7">
+    <row r="1232" spans="1:6">
       <c r="A1232" s="6">
         <v>46183</v>
       </c>
@@ -18906,9 +18510,8 @@
         <v>3</v>
       </c>
       <c r="F1232" s="1"/>
-      <c r="G1232" s="27"/>
-    </row>
-    <row r="1233" spans="1:7">
+    </row>
+    <row r="1233" spans="1:6">
       <c r="A1233" s="6">
         <v>46183</v>
       </c>
@@ -18922,9 +18525,8 @@
         <v>3</v>
       </c>
       <c r="F1233" s="1"/>
-      <c r="G1233" s="27"/>
-    </row>
-    <row r="1234" spans="1:7">
+    </row>
+    <row r="1234" spans="1:6">
       <c r="A1234" s="6">
         <v>46183</v>
       </c>
@@ -18938,9 +18540,8 @@
         <v>6</v>
       </c>
       <c r="F1234" s="1"/>
-      <c r="G1234" s="27"/>
-    </row>
-    <row r="1235" spans="1:7">
+    </row>
+    <row r="1235" spans="1:6">
       <c r="A1235" s="6">
         <v>46184</v>
       </c>
@@ -18954,9 +18555,8 @@
         <v>1</v>
       </c>
       <c r="F1235" s="1"/>
-      <c r="G1235" s="27"/>
-    </row>
-    <row r="1236" spans="1:7">
+    </row>
+    <row r="1236" spans="1:6">
       <c r="A1236" s="6">
         <v>46184</v>
       </c>
@@ -18970,9 +18570,8 @@
         <v>1</v>
       </c>
       <c r="F1236" s="1"/>
-      <c r="G1236" s="27"/>
-    </row>
-    <row r="1237" spans="1:7">
+    </row>
+    <row r="1237" spans="1:6">
       <c r="A1237" s="6">
         <v>46184</v>
       </c>
@@ -18986,7 +18585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1238" spans="1:7">
+    <row r="1238" spans="1:6">
       <c r="A1238" s="6">
         <v>46184</v>
       </c>
@@ -19000,9 +18599,8 @@
         <v>2</v>
       </c>
       <c r="F1238" s="1"/>
-      <c r="G1238" s="27"/>
-    </row>
-    <row r="1239" spans="1:7">
+    </row>
+    <row r="1239" spans="1:6">
       <c r="A1239" s="6">
         <v>46184</v>
       </c>
@@ -19016,9 +18614,8 @@
         <v>9</v>
       </c>
       <c r="F1239" s="1"/>
-      <c r="G1239" s="27"/>
-    </row>
-    <row r="1240" spans="1:7">
+    </row>
+    <row r="1240" spans="1:6">
       <c r="A1240" s="6">
         <v>46184</v>
       </c>
@@ -19032,9 +18629,8 @@
         <v>6</v>
       </c>
       <c r="F1240" s="1"/>
-      <c r="G1240" s="27"/>
-    </row>
-    <row r="1241" spans="1:7">
+    </row>
+    <row r="1241" spans="1:6">
       <c r="A1241" s="6">
         <v>46184</v>
       </c>
@@ -19048,9 +18644,8 @@
         <v>1</v>
       </c>
       <c r="F1241" s="1"/>
-      <c r="G1241" s="27"/>
-    </row>
-    <row r="1242" spans="1:7">
+    </row>
+    <row r="1242" spans="1:6">
       <c r="A1242" s="6">
         <v>46184</v>
       </c>
@@ -19064,9 +18659,8 @@
         <v>1</v>
       </c>
       <c r="F1242" s="1"/>
-      <c r="G1242" s="27"/>
-    </row>
-    <row r="1243" spans="1:7">
+    </row>
+    <row r="1243" spans="1:6">
       <c r="A1243" s="6">
         <v>46184</v>
       </c>
@@ -19080,9 +18674,8 @@
         <v>1</v>
       </c>
       <c r="F1243" s="1"/>
-      <c r="G1243" s="27"/>
-    </row>
-    <row r="1244" spans="1:7">
+    </row>
+    <row r="1244" spans="1:6">
       <c r="A1244" s="6">
         <v>46184</v>
       </c>
@@ -19096,9 +18689,8 @@
         <v>1</v>
       </c>
       <c r="F1244" s="1"/>
-      <c r="G1244" s="27"/>
-    </row>
-    <row r="1245" spans="1:7">
+    </row>
+    <row r="1245" spans="1:6">
       <c r="A1245" s="6">
         <v>46184</v>
       </c>
@@ -19112,9 +18704,8 @@
         <v>4</v>
       </c>
       <c r="F1245" s="1"/>
-      <c r="G1245" s="27"/>
-    </row>
-    <row r="1246" spans="1:7">
+    </row>
+    <row r="1246" spans="1:6">
       <c r="A1246" s="6">
         <v>46184</v>
       </c>
@@ -19128,9 +18719,8 @@
         <v>4</v>
       </c>
       <c r="F1246" s="1"/>
-      <c r="G1246" s="27"/>
-    </row>
-    <row r="1247" spans="1:7">
+    </row>
+    <row r="1247" spans="1:6">
       <c r="A1247" s="6">
         <v>46185</v>
       </c>
@@ -19144,9 +18734,8 @@
         <v>10</v>
       </c>
       <c r="F1247" s="1"/>
-      <c r="G1247" s="27"/>
-    </row>
-    <row r="1248" spans="1:7">
+    </row>
+    <row r="1248" spans="1:6">
       <c r="A1248" s="6">
         <v>46185</v>
       </c>
@@ -19160,9 +18749,8 @@
         <v>10</v>
       </c>
       <c r="F1248" s="1"/>
-      <c r="G1248" s="27"/>
-    </row>
-    <row r="1249" spans="1:7">
+    </row>
+    <row r="1249" spans="1:6">
       <c r="A1249" s="6">
         <v>46185</v>
       </c>
@@ -19176,7 +18764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1250" spans="1:7">
+    <row r="1250" spans="1:6">
       <c r="A1250" s="6">
         <v>46185</v>
       </c>
@@ -19190,9 +18778,8 @@
         <v>4</v>
       </c>
       <c r="F1250" s="1"/>
-      <c r="G1250" s="27"/>
-    </row>
-    <row r="1251" spans="1:7">
+    </row>
+    <row r="1251" spans="1:6">
       <c r="A1251" s="6">
         <v>46185</v>
       </c>
@@ -19206,9 +18793,8 @@
         <v>4</v>
       </c>
       <c r="F1251" s="1"/>
-      <c r="G1251" s="27"/>
-    </row>
-    <row r="1252" spans="1:7">
+    </row>
+    <row r="1252" spans="1:6">
       <c r="A1252" s="6">
         <v>46185</v>
       </c>
@@ -19222,9 +18808,8 @@
         <v>3</v>
       </c>
       <c r="F1252" s="1"/>
-      <c r="G1252" s="27"/>
-    </row>
-    <row r="1253" spans="1:7">
+    </row>
+    <row r="1253" spans="1:6">
       <c r="A1253" s="6">
         <v>46185</v>
       </c>
@@ -19238,9 +18823,8 @@
         <v>3</v>
       </c>
       <c r="F1253" s="1"/>
-      <c r="G1253" s="27"/>
-    </row>
-    <row r="1254" spans="1:7">
+    </row>
+    <row r="1254" spans="1:6">
       <c r="A1254" s="6">
         <v>46185</v>
       </c>
@@ -19254,9 +18838,8 @@
         <v>1</v>
       </c>
       <c r="F1254" s="1"/>
-      <c r="G1254" s="27"/>
-    </row>
-    <row r="1255" spans="1:7">
+    </row>
+    <row r="1255" spans="1:6">
       <c r="A1255" s="6">
         <v>46185</v>
       </c>
@@ -19270,9 +18853,8 @@
         <v>1</v>
       </c>
       <c r="F1255" s="1"/>
-      <c r="G1255" s="27"/>
-    </row>
-    <row r="1256" spans="1:7">
+    </row>
+    <row r="1256" spans="1:6">
       <c r="A1256" s="6">
         <v>46185</v>
       </c>
@@ -19286,9 +18868,8 @@
         <v>1</v>
       </c>
       <c r="F1256" s="1"/>
-      <c r="G1256" s="27"/>
-    </row>
-    <row r="1257" spans="1:7">
+    </row>
+    <row r="1257" spans="1:6">
       <c r="A1257" s="6">
         <v>46185</v>
       </c>
@@ -19302,9 +18883,8 @@
         <v>1</v>
       </c>
       <c r="F1257" s="1"/>
-      <c r="G1257" s="27"/>
-    </row>
-    <row r="1258" spans="1:7">
+    </row>
+    <row r="1258" spans="1:6">
       <c r="A1258" s="6">
         <v>46186</v>
       </c>
@@ -19318,7 +18898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1259" spans="1:7">
+    <row r="1259" spans="1:6">
       <c r="A1259" s="6">
         <v>46186</v>
       </c>
@@ -19332,9 +18912,8 @@
         <v>1</v>
       </c>
       <c r="F1259" s="1"/>
-      <c r="G1259" s="27"/>
-    </row>
-    <row r="1260" spans="1:7">
+    </row>
+    <row r="1260" spans="1:6">
       <c r="A1260" s="6">
         <v>46186</v>
       </c>
@@ -19348,9 +18927,8 @@
         <v>1</v>
       </c>
       <c r="F1260" s="1"/>
-      <c r="G1260" s="27"/>
-    </row>
-    <row r="1261" spans="1:7">
+    </row>
+    <row r="1261" spans="1:6">
       <c r="A1261" s="6">
         <v>46186</v>
       </c>
@@ -19364,9 +18942,8 @@
         <v>8</v>
       </c>
       <c r="F1261" s="1"/>
-      <c r="G1261" s="27"/>
-    </row>
-    <row r="1262" spans="1:7">
+    </row>
+    <row r="1262" spans="1:6">
       <c r="A1262" s="6">
         <v>46186</v>
       </c>
@@ -19380,9 +18957,8 @@
         <v>11</v>
       </c>
       <c r="F1262" s="1"/>
-      <c r="G1262" s="27"/>
-    </row>
-    <row r="1263" spans="1:7">
+    </row>
+    <row r="1263" spans="1:6">
       <c r="A1263" s="6">
         <v>46188</v>
       </c>
@@ -19396,7 +18972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1264" spans="1:7">
+    <row r="1264" spans="1:6">
       <c r="A1264" s="6">
         <v>46188</v>
       </c>
@@ -19410,9 +18986,8 @@
         <v>0</v>
       </c>
       <c r="F1264" s="1"/>
-      <c r="G1264" s="27"/>
-    </row>
-    <row r="1265" spans="1:7">
+    </row>
+    <row r="1265" spans="1:6">
       <c r="A1265" s="6">
         <v>46188</v>
       </c>
@@ -19426,9 +19001,8 @@
         <v>0</v>
       </c>
       <c r="F1265" s="1"/>
-      <c r="G1265" s="27"/>
-    </row>
-    <row r="1266" spans="1:7">
+    </row>
+    <row r="1266" spans="1:6">
       <c r="A1266" s="6">
         <v>46188</v>
       </c>
@@ -19442,9 +19016,8 @@
         <v>1</v>
       </c>
       <c r="F1266" s="1"/>
-      <c r="G1266" s="27"/>
-    </row>
-    <row r="1267" spans="1:7">
+    </row>
+    <row r="1267" spans="1:6">
       <c r="A1267" s="6">
         <v>46188</v>
       </c>
@@ -19458,9 +19031,8 @@
         <v>1</v>
       </c>
       <c r="F1267" s="1"/>
-      <c r="G1267" s="27"/>
-    </row>
-    <row r="1268" spans="1:7">
+    </row>
+    <row r="1268" spans="1:6">
       <c r="A1268" s="6">
         <v>46188</v>
       </c>
@@ -19474,9 +19046,8 @@
         <v>0</v>
       </c>
       <c r="F1268" s="1"/>
-      <c r="G1268" s="27"/>
-    </row>
-    <row r="1269" spans="1:7">
+    </row>
+    <row r="1269" spans="1:6">
       <c r="A1269" s="6">
         <v>46188</v>
       </c>
@@ -19490,7 +19061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1270" spans="1:7">
+    <row r="1270" spans="1:6">
       <c r="A1270" s="6">
         <v>46189</v>
       </c>
@@ -19504,7 +19075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1271" spans="1:7">
+    <row r="1271" spans="1:6">
       <c r="A1271" s="6">
         <v>46189</v>
       </c>
@@ -19518,7 +19089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1272" spans="1:7">
+    <row r="1272" spans="1:6">
       <c r="A1272" s="6">
         <v>46189</v>
       </c>
@@ -19532,7 +19103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1273" spans="1:7">
+    <row r="1273" spans="1:6">
       <c r="A1273" s="6">
         <v>46189</v>
       </c>
@@ -19546,9 +19117,8 @@
         <v>0</v>
       </c>
       <c r="F1273" s="1"/>
-      <c r="G1273" s="27"/>
-    </row>
-    <row r="1274" spans="1:7">
+    </row>
+    <row r="1274" spans="1:6">
       <c r="A1274" s="6">
         <v>46189</v>
       </c>
@@ -19562,9 +19132,8 @@
         <v>10</v>
       </c>
       <c r="F1274" s="1"/>
-      <c r="G1274" s="27"/>
-    </row>
-    <row r="1275" spans="1:7">
+    </row>
+    <row r="1275" spans="1:6">
       <c r="A1275" s="6">
         <v>46189</v>
       </c>
@@ -19578,9 +19147,8 @@
         <v>13</v>
       </c>
       <c r="F1275" s="1"/>
-      <c r="G1275" s="27"/>
-    </row>
-    <row r="1276" spans="1:7">
+    </row>
+    <row r="1276" spans="1:6">
       <c r="A1276" s="6">
         <v>46189</v>
       </c>
@@ -19594,9 +19162,8 @@
         <v>2</v>
       </c>
       <c r="F1276" s="1"/>
-      <c r="G1276" s="27"/>
-    </row>
-    <row r="1277" spans="1:7">
+    </row>
+    <row r="1277" spans="1:6">
       <c r="A1277" s="6">
         <v>46190</v>
       </c>
@@ -19610,7 +19177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1278" spans="1:7">
+    <row r="1278" spans="1:6">
       <c r="A1278" s="6">
         <v>46190</v>
       </c>
@@ -19624,9 +19191,8 @@
         <v>0</v>
       </c>
       <c r="F1278" s="1"/>
-      <c r="G1278" s="27"/>
-    </row>
-    <row r="1279" spans="1:7">
+    </row>
+    <row r="1279" spans="1:6">
       <c r="A1279" s="6">
         <v>46190</v>
       </c>
@@ -19640,9 +19206,8 @@
         <v>0</v>
       </c>
       <c r="F1279" s="1"/>
-      <c r="G1279" s="27"/>
-    </row>
-    <row r="1280" spans="1:7">
+    </row>
+    <row r="1280" spans="1:6">
       <c r="A1280" s="6">
         <v>46190</v>
       </c>
@@ -19656,9 +19221,8 @@
         <v>1</v>
       </c>
       <c r="F1280" s="1"/>
-      <c r="G1280" s="27"/>
-    </row>
-    <row r="1281" spans="1:7">
+    </row>
+    <row r="1281" spans="1:6">
       <c r="A1281" s="6">
         <v>46190</v>
       </c>
@@ -19672,9 +19236,8 @@
         <v>0</v>
       </c>
       <c r="F1281" s="1"/>
-      <c r="G1281" s="27"/>
-    </row>
-    <row r="1282" spans="1:7">
+    </row>
+    <row r="1282" spans="1:6">
       <c r="A1282" s="6">
         <v>46190</v>
       </c>
@@ -19688,9 +19251,8 @@
         <v>0</v>
       </c>
       <c r="F1282" s="1"/>
-      <c r="G1282" s="27"/>
-    </row>
-    <row r="1283" spans="1:7">
+    </row>
+    <row r="1283" spans="1:6">
       <c r="A1283" s="6">
         <v>46190</v>
       </c>
@@ -19704,9 +19266,8 @@
         <v>0</v>
       </c>
       <c r="F1283" s="1"/>
-      <c r="G1283" s="27"/>
-    </row>
-    <row r="1284" spans="1:7">
+    </row>
+    <row r="1284" spans="1:6">
       <c r="A1284" s="6">
         <v>46190</v>
       </c>
@@ -19720,9 +19281,8 @@
         <v>0</v>
       </c>
       <c r="F1284" s="1"/>
-      <c r="G1284" s="27"/>
-    </row>
-    <row r="1285" spans="1:7">
+    </row>
+    <row r="1285" spans="1:6">
       <c r="A1285" s="6">
         <v>46190</v>
       </c>
@@ -19736,7 +19296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1286" spans="1:7">
+    <row r="1286" spans="1:6">
       <c r="A1286" s="6">
         <v>46190</v>
       </c>
@@ -19750,7 +19310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1287" spans="1:7">
+    <row r="1287" spans="1:6">
       <c r="A1287" s="6">
         <v>46190</v>
       </c>
@@ -19764,7 +19324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1288" spans="1:7">
+    <row r="1288" spans="1:6">
       <c r="A1288" s="6">
         <v>46190</v>
       </c>
@@ -19778,7 +19338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1289" spans="1:7">
+    <row r="1289" spans="1:6">
       <c r="A1289" s="6">
         <v>46190</v>
       </c>
@@ -19792,7 +19352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1290" spans="1:7">
+    <row r="1290" spans="1:6">
       <c r="A1290" s="6">
         <v>46191</v>
       </c>
@@ -19806,7 +19366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1291" spans="1:7">
+    <row r="1291" spans="1:6">
       <c r="A1291" s="6">
         <v>46191</v>
       </c>
@@ -19820,7 +19380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1292" spans="1:7">
+    <row r="1292" spans="1:6">
       <c r="A1292" s="6">
         <v>46191</v>
       </c>
@@ -19834,7 +19394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1293" spans="1:7">
+    <row r="1293" spans="1:6">
       <c r="A1293" s="6">
         <v>46191</v>
       </c>
@@ -19848,7 +19408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1294" spans="1:7">
+    <row r="1294" spans="1:6">
       <c r="A1294" s="6">
         <v>46191</v>
       </c>
@@ -19862,7 +19422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1295" spans="1:7">
+    <row r="1295" spans="1:6">
       <c r="A1295" s="6">
         <v>46191</v>
       </c>
@@ -19876,7 +19436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1296" spans="1:7">
+    <row r="1296" spans="1:6">
       <c r="A1296" s="6">
         <v>46191</v>
       </c>
@@ -19890,7 +19450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1297" spans="1:7">
+    <row r="1297" spans="1:6">
       <c r="A1297" s="6">
         <v>46191</v>
       </c>
@@ -19904,7 +19464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1298" spans="1:7">
+    <row r="1298" spans="1:6">
       <c r="A1298" s="6">
         <v>46191</v>
       </c>
@@ -19918,7 +19478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1299" spans="1:7">
+    <row r="1299" spans="1:6">
       <c r="A1299" s="6">
         <v>46191</v>
       </c>
@@ -19932,7 +19492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1300" spans="1:7">
+    <row r="1300" spans="1:6">
       <c r="A1300" s="6">
         <v>46191</v>
       </c>
@@ -19946,7 +19506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1301" spans="1:7">
+    <row r="1301" spans="1:6">
       <c r="A1301" s="6">
         <v>46191</v>
       </c>
@@ -19960,7 +19520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1302" spans="1:7">
+    <row r="1302" spans="1:6">
       <c r="A1302" s="6">
         <v>46191</v>
       </c>
@@ -19974,7 +19534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1303" spans="1:7">
+    <row r="1303" spans="1:6">
       <c r="A1303" s="6">
         <v>46192</v>
       </c>
@@ -19988,7 +19548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1304" spans="1:7">
+    <row r="1304" spans="1:6">
       <c r="A1304" s="6">
         <v>46192</v>
       </c>
@@ -20002,7 +19562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1305" spans="1:7">
+    <row r="1305" spans="1:6">
       <c r="A1305" s="6">
         <v>46192</v>
       </c>
@@ -20016,7 +19576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1306" spans="1:7">
+    <row r="1306" spans="1:6">
       <c r="A1306" s="6">
         <v>46192</v>
       </c>
@@ -20030,9 +19590,8 @@
         <v>4</v>
       </c>
       <c r="F1306" s="1"/>
-      <c r="G1306" s="27"/>
-    </row>
-    <row r="1307" spans="1:7">
+    </row>
+    <row r="1307" spans="1:6">
       <c r="A1307" s="6">
         <v>46192</v>
       </c>
@@ -20046,9 +19605,8 @@
         <v>14</v>
       </c>
       <c r="F1307" s="1"/>
-      <c r="G1307" s="27"/>
-    </row>
-    <row r="1308" spans="1:7">
+    </row>
+    <row r="1308" spans="1:6">
       <c r="A1308" s="6">
         <v>46192</v>
       </c>
@@ -20062,9 +19620,8 @@
         <v>6</v>
       </c>
       <c r="F1308" s="1"/>
-      <c r="G1308" s="27"/>
-    </row>
-    <row r="1309" spans="1:7">
+    </row>
+    <row r="1309" spans="1:6">
       <c r="A1309" s="6">
         <v>46192</v>
       </c>
@@ -20078,9 +19635,8 @@
         <v>0</v>
       </c>
       <c r="F1309" s="1"/>
-      <c r="G1309" s="27"/>
-    </row>
-    <row r="1310" spans="1:7">
+    </row>
+    <row r="1310" spans="1:6">
       <c r="A1310" s="6">
         <v>46192</v>
       </c>
@@ -20094,9 +19650,8 @@
         <v>0</v>
       </c>
       <c r="F1310" s="1"/>
-      <c r="G1310" s="27"/>
-    </row>
-    <row r="1311" spans="1:7">
+    </row>
+    <row r="1311" spans="1:6">
       <c r="A1311" s="6">
         <v>46192</v>
       </c>
@@ -20110,9 +19665,8 @@
         <v>1</v>
       </c>
       <c r="F1311" s="1"/>
-      <c r="G1311" s="27"/>
-    </row>
-    <row r="1312" spans="1:7">
+    </row>
+    <row r="1312" spans="1:6">
       <c r="A1312" s="6">
         <v>46192</v>
       </c>
@@ -20126,9 +19680,8 @@
         <v>1</v>
       </c>
       <c r="F1312" s="1"/>
-      <c r="G1312" s="27"/>
-    </row>
-    <row r="1313" spans="1:7">
+    </row>
+    <row r="1313" spans="1:6">
       <c r="A1313" s="6">
         <v>46192</v>
       </c>
@@ -20142,9 +19695,8 @@
         <v>11</v>
       </c>
       <c r="F1313" s="1"/>
-      <c r="G1313" s="27"/>
-    </row>
-    <row r="1314" spans="1:7">
+    </row>
+    <row r="1314" spans="1:6">
       <c r="A1314" s="6">
         <v>46193</v>
       </c>
@@ -20158,7 +19710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1315" spans="1:7">
+    <row r="1315" spans="1:6">
       <c r="A1315" s="6">
         <v>46193</v>
       </c>
@@ -20172,9 +19724,8 @@
         <v>11</v>
       </c>
       <c r="F1315" s="1"/>
-      <c r="G1315" s="27"/>
-    </row>
-    <row r="1316" spans="1:7">
+    </row>
+    <row r="1316" spans="1:6">
       <c r="A1316" s="6">
         <v>46193</v>
       </c>
@@ -20188,9 +19739,8 @@
         <v>8</v>
       </c>
       <c r="F1316" s="1"/>
-      <c r="G1316" s="27"/>
-    </row>
-    <row r="1317" spans="1:7">
+    </row>
+    <row r="1317" spans="1:6">
       <c r="A1317" s="6">
         <v>46193</v>
       </c>
@@ -20204,9 +19754,8 @@
         <v>8</v>
       </c>
       <c r="F1317" s="1"/>
-      <c r="G1317" s="27"/>
-    </row>
-    <row r="1318" spans="1:7">
+    </row>
+    <row r="1318" spans="1:6">
       <c r="A1318" s="6">
         <v>46195</v>
       </c>
@@ -20220,7 +19769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1319" spans="1:7">
+    <row r="1319" spans="1:6">
       <c r="A1319" s="6">
         <v>46195</v>
       </c>
@@ -20234,9 +19783,8 @@
         <v>4</v>
       </c>
       <c r="F1319" s="1"/>
-      <c r="G1319" s="27"/>
-    </row>
-    <row r="1320" spans="1:7">
+    </row>
+    <row r="1320" spans="1:6">
       <c r="A1320" s="6">
         <v>46195</v>
       </c>
@@ -20250,9 +19798,8 @@
         <v>4</v>
       </c>
       <c r="F1320" s="1"/>
-      <c r="G1320" s="27"/>
-    </row>
-    <row r="1321" spans="1:7">
+    </row>
+    <row r="1321" spans="1:6">
       <c r="A1321" s="6">
         <v>46195</v>
       </c>
@@ -20266,9 +19813,8 @@
         <v>3</v>
       </c>
       <c r="F1321" s="1"/>
-      <c r="G1321" s="27"/>
-    </row>
-    <row r="1322" spans="1:7">
+    </row>
+    <row r="1322" spans="1:6">
       <c r="A1322" s="6">
         <v>46195</v>
       </c>
@@ -20282,9 +19828,8 @@
         <v>3</v>
       </c>
       <c r="F1322" s="1"/>
-      <c r="G1322" s="27"/>
-    </row>
-    <row r="1323" spans="1:7">
+    </row>
+    <row r="1323" spans="1:6">
       <c r="A1323" s="6">
         <v>46195</v>
       </c>
@@ -20298,9 +19843,8 @@
         <v>6</v>
       </c>
       <c r="F1323" s="1"/>
-      <c r="G1323" s="27"/>
-    </row>
-    <row r="1324" spans="1:7">
+    </row>
+    <row r="1324" spans="1:6">
       <c r="A1324" s="6">
         <v>46195</v>
       </c>
@@ -20314,9 +19858,8 @@
         <v>6</v>
       </c>
       <c r="F1324" s="1"/>
-      <c r="G1324" s="27"/>
-    </row>
-    <row r="1325" spans="1:7">
+    </row>
+    <row r="1325" spans="1:6">
       <c r="A1325" s="6">
         <v>46195</v>
       </c>
@@ -20330,7 +19873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1326" spans="1:7">
+    <row r="1326" spans="1:6">
       <c r="A1326" s="6">
         <v>46196</v>
       </c>
@@ -20344,7 +19887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1327" spans="1:7">
+    <row r="1327" spans="1:6">
       <c r="A1327" s="6">
         <v>46196</v>
       </c>
@@ -20358,7 +19901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1328" spans="1:7">
+    <row r="1328" spans="1:6">
       <c r="A1328" s="6">
         <v>46196</v>
       </c>
@@ -20372,7 +19915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1329" spans="1:7">
+    <row r="1329" spans="1:6">
       <c r="A1329" s="6">
         <v>46196</v>
       </c>
@@ -20386,7 +19929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1330" spans="1:7">
+    <row r="1330" spans="1:6">
       <c r="A1330" s="6">
         <v>46196</v>
       </c>
@@ -20400,7 +19943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1331" spans="1:7">
+    <row r="1331" spans="1:6">
       <c r="A1331" s="6">
         <v>46196</v>
       </c>
@@ -20414,9 +19957,8 @@
         <v>3</v>
       </c>
       <c r="F1331" s="1"/>
-      <c r="G1331" s="27"/>
-    </row>
-    <row r="1332" spans="1:7">
+    </row>
+    <row r="1332" spans="1:6">
       <c r="A1332" s="6">
         <v>46196</v>
       </c>
@@ -20430,9 +19972,8 @@
         <v>1</v>
       </c>
       <c r="F1332" s="1"/>
-      <c r="G1332" s="27"/>
-    </row>
-    <row r="1333" spans="1:7">
+    </row>
+    <row r="1333" spans="1:6">
       <c r="A1333" s="6">
         <v>46196</v>
       </c>
@@ -20446,9 +19987,8 @@
         <v>1</v>
       </c>
       <c r="F1333" s="1"/>
-      <c r="G1333" s="27"/>
-    </row>
-    <row r="1334" spans="1:7">
+    </row>
+    <row r="1334" spans="1:6">
       <c r="A1334" s="6">
         <v>46196</v>
       </c>
@@ -20462,9 +20002,8 @@
         <v>7</v>
       </c>
       <c r="F1334" s="1"/>
-      <c r="G1334" s="27"/>
-    </row>
-    <row r="1335" spans="1:7">
+    </row>
+    <row r="1335" spans="1:6">
       <c r="A1335" s="6">
         <v>46196</v>
       </c>
@@ -20478,9 +20017,8 @@
         <v>4</v>
       </c>
       <c r="F1335" s="1"/>
-      <c r="G1335" s="27"/>
-    </row>
-    <row r="1336" spans="1:7">
+    </row>
+    <row r="1336" spans="1:6">
       <c r="A1336" s="6">
         <v>46197</v>
       </c>
@@ -20494,7 +20032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1337" spans="1:7">
+    <row r="1337" spans="1:6">
       <c r="A1337" s="6">
         <v>46197</v>
       </c>
@@ -20508,9 +20046,8 @@
         <v>3</v>
       </c>
       <c r="F1337" s="1"/>
-      <c r="G1337" s="27"/>
-    </row>
-    <row r="1338" spans="1:7">
+    </row>
+    <row r="1338" spans="1:6">
       <c r="A1338" s="6">
         <v>46197</v>
       </c>
@@ -20524,9 +20061,8 @@
         <v>0</v>
       </c>
       <c r="F1338" s="1"/>
-      <c r="G1338" s="27"/>
-    </row>
-    <row r="1339" spans="1:7">
+    </row>
+    <row r="1339" spans="1:6">
       <c r="A1339" s="6">
         <v>46197</v>
       </c>
@@ -20540,9 +20076,8 @@
         <v>0</v>
       </c>
       <c r="F1339" s="1"/>
-      <c r="G1339" s="27"/>
-    </row>
-    <row r="1340" spans="1:7">
+    </row>
+    <row r="1340" spans="1:6">
       <c r="A1340" s="6">
         <v>46197</v>
       </c>
@@ -20556,9 +20091,8 @@
         <v>7</v>
       </c>
       <c r="F1340" s="1"/>
-      <c r="G1340" s="27"/>
-    </row>
-    <row r="1341" spans="1:7">
+    </row>
+    <row r="1341" spans="1:6">
       <c r="A1341" s="6">
         <v>46197</v>
       </c>
@@ -20572,9 +20106,8 @@
         <v>8</v>
       </c>
       <c r="F1341" s="1"/>
-      <c r="G1341" s="27"/>
-    </row>
-    <row r="1342" spans="1:7">
+    </row>
+    <row r="1342" spans="1:6">
       <c r="A1342" s="6">
         <v>46197</v>
       </c>
@@ -20588,9 +20121,8 @@
         <v>0</v>
       </c>
       <c r="F1342" s="1"/>
-      <c r="G1342" s="27"/>
-    </row>
-    <row r="1343" spans="1:7">
+    </row>
+    <row r="1343" spans="1:6">
       <c r="A1343" s="6">
         <v>46197</v>
       </c>
@@ -20604,9 +20136,8 @@
         <v>0</v>
       </c>
       <c r="F1343" s="1"/>
-      <c r="G1343" s="27"/>
-    </row>
-    <row r="1344" spans="1:7">
+    </row>
+    <row r="1344" spans="1:6">
       <c r="A1344" s="6">
         <v>46197</v>
       </c>
@@ -20620,7 +20151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1345" spans="1:7">
+    <row r="1345" spans="1:6">
       <c r="A1345" s="6">
         <v>46197</v>
       </c>
@@ -20634,7 +20165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1346" spans="1:7">
+    <row r="1346" spans="1:6">
       <c r="A1346" s="6">
         <v>46198</v>
       </c>
@@ -20648,7 +20179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1347" spans="1:7">
+    <row r="1347" spans="1:6">
       <c r="A1347" s="6">
         <v>46198</v>
       </c>
@@ -20662,7 +20193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1348" spans="1:7">
+    <row r="1348" spans="1:6">
       <c r="A1348" s="6">
         <v>46198</v>
       </c>
@@ -20676,7 +20207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1349" spans="1:7">
+    <row r="1349" spans="1:6">
       <c r="A1349" s="6">
         <v>46198</v>
       </c>
@@ -20690,7 +20221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1350" spans="1:7">
+    <row r="1350" spans="1:6">
       <c r="A1350" s="6">
         <v>46198</v>
       </c>
@@ -20704,7 +20235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1351" spans="1:7">
+    <row r="1351" spans="1:6">
       <c r="A1351" s="6">
         <v>46198</v>
       </c>
@@ -20718,7 +20249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1352" spans="1:7">
+    <row r="1352" spans="1:6">
       <c r="A1352" s="6">
         <v>46198</v>
       </c>
@@ -20732,7 +20263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1353" spans="1:7">
+    <row r="1353" spans="1:6">
       <c r="A1353" s="6">
         <v>46198</v>
       </c>
@@ -20746,9 +20277,8 @@
         <v>3</v>
       </c>
       <c r="F1353" s="1"/>
-      <c r="G1353" s="27"/>
-    </row>
-    <row r="1354" spans="1:7">
+    </row>
+    <row r="1354" spans="1:6">
       <c r="A1354" s="6">
         <v>46198</v>
       </c>
@@ -20762,9 +20292,8 @@
         <v>3</v>
       </c>
       <c r="F1354" s="1"/>
-      <c r="G1354" s="27"/>
-    </row>
-    <row r="1355" spans="1:7">
+    </row>
+    <row r="1355" spans="1:6">
       <c r="A1355" s="6">
         <v>46198</v>
       </c>
@@ -20778,9 +20307,8 @@
         <v>1</v>
       </c>
       <c r="F1355" s="1"/>
-      <c r="G1355" s="27"/>
-    </row>
-    <row r="1356" spans="1:7">
+    </row>
+    <row r="1356" spans="1:6">
       <c r="A1356" s="6">
         <v>46198</v>
       </c>
@@ -20794,9 +20322,8 @@
         <v>1</v>
       </c>
       <c r="F1356" s="1"/>
-      <c r="G1356" s="27"/>
-    </row>
-    <row r="1357" spans="1:7">
+    </row>
+    <row r="1357" spans="1:6">
       <c r="A1357" s="6">
         <v>46199</v>
       </c>
@@ -20810,9 +20337,8 @@
         <v>1</v>
       </c>
       <c r="F1357" s="1"/>
-      <c r="G1357" s="27"/>
-    </row>
-    <row r="1358" spans="1:7">
+    </row>
+    <row r="1358" spans="1:6">
       <c r="A1358" s="6">
         <v>46199</v>
       </c>
@@ -20826,9 +20352,8 @@
         <v>1</v>
       </c>
       <c r="F1358" s="1"/>
-      <c r="G1358" s="27"/>
-    </row>
-    <row r="1359" spans="1:7">
+    </row>
+    <row r="1359" spans="1:6">
       <c r="A1359" s="6">
         <v>46199</v>
       </c>
@@ -20842,9 +20367,8 @@
         <v>1</v>
       </c>
       <c r="F1359" s="1"/>
-      <c r="G1359" s="27"/>
-    </row>
-    <row r="1360" spans="1:7">
+    </row>
+    <row r="1360" spans="1:6">
       <c r="A1360" s="6">
         <v>46199</v>
       </c>
@@ -20858,9 +20382,8 @@
         <v>1</v>
       </c>
       <c r="F1360" s="1"/>
-      <c r="G1360" s="27"/>
-    </row>
-    <row r="1361" spans="1:7">
+    </row>
+    <row r="1361" spans="1:6">
       <c r="A1361" s="6">
         <v>46199</v>
       </c>
@@ -20874,9 +20397,8 @@
         <v>2</v>
       </c>
       <c r="F1361" s="1"/>
-      <c r="G1361" s="27"/>
-    </row>
-    <row r="1362" spans="1:7">
+    </row>
+    <row r="1362" spans="1:6">
       <c r="A1362" s="6">
         <v>46199</v>
       </c>
@@ -20890,9 +20412,8 @@
         <v>2</v>
       </c>
       <c r="F1362" s="1"/>
-      <c r="G1362" s="27"/>
-    </row>
-    <row r="1363" spans="1:7">
+    </row>
+    <row r="1363" spans="1:6">
       <c r="A1363" s="6">
         <v>46199</v>
       </c>
@@ -20906,7 +20427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1364" spans="1:7">
+    <row r="1364" spans="1:6">
       <c r="A1364" s="6">
         <v>46199</v>
       </c>
@@ -20920,9 +20441,8 @@
         <v>1</v>
       </c>
       <c r="F1364" s="1"/>
-      <c r="G1364" s="27"/>
-    </row>
-    <row r="1365" spans="1:7">
+    </row>
+    <row r="1365" spans="1:6">
       <c r="A1365" s="6">
         <v>46199</v>
       </c>
@@ -20936,9 +20456,8 @@
         <v>1</v>
       </c>
       <c r="F1365" s="1"/>
-      <c r="G1365" s="27"/>
-    </row>
-    <row r="1366" spans="1:7">
+    </row>
+    <row r="1366" spans="1:6">
       <c r="A1366" s="6">
         <v>46199</v>
       </c>
@@ -20952,9 +20471,8 @@
         <v>3</v>
       </c>
       <c r="F1366" s="1"/>
-      <c r="G1366" s="27"/>
-    </row>
-    <row r="1367" spans="1:7">
+    </row>
+    <row r="1367" spans="1:6">
       <c r="A1367" s="6">
         <v>46199</v>
       </c>
@@ -20968,9 +20486,8 @@
         <v>3</v>
       </c>
       <c r="F1367" s="1"/>
-      <c r="G1367" s="27"/>
-    </row>
-    <row r="1368" spans="1:7">
+    </row>
+    <row r="1368" spans="1:6">
       <c r="A1368" s="6">
         <v>46199</v>
       </c>
@@ -20984,9 +20501,8 @@
         <v>4</v>
       </c>
       <c r="F1368" s="1"/>
-      <c r="G1368" s="27"/>
-    </row>
-    <row r="1369" spans="1:7">
+    </row>
+    <row r="1369" spans="1:6">
       <c r="A1369" s="6">
         <v>46200</v>
       </c>
@@ -21000,9 +20516,8 @@
         <v>3</v>
       </c>
       <c r="F1369" s="1"/>
-      <c r="G1369" s="27"/>
-    </row>
-    <row r="1370" spans="1:7">
+    </row>
+    <row r="1370" spans="1:6">
       <c r="A1370" s="6">
         <v>46200</v>
       </c>
@@ -21016,9 +20531,8 @@
         <v>3</v>
       </c>
       <c r="F1370" s="1"/>
-      <c r="G1370" s="27"/>
-    </row>
-    <row r="1371" spans="1:7">
+    </row>
+    <row r="1371" spans="1:6">
       <c r="A1371" s="6">
         <v>46200</v>
       </c>
@@ -21032,7 +20546,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1372" spans="1:7">
+    <row r="1372" spans="1:6">
       <c r="A1372" s="6">
         <v>46200</v>
       </c>
@@ -21046,9 +20560,8 @@
         <v>5</v>
       </c>
       <c r="F1372" s="1"/>
-      <c r="G1372" s="27"/>
-    </row>
-    <row r="1373" spans="1:7">
+    </row>
+    <row r="1373" spans="1:6">
       <c r="A1373" s="6">
         <v>46200</v>
       </c>
@@ -21062,9 +20575,8 @@
         <v>5</v>
       </c>
       <c r="F1373" s="1"/>
-      <c r="G1373" s="27"/>
-    </row>
-    <row r="1374" spans="1:7">
+    </row>
+    <row r="1374" spans="1:6">
       <c r="A1374" s="6">
         <v>46200</v>
       </c>
@@ -21078,9 +20590,8 @@
         <v>11</v>
       </c>
       <c r="F1374" s="1"/>
-      <c r="G1374" s="27"/>
-    </row>
-    <row r="1375" spans="1:7">
+    </row>
+    <row r="1375" spans="1:6">
       <c r="A1375" s="6">
         <v>46202</v>
       </c>
@@ -21094,7 +20605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1376" spans="1:7">
+    <row r="1376" spans="1:6">
       <c r="A1376" s="6">
         <v>46202</v>
       </c>
@@ -21108,9 +20619,8 @@
         <v>3</v>
       </c>
       <c r="F1376" s="1"/>
-      <c r="G1376" s="27"/>
-    </row>
-    <row r="1377" spans="1:7">
+    </row>
+    <row r="1377" spans="1:6">
       <c r="A1377" s="6">
         <v>46202</v>
       </c>
@@ -21124,9 +20634,8 @@
         <v>2</v>
       </c>
       <c r="F1377" s="1"/>
-      <c r="G1377" s="27"/>
-    </row>
-    <row r="1378" spans="1:7">
+    </row>
+    <row r="1378" spans="1:6">
       <c r="A1378" s="6">
         <v>46202</v>
       </c>
@@ -21140,9 +20649,8 @@
         <v>2</v>
       </c>
       <c r="F1378" s="1"/>
-      <c r="G1378" s="27"/>
-    </row>
-    <row r="1379" spans="1:7">
+    </row>
+    <row r="1379" spans="1:6">
       <c r="A1379" s="6">
         <v>46202</v>
       </c>
@@ -21156,9 +20664,8 @@
         <v>2</v>
       </c>
       <c r="F1379" s="1"/>
-      <c r="G1379" s="27"/>
-    </row>
-    <row r="1380" spans="1:7">
+    </row>
+    <row r="1380" spans="1:6">
       <c r="A1380" s="6">
         <v>46202</v>
       </c>
@@ -21172,9 +20679,8 @@
         <v>2</v>
       </c>
       <c r="F1380" s="1"/>
-      <c r="G1380" s="27"/>
-    </row>
-    <row r="1381" spans="1:7">
+    </row>
+    <row r="1381" spans="1:6">
       <c r="A1381" s="6">
         <v>46202</v>
       </c>
@@ -21188,9 +20694,8 @@
         <v>4</v>
       </c>
       <c r="F1381" s="1"/>
-      <c r="G1381" s="27"/>
-    </row>
-    <row r="1382" spans="1:7">
+    </row>
+    <row r="1382" spans="1:6">
       <c r="A1382" s="6">
         <v>46202</v>
       </c>
@@ -21204,9 +20709,8 @@
         <v>4</v>
       </c>
       <c r="F1382" s="1"/>
-      <c r="G1382" s="27"/>
-    </row>
-    <row r="1383" spans="1:7">
+    </row>
+    <row r="1383" spans="1:6">
       <c r="A1383" s="6">
         <v>46202</v>
       </c>
@@ -21220,9 +20724,8 @@
         <v>3</v>
       </c>
       <c r="F1383" s="1"/>
-      <c r="G1383" s="27"/>
-    </row>
-    <row r="1384" spans="1:7">
+    </row>
+    <row r="1384" spans="1:6">
       <c r="A1384" s="6">
         <v>46202</v>
       </c>
@@ -21236,7 +20739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1385" spans="1:7">
+    <row r="1385" spans="1:6">
       <c r="A1385" s="6">
         <v>46202</v>
       </c>
@@ -21250,7 +20753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1386" spans="1:7">
+    <row r="1386" spans="1:6">
       <c r="A1386" s="6">
         <v>46202</v>
       </c>
@@ -21264,7 +20767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1387" spans="1:7">
+    <row r="1387" spans="1:6">
       <c r="A1387" s="6">
         <v>46203</v>
       </c>
@@ -21278,7 +20781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1388" spans="1:7">
+    <row r="1388" spans="1:6">
       <c r="A1388" s="6">
         <v>46203</v>
       </c>
@@ -21292,7 +20795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1389" spans="1:7">
+    <row r="1389" spans="1:6">
       <c r="A1389" s="6">
         <v>46203</v>
       </c>
@@ -21306,7 +20809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1390" spans="1:7">
+    <row r="1390" spans="1:6">
       <c r="A1390" s="6">
         <v>46203</v>
       </c>
@@ -21320,7 +20823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1391" spans="1:7">
+    <row r="1391" spans="1:6">
       <c r="A1391" s="6">
         <v>46203</v>
       </c>
@@ -21334,7 +20837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1392" spans="1:7">
+    <row r="1392" spans="1:6">
       <c r="A1392" s="6">
         <v>46203</v>
       </c>
@@ -21348,7 +20851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1393" spans="1:7">
+    <row r="1393" spans="1:6">
       <c r="A1393" s="6">
         <v>46203</v>
       </c>
@@ -21362,7 +20865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1394" spans="1:7">
+    <row r="1394" spans="1:6">
       <c r="A1394" s="6">
         <v>46203</v>
       </c>
@@ -21376,9 +20879,8 @@
         <v>3</v>
       </c>
       <c r="F1394" s="1"/>
-      <c r="G1394" s="27"/>
-    </row>
-    <row r="1395" spans="1:7">
+    </row>
+    <row r="1395" spans="1:6">
       <c r="A1395" s="6">
         <v>46203</v>
       </c>
@@ -21392,9 +20894,8 @@
         <v>0</v>
       </c>
       <c r="F1395" s="1"/>
-      <c r="G1395" s="27"/>
-    </row>
-    <row r="1396" spans="1:7">
+    </row>
+    <row r="1396" spans="1:6">
       <c r="A1396" s="6">
         <v>46203</v>
       </c>
@@ -21408,9 +20909,8 @@
         <v>0</v>
       </c>
       <c r="F1396" s="1"/>
-      <c r="G1396" s="27"/>
-    </row>
-    <row r="1397" spans="1:7">
+    </row>
+    <row r="1397" spans="1:6">
       <c r="A1397" s="6">
         <v>46203</v>
       </c>
@@ -21424,9 +20924,8 @@
         <v>4</v>
       </c>
       <c r="F1397" s="1"/>
-      <c r="G1397" s="27"/>
-    </row>
-    <row r="1398" spans="1:7">
+    </row>
+    <row r="1398" spans="1:6">
       <c r="A1398" s="6">
         <v>46203</v>
       </c>
@@ -21440,9 +20939,8 @@
         <v>4</v>
       </c>
       <c r="F1398" s="1"/>
-      <c r="G1398" s="27"/>
-    </row>
-    <row r="1399" spans="1:7">
+    </row>
+    <row r="1399" spans="1:6">
       <c r="A1399" s="6">
         <v>46204</v>
       </c>
@@ -21456,7 +20954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1400" spans="1:7">
+    <row r="1400" spans="1:6">
       <c r="A1400" s="6">
         <v>46204</v>
       </c>
@@ -21470,9 +20968,8 @@
         <v>1</v>
       </c>
       <c r="F1400" s="1"/>
-      <c r="G1400" s="27"/>
-    </row>
-    <row r="1401" spans="1:7">
+    </row>
+    <row r="1401" spans="1:6">
       <c r="A1401" s="6">
         <v>46204</v>
       </c>
@@ -21486,9 +20983,8 @@
         <v>2</v>
       </c>
       <c r="F1401" s="1"/>
-      <c r="G1401" s="27"/>
-    </row>
-    <row r="1402" spans="1:7">
+    </row>
+    <row r="1402" spans="1:6">
       <c r="A1402" s="6">
         <v>46204</v>
       </c>
@@ -21502,9 +20998,8 @@
         <v>0</v>
       </c>
       <c r="F1402" s="1"/>
-      <c r="G1402" s="27"/>
-    </row>
-    <row r="1403" spans="1:7">
+    </row>
+    <row r="1403" spans="1:6">
       <c r="A1403" s="6">
         <v>46204</v>
       </c>
@@ -21518,9 +21013,8 @@
         <v>0</v>
       </c>
       <c r="F1403" s="1"/>
-      <c r="G1403" s="27"/>
-    </row>
-    <row r="1404" spans="1:7">
+    </row>
+    <row r="1404" spans="1:6">
       <c r="A1404" s="6">
         <v>46204</v>
       </c>
@@ -21534,9 +21028,8 @@
         <v>1</v>
       </c>
       <c r="F1404" s="1"/>
-      <c r="G1404" s="27"/>
-    </row>
-    <row r="1405" spans="1:7">
+    </row>
+    <row r="1405" spans="1:6">
       <c r="A1405" s="6">
         <v>46204</v>
       </c>
@@ -21550,9 +21043,8 @@
         <v>1</v>
       </c>
       <c r="F1405" s="1"/>
-      <c r="G1405" s="27"/>
-    </row>
-    <row r="1406" spans="1:7">
+    </row>
+    <row r="1406" spans="1:6">
       <c r="A1406" s="6">
         <v>46204</v>
       </c>
@@ -21566,9 +21058,8 @@
         <v>1</v>
       </c>
       <c r="F1406" s="1"/>
-      <c r="G1406" s="27"/>
-    </row>
-    <row r="1407" spans="1:7">
+    </row>
+    <row r="1407" spans="1:6">
       <c r="A1407" s="6">
         <v>46204</v>
       </c>
@@ -21582,7 +21073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1408" spans="1:7">
+    <row r="1408" spans="1:6">
       <c r="A1408" s="6">
         <v>46204</v>
       </c>
@@ -21611,100 +21102,1148 @@
       </c>
     </row>
     <row r="1410" spans="1:4">
-      <c r="A1410" s="6">
+      <c r="A1410" s="7">
         <v>46205</v>
       </c>
-      <c r="B1410" s="9" t="s">
+      <c r="B1410" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1410" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1410" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4">
+      <c r="A1411" s="7">
+        <v>46205</v>
+      </c>
+      <c r="B1411" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1411" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1411" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4">
+      <c r="A1412" s="7">
+        <v>46205</v>
+      </c>
+      <c r="B1412" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1410" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1410" s="2"/>
-    </row>
-    <row r="1411" spans="1:4">
-      <c r="A1411" s="6">
+      <c r="C1412" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1412" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4">
+      <c r="A1413" s="7">
         <v>46205</v>
       </c>
-      <c r="B1411" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1411" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1411" s="2"/>
-    </row>
-    <row r="1412" spans="1:4">
-      <c r="A1412" s="6">
+      <c r="B1413" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1413" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1413" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4">
+      <c r="A1414" s="7">
         <v>46205</v>
       </c>
-      <c r="B1412" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1412" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1412" s="2"/>
-    </row>
-    <row r="1413" spans="1:4">
-      <c r="A1413" s="6">
+      <c r="B1414" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1414" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1414" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4">
+      <c r="A1415" s="7">
         <v>46205</v>
       </c>
-      <c r="B1413" s="8" t="s">
+      <c r="B1415" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C1413" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1413" s="2"/>
-    </row>
-    <row r="1414" spans="1:4">
-      <c r="A1414" s="6">
+      <c r="C1415" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1415" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4">
+      <c r="A1416" s="7">
         <v>46205</v>
       </c>
-      <c r="B1414" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1414" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1414" s="2"/>
-    </row>
-    <row r="1415" spans="1:4">
-      <c r="A1415" s="6">
+      <c r="B1416" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1416" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1416" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4">
+      <c r="A1417" s="7">
         <v>46205</v>
       </c>
-      <c r="B1415" s="23" t="s">
+      <c r="B1417" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C1415" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1415" s="2"/>
-    </row>
-    <row r="1416" spans="1:4">
-      <c r="A1416" s="6">
+      <c r="C1417" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1417" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4">
+      <c r="A1418" s="7">
         <v>46205</v>
       </c>
-      <c r="B1416" s="24" t="s">
+      <c r="B1418" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C1416" s="5">
+      <c r="C1418" s="5">
         <v>9</v>
       </c>
-      <c r="D1416" s="2"/>
-    </row>
-    <row r="1417" spans="1:4">
-      <c r="A1417" s="6">
+      <c r="D1418" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4">
+      <c r="A1419" s="7">
         <v>46205</v>
       </c>
-      <c r="B1417" s="24" t="s">
+      <c r="B1419" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C1417" s="5">
+      <c r="C1419" s="5">
         <v>9</v>
       </c>
-      <c r="D1417" s="2"/>
+      <c r="D1419" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4">
+      <c r="A1420" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1420" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1420" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1420" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4">
+      <c r="A1421" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1421" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1421" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1421" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4">
+      <c r="A1422" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1422" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1422" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1422" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4">
+      <c r="A1423" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1423" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1423" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1423" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4">
+      <c r="A1424" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1424" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1424" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1424" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4">
+      <c r="A1425" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1425" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1425" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1425" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4">
+      <c r="A1426" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1426" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1426" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1426" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4">
+      <c r="A1427" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1427" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1427" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1427" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4">
+      <c r="A1428" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B1428" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1428" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1428" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4">
+      <c r="A1429" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B1429" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1429" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1429" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4">
+      <c r="A1430" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B1430" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1430" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1430" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4">
+      <c r="A1431" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B1431" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1431" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1431" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4">
+      <c r="A1432" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B1432" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1432" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1432" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4">
+      <c r="A1433" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1433" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1433" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1433" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4">
+      <c r="A1434" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1434" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1434" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1434" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4">
+      <c r="A1435" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1435" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1435" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1435" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4">
+      <c r="A1436" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1436" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1436" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1436" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4">
+      <c r="A1437" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1437" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1437" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1437" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4">
+      <c r="A1438" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1438" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1438" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1438" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4">
+      <c r="A1439" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1439" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1439" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1439" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4">
+      <c r="A1440" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1440" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1440" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1440" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4">
+      <c r="A1441" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1441" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1441" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1441" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4">
+      <c r="A1442" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1442" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1442" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1442" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4">
+      <c r="A1443" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1443" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1443" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1443" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4">
+      <c r="A1444" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B1444" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1444" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1444" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4">
+      <c r="A1445" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1445" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1445" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1445" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4">
+      <c r="A1446" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1446" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1446" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1446" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4">
+      <c r="A1447" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1447" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1447" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1447" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4">
+      <c r="A1448" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1448" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1448" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1448" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4">
+      <c r="A1449" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1449" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1449" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1449" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4">
+      <c r="A1450" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1450" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1450" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1450" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4">
+      <c r="A1451" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1451" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1451" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1451" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4">
+      <c r="A1452" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B1452" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1452" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1452" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4">
+      <c r="A1453" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1453" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1453" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1453" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4">
+      <c r="A1454" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1454" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1454" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1454" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4">
+      <c r="A1455" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1455" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1455" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1455" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4">
+      <c r="A1456" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1456" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1456" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1456" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4">
+      <c r="A1457" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1457" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1457" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1457" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4">
+      <c r="A1458" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1458" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1458" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1458" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4">
+      <c r="A1459" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1459" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1459" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1459" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4">
+      <c r="A1460" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1460" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1460" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1460" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4">
+      <c r="A1461" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B1461" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1461" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1461" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4">
+      <c r="A1462" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1462" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1462" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1462" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4">
+      <c r="A1463" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1463" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1463" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1463" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4">
+      <c r="A1464" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1464" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1464" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1464" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4">
+      <c r="A1465" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1465" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1465" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1465" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4">
+      <c r="A1466" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1466" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1466" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1466" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4">
+      <c r="A1467" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1467" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1467" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1467" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4">
+      <c r="A1468" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1468" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1468" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1468" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4">
+      <c r="A1469" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1469" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1469" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1469" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4">
+      <c r="A1470" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B1470" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1470" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1470" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4">
+      <c r="A1471" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1471" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1471" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1471" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4">
+      <c r="A1472" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1472" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1472" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1472" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4">
+      <c r="A1473" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1473" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1473" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1473" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4">
+      <c r="A1474" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1474" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1474" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1474" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4">
+      <c r="A1475" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1475" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1475" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1475" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4">
+      <c r="A1476" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1476" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1476" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1476" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4">
+      <c r="A1477" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1477" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1477" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1477" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4">
+      <c r="A1478" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1478" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1478" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1478" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4">
+      <c r="A1479" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B1479" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1479" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1479" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:4">
+      <c r="A1480" s="6">
+        <v>46214</v>
+      </c>
+      <c r="B1480" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1480" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1480" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:4">
+      <c r="A1481" s="6">
+        <v>46214</v>
+      </c>
+      <c r="B1481" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1481" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1481" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:4">
+      <c r="A1482" s="6">
+        <v>46214</v>
+      </c>
+      <c r="B1482" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1482" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1482" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:4">
+      <c r="A1483" s="6">
+        <v>46214</v>
+      </c>
+      <c r="B1483" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1483" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1483" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:4">
+      <c r="A1484" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1484" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1484" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1484" s="2"/>
+    </row>
+    <row r="1485" spans="1:4">
+      <c r="A1485" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1485" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1485" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1485" s="2"/>
+    </row>
+    <row r="1486" spans="1:4">
+      <c r="A1486" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1486" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1486" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1486" s="2"/>
+    </row>
+    <row r="1487" spans="1:4">
+      <c r="A1487" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1487" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1487" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1487" s="2"/>
+    </row>
+    <row r="1488" spans="1:4">
+      <c r="A1488" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1488" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1488" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1488" s="2"/>
+    </row>
+    <row r="1489" spans="1:4">
+      <c r="A1489" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1489" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1489" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1489" s="2"/>
+    </row>
+    <row r="1490" spans="1:4">
+      <c r="A1490" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1490" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1490" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1490" s="2"/>
+    </row>
+    <row r="1491" spans="1:4">
+      <c r="A1491" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1491" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1491" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1491" s="2"/>
+    </row>
+    <row r="1492" spans="1:4">
+      <c r="A1492" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B1492" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1492" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1492" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -283,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -320,6 +320,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -615,16 +616,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1492"/>
+  <dimension ref="A1:H1495"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.28515625" customWidth="1"/>
@@ -21983,7 +21983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1473" spans="1:4">
+    <row r="1473" spans="1:8">
       <c r="A1473" s="7">
         <v>46213</v>
       </c>
@@ -21997,7 +21997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1474" spans="1:4">
+    <row r="1474" spans="1:8">
       <c r="A1474" s="7">
         <v>46213</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1475" spans="1:4">
+    <row r="1475" spans="1:8">
       <c r="A1475" s="7">
         <v>46213</v>
       </c>
@@ -22025,7 +22025,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1476" spans="1:4">
+    <row r="1476" spans="1:8">
       <c r="A1476" s="7">
         <v>46213</v>
       </c>
@@ -22039,7 +22039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1477" spans="1:4">
+    <row r="1477" spans="1:8">
       <c r="A1477" s="7">
         <v>46213</v>
       </c>
@@ -22053,7 +22053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1478" spans="1:4">
+    <row r="1478" spans="1:8">
       <c r="A1478" s="7">
         <v>46213</v>
       </c>
@@ -22067,7 +22067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1479" spans="1:4">
+    <row r="1479" spans="1:8">
       <c r="A1479" s="7">
         <v>46213</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1480" spans="1:4">
+    <row r="1480" spans="1:8">
       <c r="A1480" s="6">
         <v>46214</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1481" spans="1:4">
+    <row r="1481" spans="1:8">
       <c r="A1481" s="6">
         <v>46214</v>
       </c>
@@ -22109,7 +22109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1482" spans="1:4">
+    <row r="1482" spans="1:8">
       <c r="A1482" s="6">
         <v>46214</v>
       </c>
@@ -22123,7 +22123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1483" spans="1:4">
+    <row r="1483" spans="1:8">
       <c r="A1483" s="6">
         <v>46214</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1484" spans="1:4">
+    <row r="1484" spans="1:8">
       <c r="A1484" s="6">
         <v>46216</v>
       </c>
@@ -22147,9 +22147,11 @@
       <c r="C1484" s="5">
         <v>6</v>
       </c>
-      <c r="D1484" s="2"/>
-    </row>
-    <row r="1485" spans="1:4">
+      <c r="D1484" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:8">
       <c r="A1485" s="6">
         <v>46216</v>
       </c>
@@ -22159,9 +22161,13 @@
       <c r="C1485" s="5">
         <v>6</v>
       </c>
-      <c r="D1485" s="2"/>
-    </row>
-    <row r="1486" spans="1:4">
+      <c r="D1485" s="2">
+        <v>8</v>
+      </c>
+      <c r="G1485" s="1"/>
+      <c r="H1485" s="28"/>
+    </row>
+    <row r="1486" spans="1:8">
       <c r="A1486" s="6">
         <v>46216</v>
       </c>
@@ -22171,9 +22177,13 @@
       <c r="C1486" s="5">
         <v>2</v>
       </c>
-      <c r="D1486" s="2"/>
-    </row>
-    <row r="1487" spans="1:4">
+      <c r="D1486" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1486" s="1"/>
+      <c r="H1486" s="28"/>
+    </row>
+    <row r="1487" spans="1:8">
       <c r="A1487" s="6">
         <v>46216</v>
       </c>
@@ -22183,9 +22193,13 @@
       <c r="C1487" s="5">
         <v>2</v>
       </c>
-      <c r="D1487" s="2"/>
-    </row>
-    <row r="1488" spans="1:4">
+      <c r="D1487" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1487" s="1"/>
+      <c r="H1487" s="28"/>
+    </row>
+    <row r="1488" spans="1:8">
       <c r="A1488" s="6">
         <v>46216</v>
       </c>
@@ -22195,9 +22209,13 @@
       <c r="C1488" s="5">
         <v>4</v>
       </c>
-      <c r="D1488" s="2"/>
-    </row>
-    <row r="1489" spans="1:4">
+      <c r="D1488" s="2">
+        <v>9</v>
+      </c>
+      <c r="G1488" s="1"/>
+      <c r="H1488" s="28"/>
+    </row>
+    <row r="1489" spans="1:8">
       <c r="A1489" s="6">
         <v>46216</v>
       </c>
@@ -22207,9 +22225,13 @@
       <c r="C1489" s="5">
         <v>4</v>
       </c>
-      <c r="D1489" s="2"/>
-    </row>
-    <row r="1490" spans="1:4">
+      <c r="D1489" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1489" s="1"/>
+      <c r="H1489" s="28"/>
+    </row>
+    <row r="1490" spans="1:8">
       <c r="A1490" s="6">
         <v>46216</v>
       </c>
@@ -22219,9 +22241,13 @@
       <c r="C1490" s="5">
         <v>4</v>
       </c>
-      <c r="D1490" s="2"/>
-    </row>
-    <row r="1491" spans="1:4">
+      <c r="D1490" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1490" s="1"/>
+      <c r="H1490" s="28"/>
+    </row>
+    <row r="1491" spans="1:8">
       <c r="A1491" s="6">
         <v>46216</v>
       </c>
@@ -22231,9 +22257,11 @@
       <c r="C1491" s="5">
         <v>2</v>
       </c>
-      <c r="D1491" s="2"/>
-    </row>
-    <row r="1492" spans="1:4">
+      <c r="D1491" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:8">
       <c r="A1492" s="6">
         <v>46216</v>
       </c>
@@ -22243,7 +22271,45 @@
       <c r="C1492" s="5">
         <v>2</v>
       </c>
-      <c r="D1492" s="2"/>
+      <c r="D1492" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:8">
+      <c r="A1493" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1493" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1493" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1493" s="2"/>
+    </row>
+    <row r="1494" spans="1:8">
+      <c r="A1494" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1494" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1494" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1494" s="2"/>
+    </row>
+    <row r="1495" spans="1:8">
+      <c r="A1495" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1495" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1495" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1495" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,14 +616,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1495"/>
+  <dimension ref="A1:H1509"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -22285,7 +22286,9 @@
       <c r="C1493" s="5">
         <v>2</v>
       </c>
-      <c r="D1493" s="2"/>
+      <c r="D1493" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1494" spans="1:8">
       <c r="A1494" s="6">
@@ -22297,7 +22300,9 @@
       <c r="C1494" s="5">
         <v>8</v>
       </c>
-      <c r="D1494" s="2"/>
+      <c r="D1494" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1495" spans="1:8">
       <c r="A1495" s="6">
@@ -22309,7 +22314,183 @@
       <c r="C1495" s="5">
         <v>8</v>
       </c>
-      <c r="D1495" s="2"/>
+      <c r="D1495" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:8">
+      <c r="A1496" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1496" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1496" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1496" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:8">
+      <c r="A1497" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1497" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1497" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1497" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8">
+      <c r="A1498" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1498" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1498" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1498" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8">
+      <c r="A1499" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B1499" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1499" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1499" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8">
+      <c r="A1500" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1500" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1500" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1500" s="2"/>
+    </row>
+    <row r="1501" spans="1:8">
+      <c r="A1501" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1501" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1501" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1501" s="2"/>
+      <c r="F1501" s="1"/>
+      <c r="G1501" s="28"/>
+    </row>
+    <row r="1502" spans="1:8">
+      <c r="A1502" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1502" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1502" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1502" s="2"/>
+      <c r="F1502" s="1"/>
+      <c r="G1502" s="28"/>
+    </row>
+    <row r="1503" spans="1:8">
+      <c r="A1503" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1503" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1503" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1503" s="2"/>
+      <c r="F1503" s="1"/>
+      <c r="G1503" s="28"/>
+    </row>
+    <row r="1504" spans="1:8">
+      <c r="A1504" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1504" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1504" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1504" s="2"/>
+      <c r="F1504" s="1"/>
+      <c r="G1504" s="28"/>
+    </row>
+    <row r="1505" spans="1:7">
+      <c r="A1505" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1505" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1505" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1505" s="2"/>
+      <c r="F1505" s="1"/>
+      <c r="G1505" s="28"/>
+    </row>
+    <row r="1506" spans="1:7">
+      <c r="A1506" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1506" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1506" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1506" s="2"/>
+      <c r="F1506" s="1"/>
+      <c r="G1506" s="28"/>
+    </row>
+    <row r="1507" spans="1:7">
+      <c r="A1507" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B1507" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1507" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1507" s="2"/>
+      <c r="F1507" s="1"/>
+      <c r="G1507" s="28"/>
+    </row>
+    <row r="1508" spans="1:7">
+      <c r="F1508" s="1"/>
+      <c r="G1508" s="28"/>
+    </row>
+    <row r="1509" spans="1:7">
+      <c r="F1509" s="1"/>
+      <c r="G1509" s="28"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1509"/>
+  <dimension ref="A1:H1515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22301,7 +22301,7 @@
         <v>8</v>
       </c>
       <c r="D1494" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1495" spans="1:8">
@@ -22384,7 +22384,9 @@
       <c r="C1500" s="5">
         <v>5</v>
       </c>
-      <c r="D1500" s="2"/>
+      <c r="D1500" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="1501" spans="1:8">
       <c r="A1501" s="6">
@@ -22396,7 +22398,9 @@
       <c r="C1501" s="5">
         <v>1</v>
       </c>
-      <c r="D1501" s="2"/>
+      <c r="D1501" s="2">
+        <v>0</v>
+      </c>
       <c r="F1501" s="1"/>
       <c r="G1501" s="28"/>
     </row>
@@ -22410,7 +22414,9 @@
       <c r="C1502" s="5">
         <v>1</v>
       </c>
-      <c r="D1502" s="2"/>
+      <c r="D1502" s="2">
+        <v>0</v>
+      </c>
       <c r="F1502" s="1"/>
       <c r="G1502" s="28"/>
     </row>
@@ -22424,7 +22430,9 @@
       <c r="C1503" s="5">
         <v>8</v>
       </c>
-      <c r="D1503" s="2"/>
+      <c r="D1503" s="2">
+        <v>9</v>
+      </c>
       <c r="F1503" s="1"/>
       <c r="G1503" s="28"/>
     </row>
@@ -22438,7 +22446,9 @@
       <c r="C1504" s="5">
         <v>3</v>
       </c>
-      <c r="D1504" s="2"/>
+      <c r="D1504" s="2">
+        <v>1</v>
+      </c>
       <c r="F1504" s="1"/>
       <c r="G1504" s="28"/>
     </row>
@@ -22452,7 +22462,9 @@
       <c r="C1505" s="5">
         <v>3</v>
       </c>
-      <c r="D1505" s="2"/>
+      <c r="D1505" s="2">
+        <v>1</v>
+      </c>
       <c r="F1505" s="1"/>
       <c r="G1505" s="28"/>
     </row>
@@ -22466,7 +22478,9 @@
       <c r="C1506" s="5">
         <v>3</v>
       </c>
-      <c r="D1506" s="2"/>
+      <c r="D1506" s="2">
+        <v>1</v>
+      </c>
       <c r="F1506" s="1"/>
       <c r="G1506" s="28"/>
     </row>
@@ -22480,17 +22494,107 @@
       <c r="C1507" s="5">
         <v>3</v>
       </c>
-      <c r="D1507" s="2"/>
+      <c r="D1507" s="2">
+        <v>1</v>
+      </c>
       <c r="F1507" s="1"/>
       <c r="G1507" s="28"/>
     </row>
     <row r="1508" spans="1:7">
-      <c r="F1508" s="1"/>
-      <c r="G1508" s="28"/>
+      <c r="A1508" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1508" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1508" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1508" s="2"/>
     </row>
     <row r="1509" spans="1:7">
-      <c r="F1509" s="1"/>
-      <c r="G1509" s="28"/>
+      <c r="A1509" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1509" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1509" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1509" s="2"/>
+    </row>
+    <row r="1510" spans="1:7">
+      <c r="A1510" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1510" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1510" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1510" s="2"/>
+    </row>
+    <row r="1511" spans="1:7">
+      <c r="A1511" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1511" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1511" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1511" s="2"/>
+    </row>
+    <row r="1512" spans="1:7">
+      <c r="A1512" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1512" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1512" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1512" s="2"/>
+    </row>
+    <row r="1513" spans="1:7">
+      <c r="A1513" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1513" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1513" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1513" s="2"/>
+    </row>
+    <row r="1514" spans="1:7">
+      <c r="A1514" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1514" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1514" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1514" s="2"/>
+    </row>
+    <row r="1515" spans="1:7">
+      <c r="A1515" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B1515" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1515" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1515" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1515"/>
+  <dimension ref="A1:H1523"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22510,7 +22510,9 @@
       <c r="C1508" s="5">
         <v>8</v>
       </c>
-      <c r="D1508" s="2"/>
+      <c r="D1508" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1509" spans="1:7">
       <c r="A1509" s="6">
@@ -22522,7 +22524,11 @@
       <c r="C1509" s="5">
         <v>5</v>
       </c>
-      <c r="D1509" s="2"/>
+      <c r="D1509" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1509" s="1"/>
+      <c r="G1509" s="28"/>
     </row>
     <row r="1510" spans="1:7">
       <c r="A1510" s="6">
@@ -22534,7 +22540,11 @@
       <c r="C1510" s="5">
         <v>2</v>
       </c>
-      <c r="D1510" s="2"/>
+      <c r="D1510" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1510" s="1"/>
+      <c r="G1510" s="28"/>
     </row>
     <row r="1511" spans="1:7">
       <c r="A1511" s="6">
@@ -22546,7 +22556,11 @@
       <c r="C1511" s="5">
         <v>2</v>
       </c>
-      <c r="D1511" s="2"/>
+      <c r="D1511" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1511" s="1"/>
+      <c r="G1511" s="28"/>
     </row>
     <row r="1512" spans="1:7">
       <c r="A1512" s="6">
@@ -22558,7 +22572,11 @@
       <c r="C1512" s="5">
         <v>1</v>
       </c>
-      <c r="D1512" s="2"/>
+      <c r="D1512" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1512" s="1"/>
+      <c r="G1512" s="28"/>
     </row>
     <row r="1513" spans="1:7">
       <c r="A1513" s="6">
@@ -22570,7 +22588,11 @@
       <c r="C1513" s="5">
         <v>1</v>
       </c>
-      <c r="D1513" s="2"/>
+      <c r="D1513" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1513" s="1"/>
+      <c r="G1513" s="28"/>
     </row>
     <row r="1514" spans="1:7">
       <c r="A1514" s="6">
@@ -22582,7 +22604,11 @@
       <c r="C1514" s="2">
         <v>5</v>
       </c>
-      <c r="D1514" s="2"/>
+      <c r="D1514" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1514" s="1"/>
+      <c r="G1514" s="28"/>
     </row>
     <row r="1515" spans="1:7">
       <c r="A1515" s="6">
@@ -22594,7 +22620,105 @@
       <c r="C1515" s="2">
         <v>5</v>
       </c>
-      <c r="D1515" s="2"/>
+      <c r="D1515" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:7">
+      <c r="A1516" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1516" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1516" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1516" s="5"/>
+    </row>
+    <row r="1517" spans="1:7">
+      <c r="A1517" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1517" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1517" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1517" s="2"/>
+    </row>
+    <row r="1518" spans="1:7">
+      <c r="A1518" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1518" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1518" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1518" s="2"/>
+    </row>
+    <row r="1519" spans="1:7">
+      <c r="A1519" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1519" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1519" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1519" s="2"/>
+    </row>
+    <row r="1520" spans="1:7">
+      <c r="A1520" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1520" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1520" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1520" s="2"/>
+    </row>
+    <row r="1521" spans="1:4">
+      <c r="A1521" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1521" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1521" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1521" s="2"/>
+    </row>
+    <row r="1522" spans="1:4">
+      <c r="A1522" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1522" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1522" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1522" s="2"/>
+    </row>
+    <row r="1523" spans="1:4">
+      <c r="A1523" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B1523" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1523" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1523" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>AMENTA SONNY</t>
+  </si>
+  <si>
+    <t>SPAMPINATO MICHELE</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1523"/>
+  <dimension ref="A1:H1547"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22634,7 +22637,9 @@
       <c r="C1516" s="5">
         <v>1</v>
       </c>
-      <c r="D1516" s="5"/>
+      <c r="D1516" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="1517" spans="1:7">
       <c r="A1517" s="6">
@@ -22646,7 +22651,11 @@
       <c r="C1517" s="5">
         <v>5</v>
       </c>
-      <c r="D1517" s="2"/>
+      <c r="D1517" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1517" s="1"/>
+      <c r="G1517" s="28"/>
     </row>
     <row r="1518" spans="1:7">
       <c r="A1518" s="6">
@@ -22658,7 +22667,11 @@
       <c r="C1518" s="5">
         <v>6</v>
       </c>
-      <c r="D1518" s="2"/>
+      <c r="D1518" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1518" s="1"/>
+      <c r="G1518" s="28"/>
     </row>
     <row r="1519" spans="1:7">
       <c r="A1519" s="6">
@@ -22670,7 +22683,11 @@
       <c r="C1519" s="5">
         <v>6</v>
       </c>
-      <c r="D1519" s="2"/>
+      <c r="D1519" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1519" s="1"/>
+      <c r="G1519" s="28"/>
     </row>
     <row r="1520" spans="1:7">
       <c r="A1520" s="6">
@@ -22682,9 +22699,13 @@
       <c r="C1520" s="5">
         <v>6</v>
       </c>
-      <c r="D1520" s="2"/>
-    </row>
-    <row r="1521" spans="1:4">
+      <c r="D1520" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1520" s="1"/>
+      <c r="G1520" s="28"/>
+    </row>
+    <row r="1521" spans="1:7">
       <c r="A1521" s="6">
         <v>46220</v>
       </c>
@@ -22694,9 +22715,13 @@
       <c r="C1521" s="2">
         <v>6</v>
       </c>
-      <c r="D1521" s="2"/>
-    </row>
-    <row r="1522" spans="1:4">
+      <c r="D1521" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1521" s="1"/>
+      <c r="G1521" s="28"/>
+    </row>
+    <row r="1522" spans="1:7">
       <c r="A1522" s="6">
         <v>46220</v>
       </c>
@@ -22706,9 +22731,13 @@
       <c r="C1522" s="2">
         <v>2</v>
       </c>
-      <c r="D1522" s="2"/>
-    </row>
-    <row r="1523" spans="1:4">
+      <c r="D1522" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1522" s="1"/>
+      <c r="G1522" s="28"/>
+    </row>
+    <row r="1523" spans="1:7">
       <c r="A1523" s="6">
         <v>46220</v>
       </c>
@@ -22718,7 +22747,337 @@
       <c r="C1523" s="2">
         <v>2</v>
       </c>
-      <c r="D1523" s="2"/>
+      <c r="D1523" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:7">
+      <c r="A1524" s="6">
+        <v>46221</v>
+      </c>
+      <c r="B1524" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1524" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1524" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:7">
+      <c r="A1525" s="6">
+        <v>46221</v>
+      </c>
+      <c r="B1525" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1525" s="5">
+        <v>11</v>
+      </c>
+      <c r="D1525" s="5">
+        <v>6</v>
+      </c>
+      <c r="F1525" s="1"/>
+      <c r="G1525" s="28"/>
+    </row>
+    <row r="1526" spans="1:7">
+      <c r="A1526" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1526" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1526" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1526" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:7">
+      <c r="A1527" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1527" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1527" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1527" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1527" s="1"/>
+      <c r="G1527" s="28"/>
+    </row>
+    <row r="1528" spans="1:7">
+      <c r="A1528" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1528" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1528" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1528" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1528" s="1"/>
+      <c r="G1528" s="28"/>
+    </row>
+    <row r="1529" spans="1:7">
+      <c r="A1529" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1529" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1529" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1529" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1529" s="1"/>
+      <c r="G1529" s="28"/>
+    </row>
+    <row r="1530" spans="1:7">
+      <c r="A1530" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1530" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1530" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1530" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1530" s="1"/>
+      <c r="G1530" s="28"/>
+    </row>
+    <row r="1531" spans="1:7">
+      <c r="A1531" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1531" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1531" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1531" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1531" s="1"/>
+      <c r="G1531" s="28"/>
+    </row>
+    <row r="1532" spans="1:7">
+      <c r="A1532" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1532" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1532" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1532" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1532" s="1"/>
+      <c r="G1532" s="28"/>
+    </row>
+    <row r="1533" spans="1:7">
+      <c r="A1533" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1533" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1533" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1533" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:7">
+      <c r="A1534" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1534" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1534" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1534" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:7">
+      <c r="A1535" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1535" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1535" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1535" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:7">
+      <c r="A1536" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B1536" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1536" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1536" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4">
+      <c r="A1537" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1537" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1537" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1537" s="2"/>
+    </row>
+    <row r="1538" spans="1:4">
+      <c r="A1538" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1538" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1538" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1538" s="2"/>
+    </row>
+    <row r="1539" spans="1:4">
+      <c r="A1539" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1539" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1539" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1539" s="2"/>
+    </row>
+    <row r="1540" spans="1:4">
+      <c r="A1540" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1540" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1540" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1540" s="2"/>
+    </row>
+    <row r="1541" spans="1:4">
+      <c r="A1541" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1541" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1541" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1541" s="2"/>
+    </row>
+    <row r="1542" spans="1:4">
+      <c r="A1542" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1542" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1542" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1542" s="2"/>
+    </row>
+    <row r="1543" spans="1:4">
+      <c r="A1543" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1543" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1543" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1543" s="2"/>
+    </row>
+    <row r="1544" spans="1:4">
+      <c r="A1544" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1544" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1544" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1544" s="2"/>
+    </row>
+    <row r="1545" spans="1:4">
+      <c r="A1545" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1545" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1545" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1545" s="2"/>
+    </row>
+    <row r="1546" spans="1:4">
+      <c r="A1546" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1546" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1546" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1546" s="2"/>
+    </row>
+    <row r="1547" spans="1:4">
+      <c r="A1547" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B1547" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1547" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1547" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1547"/>
+  <dimension ref="A1:H1557"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -22947,7 +22947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1537" spans="1:4">
+    <row r="1537" spans="1:7">
       <c r="A1537" s="6">
         <v>46224</v>
       </c>
@@ -22957,9 +22957,11 @@
       <c r="C1537" s="5">
         <v>6</v>
       </c>
-      <c r="D1537" s="2"/>
-    </row>
-    <row r="1538" spans="1:4">
+      <c r="D1537" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:7">
       <c r="A1538" s="6">
         <v>46224</v>
       </c>
@@ -22969,9 +22971,13 @@
       <c r="C1538" s="5">
         <v>2</v>
       </c>
-      <c r="D1538" s="2"/>
-    </row>
-    <row r="1539" spans="1:4">
+      <c r="D1538" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1538" s="1"/>
+      <c r="G1538" s="28"/>
+    </row>
+    <row r="1539" spans="1:7">
       <c r="A1539" s="6">
         <v>46224</v>
       </c>
@@ -22981,9 +22987,13 @@
       <c r="C1539" s="5">
         <v>2</v>
       </c>
-      <c r="D1539" s="2"/>
-    </row>
-    <row r="1540" spans="1:4">
+      <c r="D1539" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1539" s="1"/>
+      <c r="G1539" s="28"/>
+    </row>
+    <row r="1540" spans="1:7">
       <c r="A1540" s="6">
         <v>46224</v>
       </c>
@@ -22993,9 +23003,13 @@
       <c r="C1540" s="5">
         <v>5</v>
       </c>
-      <c r="D1540" s="2"/>
-    </row>
-    <row r="1541" spans="1:4">
+      <c r="D1540" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1540" s="1"/>
+      <c r="G1540" s="28"/>
+    </row>
+    <row r="1541" spans="1:7">
       <c r="A1541" s="6">
         <v>46224</v>
       </c>
@@ -23005,9 +23019,13 @@
       <c r="C1541" s="5">
         <v>5</v>
       </c>
-      <c r="D1541" s="2"/>
-    </row>
-    <row r="1542" spans="1:4">
+      <c r="D1541" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1541" s="1"/>
+      <c r="G1541" s="28"/>
+    </row>
+    <row r="1542" spans="1:7">
       <c r="A1542" s="6">
         <v>46224</v>
       </c>
@@ -23017,9 +23035,13 @@
       <c r="C1542" s="5">
         <v>2</v>
       </c>
-      <c r="D1542" s="2"/>
-    </row>
-    <row r="1543" spans="1:4">
+      <c r="D1542" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1542" s="1"/>
+      <c r="G1542" s="28"/>
+    </row>
+    <row r="1543" spans="1:7">
       <c r="A1543" s="6">
         <v>46224</v>
       </c>
@@ -23029,9 +23051,13 @@
       <c r="C1543" s="2">
         <v>2</v>
       </c>
-      <c r="D1543" s="2"/>
-    </row>
-    <row r="1544" spans="1:4">
+      <c r="D1543" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1543" s="1"/>
+      <c r="G1543" s="28"/>
+    </row>
+    <row r="1544" spans="1:7">
       <c r="A1544" s="6">
         <v>46224</v>
       </c>
@@ -23041,9 +23067,13 @@
       <c r="C1544" s="2">
         <v>3</v>
       </c>
-      <c r="D1544" s="2"/>
-    </row>
-    <row r="1545" spans="1:4">
+      <c r="D1544" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1544" s="1"/>
+      <c r="G1544" s="28"/>
+    </row>
+    <row r="1545" spans="1:7">
       <c r="A1545" s="6">
         <v>46224</v>
       </c>
@@ -23053,9 +23083,13 @@
       <c r="C1545" s="2">
         <v>3</v>
       </c>
-      <c r="D1545" s="2"/>
-    </row>
-    <row r="1546" spans="1:4">
+      <c r="D1545" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1545" s="1"/>
+      <c r="G1545" s="28"/>
+    </row>
+    <row r="1546" spans="1:7">
       <c r="A1546" s="6">
         <v>46224</v>
       </c>
@@ -23065,9 +23099,11 @@
       <c r="C1546" s="2">
         <v>4</v>
       </c>
-      <c r="D1546" s="2"/>
-    </row>
-    <row r="1547" spans="1:4">
+      <c r="D1546" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:7">
       <c r="A1547" s="6">
         <v>46224</v>
       </c>
@@ -23077,7 +23113,129 @@
       <c r="C1547" s="2">
         <v>4</v>
       </c>
-      <c r="D1547" s="2"/>
+      <c r="D1547" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:7">
+      <c r="A1548" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1548" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1548" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1548" s="2"/>
+    </row>
+    <row r="1549" spans="1:7">
+      <c r="A1549" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1549" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1549" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1549" s="2"/>
+    </row>
+    <row r="1550" spans="1:7">
+      <c r="A1550" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1550" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1550" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1550" s="2"/>
+    </row>
+    <row r="1551" spans="1:7">
+      <c r="A1551" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1551" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1551" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1551" s="2"/>
+    </row>
+    <row r="1552" spans="1:7">
+      <c r="A1552" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1552" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1552" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1552" s="2"/>
+    </row>
+    <row r="1553" spans="1:4">
+      <c r="A1553" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1553" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1553" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1553" s="2"/>
+    </row>
+    <row r="1554" spans="1:4">
+      <c r="A1554" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1554" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1554" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1554" s="2"/>
+    </row>
+    <row r="1555" spans="1:4">
+      <c r="A1555" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1555" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1555" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1555" s="2"/>
+    </row>
+    <row r="1556" spans="1:4">
+      <c r="A1556" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1556" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1556" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1556" s="2"/>
+    </row>
+    <row r="1557" spans="1:4">
+      <c r="A1557" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B1557" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1557" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1557" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1557"/>
+  <dimension ref="A1:H1562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23127,7 +23127,9 @@
       <c r="C1548" s="5">
         <v>10</v>
       </c>
-      <c r="D1548" s="2"/>
+      <c r="D1548" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="1549" spans="1:7">
       <c r="A1549" s="6">
@@ -23139,7 +23141,11 @@
       <c r="C1549" s="5">
         <v>2</v>
       </c>
-      <c r="D1549" s="2"/>
+      <c r="D1549" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1549" s="1"/>
+      <c r="G1549" s="28"/>
     </row>
     <row r="1550" spans="1:7">
       <c r="A1550" s="6">
@@ -23151,7 +23157,11 @@
       <c r="C1550" s="5">
         <v>6</v>
       </c>
-      <c r="D1550" s="2"/>
+      <c r="D1550" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1550" s="1"/>
+      <c r="G1550" s="28"/>
     </row>
     <row r="1551" spans="1:7">
       <c r="A1551" s="6">
@@ -23161,9 +23171,13 @@
         <v>27</v>
       </c>
       <c r="C1551" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1551" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D1551" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1551" s="1"/>
+      <c r="G1551" s="28"/>
     </row>
     <row r="1552" spans="1:7">
       <c r="A1552" s="6">
@@ -23175,9 +23189,13 @@
       <c r="C1552" s="5">
         <v>1</v>
       </c>
-      <c r="D1552" s="2"/>
-    </row>
-    <row r="1553" spans="1:4">
+      <c r="D1552" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1552" s="1"/>
+      <c r="G1552" s="28"/>
+    </row>
+    <row r="1553" spans="1:7">
       <c r="A1553" s="6">
         <v>46225</v>
       </c>
@@ -23187,9 +23205,13 @@
       <c r="C1553" s="5">
         <v>1</v>
       </c>
-      <c r="D1553" s="2"/>
-    </row>
-    <row r="1554" spans="1:4">
+      <c r="D1553" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1553" s="1"/>
+      <c r="G1553" s="28"/>
+    </row>
+    <row r="1554" spans="1:7">
       <c r="A1554" s="6">
         <v>46225</v>
       </c>
@@ -23199,9 +23221,13 @@
       <c r="C1554" s="5">
         <v>10</v>
       </c>
-      <c r="D1554" s="2"/>
-    </row>
-    <row r="1555" spans="1:4">
+      <c r="D1554" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1554" s="1"/>
+      <c r="G1554" s="28"/>
+    </row>
+    <row r="1555" spans="1:7">
       <c r="A1555" s="6">
         <v>46225</v>
       </c>
@@ -23211,9 +23237,13 @@
       <c r="C1555" s="5">
         <v>1</v>
       </c>
-      <c r="D1555" s="2"/>
-    </row>
-    <row r="1556" spans="1:4">
+      <c r="D1555" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1555" s="1"/>
+      <c r="G1555" s="28"/>
+    </row>
+    <row r="1556" spans="1:7">
       <c r="A1556" s="6">
         <v>46225</v>
       </c>
@@ -23223,9 +23253,11 @@
       <c r="C1556" s="5">
         <v>1</v>
       </c>
-      <c r="D1556" s="2"/>
-    </row>
-    <row r="1557" spans="1:4">
+      <c r="D1556" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:7">
       <c r="A1557" s="6">
         <v>46225</v>
       </c>
@@ -23235,7 +23267,69 @@
       <c r="C1557" s="5">
         <v>8</v>
       </c>
-      <c r="D1557" s="2"/>
+      <c r="D1557" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:7">
+      <c r="A1558" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B1558" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1558" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1558" s="2"/>
+    </row>
+    <row r="1559" spans="1:7">
+      <c r="A1559" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B1559" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1559" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1559" s="2"/>
+    </row>
+    <row r="1560" spans="1:7">
+      <c r="A1560" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B1560" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1560" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1560" s="2"/>
+    </row>
+    <row r="1561" spans="1:7">
+      <c r="A1561" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B1561" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1561" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1561" s="2"/>
+    </row>
+    <row r="1562" spans="1:7">
+      <c r="A1562" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B1562" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1562" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1562" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1562"/>
+  <dimension ref="A1:H1567"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23281,7 +23281,9 @@
       <c r="C1558" s="5">
         <v>8</v>
       </c>
-      <c r="D1558" s="2"/>
+      <c r="D1558" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="1559" spans="1:7">
       <c r="A1559" s="6">
@@ -23293,7 +23295,11 @@
       <c r="C1559" s="5">
         <v>8</v>
       </c>
-      <c r="D1559" s="2"/>
+      <c r="D1559" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1559" s="1"/>
+      <c r="G1559" s="28"/>
     </row>
     <row r="1560" spans="1:7">
       <c r="A1560" s="6">
@@ -23305,7 +23311,11 @@
       <c r="C1560" s="5">
         <v>5</v>
       </c>
-      <c r="D1560" s="2"/>
+      <c r="D1560" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1560" s="1"/>
+      <c r="G1560" s="28"/>
     </row>
     <row r="1561" spans="1:7">
       <c r="A1561" s="6">
@@ -23317,7 +23327,11 @@
       <c r="C1561" s="5">
         <v>9</v>
       </c>
-      <c r="D1561" s="2"/>
+      <c r="D1561" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1561" s="1"/>
+      <c r="G1561" s="28"/>
     </row>
     <row r="1562" spans="1:7">
       <c r="A1562" s="6">
@@ -23329,7 +23343,77 @@
       <c r="C1562" s="5">
         <v>6</v>
       </c>
-      <c r="D1562" s="2"/>
+      <c r="D1562" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1562" s="1"/>
+      <c r="G1562" s="28"/>
+    </row>
+    <row r="1563" spans="1:7">
+      <c r="A1563" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B1563" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1563" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1563" s="2"/>
+      <c r="F1563" s="1"/>
+      <c r="G1563" s="28"/>
+    </row>
+    <row r="1564" spans="1:7">
+      <c r="A1564" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B1564" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1564" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1564" s="2"/>
+      <c r="F1564" s="1"/>
+      <c r="G1564" s="28"/>
+    </row>
+    <row r="1565" spans="1:7">
+      <c r="A1565" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B1565" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1565" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1565" s="2"/>
+      <c r="F1565" s="1"/>
+      <c r="G1565" s="28"/>
+    </row>
+    <row r="1566" spans="1:7">
+      <c r="A1566" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B1566" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1566" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1566" s="2"/>
+    </row>
+    <row r="1567" spans="1:7">
+      <c r="A1567" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B1567" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1567" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1567" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1567"/>
+  <dimension ref="A1:H1590"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23195,7 +23195,7 @@
       <c r="F1552" s="1"/>
       <c r="G1552" s="28"/>
     </row>
-    <row r="1553" spans="1:7">
+    <row r="1553" spans="1:8">
       <c r="A1553" s="6">
         <v>46225</v>
       </c>
@@ -23211,7 +23211,7 @@
       <c r="F1553" s="1"/>
       <c r="G1553" s="28"/>
     </row>
-    <row r="1554" spans="1:7">
+    <row r="1554" spans="1:8">
       <c r="A1554" s="6">
         <v>46225</v>
       </c>
@@ -23227,7 +23227,7 @@
       <c r="F1554" s="1"/>
       <c r="G1554" s="28"/>
     </row>
-    <row r="1555" spans="1:7">
+    <row r="1555" spans="1:8">
       <c r="A1555" s="6">
         <v>46225</v>
       </c>
@@ -23243,7 +23243,7 @@
       <c r="F1555" s="1"/>
       <c r="G1555" s="28"/>
     </row>
-    <row r="1556" spans="1:7">
+    <row r="1556" spans="1:8">
       <c r="A1556" s="6">
         <v>46225</v>
       </c>
@@ -23257,7 +23257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1557" spans="1:7">
+    <row r="1557" spans="1:8">
       <c r="A1557" s="6">
         <v>46225</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1558" spans="1:7">
+    <row r="1558" spans="1:8">
       <c r="A1558" s="6">
         <v>46226</v>
       </c>
@@ -23285,7 +23285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1559" spans="1:7">
+    <row r="1559" spans="1:8">
       <c r="A1559" s="6">
         <v>46226</v>
       </c>
@@ -23301,7 +23301,7 @@
       <c r="F1559" s="1"/>
       <c r="G1559" s="28"/>
     </row>
-    <row r="1560" spans="1:7">
+    <row r="1560" spans="1:8">
       <c r="A1560" s="6">
         <v>46226</v>
       </c>
@@ -23317,7 +23317,7 @@
       <c r="F1560" s="1"/>
       <c r="G1560" s="28"/>
     </row>
-    <row r="1561" spans="1:7">
+    <row r="1561" spans="1:8">
       <c r="A1561" s="6">
         <v>46226</v>
       </c>
@@ -23333,7 +23333,7 @@
       <c r="F1561" s="1"/>
       <c r="G1561" s="28"/>
     </row>
-    <row r="1562" spans="1:7">
+    <row r="1562" spans="1:8">
       <c r="A1562" s="6">
         <v>46226</v>
       </c>
@@ -23349,7 +23349,7 @@
       <c r="F1562" s="1"/>
       <c r="G1562" s="28"/>
     </row>
-    <row r="1563" spans="1:7">
+    <row r="1563" spans="1:8">
       <c r="A1563" s="6">
         <v>46227</v>
       </c>
@@ -23359,11 +23359,12 @@
       <c r="C1563" s="5">
         <v>9</v>
       </c>
-      <c r="D1563" s="2"/>
+      <c r="D1563" s="2">
+        <v>5</v>
+      </c>
       <c r="F1563" s="1"/>
-      <c r="G1563" s="28"/>
-    </row>
-    <row r="1564" spans="1:7">
+    </row>
+    <row r="1564" spans="1:8">
       <c r="A1564" s="6">
         <v>46227</v>
       </c>
@@ -23373,11 +23374,14 @@
       <c r="C1564" s="5">
         <v>7</v>
       </c>
-      <c r="D1564" s="2"/>
+      <c r="D1564" s="2">
+        <v>11</v>
+      </c>
       <c r="F1564" s="1"/>
-      <c r="G1564" s="28"/>
-    </row>
-    <row r="1565" spans="1:7">
+      <c r="G1564" s="1"/>
+      <c r="H1564" s="28"/>
+    </row>
+    <row r="1565" spans="1:8">
       <c r="A1565" s="6">
         <v>46227</v>
       </c>
@@ -23387,11 +23391,14 @@
       <c r="C1565" s="5">
         <v>8</v>
       </c>
-      <c r="D1565" s="2"/>
+      <c r="D1565" s="2">
+        <v>6</v>
+      </c>
       <c r="F1565" s="1"/>
-      <c r="G1565" s="28"/>
-    </row>
-    <row r="1566" spans="1:7">
+      <c r="G1565" s="1"/>
+      <c r="H1565" s="28"/>
+    </row>
+    <row r="1566" spans="1:8">
       <c r="A1566" s="6">
         <v>46227</v>
       </c>
@@ -23401,9 +23408,13 @@
       <c r="C1566" s="5">
         <v>8</v>
       </c>
-      <c r="D1566" s="2"/>
-    </row>
-    <row r="1567" spans="1:7">
+      <c r="D1566" s="2">
+        <v>7</v>
+      </c>
+      <c r="G1566" s="1"/>
+      <c r="H1566" s="28"/>
+    </row>
+    <row r="1567" spans="1:8">
       <c r="A1567" s="6">
         <v>46227</v>
       </c>
@@ -23413,7 +23424,337 @@
       <c r="C1567" s="5">
         <v>6</v>
       </c>
-      <c r="D1567" s="2"/>
+      <c r="D1567" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1567" s="1"/>
+      <c r="H1567" s="28"/>
+    </row>
+    <row r="1568" spans="1:8">
+      <c r="A1568" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B1568" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1568" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1568" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:7">
+      <c r="A1569" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B1569" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1569" s="5">
+        <v>13</v>
+      </c>
+      <c r="D1569" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1569" s="1"/>
+      <c r="G1569" s="28"/>
+    </row>
+    <row r="1570" spans="1:7">
+      <c r="A1570" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B1570" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1570" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1570" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1570" s="1"/>
+      <c r="G1570" s="28"/>
+    </row>
+    <row r="1571" spans="1:7">
+      <c r="A1571" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B1571" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1571" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1571" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1571" s="1"/>
+      <c r="G1571" s="28"/>
+    </row>
+    <row r="1572" spans="1:7">
+      <c r="A1572" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B1572" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1572" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1572" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:7">
+      <c r="A1573" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B1573" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1573" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1573" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1573" s="1"/>
+      <c r="G1573" s="28"/>
+    </row>
+    <row r="1574" spans="1:7">
+      <c r="A1574" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B1574" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1574" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1574" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1574" s="1"/>
+      <c r="G1574" s="28"/>
+    </row>
+    <row r="1575" spans="1:7">
+      <c r="A1575" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B1575" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1575" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1575" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1575" s="1"/>
+      <c r="G1575" s="28"/>
+    </row>
+    <row r="1576" spans="1:7">
+      <c r="A1576" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B1576" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1576" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1576" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1576" s="1"/>
+      <c r="G1576" s="28"/>
+    </row>
+    <row r="1577" spans="1:7">
+      <c r="A1577" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B1577" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1577" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1577" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:7">
+      <c r="A1578" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B1578" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1578" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1578" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1578" s="1"/>
+      <c r="G1578" s="28"/>
+    </row>
+    <row r="1579" spans="1:7">
+      <c r="A1579" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B1579" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1579" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1579" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1579" s="1"/>
+      <c r="G1579" s="28"/>
+    </row>
+    <row r="1580" spans="1:7">
+      <c r="A1580" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B1580" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1580" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1580" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1580" s="1"/>
+      <c r="G1580" s="28"/>
+    </row>
+    <row r="1581" spans="1:7">
+      <c r="A1581" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B1581" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1581" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1581" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1581" s="1"/>
+      <c r="G1581" s="28"/>
+    </row>
+    <row r="1582" spans="1:7">
+      <c r="A1582" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1582" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1582" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1582" s="2"/>
+    </row>
+    <row r="1583" spans="1:7">
+      <c r="A1583" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1583" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1583" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1583" s="2"/>
+    </row>
+    <row r="1584" spans="1:7">
+      <c r="A1584" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1584" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1584" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1584" s="2"/>
+    </row>
+    <row r="1585" spans="1:4">
+      <c r="A1585" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1585" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1585" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1585" s="2"/>
+    </row>
+    <row r="1586" spans="1:4">
+      <c r="A1586" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1586" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1586" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1586" s="2"/>
+    </row>
+    <row r="1587" spans="1:4">
+      <c r="A1587" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1587" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1587" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1587" s="2"/>
+    </row>
+    <row r="1588" spans="1:4">
+      <c r="A1588" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1588" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1588" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1588" s="2"/>
+    </row>
+    <row r="1589" spans="1:4">
+      <c r="A1589" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1589" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1589" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1589" s="2"/>
+    </row>
+    <row r="1590" spans="1:4">
+      <c r="A1590" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B1590" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1590" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1590" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1590"/>
+  <dimension ref="A1:H1600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23658,7 +23658,9 @@
       <c r="C1582" s="5">
         <v>8</v>
       </c>
-      <c r="D1582" s="2"/>
+      <c r="D1582" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="1583" spans="1:7">
       <c r="A1583" s="6">
@@ -23670,7 +23672,11 @@
       <c r="C1583" s="5">
         <v>1</v>
       </c>
-      <c r="D1583" s="2"/>
+      <c r="D1583" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1583" s="1"/>
+      <c r="G1583" s="28"/>
     </row>
     <row r="1584" spans="1:7">
       <c r="A1584" s="6">
@@ -23682,9 +23688,13 @@
       <c r="C1584" s="5">
         <v>1</v>
       </c>
-      <c r="D1584" s="2"/>
-    </row>
-    <row r="1585" spans="1:4">
+      <c r="D1584" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1584" s="1"/>
+      <c r="G1584" s="28"/>
+    </row>
+    <row r="1585" spans="1:7">
       <c r="A1585" s="6">
         <v>46232</v>
       </c>
@@ -23694,9 +23704,13 @@
       <c r="C1585" s="5">
         <v>1</v>
       </c>
-      <c r="D1585" s="2"/>
-    </row>
-    <row r="1586" spans="1:4">
+      <c r="D1585" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1585" s="1"/>
+      <c r="G1585" s="28"/>
+    </row>
+    <row r="1586" spans="1:7">
       <c r="A1586" s="6">
         <v>46232</v>
       </c>
@@ -23706,9 +23720,13 @@
       <c r="C1586" s="5">
         <v>1</v>
       </c>
-      <c r="D1586" s="2"/>
-    </row>
-    <row r="1587" spans="1:4">
+      <c r="D1586" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1586" s="1"/>
+      <c r="G1586" s="28"/>
+    </row>
+    <row r="1587" spans="1:7">
       <c r="A1587" s="6">
         <v>46232</v>
       </c>
@@ -23718,9 +23736,13 @@
       <c r="C1587" s="5">
         <v>10</v>
       </c>
-      <c r="D1587" s="2"/>
-    </row>
-    <row r="1588" spans="1:4">
+      <c r="D1587" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1587" s="1"/>
+      <c r="G1587" s="28"/>
+    </row>
+    <row r="1588" spans="1:7">
       <c r="A1588" s="6">
         <v>46232</v>
       </c>
@@ -23730,9 +23752,13 @@
       <c r="C1588" s="2">
         <v>10</v>
       </c>
-      <c r="D1588" s="2"/>
-    </row>
-    <row r="1589" spans="1:4">
+      <c r="D1588" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1588" s="1"/>
+      <c r="G1588" s="28"/>
+    </row>
+    <row r="1589" spans="1:7">
       <c r="A1589" s="6">
         <v>46232</v>
       </c>
@@ -23742,9 +23768,11 @@
       <c r="C1589" s="2">
         <v>2</v>
       </c>
-      <c r="D1589" s="2"/>
-    </row>
-    <row r="1590" spans="1:4">
+      <c r="D1589" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:7">
       <c r="A1590" s="6">
         <v>46232</v>
       </c>
@@ -23754,7 +23782,129 @@
       <c r="C1590" s="2">
         <v>2</v>
       </c>
-      <c r="D1590" s="2"/>
+      <c r="D1590" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:7">
+      <c r="A1591" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1591" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1591" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1591" s="2"/>
+    </row>
+    <row r="1592" spans="1:7">
+      <c r="A1592" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1592" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1592" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1592" s="2"/>
+    </row>
+    <row r="1593" spans="1:7">
+      <c r="A1593" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1593" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1593" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1593" s="2"/>
+    </row>
+    <row r="1594" spans="1:7">
+      <c r="A1594" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1594" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1594" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1594" s="2"/>
+    </row>
+    <row r="1595" spans="1:7">
+      <c r="A1595" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1595" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1595" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1595" s="2"/>
+    </row>
+    <row r="1596" spans="1:7">
+      <c r="A1596" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1596" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1596" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1596" s="2"/>
+    </row>
+    <row r="1597" spans="1:7">
+      <c r="A1597" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1597" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1597" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1597" s="2"/>
+    </row>
+    <row r="1598" spans="1:7">
+      <c r="A1598" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1598" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1598" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1598" s="2"/>
+    </row>
+    <row r="1599" spans="1:7">
+      <c r="A1599" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1599" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1599" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1599" s="2"/>
+    </row>
+    <row r="1600" spans="1:7">
+      <c r="A1600" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B1600" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1600" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1600" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -619,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1600"/>
+  <dimension ref="A1:H1607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -23796,7 +23796,9 @@
       <c r="C1591" s="5">
         <v>10</v>
       </c>
-      <c r="D1591" s="2"/>
+      <c r="D1591" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1592" spans="1:7">
       <c r="A1592" s="6">
@@ -23808,7 +23810,11 @@
       <c r="C1592" s="2">
         <v>10</v>
       </c>
-      <c r="D1592" s="2"/>
+      <c r="D1592" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1592" s="1"/>
+      <c r="G1592" s="28"/>
     </row>
     <row r="1593" spans="1:7">
       <c r="A1593" s="6">
@@ -23820,7 +23826,11 @@
       <c r="C1593" s="2">
         <v>1</v>
       </c>
-      <c r="D1593" s="2"/>
+      <c r="D1593" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1593" s="1"/>
+      <c r="G1593" s="28"/>
     </row>
     <row r="1594" spans="1:7">
       <c r="A1594" s="6">
@@ -23832,7 +23842,11 @@
       <c r="C1594" s="2">
         <v>1</v>
       </c>
-      <c r="D1594" s="2"/>
+      <c r="D1594" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1594" s="1"/>
+      <c r="G1594" s="28"/>
     </row>
     <row r="1595" spans="1:7">
       <c r="A1595" s="6">
@@ -23844,7 +23858,11 @@
       <c r="C1595" s="2">
         <v>3</v>
       </c>
-      <c r="D1595" s="2"/>
+      <c r="D1595" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1595" s="1"/>
+      <c r="G1595" s="28"/>
     </row>
     <row r="1596" spans="1:7">
       <c r="A1596" s="6">
@@ -23856,7 +23874,11 @@
       <c r="C1596" s="2">
         <v>3</v>
       </c>
-      <c r="D1596" s="2"/>
+      <c r="D1596" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1596" s="1"/>
+      <c r="G1596" s="28"/>
     </row>
     <row r="1597" spans="1:7">
       <c r="A1597" s="6">
@@ -23868,7 +23890,9 @@
       <c r="C1597" s="2">
         <v>2</v>
       </c>
-      <c r="D1597" s="2"/>
+      <c r="D1597" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1598" spans="1:7">
       <c r="A1598" s="6">
@@ -23880,7 +23904,9 @@
       <c r="C1598" s="2">
         <v>2</v>
       </c>
-      <c r="D1598" s="2"/>
+      <c r="D1598" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1599" spans="1:7">
       <c r="A1599" s="6">
@@ -23892,7 +23918,9 @@
       <c r="C1599" s="2">
         <v>11</v>
       </c>
-      <c r="D1599" s="2"/>
+      <c r="D1599" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1600" spans="1:7">
       <c r="A1600" s="6">
@@ -23904,7 +23932,93 @@
       <c r="C1600" s="2">
         <v>11</v>
       </c>
-      <c r="D1600" s="2"/>
+      <c r="D1600" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4">
+      <c r="A1601" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1601" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1601" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1601" s="2"/>
+    </row>
+    <row r="1602" spans="1:4">
+      <c r="A1602" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1602" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1602" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1602" s="2"/>
+    </row>
+    <row r="1603" spans="1:4">
+      <c r="A1603" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1603" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1603" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1603" s="2"/>
+    </row>
+    <row r="1604" spans="1:4">
+      <c r="A1604" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1604" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1604" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1604" s="2"/>
+    </row>
+    <row r="1605" spans="1:4">
+      <c r="A1605" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1605" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1605" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1605" s="2"/>
+    </row>
+    <row r="1606" spans="1:4">
+      <c r="A1606" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1606" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1606" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1606" s="2"/>
+    </row>
+    <row r="1607" spans="1:4">
+      <c r="A1607" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B1607" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1607" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1607" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="21015" windowHeight="7950"/>
+    <workbookView xWindow="240" yWindow="60" windowWidth="21012" windowHeight="7956"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -324,6 +324,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -619,20 +623,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1607"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H1672"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -23937,88 +23941,1016 @@
       </c>
     </row>
     <row r="1601" spans="1:4">
-      <c r="A1601" s="6">
+      <c r="A1601" s="7">
         <v>46234</v>
       </c>
-      <c r="B1601" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1601" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1601" s="2"/>
+      <c r="B1601" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1601" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1601" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="1602" spans="1:4">
-      <c r="A1602" s="6">
+      <c r="A1602" s="7">
         <v>46234</v>
       </c>
-      <c r="B1602" s="8" t="s">
+      <c r="B1602" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1602" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1602" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4">
+      <c r="A1603" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B1603" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1603" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1603" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4">
+      <c r="A1604" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B1604" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C1602" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1602" s="2"/>
-    </row>
-    <row r="1603" spans="1:4">
-      <c r="A1603" s="6">
+      <c r="C1604" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1604" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4">
+      <c r="A1605" s="7">
         <v>46234</v>
       </c>
-      <c r="B1603" s="2" t="s">
+      <c r="B1605" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1603" s="5">
+      <c r="C1605" s="5">
         <v>7</v>
       </c>
-      <c r="D1603" s="2"/>
-    </row>
-    <row r="1604" spans="1:4">
-      <c r="A1604" s="6">
+      <c r="D1605" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4">
+      <c r="A1606" s="7">
         <v>46234</v>
       </c>
-      <c r="B1604" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1604" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1604" s="2"/>
-    </row>
-    <row r="1605" spans="1:4">
-      <c r="A1605" s="6">
+      <c r="B1606" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1606" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1606" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4">
+      <c r="A1607" s="7">
         <v>46234</v>
       </c>
-      <c r="B1605" s="18" t="s">
+      <c r="B1607" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C1605" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1605" s="2"/>
-    </row>
-    <row r="1606" spans="1:4">
-      <c r="A1606" s="6">
+      <c r="C1607" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1607" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4">
+      <c r="A1608" s="7">
         <v>46234</v>
       </c>
-      <c r="B1606" s="17" t="s">
+      <c r="B1608" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C1606" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1606" s="2"/>
-    </row>
-    <row r="1607" spans="1:4">
-      <c r="A1607" s="6">
+      <c r="C1608" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1608" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4">
+      <c r="A1609" s="7">
         <v>46234</v>
       </c>
-      <c r="B1607" s="17" t="s">
+      <c r="B1609" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C1607" s="5">
-        <v>5</v>
-      </c>
-      <c r="D1607" s="2"/>
+      <c r="C1609" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1609" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4">
+      <c r="A1610" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1610" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1610" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1610" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4">
+      <c r="A1611" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1611" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1611" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1611" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4">
+      <c r="A1612" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1612" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1612" s="5">
+        <v>19</v>
+      </c>
+      <c r="D1612" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4">
+      <c r="A1613" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1613" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1613" s="5">
+        <v>19</v>
+      </c>
+      <c r="D1613" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4">
+      <c r="A1614" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1614" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1614" s="5">
+        <v>18</v>
+      </c>
+      <c r="D1614" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4">
+      <c r="A1615" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B1615" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1615" s="5">
+        <v>17</v>
+      </c>
+      <c r="D1615" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4">
+      <c r="A1616" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1616" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1616" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1616" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:7">
+      <c r="A1617" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1617" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1617" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1617" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:7">
+      <c r="A1618" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1618" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1618" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1618" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:7">
+      <c r="A1619" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1619" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1619" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1619" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:7">
+      <c r="A1620" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1620" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1620" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1620" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:7">
+      <c r="A1621" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1621" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1621" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1621" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:7">
+      <c r="A1622" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1622" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1622" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1622" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:7">
+      <c r="A1623" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1623" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1623" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1623" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:7">
+      <c r="A1624" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B1624" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1624" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1624" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:7">
+      <c r="A1625" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1625" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1625" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1625" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:7">
+      <c r="A1626" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1626" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1626" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1626" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:7">
+      <c r="A1627" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1627" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1627" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1627" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:7">
+      <c r="A1628" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1628" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1628" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1628" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:7">
+      <c r="A1629" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1629" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1629" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1629" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:7">
+      <c r="A1630" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1630" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1630" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1630" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:7">
+      <c r="A1631" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1631" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1631" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1631" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1631" s="1"/>
+      <c r="G1631" s="28"/>
+    </row>
+    <row r="1632" spans="1:7">
+      <c r="A1632" s="30">
+        <v>46238</v>
+      </c>
+      <c r="B1632" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1632" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1632" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1632" s="1"/>
+      <c r="G1632" s="28"/>
+    </row>
+    <row r="1633" spans="1:7">
+      <c r="A1633" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1633" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1633" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1633" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1633" s="1"/>
+      <c r="G1633" s="28"/>
+    </row>
+    <row r="1634" spans="1:7">
+      <c r="A1634" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1634" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1634" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1634" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1634" s="1"/>
+      <c r="G1634" s="28"/>
+    </row>
+    <row r="1635" spans="1:7">
+      <c r="A1635" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1635" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1635" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1635" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1635" s="1"/>
+      <c r="G1635" s="28"/>
+    </row>
+    <row r="1636" spans="1:7">
+      <c r="A1636" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1636" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1636" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1636" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1636" s="1"/>
+      <c r="G1636" s="28"/>
+    </row>
+    <row r="1637" spans="1:7">
+      <c r="A1637" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1637" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1637" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1637" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1637" s="1"/>
+      <c r="G1637" s="28"/>
+    </row>
+    <row r="1638" spans="1:7">
+      <c r="A1638" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1638" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1638" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1638" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1638" s="29"/>
+      <c r="G1638" s="28"/>
+    </row>
+    <row r="1639" spans="1:7">
+      <c r="A1639" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1639" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1639" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1639" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1639" s="29"/>
+      <c r="G1639" s="28"/>
+    </row>
+    <row r="1640" spans="1:7">
+      <c r="A1640" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B1640" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1640" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1640" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1640" s="29"/>
+      <c r="G1640" s="28"/>
+    </row>
+    <row r="1641" spans="1:7">
+      <c r="A1641" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1641" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1641" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1641" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1641" s="1"/>
+      <c r="G1641" s="28"/>
+    </row>
+    <row r="1642" spans="1:7">
+      <c r="A1642" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1642" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1642" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1642" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1642" s="1"/>
+      <c r="G1642" s="28"/>
+    </row>
+    <row r="1643" spans="1:7">
+      <c r="A1643" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1643" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1643" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1643" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1643" s="29"/>
+      <c r="G1643" s="28"/>
+    </row>
+    <row r="1644" spans="1:7">
+      <c r="A1644" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1644" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1644" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1644" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1644" s="1"/>
+      <c r="G1644" s="28"/>
+    </row>
+    <row r="1645" spans="1:7">
+      <c r="A1645" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1645" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1645" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1645" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:7">
+      <c r="A1646" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B1646" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1646" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1646" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:7">
+      <c r="A1647" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1647" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1647" s="5">
+        <v>12</v>
+      </c>
+      <c r="D1647" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:7">
+      <c r="A1648" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1648" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1648" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1648" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4">
+      <c r="A1649" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1649" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1649" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1649" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4">
+      <c r="A1650" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1650" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1650" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1650" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:4">
+      <c r="A1651" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1651" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1651" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1651" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:4">
+      <c r="A1652" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1652" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1652" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1652" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:4">
+      <c r="A1653" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1653" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1653" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1653" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:4">
+      <c r="A1654" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1654" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1654" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1654" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:4">
+      <c r="A1655" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1655" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1655" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1655" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4">
+      <c r="A1656" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1656" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1656" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1656" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4">
+      <c r="A1657" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B1657" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1657" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1657" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:4">
+      <c r="A1658" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B1658" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1658" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1658" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:4">
+      <c r="A1659" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B1659" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1659" s="5">
+        <v>9</v>
+      </c>
+      <c r="D1659" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:4">
+      <c r="A1660" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B1660" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1660" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1660" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:4">
+      <c r="A1661" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1661" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1661" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1661" s="2"/>
+    </row>
+    <row r="1662" spans="1:4">
+      <c r="A1662" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1662" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1662" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1662" s="2"/>
+    </row>
+    <row r="1663" spans="1:4">
+      <c r="A1663" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1663" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1663" s="2"/>
+    </row>
+    <row r="1664" spans="1:4">
+      <c r="A1664" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1664" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1664" s="2"/>
+    </row>
+    <row r="1665" spans="1:4">
+      <c r="A1665" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1665" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1665" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1665" s="2"/>
+    </row>
+    <row r="1666" spans="1:4">
+      <c r="A1666" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1666" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1666" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1666" s="2"/>
+    </row>
+    <row r="1667" spans="1:4">
+      <c r="A1667" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1667" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1667" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1667" s="2"/>
+    </row>
+    <row r="1668" spans="1:4">
+      <c r="A1668" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1668" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1668" s="5">
+        <v>7</v>
+      </c>
+      <c r="D1668" s="2"/>
+    </row>
+    <row r="1669" spans="1:4">
+      <c r="A1669" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1669" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1669" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1669" s="2"/>
+    </row>
+    <row r="1670" spans="1:4">
+      <c r="A1670" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1670" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1670" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1670" s="2"/>
+    </row>
+    <row r="1671" spans="1:4">
+      <c r="A1671" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1671" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1671" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1671" s="2"/>
+    </row>
+    <row r="1672" spans="1:4">
+      <c r="A1672" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B1672" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1672" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1672" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
@@ -24030,7 +24962,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -623,14 +623,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1672"/>
+  <dimension ref="A1:H1681"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
     <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.88671875" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -24640,7 +24640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1649" spans="1:4">
+    <row r="1649" spans="1:7">
       <c r="A1649" s="6">
         <v>46241</v>
       </c>
@@ -24654,7 +24654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1650" spans="1:4">
+    <row r="1650" spans="1:7">
       <c r="A1650" s="6">
         <v>46241</v>
       </c>
@@ -24668,7 +24668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1651" spans="1:4">
+    <row r="1651" spans="1:7">
       <c r="A1651" s="6">
         <v>46241</v>
       </c>
@@ -24682,7 +24682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1652" spans="1:4">
+    <row r="1652" spans="1:7">
       <c r="A1652" s="6">
         <v>46241</v>
       </c>
@@ -24696,7 +24696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1653" spans="1:4">
+    <row r="1653" spans="1:7">
       <c r="A1653" s="6">
         <v>46241</v>
       </c>
@@ -24710,7 +24710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1654" spans="1:4">
+    <row r="1654" spans="1:7">
       <c r="A1654" s="6">
         <v>46241</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1655" spans="1:4">
+    <row r="1655" spans="1:7">
       <c r="A1655" s="6">
         <v>46241</v>
       </c>
@@ -24738,7 +24738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1656" spans="1:4">
+    <row r="1656" spans="1:7">
       <c r="A1656" s="6">
         <v>46241</v>
       </c>
@@ -24752,7 +24752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1657" spans="1:4">
+    <row r="1657" spans="1:7">
       <c r="A1657" s="6">
         <v>46241</v>
       </c>
@@ -24766,7 +24766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1658" spans="1:4">
+    <row r="1658" spans="1:7">
       <c r="A1658" s="6">
         <v>46242</v>
       </c>
@@ -24780,7 +24780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1659" spans="1:4">
+    <row r="1659" spans="1:7">
       <c r="A1659" s="6">
         <v>46242</v>
       </c>
@@ -24794,7 +24794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1660" spans="1:4">
+    <row r="1660" spans="1:7">
       <c r="A1660" s="6">
         <v>46242</v>
       </c>
@@ -24808,7 +24808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1661" spans="1:4">
+    <row r="1661" spans="1:7">
       <c r="A1661" s="6">
         <v>46244</v>
       </c>
@@ -24818,9 +24818,11 @@
       <c r="C1661" s="2">
         <v>3</v>
       </c>
-      <c r="D1661" s="2"/>
-    </row>
-    <row r="1662" spans="1:4">
+      <c r="D1661" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:7">
       <c r="A1662" s="6">
         <v>46244</v>
       </c>
@@ -24830,9 +24832,13 @@
       <c r="C1662" s="2">
         <v>3</v>
       </c>
-      <c r="D1662" s="2"/>
-    </row>
-    <row r="1663" spans="1:4">
+      <c r="D1662" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1662" s="1"/>
+      <c r="G1662" s="28"/>
+    </row>
+    <row r="1663" spans="1:7">
       <c r="A1663" s="6">
         <v>46244</v>
       </c>
@@ -24842,9 +24848,13 @@
       <c r="C1663" s="2">
         <v>9</v>
       </c>
-      <c r="D1663" s="2"/>
-    </row>
-    <row r="1664" spans="1:4">
+      <c r="D1663" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1663" s="1"/>
+      <c r="G1663" s="28"/>
+    </row>
+    <row r="1664" spans="1:7">
       <c r="A1664" s="6">
         <v>46244</v>
       </c>
@@ -24854,9 +24864,13 @@
       <c r="C1664" s="2">
         <v>9</v>
       </c>
-      <c r="D1664" s="2"/>
-    </row>
-    <row r="1665" spans="1:4">
+      <c r="D1664" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1664" s="1"/>
+      <c r="G1664" s="28"/>
+    </row>
+    <row r="1665" spans="1:7">
       <c r="A1665" s="6">
         <v>46244</v>
       </c>
@@ -24866,9 +24880,13 @@
       <c r="C1665" s="2">
         <v>11</v>
       </c>
-      <c r="D1665" s="2"/>
-    </row>
-    <row r="1666" spans="1:4">
+      <c r="D1665" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1665" s="1"/>
+      <c r="G1665" s="28"/>
+    </row>
+    <row r="1666" spans="1:7">
       <c r="A1666" s="6">
         <v>46244</v>
       </c>
@@ -24878,9 +24896,13 @@
       <c r="C1666" s="2">
         <v>11</v>
       </c>
-      <c r="D1666" s="2"/>
-    </row>
-    <row r="1667" spans="1:4">
+      <c r="D1666" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1666" s="1"/>
+      <c r="G1666" s="28"/>
+    </row>
+    <row r="1667" spans="1:7">
       <c r="A1667" s="6">
         <v>46244</v>
       </c>
@@ -24890,9 +24912,13 @@
       <c r="C1667" s="2">
         <v>7</v>
       </c>
-      <c r="D1667" s="2"/>
-    </row>
-    <row r="1668" spans="1:4">
+      <c r="D1667" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1667" s="1"/>
+      <c r="G1667" s="28"/>
+    </row>
+    <row r="1668" spans="1:7">
       <c r="A1668" s="6">
         <v>46244</v>
       </c>
@@ -24902,9 +24928,13 @@
       <c r="C1668" s="5">
         <v>7</v>
       </c>
-      <c r="D1668" s="2"/>
-    </row>
-    <row r="1669" spans="1:4">
+      <c r="D1668" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1668" s="1"/>
+      <c r="G1668" s="28"/>
+    </row>
+    <row r="1669" spans="1:7">
       <c r="A1669" s="6">
         <v>46244</v>
       </c>
@@ -24914,9 +24944,13 @@
       <c r="C1669" s="5">
         <v>5</v>
       </c>
-      <c r="D1669" s="2"/>
-    </row>
-    <row r="1670" spans="1:4">
+      <c r="D1669" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1669" s="1"/>
+      <c r="G1669" s="28"/>
+    </row>
+    <row r="1670" spans="1:7">
       <c r="A1670" s="6">
         <v>46244</v>
       </c>
@@ -24926,31 +24960,161 @@
       <c r="C1670" s="2">
         <v>5</v>
       </c>
-      <c r="D1670" s="2"/>
-    </row>
-    <row r="1671" spans="1:4">
+      <c r="D1670" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:7">
       <c r="A1671" s="6">
         <v>46244</v>
       </c>
-      <c r="B1671" s="2" t="s">
+      <c r="B1671" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C1671" s="2">
         <v>7</v>
       </c>
-      <c r="D1671" s="2"/>
-    </row>
-    <row r="1672" spans="1:4">
+      <c r="D1671" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:7">
       <c r="A1672" s="6">
         <v>46244</v>
       </c>
-      <c r="B1672" s="2" t="s">
+      <c r="B1672" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C1672" s="2">
         <v>7</v>
       </c>
-      <c r="D1672" s="2"/>
+      <c r="D1672" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:7">
+      <c r="A1673" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1673" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1673" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1673" s="2"/>
+    </row>
+    <row r="1674" spans="1:7">
+      <c r="A1674" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1674" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1674" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1674" s="2"/>
+      <c r="F1674" s="1"/>
+      <c r="G1674" s="28"/>
+    </row>
+    <row r="1675" spans="1:7">
+      <c r="A1675" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1675" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1675" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1675" s="2"/>
+      <c r="F1675" s="1"/>
+      <c r="G1675" s="28"/>
+    </row>
+    <row r="1676" spans="1:7">
+      <c r="A1676" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1676" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1676" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1676" s="2"/>
+      <c r="F1676" s="1"/>
+      <c r="G1676" s="28"/>
+    </row>
+    <row r="1677" spans="1:7">
+      <c r="A1677" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1677" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1677" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="2"/>
+      <c r="F1677" s="1"/>
+      <c r="G1677" s="28"/>
+    </row>
+    <row r="1678" spans="1:7">
+      <c r="A1678" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1678" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1678" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="2"/>
+      <c r="F1678" s="1"/>
+      <c r="G1678" s="28"/>
+    </row>
+    <row r="1679" spans="1:7">
+      <c r="A1679" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1679" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1679" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1679" s="2"/>
+      <c r="F1679" s="1"/>
+      <c r="G1679" s="28"/>
+    </row>
+    <row r="1680" spans="1:7">
+      <c r="A1680" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1680" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1680" s="5">
+        <v>8</v>
+      </c>
+      <c r="D1680" s="2"/>
+      <c r="F1680" s="1"/>
+      <c r="G1680" s="28"/>
+    </row>
+    <row r="1681" spans="1:7">
+      <c r="A1681" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B1681" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1681" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1681" s="2"/>
+      <c r="F1681" s="1"/>
+      <c r="G1681" s="28"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="21012" windowHeight="7956"/>
+    <workbookView xWindow="240" yWindow="60" windowWidth="21015" windowHeight="7950"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -623,20 +623,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1681"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H1689"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" customWidth="1"/>
-    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -25002,7 +25002,9 @@
       <c r="C1673" s="5">
         <v>3</v>
       </c>
-      <c r="D1673" s="2"/>
+      <c r="D1673" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="1674" spans="1:7">
       <c r="A1674" s="6">
@@ -25014,7 +25016,9 @@
       <c r="C1674" s="5">
         <v>3</v>
       </c>
-      <c r="D1674" s="2"/>
+      <c r="D1674" s="2">
+        <v>6</v>
+      </c>
       <c r="F1674" s="1"/>
       <c r="G1674" s="28"/>
     </row>
@@ -25028,7 +25032,9 @@
       <c r="C1675" s="5">
         <v>3</v>
       </c>
-      <c r="D1675" s="2"/>
+      <c r="D1675" s="2">
+        <v>1</v>
+      </c>
       <c r="F1675" s="1"/>
       <c r="G1675" s="28"/>
     </row>
@@ -25042,7 +25048,9 @@
       <c r="C1676" s="5">
         <v>3</v>
       </c>
-      <c r="D1676" s="2"/>
+      <c r="D1676" s="2">
+        <v>1</v>
+      </c>
       <c r="F1676" s="1"/>
       <c r="G1676" s="28"/>
     </row>
@@ -25056,7 +25064,9 @@
       <c r="C1677" s="5">
         <v>4</v>
       </c>
-      <c r="D1677" s="2"/>
+      <c r="D1677" s="2">
+        <v>5</v>
+      </c>
       <c r="F1677" s="1"/>
       <c r="G1677" s="28"/>
     </row>
@@ -25070,7 +25080,9 @@
       <c r="C1678" s="5">
         <v>4</v>
       </c>
-      <c r="D1678" s="2"/>
+      <c r="D1678" s="2">
+        <v>5</v>
+      </c>
       <c r="F1678" s="1"/>
       <c r="G1678" s="28"/>
     </row>
@@ -25084,7 +25096,9 @@
       <c r="C1679" s="5">
         <v>8</v>
       </c>
-      <c r="D1679" s="2"/>
+      <c r="D1679" s="2">
+        <v>7</v>
+      </c>
       <c r="F1679" s="1"/>
       <c r="G1679" s="28"/>
     </row>
@@ -25098,7 +25112,9 @@
       <c r="C1680" s="5">
         <v>8</v>
       </c>
-      <c r="D1680" s="2"/>
+      <c r="D1680" s="2">
+        <v>7</v>
+      </c>
       <c r="F1680" s="1"/>
       <c r="G1680" s="28"/>
     </row>
@@ -25112,9 +25128,107 @@
       <c r="C1681" s="5">
         <v>3</v>
       </c>
-      <c r="D1681" s="2"/>
+      <c r="D1681" s="2">
+        <v>4</v>
+      </c>
       <c r="F1681" s="1"/>
       <c r="G1681" s="28"/>
+    </row>
+    <row r="1682" spans="1:7">
+      <c r="A1682" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1682" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1682" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1682" s="2"/>
+    </row>
+    <row r="1683" spans="1:7">
+      <c r="A1683" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1683" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1683" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1683" s="2"/>
+    </row>
+    <row r="1684" spans="1:7">
+      <c r="A1684" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1684" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1684" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="2"/>
+    </row>
+    <row r="1685" spans="1:7">
+      <c r="A1685" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1685" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1685" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="2"/>
+    </row>
+    <row r="1686" spans="1:7">
+      <c r="A1686" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1686" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1686" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="2"/>
+    </row>
+    <row r="1687" spans="1:7">
+      <c r="A1687" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1687" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1687" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="2"/>
+    </row>
+    <row r="1688" spans="1:7">
+      <c r="A1688" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1688" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1688" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1688" s="2"/>
+    </row>
+    <row r="1689" spans="1:7">
+      <c r="A1689" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1689" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1689" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1689" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
@@ -25126,7 +25240,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -328,6 +328,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -623,14 +624,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1689"/>
+  <dimension ref="A1:H1699"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -25144,7 +25145,9 @@
       <c r="C1682" s="5">
         <v>1</v>
       </c>
-      <c r="D1682" s="2"/>
+      <c r="D1682" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1683" spans="1:7">
       <c r="A1683" s="6">
@@ -25156,7 +25159,11 @@
       <c r="C1683" s="5">
         <v>1</v>
       </c>
-      <c r="D1683" s="2"/>
+      <c r="D1683" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1683" s="1"/>
+      <c r="G1683" s="28"/>
     </row>
     <row r="1684" spans="1:7">
       <c r="A1684" s="6">
@@ -25168,7 +25175,11 @@
       <c r="C1684" s="5">
         <v>4</v>
       </c>
-      <c r="D1684" s="2"/>
+      <c r="D1684" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1684" s="1"/>
+      <c r="G1684" s="28"/>
     </row>
     <row r="1685" spans="1:7">
       <c r="A1685" s="6">
@@ -25180,7 +25191,11 @@
       <c r="C1685" s="5">
         <v>4</v>
       </c>
-      <c r="D1685" s="2"/>
+      <c r="D1685" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1685" s="1"/>
+      <c r="G1685" s="28"/>
     </row>
     <row r="1686" spans="1:7">
       <c r="A1686" s="6">
@@ -25192,7 +25207,11 @@
       <c r="C1686" s="5">
         <v>4</v>
       </c>
-      <c r="D1686" s="2"/>
+      <c r="D1686" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1686" s="1"/>
+      <c r="G1686" s="28"/>
     </row>
     <row r="1687" spans="1:7">
       <c r="A1687" s="6">
@@ -25204,7 +25223,11 @@
       <c r="C1687" s="5">
         <v>4</v>
       </c>
-      <c r="D1687" s="2"/>
+      <c r="D1687" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1687" s="1"/>
+      <c r="G1687" s="28"/>
     </row>
     <row r="1688" spans="1:7">
       <c r="A1688" s="6">
@@ -25216,7 +25239,11 @@
       <c r="C1688" s="5">
         <v>2</v>
       </c>
-      <c r="D1688" s="2"/>
+      <c r="D1688" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1688" s="1"/>
+      <c r="G1688" s="28"/>
     </row>
     <row r="1689" spans="1:7">
       <c r="A1689" s="6">
@@ -25228,7 +25255,115 @@
       <c r="C1689" s="5">
         <v>2</v>
       </c>
-      <c r="D1689" s="2"/>
+      <c r="D1689" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:7">
+      <c r="A1690" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1690" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1690" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:7">
+      <c r="A1691" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1691" s="5">
+        <v>0</v>
+      </c>
+      <c r="D1691" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:7">
+      <c r="A1692" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1692" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1692" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1692" s="2"/>
+    </row>
+    <row r="1693" spans="1:7">
+      <c r="A1693" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1693" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1693" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1693" s="2"/>
+    </row>
+    <row r="1694" spans="1:7">
+      <c r="A1694" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1694" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1694" s="2"/>
+    </row>
+    <row r="1695" spans="1:7">
+      <c r="A1695" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1695" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1695" s="2"/>
+    </row>
+    <row r="1696" spans="1:7">
+      <c r="A1696" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1696" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1696" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1696" s="2"/>
+    </row>
+    <row r="1697" spans="1:4">
+      <c r="A1697" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1697" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1697" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1697" s="2"/>
+    </row>
+    <row r="1698" spans="1:4">
+      <c r="A1698" s="31"/>
+    </row>
+    <row r="1699" spans="1:4">
+      <c r="A1699" s="31"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -328,7 +328,6 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -624,14 +623,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1699"/>
+  <dimension ref="A1:H1709"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -25292,78 +25291,248 @@
         <v>46247</v>
       </c>
       <c r="B1692" s="24" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1692" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1692" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1692" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1693" spans="1:7">
       <c r="A1693" s="6">
         <v>46247</v>
       </c>
       <c r="B1693" s="24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C1693" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1693" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1693" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="1694" spans="1:7">
       <c r="A1694" s="6">
         <v>46247</v>
       </c>
-      <c r="B1694" s="20" t="s">
-        <v>10</v>
+      <c r="B1694" s="23" t="s">
+        <v>4</v>
       </c>
       <c r="C1694" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1694" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1694" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1695" spans="1:7">
       <c r="A1695" s="6">
         <v>46247</v>
       </c>
-      <c r="B1695" s="20" t="s">
-        <v>7</v>
+      <c r="B1695" s="23" t="s">
+        <v>23</v>
       </c>
       <c r="C1695" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1695" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D1695" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1696" spans="1:7">
       <c r="A1696" s="6">
         <v>46247</v>
       </c>
-      <c r="B1696" s="18" t="s">
-        <v>21</v>
+      <c r="B1696" s="24" t="s">
+        <v>11</v>
       </c>
       <c r="C1696" s="5">
-        <v>10</v>
-      </c>
-      <c r="D1696" s="2"/>
-    </row>
-    <row r="1697" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D1696" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:7">
       <c r="A1697" s="6">
         <v>46247</v>
       </c>
-      <c r="B1697" s="18" t="s">
+      <c r="B1697" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1697" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1697" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:7">
+      <c r="A1698" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1698" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1698" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:7">
+      <c r="A1699" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1699" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1699" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:7">
+      <c r="A1700" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1700" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1700" s="5">
+        <v>10</v>
+      </c>
+      <c r="D1700" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:7">
+      <c r="A1701" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B1701" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C1697" s="2">
+      <c r="C1701" s="2">
         <v>10</v>
       </c>
-      <c r="D1697" s="2"/>
-    </row>
-    <row r="1698" spans="1:4">
-      <c r="A1698" s="31"/>
-    </row>
-    <row r="1699" spans="1:4">
-      <c r="A1699" s="31"/>
+      <c r="D1701" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:7">
+      <c r="A1702" s="6">
+        <v>46248</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1702" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1702" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:7">
+      <c r="A1703" s="6">
+        <v>46248</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1703" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1703" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1703" s="1"/>
+      <c r="G1703" s="28"/>
+    </row>
+    <row r="1704" spans="1:7">
+      <c r="A1704" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1704" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1704" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1704" s="2"/>
+      <c r="F1704" s="1"/>
+      <c r="G1704" s="28"/>
+    </row>
+    <row r="1705" spans="1:7">
+      <c r="A1705" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1705" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1705" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="2"/>
+      <c r="F1705" s="1"/>
+      <c r="G1705" s="28"/>
+    </row>
+    <row r="1706" spans="1:7">
+      <c r="A1706" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1706" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1706" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1706" s="2"/>
+      <c r="F1706" s="1"/>
+      <c r="G1706" s="28"/>
+    </row>
+    <row r="1707" spans="1:7">
+      <c r="A1707" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1707" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1707" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1707" s="2"/>
+    </row>
+    <row r="1708" spans="1:7">
+      <c r="A1708" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1708" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1708" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1708" s="2"/>
+    </row>
+    <row r="1709" spans="1:7">
+      <c r="A1709" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1709" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1709" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1709" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -623,14 +623,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1709"/>
+  <dimension ref="A1:H1716"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -25460,13 +25460,15 @@
       <c r="A1704" s="6">
         <v>46251</v>
       </c>
-      <c r="B1704" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1704" s="5">
-        <v>6</v>
-      </c>
-      <c r="D1704" s="2"/>
+      <c r="B1704" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1704" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1704" s="2">
+        <v>1</v>
+      </c>
       <c r="F1704" s="1"/>
       <c r="G1704" s="28"/>
     </row>
@@ -25474,27 +25476,29 @@
       <c r="A1705" s="6">
         <v>46251</v>
       </c>
-      <c r="B1705" s="2" t="s">
-        <v>5</v>
+      <c r="B1705" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C1705" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1705" s="2"/>
-      <c r="F1705" s="1"/>
-      <c r="G1705" s="28"/>
+        <v>6</v>
+      </c>
+      <c r="D1705" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1706" spans="1:7">
       <c r="A1706" s="6">
         <v>46251</v>
       </c>
-      <c r="B1706" s="17" t="s">
-        <v>13</v>
+      <c r="B1706" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1706" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1706" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="D1706" s="2">
+        <v>6</v>
+      </c>
       <c r="F1706" s="1"/>
       <c r="G1706" s="28"/>
     </row>
@@ -25503,36 +25507,140 @@
         <v>46251</v>
       </c>
       <c r="B1707" s="17" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C1707" s="5">
         <v>2</v>
       </c>
-      <c r="D1707" s="2"/>
+      <c r="D1707" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1707" s="1"/>
+      <c r="G1707" s="28"/>
     </row>
     <row r="1708" spans="1:7">
       <c r="A1708" s="6">
         <v>46251</v>
       </c>
-      <c r="B1708" s="13" t="s">
-        <v>4</v>
+      <c r="B1708" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="C1708" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1708" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D1708" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1708" s="1"/>
+      <c r="G1708" s="28"/>
     </row>
     <row r="1709" spans="1:7">
       <c r="A1709" s="6">
         <v>46251</v>
       </c>
       <c r="B1709" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1709" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1709" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1709" s="1"/>
+      <c r="G1709" s="28"/>
+    </row>
+    <row r="1710" spans="1:7">
+      <c r="A1710" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B1710" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C1709" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1709" s="2"/>
+      <c r="C1710" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1710" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1710" s="1"/>
+      <c r="G1710" s="28"/>
+    </row>
+    <row r="1711" spans="1:7">
+      <c r="A1711" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1711" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1711" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1711" s="2"/>
+      <c r="F1711" s="1"/>
+      <c r="G1711" s="28"/>
+    </row>
+    <row r="1712" spans="1:7">
+      <c r="A1712" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1712" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1712" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1712" s="2"/>
+      <c r="F1712" s="1"/>
+      <c r="G1712" s="28"/>
+    </row>
+    <row r="1713" spans="1:4">
+      <c r="A1713" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1713" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1713" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1713" s="2"/>
+    </row>
+    <row r="1714" spans="1:4">
+      <c r="A1714" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1714" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1714" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1714" s="2"/>
+    </row>
+    <row r="1715" spans="1:4">
+      <c r="A1715" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1715" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1715" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1715" s="2"/>
+    </row>
+    <row r="1716" spans="1:4">
+      <c r="A1716" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B1716" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1716" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1716" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>

--- a/giacenza.xlsx
+++ b/giacenza.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -623,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1716"/>
+  <dimension ref="A1:H1722"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
@@ -25576,9 +25576,9 @@
       <c r="C1711" s="5">
         <v>2</v>
       </c>
-      <c r="D1711" s="2"/>
-      <c r="F1711" s="1"/>
-      <c r="G1711" s="28"/>
+      <c r="D1711" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="1712" spans="1:7">
       <c r="A1712" s="6">
@@ -25590,11 +25590,13 @@
       <c r="C1712" s="5">
         <v>3</v>
       </c>
-      <c r="D1712" s="2"/>
+      <c r="D1712" s="2">
+        <v>6</v>
+      </c>
       <c r="F1712" s="1"/>
       <c r="G1712" s="28"/>
     </row>
-    <row r="1713" spans="1:4">
+    <row r="1713" spans="1:7">
       <c r="A1713" s="6">
         <v>46252</v>
       </c>
@@ -25604,9 +25606,13 @@
       <c r="C1713" s="5">
         <v>3</v>
       </c>
-      <c r="D1713" s="2"/>
-    </row>
-    <row r="1714" spans="1:4">
+      <c r="D1713" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1713" s="1"/>
+      <c r="G1713" s="28"/>
+    </row>
+    <row r="1714" spans="1:7">
       <c r="A1714" s="6">
         <v>46252</v>
       </c>
@@ -25616,9 +25622,13 @@
       <c r="C1714" s="5">
         <v>3</v>
       </c>
-      <c r="D1714" s="2"/>
-    </row>
-    <row r="1715" spans="1:4">
+      <c r="D1714" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1714" s="1"/>
+      <c r="G1714" s="28"/>
+    </row>
+    <row r="1715" spans="1:7">
       <c r="A1715" s="6">
         <v>46252</v>
       </c>
@@ -25628,9 +25638,13 @@
       <c r="C1715" s="5">
         <v>2</v>
       </c>
-      <c r="D1715" s="2"/>
-    </row>
-    <row r="1716" spans="1:4">
+      <c r="D1715" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1715" s="1"/>
+      <c r="G1715" s="28"/>
+    </row>
+    <row r="1716" spans="1:7">
       <c r="A1716" s="6">
         <v>46252</v>
       </c>
@@ -25640,7 +25654,87 @@
       <c r="C1716" s="5">
         <v>2</v>
       </c>
-      <c r="D1716" s="2"/>
+      <c r="D1716" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1716" s="1"/>
+      <c r="G1716" s="28"/>
+    </row>
+    <row r="1717" spans="1:7">
+      <c r="A1717" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1717" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1717" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1717" s="2"/>
+      <c r="F1717" s="1"/>
+      <c r="G1717" s="28"/>
+    </row>
+    <row r="1718" spans="1:7">
+      <c r="A1718" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1718" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1718" s="5">
+        <v>6</v>
+      </c>
+      <c r="D1718" s="2"/>
+      <c r="F1718" s="1"/>
+      <c r="G1718" s="28"/>
+    </row>
+    <row r="1719" spans="1:7">
+      <c r="A1719" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1719" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1719" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="2"/>
+    </row>
+    <row r="1720" spans="1:7">
+      <c r="A1720" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1720" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1720" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="2"/>
+    </row>
+    <row r="1721" spans="1:7">
+      <c r="A1721" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1721" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1721" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="2"/>
+    </row>
+    <row r="1722" spans="1:7">
+      <c r="A1722" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B1722" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1722" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
